--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -8,14 +8,14 @@
     <sheet state="visible" name="I-shift" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$436</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$437</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1552" uniqueCount="1046">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1555" uniqueCount="1048">
   <si>
     <t>Word</t>
   </si>
@@ -2433,6 +2433,12 @@
   </si>
   <si>
     <t>to read</t>
+  </si>
+  <si>
+    <t>til-røden</t>
+  </si>
+  <si>
+    <t>to redden, to fluster, to blush</t>
   </si>
   <si>
     <t>rulen</t>
@@ -3409,10 +3415,10 @@
         <color rgb="FF284E3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3420,13 +3426,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3434,13 +3440,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </left>
       <right style="thin">
         <color rgb="FF284E3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3450,7 +3456,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="66">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -3603,9 +3609,6 @@
     <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
     <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -3714,8 +3717,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C436" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$436"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C437" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$437"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Type" id="2"/>
@@ -4045,7 +4048,7 @@
         <v>25</v>
       </c>
       <c r="H4" s="21" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C436, REGEXMATCH(C2:C436, I3)), 2, TRUE)"),"ibyrten")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C437, REGEXMATCH(C2:C437, I3)), 2, TRUE)"),"ibyrten")</f>
         <v>ibyrten</v>
       </c>
       <c r="I4" s="4" t="str">
@@ -10866,7 +10869,7 @@
       <c r="B354" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C354" s="20" t="s">
+      <c r="C354" s="12" t="s">
         <v>809</v>
       </c>
       <c r="D354" s="4"/>
@@ -10904,7 +10907,7 @@
       <c r="B356" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C356" s="12" t="s">
+      <c r="C356" s="20" t="s">
         <v>813</v>
       </c>
       <c r="D356" s="4"/>
@@ -10917,13 +10920,13 @@
       <c r="K356" s="9"/>
     </row>
     <row r="357" ht="15.75" customHeight="1">
-      <c r="A357" s="41" t="s">
+      <c r="A357" s="15" t="s">
         <v>814</v>
       </c>
       <c r="B357" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C357" s="42" t="s">
+      <c r="C357" s="24" t="s">
         <v>815</v>
       </c>
       <c r="D357" s="4"/>
@@ -10936,13 +10939,13 @@
       <c r="K357" s="9"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="10" t="s">
+      <c r="A358" s="34" t="s">
         <v>816</v>
       </c>
       <c r="B358" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C358" s="20" t="s">
+      <c r="C358" s="36" t="s">
         <v>817</v>
       </c>
       <c r="D358" s="4"/>
@@ -10955,13 +10958,13 @@
       <c r="K358" s="9"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="39" t="s">
+      <c r="A359" s="15" t="s">
         <v>818</v>
       </c>
       <c r="B359" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C359" s="49" t="s">
+      <c r="C359" s="17" t="s">
         <v>819</v>
       </c>
       <c r="D359" s="4"/>
@@ -10974,13 +10977,13 @@
       <c r="K359" s="9"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="10" t="s">
+      <c r="A360" s="44" t="s">
         <v>820</v>
       </c>
       <c r="B360" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C360" s="12" t="s">
+      <c r="C360" s="46" t="s">
         <v>821</v>
       </c>
       <c r="D360" s="4"/>
@@ -10999,7 +11002,7 @@
       <c r="B361" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C361" s="17" t="s">
+      <c r="C361" s="24" t="s">
         <v>823</v>
       </c>
       <c r="D361" s="4"/>
@@ -11012,13 +11015,13 @@
       <c r="K361" s="9"/>
     </row>
     <row r="362" ht="15.75" customHeight="1">
-      <c r="A362" s="44" t="s">
+      <c r="A362" s="10" t="s">
         <v>824</v>
       </c>
       <c r="B362" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C362" s="45" t="s">
+      <c r="C362" s="20" t="s">
         <v>825</v>
       </c>
       <c r="D362" s="4"/>
@@ -11031,13 +11034,13 @@
       <c r="K362" s="9"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="15" t="s">
+      <c r="A363" s="39" t="s">
         <v>826</v>
       </c>
       <c r="B363" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C363" s="17" t="s">
+      <c r="C363" s="40" t="s">
         <v>827</v>
       </c>
       <c r="D363" s="4"/>
@@ -11075,7 +11078,7 @@
       <c r="B365" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C365" s="24" t="s">
+      <c r="C365" s="17" t="s">
         <v>831</v>
       </c>
       <c r="D365" s="4"/>
@@ -11094,7 +11097,7 @@
       <c r="B366" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C366" s="20" t="s">
+      <c r="C366" s="12" t="s">
         <v>833</v>
       </c>
       <c r="D366" s="4"/>
@@ -11113,7 +11116,7 @@
       <c r="B367" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C367" s="24" t="s">
+      <c r="C367" s="17" t="s">
         <v>835</v>
       </c>
       <c r="D367" s="4"/>
@@ -11132,7 +11135,7 @@
       <c r="B368" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C368" s="20" t="s">
+      <c r="C368" s="12" t="s">
         <v>837</v>
       </c>
       <c r="D368" s="4"/>
@@ -11151,7 +11154,7 @@
       <c r="B369" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C369" s="24" t="s">
+      <c r="C369" s="17" t="s">
         <v>839</v>
       </c>
       <c r="D369" s="4"/>
@@ -11208,7 +11211,7 @@
       <c r="B372" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C372" s="20" t="s">
+      <c r="C372" s="12" t="s">
         <v>845</v>
       </c>
       <c r="D372" s="4"/>
@@ -11227,7 +11230,7 @@
       <c r="B373" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C373" s="24" t="s">
+      <c r="C373" s="17" t="s">
         <v>847</v>
       </c>
       <c r="D373" s="4"/>
@@ -11265,7 +11268,7 @@
       <c r="B375" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C375" s="17" t="s">
+      <c r="C375" s="24" t="s">
         <v>851</v>
       </c>
       <c r="D375" s="4"/>
@@ -11297,13 +11300,13 @@
       <c r="K376" s="9"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="41" t="s">
+      <c r="A377" s="15" t="s">
         <v>854</v>
       </c>
       <c r="B377" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C377" s="42" t="s">
+      <c r="C377" s="17" t="s">
         <v>855</v>
       </c>
       <c r="D377" s="4"/>
@@ -11316,13 +11319,13 @@
       <c r="K377" s="9"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="10" t="s">
+      <c r="A378" s="34" t="s">
         <v>856</v>
       </c>
       <c r="B378" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C378" s="12" t="s">
+      <c r="C378" s="36" t="s">
         <v>857</v>
       </c>
       <c r="D378" s="4"/>
@@ -11360,7 +11363,7 @@
       <c r="B380" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C380" s="20" t="s">
+      <c r="C380" s="12" t="s">
         <v>861</v>
       </c>
       <c r="D380" s="4"/>
@@ -11379,7 +11382,7 @@
       <c r="B381" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C381" s="24" t="s">
+      <c r="C381" s="17" t="s">
         <v>863</v>
       </c>
       <c r="D381" s="4"/>
@@ -11398,7 +11401,7 @@
       <c r="B382" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C382" s="20" t="s">
+      <c r="C382" s="12" t="s">
         <v>865</v>
       </c>
       <c r="D382" s="4"/>
@@ -11417,7 +11420,7 @@
       <c r="B383" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C383" s="24" t="s">
+      <c r="C383" s="17" t="s">
         <v>867</v>
       </c>
       <c r="D383" s="4"/>
@@ -11455,7 +11458,7 @@
       <c r="B385" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C385" s="17" t="s">
+      <c r="C385" s="24" t="s">
         <v>871</v>
       </c>
       <c r="D385" s="4"/>
@@ -11550,7 +11553,7 @@
       <c r="B390" s="11" t="s">
         <v>52</v>
       </c>
-      <c r="C390" s="12" t="s">
+      <c r="C390" s="20" t="s">
         <v>881</v>
       </c>
       <c r="D390" s="4"/>
@@ -11563,13 +11566,13 @@
       <c r="K390" s="9"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="41" t="s">
+      <c r="A391" s="15" t="s">
         <v>882</v>
       </c>
       <c r="B391" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C391" s="42" t="s">
+      <c r="C391" s="24" t="s">
         <v>883</v>
       </c>
       <c r="D391" s="4"/>
@@ -11601,13 +11604,13 @@
       <c r="K392" s="9"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="15" t="s">
+      <c r="A393" s="41" t="s">
         <v>886</v>
       </c>
       <c r="B393" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="C393" s="17" t="s">
+      <c r="C393" s="42" t="s">
         <v>887</v>
       </c>
       <c r="D393" s="4"/>
@@ -11624,9 +11627,9 @@
         <v>888</v>
       </c>
       <c r="B394" s="11" t="s">
-        <v>57</v>
-      </c>
-      <c r="C394" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="C394" s="20" t="s">
         <v>889</v>
       </c>
       <c r="D394" s="4"/>
@@ -11639,13 +11642,13 @@
       <c r="K394" s="9"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="41" t="s">
+      <c r="A395" s="15" t="s">
         <v>890</v>
       </c>
-      <c r="B395" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="C395" s="42" t="s">
+      <c r="B395" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="C395" s="24" t="s">
         <v>891</v>
       </c>
       <c r="D395" s="4"/>
@@ -11658,13 +11661,13 @@
       <c r="K395" s="9"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="22" t="s">
+      <c r="A396" s="34" t="s">
         <v>892</v>
       </c>
       <c r="B396" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C396" s="12" t="s">
+      <c r="C396" s="36" t="s">
         <v>893</v>
       </c>
       <c r="D396" s="4"/>
@@ -11677,7 +11680,7 @@
       <c r="K396" s="9"/>
     </row>
     <row r="397" ht="15.75" customHeight="1">
-      <c r="A397" s="15" t="s">
+      <c r="A397" s="31" t="s">
         <v>894</v>
       </c>
       <c r="B397" s="48" t="s">
@@ -11699,11 +11702,11 @@
       <c r="A398" s="10" t="s">
         <v>896</v>
       </c>
-      <c r="B398" s="11" t="s">
+      <c r="B398" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C398" s="12" t="s">
-        <v>896</v>
+        <v>897</v>
       </c>
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
@@ -11715,13 +11718,13 @@
       <c r="K398" s="9"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="41" t="s">
-        <v>897</v>
-      </c>
-      <c r="B399" s="48" t="s">
-        <v>9</v>
-      </c>
-      <c r="C399" s="42" t="s">
+      <c r="A399" s="15" t="s">
+        <v>898</v>
+      </c>
+      <c r="B399" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C399" s="24" t="s">
         <v>898</v>
       </c>
       <c r="D399" s="4"/>
@@ -11734,13 +11737,13 @@
       <c r="K399" s="9"/>
     </row>
     <row r="400" ht="15.75" customHeight="1">
-      <c r="A400" s="22" t="s">
+      <c r="A400" s="34" t="s">
         <v>899</v>
       </c>
-      <c r="B400" s="11" t="s">
-        <v>266</v>
-      </c>
-      <c r="C400" s="20" t="s">
+      <c r="B400" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C400" s="36" t="s">
         <v>900</v>
       </c>
       <c r="D400" s="4"/>
@@ -11753,11 +11756,11 @@
       <c r="K400" s="9"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="41" t="s">
+      <c r="A401" s="31" t="s">
         <v>901</v>
       </c>
-      <c r="B401" s="25" t="s">
-        <v>63</v>
+      <c r="B401" s="16" t="s">
+        <v>266</v>
       </c>
       <c r="C401" s="17" t="s">
         <v>902</v>
@@ -11772,13 +11775,13 @@
       <c r="K401" s="9"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="44" t="s">
+      <c r="A402" s="34" t="s">
         <v>903</v>
       </c>
-      <c r="B402" s="11" t="s">
-        <v>278</v>
-      </c>
-      <c r="C402" s="45" t="s">
+      <c r="B402" s="35" t="s">
+        <v>63</v>
+      </c>
+      <c r="C402" s="20" t="s">
         <v>904</v>
       </c>
       <c r="D402" s="4"/>
@@ -11791,13 +11794,13 @@
       <c r="K402" s="9"/>
     </row>
     <row r="403" ht="15.75" customHeight="1">
-      <c r="A403" s="15" t="s">
+      <c r="A403" s="39" t="s">
         <v>905</v>
       </c>
       <c r="B403" s="16" t="s">
-        <v>72</v>
-      </c>
-      <c r="C403" s="24" t="s">
+        <v>278</v>
+      </c>
+      <c r="C403" s="40" t="s">
         <v>906</v>
       </c>
       <c r="D403" s="4"/>
@@ -11813,8 +11816,8 @@
       <c r="A404" s="10" t="s">
         <v>907</v>
       </c>
-      <c r="B404" s="50" t="s">
-        <v>9</v>
+      <c r="B404" s="11" t="s">
+        <v>72</v>
       </c>
       <c r="C404" s="12" t="s">
         <v>908</v>
@@ -11854,7 +11857,7 @@
       <c r="B406" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C406" s="20" t="s">
+      <c r="C406" s="12" t="s">
         <v>912</v>
       </c>
       <c r="D406" s="4"/>
@@ -11870,10 +11873,10 @@
       <c r="A407" s="15" t="s">
         <v>913</v>
       </c>
-      <c r="B407" s="16" t="s">
-        <v>335</v>
-      </c>
-      <c r="C407" s="24" t="s">
+      <c r="B407" s="48" t="s">
+        <v>9</v>
+      </c>
+      <c r="C407" s="17" t="s">
         <v>914</v>
       </c>
       <c r="D407" s="4"/>
@@ -11928,7 +11931,7 @@
         <v>919</v>
       </c>
       <c r="B410" s="11" t="s">
-        <v>72</v>
+        <v>335</v>
       </c>
       <c r="C410" s="12" t="s">
         <v>920</v>
@@ -11947,7 +11950,7 @@
         <v>921</v>
       </c>
       <c r="B411" s="16" t="s">
-        <v>9</v>
+        <v>72</v>
       </c>
       <c r="C411" s="24" t="s">
         <v>922</v>
@@ -12004,9 +12007,9 @@
         <v>927</v>
       </c>
       <c r="B414" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C414" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C414" s="12" t="s">
         <v>928</v>
       </c>
       <c r="D414" s="4"/>
@@ -12019,7 +12022,7 @@
       <c r="K414" s="9"/>
     </row>
     <row r="415" ht="15.75" customHeight="1">
-      <c r="A415" s="31" t="s">
+      <c r="A415" s="15" t="s">
         <v>929</v>
       </c>
       <c r="B415" s="16" t="s">
@@ -12038,13 +12041,13 @@
       <c r="K415" s="9"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="10" t="s">
+      <c r="A416" s="22" t="s">
         <v>931</v>
       </c>
       <c r="B416" s="11" t="s">
-        <v>63</v>
-      </c>
-      <c r="C416" s="12" t="s">
+        <v>72</v>
+      </c>
+      <c r="C416" s="20" t="s">
         <v>932</v>
       </c>
       <c r="D416" s="4"/>
@@ -12061,7 +12064,7 @@
         <v>933</v>
       </c>
       <c r="B417" s="16" t="s">
-        <v>52</v>
+        <v>63</v>
       </c>
       <c r="C417" s="24" t="s">
         <v>934</v>
@@ -12080,7 +12083,7 @@
         <v>935</v>
       </c>
       <c r="B418" s="11" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="C418" s="12" t="s">
         <v>936</v>
@@ -12101,7 +12104,7 @@
       <c r="B419" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C419" s="17" t="s">
+      <c r="C419" s="24" t="s">
         <v>938</v>
       </c>
       <c r="D419" s="4"/>
@@ -12120,7 +12123,7 @@
       <c r="B420" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C420" s="12" t="s">
+      <c r="C420" s="20" t="s">
         <v>940</v>
       </c>
       <c r="D420" s="4"/>
@@ -12133,13 +12136,13 @@
       <c r="K420" s="9"/>
     </row>
     <row r="421" ht="15.75" customHeight="1">
-      <c r="A421" s="41" t="s">
+      <c r="A421" s="15" t="s">
         <v>941</v>
       </c>
       <c r="B421" s="16" t="s">
         <v>87</v>
       </c>
-      <c r="C421" s="42" t="s">
+      <c r="C421" s="24" t="s">
         <v>942</v>
       </c>
       <c r="D421" s="4"/>
@@ -12152,13 +12155,13 @@
       <c r="K421" s="9"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="10" t="s">
+      <c r="A422" s="34" t="s">
         <v>943</v>
       </c>
       <c r="B422" s="11" t="s">
-        <v>72</v>
-      </c>
-      <c r="C422" s="20" t="s">
+        <v>87</v>
+      </c>
+      <c r="C422" s="36" t="s">
         <v>944</v>
       </c>
       <c r="D422" s="4"/>
@@ -12171,13 +12174,13 @@
       <c r="K422" s="9"/>
     </row>
     <row r="423" ht="15.75" customHeight="1">
-      <c r="A423" s="41" t="s">
+      <c r="A423" s="15" t="s">
         <v>945</v>
       </c>
       <c r="B423" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C423" s="42" t="s">
+        <v>72</v>
+      </c>
+      <c r="C423" s="17" t="s">
         <v>946</v>
       </c>
       <c r="D423" s="4"/>
@@ -12191,13 +12194,13 @@
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="34" t="s">
-        <v>915</v>
+        <v>947</v>
       </c>
       <c r="B424" s="11" t="s">
         <v>87</v>
       </c>
       <c r="C424" s="36" t="s">
-        <v>947</v>
+        <v>948</v>
       </c>
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
@@ -12209,13 +12212,13 @@
       <c r="K424" s="9"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="15" t="s">
-        <v>948</v>
+      <c r="A425" s="41" t="s">
+        <v>917</v>
       </c>
       <c r="B425" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C425" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C425" s="42" t="s">
         <v>949</v>
       </c>
       <c r="D425" s="4"/>
@@ -12228,13 +12231,13 @@
       <c r="K425" s="9"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="34" t="s">
+      <c r="A426" s="10" t="s">
         <v>950</v>
       </c>
       <c r="B426" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C426" s="36" t="s">
+      <c r="C426" s="20" t="s">
         <v>951</v>
       </c>
       <c r="D426" s="4"/>
@@ -12250,8 +12253,8 @@
       <c r="A427" s="41" t="s">
         <v>952</v>
       </c>
-      <c r="B427" s="25" t="s">
-        <v>57</v>
+      <c r="B427" s="16" t="s">
+        <v>9</v>
       </c>
       <c r="C427" s="42" t="s">
         <v>953</v>
@@ -12266,13 +12269,13 @@
       <c r="K427" s="9"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="10" t="s">
+      <c r="A428" s="34" t="s">
         <v>954</v>
       </c>
-      <c r="B428" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C428" s="12" t="s">
+      <c r="B428" s="35" t="s">
+        <v>57</v>
+      </c>
+      <c r="C428" s="36" t="s">
         <v>955</v>
       </c>
       <c r="D428" s="4"/>
@@ -12323,13 +12326,13 @@
       <c r="K430" s="9"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="31" t="s">
+      <c r="A431" s="15" t="s">
         <v>960</v>
       </c>
       <c r="B431" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C431" s="17" t="s">
+      <c r="C431" s="24" t="s">
         <v>961</v>
       </c>
       <c r="D431" s="4"/>
@@ -12342,13 +12345,13 @@
       <c r="K431" s="9"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="10" t="s">
+      <c r="A432" s="22" t="s">
         <v>962</v>
       </c>
       <c r="B432" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C432" s="12" t="s">
+      <c r="C432" s="20" t="s">
         <v>963</v>
       </c>
       <c r="D432" s="4"/>
@@ -12361,13 +12364,13 @@
       <c r="K432" s="9"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="52" t="s">
+      <c r="A433" s="15" t="s">
         <v>964</v>
       </c>
       <c r="B433" s="16" t="s">
-        <v>275</v>
-      </c>
-      <c r="C433" s="49" t="s">
+        <v>9</v>
+      </c>
+      <c r="C433" s="24" t="s">
         <v>965</v>
       </c>
       <c r="D433" s="4"/>
@@ -12380,13 +12383,13 @@
       <c r="K433" s="9"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="10" t="s">
+      <c r="A434" s="47" t="s">
         <v>966</v>
       </c>
       <c r="B434" s="11" t="s">
-        <v>335</v>
-      </c>
-      <c r="C434" s="12" t="s">
+        <v>275</v>
+      </c>
+      <c r="C434" s="46" t="s">
         <v>967</v>
       </c>
       <c r="D434" s="4"/>
@@ -12418,13 +12421,13 @@
       <c r="K435" s="9"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="53" t="s">
+      <c r="A436" s="10" t="s">
         <v>970</v>
       </c>
-      <c r="B436" s="54" t="s">
+      <c r="B436" s="11" t="s">
         <v>335</v>
       </c>
-      <c r="C436" s="55" t="s">
+      <c r="C436" s="12" t="s">
         <v>971</v>
       </c>
       <c r="D436" s="4"/>
@@ -12436,9 +12439,28 @@
       <c r="J436" s="9"/>
       <c r="K436" s="9"/>
     </row>
+    <row r="437" ht="15.75" customHeight="1">
+      <c r="A437" s="52" t="s">
+        <v>972</v>
+      </c>
+      <c r="B437" s="53" t="s">
+        <v>335</v>
+      </c>
+      <c r="C437" s="54" t="s">
+        <v>973</v>
+      </c>
+      <c r="D437" s="4"/>
+      <c r="E437" s="4"/>
+      <c r="F437" s="4"/>
+      <c r="G437" s="4"/>
+      <c r="H437" s="4"/>
+      <c r="I437" s="4"/>
+      <c r="J437" s="9"/>
+      <c r="K437" s="9"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B436">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B437">
       <formula1>"adjective,adjective-adverb,adverb,auxiliary,conjunction,interjection,noun,numeral,preposition,pronoun,verb"</formula1>
     </dataValidation>
   </dataValidations>
@@ -12463,1317 +12485,1317 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="56" t="s">
-        <v>972</v>
-      </c>
-      <c r="D1" s="56" t="s">
-        <v>973</v>
-      </c>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
+      <c r="A1" s="55" t="s">
+        <v>974</v>
+      </c>
+      <c r="D1" s="55" t="s">
+        <v>975</v>
+      </c>
+      <c r="G1" s="56"/>
+      <c r="H1" s="56"/>
+      <c r="I1" s="56"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="56" t="s">
-        <v>974</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>975</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>974</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>826</v>
-      </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
+      <c r="A2" s="55" t="s">
+        <v>976</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>977</v>
+      </c>
+      <c r="D2" s="55" t="s">
+        <v>976</v>
+      </c>
+      <c r="E2" s="57" t="s">
+        <v>828</v>
+      </c>
+      <c r="G2" s="56"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="58" t="s">
+      <c r="B3" s="57" t="s">
+        <v>978</v>
+      </c>
+      <c r="D3" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E3" s="57" t="s">
+        <v>979</v>
+      </c>
+      <c r="G3" s="56"/>
+      <c r="H3" s="56"/>
+      <c r="I3" s="56"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="58"/>
+      <c r="B4" s="59" t="s">
+        <v>980</v>
+      </c>
+      <c r="C4" s="59" t="s">
+        <v>981</v>
+      </c>
+      <c r="D4" s="58"/>
+      <c r="E4" s="59" t="s">
+        <v>980</v>
+      </c>
+      <c r="F4" s="59" t="s">
+        <v>981</v>
+      </c>
+      <c r="G4" s="56"/>
+      <c r="H4" s="56"/>
+      <c r="I4" s="56"/>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="55" t="s">
+        <v>982</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>983</v>
+      </c>
+      <c r="C5" s="57" t="s">
+        <v>984</v>
+      </c>
+      <c r="D5" s="55" t="s">
+        <v>982</v>
+      </c>
+      <c r="E5" s="57" t="s">
+        <v>985</v>
+      </c>
+      <c r="F5" s="57" t="s">
+        <v>986</v>
+      </c>
+      <c r="G5" s="56"/>
+      <c r="H5" s="56"/>
+      <c r="I5" s="56"/>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="55" t="s">
+        <v>987</v>
+      </c>
+      <c r="B6" s="57" t="s">
+        <v>988</v>
+      </c>
+      <c r="C6" s="57" t="s">
+        <v>989</v>
+      </c>
+      <c r="D6" s="55" t="s">
+        <v>987</v>
+      </c>
+      <c r="E6" s="57" t="s">
+        <v>990</v>
+      </c>
+      <c r="F6" s="57" t="s">
+        <v>991</v>
+      </c>
+      <c r="G6" s="56"/>
+      <c r="H6" s="56"/>
+      <c r="I6" s="56"/>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="55" t="s">
+        <v>992</v>
+      </c>
+      <c r="D7" s="55" t="s">
+        <v>993</v>
+      </c>
+      <c r="G7" s="55" t="s">
+        <v>994</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
+      <c r="A8" s="55" t="s">
         <v>976</v>
       </c>
-      <c r="D3" s="56" t="s">
+      <c r="B8" s="57" t="s">
+        <v>977</v>
+      </c>
+      <c r="D8" s="55" t="s">
+        <v>976</v>
+      </c>
+      <c r="E8" s="57" t="s">
+        <v>728</v>
+      </c>
+      <c r="G8" s="55" t="s">
+        <v>976</v>
+      </c>
+      <c r="H8" s="57" t="s">
+        <v>814</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="55" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="58" t="s">
+      <c r="B9" s="57" t="s">
+        <v>978</v>
+      </c>
+      <c r="D9" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="57" t="s">
+        <v>995</v>
+      </c>
+      <c r="G9" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="57" t="s">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="58"/>
+      <c r="B10" s="59" t="s">
+        <v>980</v>
+      </c>
+      <c r="C10" s="59" t="s">
+        <v>981</v>
+      </c>
+      <c r="D10" s="58"/>
+      <c r="E10" s="59" t="s">
+        <v>980</v>
+      </c>
+      <c r="F10" s="59" t="s">
+        <v>981</v>
+      </c>
+      <c r="G10" s="58"/>
+      <c r="H10" s="59" t="s">
+        <v>980</v>
+      </c>
+      <c r="I10" s="59" t="s">
+        <v>981</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="55" t="s">
+        <v>982</v>
+      </c>
+      <c r="B11" s="57" t="s">
+        <v>983</v>
+      </c>
+      <c r="C11" s="57" t="s">
+        <v>984</v>
+      </c>
+      <c r="D11" s="55" t="s">
+        <v>982</v>
+      </c>
+      <c r="E11" s="57" t="s">
+        <v>997</v>
+      </c>
+      <c r="F11" s="57" t="s">
+        <v>998</v>
+      </c>
+      <c r="G11" s="55" t="s">
+        <v>982</v>
+      </c>
+      <c r="H11" s="57" t="s">
+        <v>999</v>
+      </c>
+      <c r="I11" s="57" t="s">
+        <v>1000</v>
+      </c>
+    </row>
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="55" t="s">
+        <v>987</v>
+      </c>
+      <c r="B12" s="57" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C12" s="57" t="s">
+        <v>1002</v>
+      </c>
+      <c r="D12" s="55" t="s">
+        <v>987</v>
+      </c>
+      <c r="E12" s="57" t="s">
+        <v>1003</v>
+      </c>
+      <c r="F12" s="57" t="s">
+        <v>1004</v>
+      </c>
+      <c r="G12" s="55" t="s">
+        <v>987</v>
+      </c>
+      <c r="H12" s="57" t="s">
+        <v>1005</v>
+      </c>
+      <c r="I12" s="57" t="s">
+        <v>1006</v>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="55" t="s">
+        <v>1007</v>
+      </c>
+      <c r="D13" s="55" t="s">
+        <v>1008</v>
+      </c>
+      <c r="G13" s="56"/>
+      <c r="H13" s="56"/>
+      <c r="I13" s="56"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="A14" s="55" t="s">
+        <v>976</v>
+      </c>
+      <c r="B14" s="57" t="s">
         <v>977</v>
       </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60" t="s">
+      <c r="D14" s="55" t="s">
+        <v>976</v>
+      </c>
+      <c r="E14" s="57" t="s">
+        <v>722</v>
+      </c>
+      <c r="G14" s="56"/>
+      <c r="H14" s="56"/>
+      <c r="I14" s="56"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="57" t="s">
         <v>978</v>
       </c>
-      <c r="C4" s="60" t="s">
-        <v>979</v>
-      </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="60" t="s">
-        <v>978</v>
-      </c>
-      <c r="F4" s="60" t="s">
-        <v>979</v>
-      </c>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="56" t="s">
+      <c r="D15" s="55" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="57" t="s">
+        <v>1009</v>
+      </c>
+      <c r="G15" s="56"/>
+      <c r="H15" s="56"/>
+      <c r="I15" s="56"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="58"/>
+      <c r="B16" s="59" t="s">
         <v>980</v>
       </c>
-      <c r="B5" s="58" t="s">
+      <c r="C16" s="59" t="s">
         <v>981</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="D16" s="58"/>
+      <c r="E16" s="59" t="s">
+        <v>980</v>
+      </c>
+      <c r="F16" s="59" t="s">
+        <v>981</v>
+      </c>
+      <c r="G16" s="56"/>
+      <c r="H16" s="56"/>
+      <c r="I16" s="56"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1">
+      <c r="A17" s="55" t="s">
         <v>982</v>
       </c>
-      <c r="D5" s="56" t="s">
-        <v>980</v>
-      </c>
-      <c r="E5" s="58" t="s">
+      <c r="B17" s="57" t="s">
         <v>983</v>
       </c>
-      <c r="F5" s="58" t="s">
+      <c r="C17" s="57" t="s">
         <v>984</v>
       </c>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="56" t="s">
-        <v>985</v>
-      </c>
-      <c r="B6" s="58" t="s">
-        <v>986</v>
-      </c>
-      <c r="C6" s="58" t="s">
+      <c r="D17" s="55" t="s">
+        <v>982</v>
+      </c>
+      <c r="E17" s="57" t="s">
+        <v>1010</v>
+      </c>
+      <c r="F17" s="57" t="s">
+        <v>1011</v>
+      </c>
+      <c r="G17" s="56"/>
+      <c r="H17" s="56"/>
+      <c r="I17" s="56"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1">
+      <c r="A18" s="55" t="s">
         <v>987</v>
       </c>
-      <c r="D6" s="56" t="s">
-        <v>985</v>
-      </c>
-      <c r="E6" s="58" t="s">
-        <v>988</v>
-      </c>
-      <c r="F6" s="58" t="s">
-        <v>989</v>
-      </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="56" t="s">
-        <v>990</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>991</v>
-      </c>
-      <c r="G7" s="56" t="s">
-        <v>992</v>
-      </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="56" t="s">
-        <v>974</v>
-      </c>
-      <c r="B8" s="58" t="s">
-        <v>975</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>974</v>
-      </c>
-      <c r="E8" s="58" t="s">
-        <v>728</v>
-      </c>
-      <c r="G8" s="56" t="s">
-        <v>974</v>
-      </c>
-      <c r="H8" s="58" t="s">
-        <v>812</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>976</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="58" t="s">
-        <v>993</v>
-      </c>
-      <c r="G9" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>994</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="60" t="s">
-        <v>978</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>979</v>
-      </c>
-      <c r="D10" s="59"/>
-      <c r="E10" s="60" t="s">
-        <v>978</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>979</v>
-      </c>
-      <c r="G10" s="59"/>
-      <c r="H10" s="60" t="s">
-        <v>978</v>
-      </c>
-      <c r="I10" s="60" t="s">
-        <v>979</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="56" t="s">
-        <v>980</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>981</v>
-      </c>
-      <c r="C11" s="58" t="s">
-        <v>982</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>980</v>
-      </c>
-      <c r="E11" s="58" t="s">
-        <v>995</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>996</v>
-      </c>
-      <c r="G11" s="56" t="s">
-        <v>980</v>
-      </c>
-      <c r="H11" s="58" t="s">
-        <v>997</v>
-      </c>
-      <c r="I11" s="58" t="s">
-        <v>998</v>
-      </c>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="56" t="s">
-        <v>985</v>
-      </c>
-      <c r="B12" s="58" t="s">
-        <v>999</v>
-      </c>
-      <c r="C12" s="58" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D12" s="56" t="s">
-        <v>985</v>
-      </c>
-      <c r="E12" s="58" t="s">
-        <v>1001</v>
-      </c>
-      <c r="F12" s="58" t="s">
+      <c r="B18" s="57" t="s">
+        <v>1012</v>
+      </c>
+      <c r="C18" s="57" t="s">
         <v>1002</v>
       </c>
-      <c r="G12" s="56" t="s">
-        <v>985</v>
-      </c>
-      <c r="H12" s="58" t="s">
-        <v>1003</v>
-      </c>
-      <c r="I12" s="58" t="s">
-        <v>1004</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="56" t="s">
-        <v>1005</v>
-      </c>
-      <c r="D13" s="56" t="s">
-        <v>1006</v>
-      </c>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="56" t="s">
-        <v>974</v>
-      </c>
-      <c r="B14" s="58" t="s">
-        <v>975</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>974</v>
-      </c>
-      <c r="E14" s="58" t="s">
-        <v>722</v>
-      </c>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>976</v>
-      </c>
-      <c r="D15" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="58" t="s">
-        <v>1007</v>
-      </c>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60" t="s">
-        <v>978</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>979</v>
-      </c>
-      <c r="D16" s="59"/>
-      <c r="E16" s="60" t="s">
-        <v>978</v>
-      </c>
-      <c r="F16" s="60" t="s">
-        <v>979</v>
-      </c>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="56" t="s">
-        <v>980</v>
-      </c>
-      <c r="B17" s="58" t="s">
-        <v>981</v>
-      </c>
-      <c r="C17" s="58" t="s">
-        <v>982</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>980</v>
-      </c>
-      <c r="E17" s="58" t="s">
-        <v>1008</v>
-      </c>
-      <c r="F17" s="58" t="s">
-        <v>1009</v>
-      </c>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="56" t="s">
-        <v>985</v>
-      </c>
-      <c r="B18" s="58" t="s">
-        <v>1010</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>1000</v>
-      </c>
-      <c r="D18" s="56" t="s">
-        <v>985</v>
-      </c>
-      <c r="E18" s="58" t="s">
-        <v>1011</v>
-      </c>
-      <c r="F18" s="58" t="s">
-        <v>1012</v>
-      </c>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
+      <c r="D18" s="55" t="s">
+        <v>987</v>
+      </c>
+      <c r="E18" s="57" t="s">
+        <v>1013</v>
+      </c>
+      <c r="F18" s="57" t="s">
+        <v>1014</v>
+      </c>
+      <c r="G18" s="56"/>
+      <c r="H18" s="56"/>
+      <c r="I18" s="56"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="61"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
+      <c r="A19" s="60"/>
+      <c r="B19" s="60"/>
+      <c r="C19" s="60"/>
+      <c r="D19" s="60"/>
+      <c r="E19" s="60"/>
+      <c r="F19" s="60"/>
+      <c r="G19" s="60"/>
+      <c r="H19" s="60"/>
+      <c r="I19" s="60"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="62" t="s">
-        <v>1013</v>
-      </c>
-      <c r="B20" s="63" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D20" s="63" t="s">
+      <c r="A20" s="61" t="s">
         <v>1015</v>
       </c>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
+      <c r="B20" s="62" t="s">
+        <v>1016</v>
+      </c>
+      <c r="D20" s="62" t="s">
+        <v>1017</v>
+      </c>
+      <c r="F20" s="60"/>
+      <c r="G20" s="60"/>
+      <c r="H20" s="60"/>
+      <c r="I20" s="60"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="B21" s="64" t="s">
+      <c r="B21" s="63" t="s">
+        <v>1018</v>
+      </c>
+      <c r="C21" s="63" t="s">
+        <v>1019</v>
+      </c>
+      <c r="D21" s="63" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E21" s="63" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F21" s="60"/>
+      <c r="G21" s="60"/>
+      <c r="H21" s="60"/>
+      <c r="I21" s="60"/>
+    </row>
+    <row r="22" ht="18.75" customHeight="1">
+      <c r="A22" s="64" t="s">
+        <v>1020</v>
+      </c>
+      <c r="B22" s="57" t="s">
+        <v>26</v>
+      </c>
+      <c r="C22" s="57" t="s">
+        <v>1021</v>
+      </c>
+      <c r="D22" s="57" t="s">
+        <v>1022</v>
+      </c>
+      <c r="E22" s="57" t="s">
+        <v>1023</v>
+      </c>
+      <c r="F22" s="60"/>
+      <c r="G22" s="60"/>
+      <c r="H22" s="60"/>
+      <c r="I22" s="60"/>
+    </row>
+    <row r="23" ht="18.75" customHeight="1">
+      <c r="A23" s="62" t="s">
+        <v>1024</v>
+      </c>
+      <c r="B23" s="57" t="s">
+        <v>1025</v>
+      </c>
+      <c r="C23" s="57" t="s">
+        <v>1026</v>
+      </c>
+      <c r="D23" s="57" t="s">
+        <v>1027</v>
+      </c>
+      <c r="E23" s="57" t="s">
+        <v>1028</v>
+      </c>
+      <c r="F23" s="60"/>
+      <c r="G23" s="60"/>
+      <c r="H23" s="60"/>
+      <c r="I23" s="60"/>
+    </row>
+    <row r="24" ht="18.75" customHeight="1">
+      <c r="D24" s="65"/>
+      <c r="E24" s="60"/>
+      <c r="F24" s="60"/>
+      <c r="G24" s="60"/>
+      <c r="H24" s="60"/>
+      <c r="I24" s="60"/>
+    </row>
+    <row r="25" ht="18.75" customHeight="1">
+      <c r="A25" s="61" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B25" s="62" t="s">
         <v>1016</v>
       </c>
-      <c r="C21" s="64" t="s">
+      <c r="D25" s="62" t="s">
         <v>1017</v>
       </c>
-      <c r="D21" s="64" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E21" s="64" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
-    </row>
-    <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="65" t="s">
+      <c r="F25" s="60"/>
+      <c r="G25" s="60"/>
+      <c r="H25" s="60"/>
+      <c r="I25" s="60"/>
+    </row>
+    <row r="26" ht="18.75" customHeight="1">
+      <c r="B26" s="63" t="s">
         <v>1018</v>
       </c>
-      <c r="B22" s="58" t="s">
-        <v>26</v>
-      </c>
-      <c r="C22" s="58" t="s">
+      <c r="C26" s="63" t="s">
         <v>1019</v>
       </c>
-      <c r="D22" s="58" t="s">
+      <c r="D26" s="63" t="s">
+        <v>1018</v>
+      </c>
+      <c r="E26" s="63" t="s">
+        <v>1019</v>
+      </c>
+      <c r="F26" s="60"/>
+      <c r="G26" s="60"/>
+      <c r="H26" s="60"/>
+      <c r="I26" s="60"/>
+    </row>
+    <row r="27" ht="18.75" customHeight="1">
+      <c r="A27" s="64" t="s">
         <v>1020</v>
       </c>
-      <c r="E22" s="58" t="s">
-        <v>1021</v>
-      </c>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
-    </row>
-    <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="63" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B23" s="58" t="s">
-        <v>1023</v>
-      </c>
-      <c r="C23" s="58" t="s">
+      <c r="B27" s="57" t="s">
+        <v>21</v>
+      </c>
+      <c r="C27" s="57" t="s">
+        <v>1030</v>
+      </c>
+      <c r="D27" s="57" t="s">
+        <v>1031</v>
+      </c>
+      <c r="E27" s="57" t="s">
+        <v>1032</v>
+      </c>
+      <c r="F27" s="60"/>
+      <c r="G27" s="60"/>
+      <c r="H27" s="60"/>
+      <c r="I27" s="60"/>
+    </row>
+    <row r="28" ht="18.75" customHeight="1">
+      <c r="A28" s="62" t="s">
         <v>1024</v>
       </c>
-      <c r="D23" s="58" t="s">
-        <v>1025</v>
-      </c>
-      <c r="E23" s="58" t="s">
-        <v>1026</v>
-      </c>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
-    </row>
-    <row r="24" ht="18.75" customHeight="1">
-      <c r="D24" s="66"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
-    </row>
-    <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="62" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B25" s="63" t="s">
-        <v>1014</v>
-      </c>
-      <c r="D25" s="63" t="s">
-        <v>1015</v>
-      </c>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
-    </row>
-    <row r="26" ht="18.75" customHeight="1">
-      <c r="B26" s="64" t="s">
-        <v>1016</v>
-      </c>
-      <c r="C26" s="64" t="s">
-        <v>1017</v>
-      </c>
-      <c r="D26" s="64" t="s">
-        <v>1016</v>
-      </c>
-      <c r="E26" s="64" t="s">
-        <v>1017</v>
-      </c>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
-    </row>
-    <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="65" t="s">
-        <v>1018</v>
-      </c>
-      <c r="B27" s="58" t="s">
-        <v>21</v>
-      </c>
-      <c r="C27" s="58" t="s">
-        <v>1028</v>
-      </c>
-      <c r="D27" s="58" t="s">
-        <v>1029</v>
-      </c>
-      <c r="E27" s="58" t="s">
-        <v>1030</v>
-      </c>
-      <c r="F27" s="61"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61"/>
-    </row>
-    <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="63" t="s">
-        <v>1022</v>
-      </c>
-      <c r="B28" s="58" t="s">
-        <v>1031</v>
-      </c>
-      <c r="C28" s="58" t="s">
-        <v>1032</v>
-      </c>
-      <c r="D28" s="58" t="s">
+      <c r="B28" s="57" t="s">
         <v>1033</v>
       </c>
-      <c r="E28" s="58" t="s">
+      <c r="C28" s="57" t="s">
         <v>1034</v>
       </c>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="61"/>
+      <c r="D28" s="57" t="s">
+        <v>1035</v>
+      </c>
+      <c r="E28" s="57" t="s">
+        <v>1036</v>
+      </c>
+      <c r="F28" s="60"/>
+      <c r="G28" s="60"/>
+      <c r="H28" s="60"/>
+      <c r="I28" s="60"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="61"/>
-      <c r="B29" s="61"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="61"/>
+      <c r="A29" s="60"/>
+      <c r="B29" s="60"/>
+      <c r="C29" s="60"/>
+      <c r="D29" s="60"/>
+      <c r="E29" s="60"/>
+      <c r="F29" s="60"/>
+      <c r="G29" s="60"/>
+      <c r="H29" s="60"/>
+      <c r="I29" s="60"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="61"/>
-      <c r="B30" s="61"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
+      <c r="A30" s="60"/>
+      <c r="B30" s="60"/>
+      <c r="C30" s="60"/>
+      <c r="D30" s="60"/>
+      <c r="E30" s="60"/>
+      <c r="F30" s="60"/>
+      <c r="G30" s="60"/>
+      <c r="H30" s="60"/>
+      <c r="I30" s="60"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="61"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
+      <c r="A31" s="60"/>
+      <c r="B31" s="60"/>
+      <c r="C31" s="60"/>
+      <c r="D31" s="60"/>
+      <c r="E31" s="60"/>
+      <c r="F31" s="60"/>
+      <c r="G31" s="60"/>
+      <c r="H31" s="60"/>
+      <c r="I31" s="60"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="61"/>
-      <c r="B32" s="61"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
+      <c r="A32" s="60"/>
+      <c r="B32" s="60"/>
+      <c r="C32" s="60"/>
+      <c r="D32" s="60"/>
+      <c r="E32" s="60"/>
+      <c r="F32" s="60"/>
+      <c r="G32" s="60"/>
+      <c r="H32" s="60"/>
+      <c r="I32" s="60"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="61"/>
-      <c r="B33" s="61"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
+      <c r="A33" s="60"/>
+      <c r="B33" s="60"/>
+      <c r="C33" s="60"/>
+      <c r="D33" s="60"/>
+      <c r="E33" s="60"/>
+      <c r="F33" s="60"/>
+      <c r="G33" s="60"/>
+      <c r="H33" s="60"/>
+      <c r="I33" s="60"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="61"/>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
+      <c r="A34" s="60"/>
+      <c r="B34" s="60"/>
+      <c r="C34" s="60"/>
+      <c r="D34" s="60"/>
+      <c r="E34" s="60"/>
+      <c r="F34" s="60"/>
+      <c r="G34" s="60"/>
+      <c r="H34" s="60"/>
+      <c r="I34" s="60"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="61"/>
-      <c r="B35" s="61"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="61"/>
+      <c r="A35" s="60"/>
+      <c r="B35" s="60"/>
+      <c r="C35" s="60"/>
+      <c r="D35" s="60"/>
+      <c r="E35" s="60"/>
+      <c r="F35" s="60"/>
+      <c r="G35" s="60"/>
+      <c r="H35" s="60"/>
+      <c r="I35" s="60"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="61"/>
-      <c r="B36" s="61"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
+      <c r="A36" s="60"/>
+      <c r="B36" s="60"/>
+      <c r="C36" s="60"/>
+      <c r="D36" s="60"/>
+      <c r="E36" s="60"/>
+      <c r="F36" s="60"/>
+      <c r="G36" s="60"/>
+      <c r="H36" s="60"/>
+      <c r="I36" s="60"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="61"/>
-      <c r="B37" s="61"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
+      <c r="A37" s="60"/>
+      <c r="B37" s="60"/>
+      <c r="C37" s="60"/>
+      <c r="D37" s="60"/>
+      <c r="E37" s="60"/>
+      <c r="F37" s="60"/>
+      <c r="G37" s="60"/>
+      <c r="H37" s="60"/>
+      <c r="I37" s="60"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="61"/>
-      <c r="B38" s="61"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="61"/>
+      <c r="A38" s="60"/>
+      <c r="B38" s="60"/>
+      <c r="C38" s="60"/>
+      <c r="D38" s="60"/>
+      <c r="E38" s="60"/>
+      <c r="F38" s="60"/>
+      <c r="G38" s="60"/>
+      <c r="H38" s="60"/>
+      <c r="I38" s="60"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="61"/>
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="61"/>
+      <c r="A39" s="60"/>
+      <c r="B39" s="60"/>
+      <c r="C39" s="60"/>
+      <c r="D39" s="60"/>
+      <c r="E39" s="60"/>
+      <c r="F39" s="60"/>
+      <c r="G39" s="60"/>
+      <c r="H39" s="60"/>
+      <c r="I39" s="60"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="61"/>
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
+      <c r="A40" s="60"/>
+      <c r="B40" s="60"/>
+      <c r="C40" s="60"/>
+      <c r="D40" s="60"/>
+      <c r="E40" s="60"/>
+      <c r="F40" s="60"/>
+      <c r="G40" s="60"/>
+      <c r="H40" s="60"/>
+      <c r="I40" s="60"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="61"/>
-      <c r="B41" s="61"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
+      <c r="A41" s="60"/>
+      <c r="B41" s="60"/>
+      <c r="C41" s="60"/>
+      <c r="D41" s="60"/>
+      <c r="E41" s="60"/>
+      <c r="F41" s="60"/>
+      <c r="G41" s="60"/>
+      <c r="H41" s="60"/>
+      <c r="I41" s="60"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="61"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
+      <c r="A42" s="60"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="60"/>
+      <c r="D42" s="60"/>
+      <c r="E42" s="60"/>
+      <c r="F42" s="60"/>
+      <c r="G42" s="60"/>
+      <c r="H42" s="60"/>
+      <c r="I42" s="60"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="61"/>
-      <c r="B43" s="61"/>
-      <c r="C43" s="61"/>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="61"/>
+      <c r="A43" s="60"/>
+      <c r="B43" s="60"/>
+      <c r="C43" s="60"/>
+      <c r="D43" s="60"/>
+      <c r="E43" s="60"/>
+      <c r="F43" s="60"/>
+      <c r="G43" s="60"/>
+      <c r="H43" s="60"/>
+      <c r="I43" s="60"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" s="61"/>
-      <c r="B44" s="61"/>
-      <c r="C44" s="61"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="61"/>
-      <c r="I44" s="61"/>
+      <c r="A44" s="60"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="60"/>
+      <c r="D44" s="60"/>
+      <c r="E44" s="60"/>
+      <c r="F44" s="60"/>
+      <c r="G44" s="60"/>
+      <c r="H44" s="60"/>
+      <c r="I44" s="60"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" s="61"/>
-      <c r="B45" s="61"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="61"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="61"/>
-      <c r="H45" s="61"/>
-      <c r="I45" s="61"/>
+      <c r="A45" s="60"/>
+      <c r="B45" s="60"/>
+      <c r="C45" s="60"/>
+      <c r="D45" s="60"/>
+      <c r="E45" s="60"/>
+      <c r="F45" s="60"/>
+      <c r="G45" s="60"/>
+      <c r="H45" s="60"/>
+      <c r="I45" s="60"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" s="61"/>
-      <c r="B46" s="61"/>
-      <c r="C46" s="61"/>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="61"/>
-      <c r="I46" s="61"/>
+      <c r="A46" s="60"/>
+      <c r="B46" s="60"/>
+      <c r="C46" s="60"/>
+      <c r="D46" s="60"/>
+      <c r="E46" s="60"/>
+      <c r="F46" s="60"/>
+      <c r="G46" s="60"/>
+      <c r="H46" s="60"/>
+      <c r="I46" s="60"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
-      <c r="A47" s="61"/>
-      <c r="B47" s="61"/>
-      <c r="C47" s="61"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="61"/>
-      <c r="I47" s="61"/>
+      <c r="A47" s="60"/>
+      <c r="B47" s="60"/>
+      <c r="C47" s="60"/>
+      <c r="D47" s="60"/>
+      <c r="E47" s="60"/>
+      <c r="F47" s="60"/>
+      <c r="G47" s="60"/>
+      <c r="H47" s="60"/>
+      <c r="I47" s="60"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
-      <c r="A48" s="61"/>
-      <c r="B48" s="61"/>
-      <c r="C48" s="61"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="61"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="61"/>
-      <c r="I48" s="61"/>
+      <c r="A48" s="60"/>
+      <c r="B48" s="60"/>
+      <c r="C48" s="60"/>
+      <c r="D48" s="60"/>
+      <c r="E48" s="60"/>
+      <c r="F48" s="60"/>
+      <c r="G48" s="60"/>
+      <c r="H48" s="60"/>
+      <c r="I48" s="60"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" s="61"/>
-      <c r="B49" s="61"/>
-      <c r="C49" s="61"/>
-      <c r="D49" s="61"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61"/>
+      <c r="A49" s="60"/>
+      <c r="B49" s="60"/>
+      <c r="C49" s="60"/>
+      <c r="D49" s="60"/>
+      <c r="E49" s="60"/>
+      <c r="F49" s="60"/>
+      <c r="G49" s="60"/>
+      <c r="H49" s="60"/>
+      <c r="I49" s="60"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="A50" s="61"/>
-      <c r="B50" s="61"/>
-      <c r="C50" s="61"/>
-      <c r="D50" s="61"/>
-      <c r="E50" s="61"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="61"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="61"/>
+      <c r="A50" s="60"/>
+      <c r="B50" s="60"/>
+      <c r="C50" s="60"/>
+      <c r="D50" s="60"/>
+      <c r="E50" s="60"/>
+      <c r="F50" s="60"/>
+      <c r="G50" s="60"/>
+      <c r="H50" s="60"/>
+      <c r="I50" s="60"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
-      <c r="A51" s="61"/>
-      <c r="B51" s="61"/>
-      <c r="C51" s="61"/>
-      <c r="D51" s="61"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="61"/>
-      <c r="G51" s="61"/>
-      <c r="H51" s="61"/>
-      <c r="I51" s="61"/>
+      <c r="A51" s="60"/>
+      <c r="B51" s="60"/>
+      <c r="C51" s="60"/>
+      <c r="D51" s="60"/>
+      <c r="E51" s="60"/>
+      <c r="F51" s="60"/>
+      <c r="G51" s="60"/>
+      <c r="H51" s="60"/>
+      <c r="I51" s="60"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
-      <c r="A52" s="61"/>
-      <c r="B52" s="61"/>
-      <c r="C52" s="61"/>
-      <c r="D52" s="61"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="61"/>
+      <c r="A52" s="60"/>
+      <c r="B52" s="60"/>
+      <c r="C52" s="60"/>
+      <c r="D52" s="60"/>
+      <c r="E52" s="60"/>
+      <c r="F52" s="60"/>
+      <c r="G52" s="60"/>
+      <c r="H52" s="60"/>
+      <c r="I52" s="60"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
-      <c r="A53" s="61"/>
-      <c r="B53" s="61"/>
-      <c r="C53" s="61"/>
-      <c r="D53" s="61"/>
-      <c r="E53" s="61"/>
-      <c r="F53" s="61"/>
-      <c r="G53" s="61"/>
-      <c r="H53" s="61"/>
-      <c r="I53" s="61"/>
+      <c r="A53" s="60"/>
+      <c r="B53" s="60"/>
+      <c r="C53" s="60"/>
+      <c r="D53" s="60"/>
+      <c r="E53" s="60"/>
+      <c r="F53" s="60"/>
+      <c r="G53" s="60"/>
+      <c r="H53" s="60"/>
+      <c r="I53" s="60"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" s="61"/>
-      <c r="B54" s="61"/>
-      <c r="C54" s="61"/>
-      <c r="D54" s="61"/>
-      <c r="E54" s="61"/>
-      <c r="F54" s="61"/>
-      <c r="G54" s="61"/>
-      <c r="H54" s="61"/>
-      <c r="I54" s="61"/>
+      <c r="A54" s="60"/>
+      <c r="B54" s="60"/>
+      <c r="C54" s="60"/>
+      <c r="D54" s="60"/>
+      <c r="E54" s="60"/>
+      <c r="F54" s="60"/>
+      <c r="G54" s="60"/>
+      <c r="H54" s="60"/>
+      <c r="I54" s="60"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
-      <c r="A55" s="61"/>
-      <c r="B55" s="61"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="61"/>
-      <c r="G55" s="61"/>
-      <c r="H55" s="61"/>
-      <c r="I55" s="61"/>
+      <c r="A55" s="60"/>
+      <c r="B55" s="60"/>
+      <c r="C55" s="60"/>
+      <c r="D55" s="60"/>
+      <c r="E55" s="60"/>
+      <c r="F55" s="60"/>
+      <c r="G55" s="60"/>
+      <c r="H55" s="60"/>
+      <c r="I55" s="60"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
-      <c r="A56" s="61"/>
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="61"/>
-      <c r="F56" s="61"/>
-      <c r="G56" s="61"/>
-      <c r="H56" s="61"/>
-      <c r="I56" s="61"/>
+      <c r="A56" s="60"/>
+      <c r="B56" s="60"/>
+      <c r="C56" s="60"/>
+      <c r="D56" s="60"/>
+      <c r="E56" s="60"/>
+      <c r="F56" s="60"/>
+      <c r="G56" s="60"/>
+      <c r="H56" s="60"/>
+      <c r="I56" s="60"/>
     </row>
     <row r="57" ht="18.75" customHeight="1">
-      <c r="A57" s="61"/>
-      <c r="B57" s="61"/>
-      <c r="C57" s="61"/>
-      <c r="D57" s="61"/>
-      <c r="E57" s="61"/>
-      <c r="F57" s="61"/>
-      <c r="G57" s="61"/>
-      <c r="H57" s="61"/>
-      <c r="I57" s="61"/>
+      <c r="A57" s="60"/>
+      <c r="B57" s="60"/>
+      <c r="C57" s="60"/>
+      <c r="D57" s="60"/>
+      <c r="E57" s="60"/>
+      <c r="F57" s="60"/>
+      <c r="G57" s="60"/>
+      <c r="H57" s="60"/>
+      <c r="I57" s="60"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
-      <c r="A58" s="61"/>
-      <c r="B58" s="61"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="61"/>
-      <c r="E58" s="61"/>
-      <c r="F58" s="61"/>
-      <c r="G58" s="61"/>
-      <c r="H58" s="61"/>
-      <c r="I58" s="61"/>
+      <c r="A58" s="60"/>
+      <c r="B58" s="60"/>
+      <c r="C58" s="60"/>
+      <c r="D58" s="60"/>
+      <c r="E58" s="60"/>
+      <c r="F58" s="60"/>
+      <c r="G58" s="60"/>
+      <c r="H58" s="60"/>
+      <c r="I58" s="60"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
-      <c r="A59" s="61"/>
-      <c r="B59" s="61"/>
-      <c r="C59" s="61"/>
-      <c r="D59" s="61"/>
-      <c r="E59" s="61"/>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="61"/>
-      <c r="I59" s="61"/>
+      <c r="A59" s="60"/>
+      <c r="B59" s="60"/>
+      <c r="C59" s="60"/>
+      <c r="D59" s="60"/>
+      <c r="E59" s="60"/>
+      <c r="F59" s="60"/>
+      <c r="G59" s="60"/>
+      <c r="H59" s="60"/>
+      <c r="I59" s="60"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
-      <c r="A60" s="61"/>
-      <c r="B60" s="61"/>
-      <c r="C60" s="61"/>
-      <c r="D60" s="61"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="61"/>
+      <c r="A60" s="60"/>
+      <c r="B60" s="60"/>
+      <c r="C60" s="60"/>
+      <c r="D60" s="60"/>
+      <c r="E60" s="60"/>
+      <c r="F60" s="60"/>
+      <c r="G60" s="60"/>
+      <c r="H60" s="60"/>
+      <c r="I60" s="60"/>
     </row>
     <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" s="61"/>
-      <c r="B61" s="61"/>
-      <c r="C61" s="61"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61"/>
+      <c r="A61" s="60"/>
+      <c r="B61" s="60"/>
+      <c r="C61" s="60"/>
+      <c r="D61" s="60"/>
+      <c r="E61" s="60"/>
+      <c r="F61" s="60"/>
+      <c r="G61" s="60"/>
+      <c r="H61" s="60"/>
+      <c r="I61" s="60"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
-      <c r="A62" s="61"/>
-      <c r="B62" s="61"/>
-      <c r="C62" s="61"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="61"/>
-      <c r="I62" s="61"/>
+      <c r="A62" s="60"/>
+      <c r="B62" s="60"/>
+      <c r="C62" s="60"/>
+      <c r="D62" s="60"/>
+      <c r="E62" s="60"/>
+      <c r="F62" s="60"/>
+      <c r="G62" s="60"/>
+      <c r="H62" s="60"/>
+      <c r="I62" s="60"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
-      <c r="A63" s="61"/>
-      <c r="B63" s="61"/>
-      <c r="C63" s="61"/>
-      <c r="D63" s="61"/>
-      <c r="E63" s="61"/>
-      <c r="F63" s="61"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="61"/>
-      <c r="I63" s="61"/>
+      <c r="A63" s="60"/>
+      <c r="B63" s="60"/>
+      <c r="C63" s="60"/>
+      <c r="D63" s="60"/>
+      <c r="E63" s="60"/>
+      <c r="F63" s="60"/>
+      <c r="G63" s="60"/>
+      <c r="H63" s="60"/>
+      <c r="I63" s="60"/>
     </row>
     <row r="64" ht="18.75" customHeight="1">
-      <c r="A64" s="61"/>
-      <c r="B64" s="61"/>
-      <c r="C64" s="61"/>
-      <c r="D64" s="61"/>
-      <c r="E64" s="61"/>
-      <c r="F64" s="61"/>
-      <c r="G64" s="61"/>
-      <c r="H64" s="61"/>
-      <c r="I64" s="61"/>
+      <c r="A64" s="60"/>
+      <c r="B64" s="60"/>
+      <c r="C64" s="60"/>
+      <c r="D64" s="60"/>
+      <c r="E64" s="60"/>
+      <c r="F64" s="60"/>
+      <c r="G64" s="60"/>
+      <c r="H64" s="60"/>
+      <c r="I64" s="60"/>
     </row>
     <row r="65" ht="18.75" customHeight="1">
-      <c r="A65" s="61"/>
-      <c r="B65" s="61"/>
-      <c r="C65" s="61"/>
-      <c r="D65" s="61"/>
-      <c r="E65" s="61"/>
-      <c r="F65" s="61"/>
-      <c r="G65" s="61"/>
-      <c r="H65" s="61"/>
-      <c r="I65" s="61"/>
+      <c r="A65" s="60"/>
+      <c r="B65" s="60"/>
+      <c r="C65" s="60"/>
+      <c r="D65" s="60"/>
+      <c r="E65" s="60"/>
+      <c r="F65" s="60"/>
+      <c r="G65" s="60"/>
+      <c r="H65" s="60"/>
+      <c r="I65" s="60"/>
     </row>
     <row r="66" ht="18.75" customHeight="1">
-      <c r="A66" s="61"/>
-      <c r="B66" s="61"/>
-      <c r="C66" s="61"/>
-      <c r="D66" s="61"/>
-      <c r="E66" s="61"/>
-      <c r="F66" s="61"/>
-      <c r="G66" s="61"/>
-      <c r="H66" s="61"/>
-      <c r="I66" s="61"/>
+      <c r="A66" s="60"/>
+      <c r="B66" s="60"/>
+      <c r="C66" s="60"/>
+      <c r="D66" s="60"/>
+      <c r="E66" s="60"/>
+      <c r="F66" s="60"/>
+      <c r="G66" s="60"/>
+      <c r="H66" s="60"/>
+      <c r="I66" s="60"/>
     </row>
     <row r="67" ht="18.75" customHeight="1">
-      <c r="A67" s="61"/>
-      <c r="B67" s="61"/>
-      <c r="C67" s="61"/>
-      <c r="D67" s="61"/>
-      <c r="E67" s="61"/>
-      <c r="F67" s="61"/>
-      <c r="G67" s="61"/>
-      <c r="H67" s="61"/>
-      <c r="I67" s="61"/>
+      <c r="A67" s="60"/>
+      <c r="B67" s="60"/>
+      <c r="C67" s="60"/>
+      <c r="D67" s="60"/>
+      <c r="E67" s="60"/>
+      <c r="F67" s="60"/>
+      <c r="G67" s="60"/>
+      <c r="H67" s="60"/>
+      <c r="I67" s="60"/>
     </row>
     <row r="68" ht="18.75" customHeight="1">
-      <c r="A68" s="61"/>
-      <c r="B68" s="61"/>
-      <c r="C68" s="61"/>
-      <c r="D68" s="61"/>
-      <c r="E68" s="61"/>
-      <c r="F68" s="61"/>
-      <c r="G68" s="61"/>
-      <c r="H68" s="61"/>
-      <c r="I68" s="61"/>
+      <c r="A68" s="60"/>
+      <c r="B68" s="60"/>
+      <c r="C68" s="60"/>
+      <c r="D68" s="60"/>
+      <c r="E68" s="60"/>
+      <c r="F68" s="60"/>
+      <c r="G68" s="60"/>
+      <c r="H68" s="60"/>
+      <c r="I68" s="60"/>
     </row>
     <row r="69" ht="18.75" customHeight="1">
-      <c r="A69" s="61"/>
-      <c r="B69" s="61"/>
-      <c r="C69" s="61"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="61"/>
-      <c r="F69" s="61"/>
-      <c r="G69" s="61"/>
-      <c r="H69" s="61"/>
-      <c r="I69" s="61"/>
+      <c r="A69" s="60"/>
+      <c r="B69" s="60"/>
+      <c r="C69" s="60"/>
+      <c r="D69" s="60"/>
+      <c r="E69" s="60"/>
+      <c r="F69" s="60"/>
+      <c r="G69" s="60"/>
+      <c r="H69" s="60"/>
+      <c r="I69" s="60"/>
     </row>
     <row r="70" ht="18.75" customHeight="1">
-      <c r="A70" s="61"/>
-      <c r="B70" s="61"/>
-      <c r="C70" s="61"/>
-      <c r="D70" s="61"/>
-      <c r="E70" s="61"/>
-      <c r="F70" s="61"/>
-      <c r="G70" s="61"/>
-      <c r="H70" s="61"/>
-      <c r="I70" s="61"/>
+      <c r="A70" s="60"/>
+      <c r="B70" s="60"/>
+      <c r="C70" s="60"/>
+      <c r="D70" s="60"/>
+      <c r="E70" s="60"/>
+      <c r="F70" s="60"/>
+      <c r="G70" s="60"/>
+      <c r="H70" s="60"/>
+      <c r="I70" s="60"/>
     </row>
     <row r="71" ht="18.75" customHeight="1">
-      <c r="A71" s="61"/>
-      <c r="B71" s="61"/>
-      <c r="C71" s="61"/>
-      <c r="D71" s="61"/>
-      <c r="E71" s="61"/>
-      <c r="F71" s="61"/>
-      <c r="G71" s="61"/>
-      <c r="H71" s="61"/>
-      <c r="I71" s="61"/>
+      <c r="A71" s="60"/>
+      <c r="B71" s="60"/>
+      <c r="C71" s="60"/>
+      <c r="D71" s="60"/>
+      <c r="E71" s="60"/>
+      <c r="F71" s="60"/>
+      <c r="G71" s="60"/>
+      <c r="H71" s="60"/>
+      <c r="I71" s="60"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
-      <c r="A72" s="61"/>
-      <c r="B72" s="61"/>
-      <c r="C72" s="61"/>
-      <c r="D72" s="61"/>
-      <c r="E72" s="61"/>
-      <c r="F72" s="61"/>
-      <c r="G72" s="61"/>
-      <c r="H72" s="61"/>
-      <c r="I72" s="61"/>
+      <c r="A72" s="60"/>
+      <c r="B72" s="60"/>
+      <c r="C72" s="60"/>
+      <c r="D72" s="60"/>
+      <c r="E72" s="60"/>
+      <c r="F72" s="60"/>
+      <c r="G72" s="60"/>
+      <c r="H72" s="60"/>
+      <c r="I72" s="60"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
-      <c r="A73" s="61"/>
-      <c r="B73" s="61"/>
-      <c r="C73" s="61"/>
-      <c r="D73" s="61"/>
-      <c r="E73" s="61"/>
-      <c r="F73" s="61"/>
-      <c r="G73" s="61"/>
-      <c r="H73" s="61"/>
-      <c r="I73" s="61"/>
+      <c r="A73" s="60"/>
+      <c r="B73" s="60"/>
+      <c r="C73" s="60"/>
+      <c r="D73" s="60"/>
+      <c r="E73" s="60"/>
+      <c r="F73" s="60"/>
+      <c r="G73" s="60"/>
+      <c r="H73" s="60"/>
+      <c r="I73" s="60"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
-      <c r="A74" s="61"/>
-      <c r="B74" s="61"/>
-      <c r="C74" s="61"/>
-      <c r="D74" s="61"/>
-      <c r="E74" s="61"/>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="61"/>
-      <c r="I74" s="61"/>
+      <c r="A74" s="60"/>
+      <c r="B74" s="60"/>
+      <c r="C74" s="60"/>
+      <c r="D74" s="60"/>
+      <c r="E74" s="60"/>
+      <c r="F74" s="60"/>
+      <c r="G74" s="60"/>
+      <c r="H74" s="60"/>
+      <c r="I74" s="60"/>
     </row>
     <row r="75" ht="18.75" customHeight="1">
-      <c r="A75" s="61"/>
-      <c r="B75" s="61"/>
-      <c r="C75" s="61"/>
-      <c r="D75" s="61"/>
-      <c r="E75" s="61"/>
-      <c r="F75" s="61"/>
-      <c r="G75" s="61"/>
-      <c r="H75" s="61"/>
-      <c r="I75" s="61"/>
+      <c r="A75" s="60"/>
+      <c r="B75" s="60"/>
+      <c r="C75" s="60"/>
+      <c r="D75" s="60"/>
+      <c r="E75" s="60"/>
+      <c r="F75" s="60"/>
+      <c r="G75" s="60"/>
+      <c r="H75" s="60"/>
+      <c r="I75" s="60"/>
     </row>
     <row r="76" ht="18.75" customHeight="1">
-      <c r="A76" s="61"/>
-      <c r="B76" s="61"/>
-      <c r="C76" s="61"/>
-      <c r="D76" s="61"/>
-      <c r="E76" s="61"/>
-      <c r="F76" s="61"/>
-      <c r="G76" s="61"/>
-      <c r="H76" s="61"/>
-      <c r="I76" s="61"/>
+      <c r="A76" s="60"/>
+      <c r="B76" s="60"/>
+      <c r="C76" s="60"/>
+      <c r="D76" s="60"/>
+      <c r="E76" s="60"/>
+      <c r="F76" s="60"/>
+      <c r="G76" s="60"/>
+      <c r="H76" s="60"/>
+      <c r="I76" s="60"/>
     </row>
     <row r="77" ht="18.75" customHeight="1">
-      <c r="A77" s="61"/>
-      <c r="B77" s="61"/>
-      <c r="C77" s="61"/>
-      <c r="D77" s="61"/>
-      <c r="E77" s="61"/>
-      <c r="F77" s="61"/>
-      <c r="G77" s="61"/>
-      <c r="H77" s="61"/>
-      <c r="I77" s="61"/>
+      <c r="A77" s="60"/>
+      <c r="B77" s="60"/>
+      <c r="C77" s="60"/>
+      <c r="D77" s="60"/>
+      <c r="E77" s="60"/>
+      <c r="F77" s="60"/>
+      <c r="G77" s="60"/>
+      <c r="H77" s="60"/>
+      <c r="I77" s="60"/>
     </row>
     <row r="78" ht="18.75" customHeight="1">
-      <c r="A78" s="61"/>
-      <c r="B78" s="61"/>
-      <c r="C78" s="61"/>
-      <c r="D78" s="61"/>
-      <c r="E78" s="61"/>
-      <c r="F78" s="61"/>
-      <c r="G78" s="61"/>
-      <c r="H78" s="61"/>
-      <c r="I78" s="61"/>
+      <c r="A78" s="60"/>
+      <c r="B78" s="60"/>
+      <c r="C78" s="60"/>
+      <c r="D78" s="60"/>
+      <c r="E78" s="60"/>
+      <c r="F78" s="60"/>
+      <c r="G78" s="60"/>
+      <c r="H78" s="60"/>
+      <c r="I78" s="60"/>
     </row>
     <row r="79" ht="18.75" customHeight="1">
-      <c r="A79" s="61"/>
-      <c r="B79" s="61"/>
-      <c r="C79" s="61"/>
-      <c r="D79" s="61"/>
-      <c r="E79" s="61"/>
-      <c r="F79" s="61"/>
-      <c r="G79" s="61"/>
-      <c r="H79" s="61"/>
-      <c r="I79" s="61"/>
+      <c r="A79" s="60"/>
+      <c r="B79" s="60"/>
+      <c r="C79" s="60"/>
+      <c r="D79" s="60"/>
+      <c r="E79" s="60"/>
+      <c r="F79" s="60"/>
+      <c r="G79" s="60"/>
+      <c r="H79" s="60"/>
+      <c r="I79" s="60"/>
     </row>
     <row r="80" ht="18.75" customHeight="1">
-      <c r="A80" s="61"/>
-      <c r="B80" s="61"/>
-      <c r="C80" s="61"/>
-      <c r="D80" s="61"/>
-      <c r="E80" s="61"/>
-      <c r="F80" s="61"/>
-      <c r="G80" s="61"/>
-      <c r="H80" s="61"/>
-      <c r="I80" s="61"/>
+      <c r="A80" s="60"/>
+      <c r="B80" s="60"/>
+      <c r="C80" s="60"/>
+      <c r="D80" s="60"/>
+      <c r="E80" s="60"/>
+      <c r="F80" s="60"/>
+      <c r="G80" s="60"/>
+      <c r="H80" s="60"/>
+      <c r="I80" s="60"/>
     </row>
     <row r="81" ht="18.75" customHeight="1">
-      <c r="A81" s="61"/>
-      <c r="B81" s="61"/>
-      <c r="C81" s="61"/>
-      <c r="D81" s="61"/>
-      <c r="E81" s="61"/>
-      <c r="F81" s="61"/>
-      <c r="G81" s="61"/>
-      <c r="H81" s="61"/>
-      <c r="I81" s="61"/>
+      <c r="A81" s="60"/>
+      <c r="B81" s="60"/>
+      <c r="C81" s="60"/>
+      <c r="D81" s="60"/>
+      <c r="E81" s="60"/>
+      <c r="F81" s="60"/>
+      <c r="G81" s="60"/>
+      <c r="H81" s="60"/>
+      <c r="I81" s="60"/>
     </row>
     <row r="82" ht="18.75" customHeight="1">
-      <c r="A82" s="61"/>
-      <c r="B82" s="61"/>
-      <c r="C82" s="61"/>
-      <c r="D82" s="61"/>
-      <c r="E82" s="61"/>
-      <c r="F82" s="61"/>
-      <c r="G82" s="61"/>
-      <c r="H82" s="61"/>
-      <c r="I82" s="61"/>
+      <c r="A82" s="60"/>
+      <c r="B82" s="60"/>
+      <c r="C82" s="60"/>
+      <c r="D82" s="60"/>
+      <c r="E82" s="60"/>
+      <c r="F82" s="60"/>
+      <c r="G82" s="60"/>
+      <c r="H82" s="60"/>
+      <c r="I82" s="60"/>
     </row>
     <row r="83" ht="18.75" customHeight="1">
-      <c r="A83" s="61"/>
-      <c r="B83" s="61"/>
-      <c r="C83" s="61"/>
-      <c r="D83" s="61"/>
-      <c r="E83" s="61"/>
-      <c r="F83" s="61"/>
-      <c r="G83" s="61"/>
-      <c r="H83" s="61"/>
-      <c r="I83" s="61"/>
+      <c r="A83" s="60"/>
+      <c r="B83" s="60"/>
+      <c r="C83" s="60"/>
+      <c r="D83" s="60"/>
+      <c r="E83" s="60"/>
+      <c r="F83" s="60"/>
+      <c r="G83" s="60"/>
+      <c r="H83" s="60"/>
+      <c r="I83" s="60"/>
     </row>
     <row r="84" ht="18.75" customHeight="1">
-      <c r="A84" s="61"/>
-      <c r="B84" s="61"/>
-      <c r="C84" s="61"/>
-      <c r="D84" s="61"/>
-      <c r="E84" s="61"/>
-      <c r="F84" s="61"/>
-      <c r="G84" s="61"/>
-      <c r="H84" s="61"/>
-      <c r="I84" s="61"/>
+      <c r="A84" s="60"/>
+      <c r="B84" s="60"/>
+      <c r="C84" s="60"/>
+      <c r="D84" s="60"/>
+      <c r="E84" s="60"/>
+      <c r="F84" s="60"/>
+      <c r="G84" s="60"/>
+      <c r="H84" s="60"/>
+      <c r="I84" s="60"/>
     </row>
     <row r="85" ht="18.75" customHeight="1">
-      <c r="A85" s="61"/>
-      <c r="B85" s="61"/>
-      <c r="C85" s="61"/>
-      <c r="D85" s="61"/>
-      <c r="E85" s="61"/>
-      <c r="F85" s="61"/>
-      <c r="G85" s="61"/>
-      <c r="H85" s="61"/>
-      <c r="I85" s="61"/>
+      <c r="A85" s="60"/>
+      <c r="B85" s="60"/>
+      <c r="C85" s="60"/>
+      <c r="D85" s="60"/>
+      <c r="E85" s="60"/>
+      <c r="F85" s="60"/>
+      <c r="G85" s="60"/>
+      <c r="H85" s="60"/>
+      <c r="I85" s="60"/>
     </row>
     <row r="86" ht="18.75" customHeight="1">
-      <c r="A86" s="61"/>
-      <c r="B86" s="61"/>
-      <c r="C86" s="61"/>
-      <c r="D86" s="61"/>
-      <c r="E86" s="61"/>
-      <c r="F86" s="61"/>
-      <c r="G86" s="61"/>
-      <c r="H86" s="61"/>
-      <c r="I86" s="61"/>
+      <c r="A86" s="60"/>
+      <c r="B86" s="60"/>
+      <c r="C86" s="60"/>
+      <c r="D86" s="60"/>
+      <c r="E86" s="60"/>
+      <c r="F86" s="60"/>
+      <c r="G86" s="60"/>
+      <c r="H86" s="60"/>
+      <c r="I86" s="60"/>
     </row>
     <row r="87" ht="18.75" customHeight="1">
-      <c r="A87" s="61"/>
-      <c r="B87" s="61"/>
-      <c r="C87" s="61"/>
-      <c r="D87" s="61"/>
-      <c r="E87" s="61"/>
-      <c r="F87" s="61"/>
-      <c r="G87" s="61"/>
-      <c r="H87" s="61"/>
-      <c r="I87" s="61"/>
+      <c r="A87" s="60"/>
+      <c r="B87" s="60"/>
+      <c r="C87" s="60"/>
+      <c r="D87" s="60"/>
+      <c r="E87" s="60"/>
+      <c r="F87" s="60"/>
+      <c r="G87" s="60"/>
+      <c r="H87" s="60"/>
+      <c r="I87" s="60"/>
     </row>
     <row r="88" ht="18.75" customHeight="1">
-      <c r="A88" s="61"/>
-      <c r="B88" s="61"/>
-      <c r="C88" s="61"/>
-      <c r="D88" s="61"/>
-      <c r="E88" s="61"/>
-      <c r="F88" s="61"/>
-      <c r="G88" s="61"/>
-      <c r="H88" s="61"/>
-      <c r="I88" s="61"/>
+      <c r="A88" s="60"/>
+      <c r="B88" s="60"/>
+      <c r="C88" s="60"/>
+      <c r="D88" s="60"/>
+      <c r="E88" s="60"/>
+      <c r="F88" s="60"/>
+      <c r="G88" s="60"/>
+      <c r="H88" s="60"/>
+      <c r="I88" s="60"/>
     </row>
     <row r="89" ht="18.75" customHeight="1">
-      <c r="A89" s="61"/>
-      <c r="B89" s="61"/>
-      <c r="C89" s="61"/>
-      <c r="D89" s="61"/>
-      <c r="E89" s="61"/>
-      <c r="F89" s="61"/>
-      <c r="G89" s="61"/>
-      <c r="H89" s="61"/>
-      <c r="I89" s="61"/>
+      <c r="A89" s="60"/>
+      <c r="B89" s="60"/>
+      <c r="C89" s="60"/>
+      <c r="D89" s="60"/>
+      <c r="E89" s="60"/>
+      <c r="F89" s="60"/>
+      <c r="G89" s="60"/>
+      <c r="H89" s="60"/>
+      <c r="I89" s="60"/>
     </row>
     <row r="90" ht="18.75" customHeight="1">
-      <c r="A90" s="61"/>
-      <c r="B90" s="61"/>
-      <c r="C90" s="61"/>
-      <c r="D90" s="61"/>
-      <c r="E90" s="61"/>
-      <c r="F90" s="61"/>
-      <c r="G90" s="61"/>
-      <c r="H90" s="61"/>
-      <c r="I90" s="61"/>
+      <c r="A90" s="60"/>
+      <c r="B90" s="60"/>
+      <c r="C90" s="60"/>
+      <c r="D90" s="60"/>
+      <c r="E90" s="60"/>
+      <c r="F90" s="60"/>
+      <c r="G90" s="60"/>
+      <c r="H90" s="60"/>
+      <c r="I90" s="60"/>
     </row>
     <row r="91" ht="18.75" customHeight="1">
-      <c r="A91" s="61"/>
-      <c r="B91" s="61"/>
-      <c r="C91" s="61"/>
-      <c r="D91" s="61"/>
-      <c r="E91" s="61"/>
-      <c r="F91" s="61"/>
-      <c r="G91" s="61"/>
-      <c r="H91" s="61"/>
-      <c r="I91" s="61"/>
+      <c r="A91" s="60"/>
+      <c r="B91" s="60"/>
+      <c r="C91" s="60"/>
+      <c r="D91" s="60"/>
+      <c r="E91" s="60"/>
+      <c r="F91" s="60"/>
+      <c r="G91" s="60"/>
+      <c r="H91" s="60"/>
+      <c r="I91" s="60"/>
     </row>
     <row r="92" ht="18.75" customHeight="1">
-      <c r="A92" s="61"/>
-      <c r="B92" s="61"/>
-      <c r="C92" s="61"/>
-      <c r="D92" s="61"/>
-      <c r="E92" s="61"/>
-      <c r="F92" s="61"/>
-      <c r="G92" s="61"/>
-      <c r="H92" s="61"/>
-      <c r="I92" s="61"/>
+      <c r="A92" s="60"/>
+      <c r="B92" s="60"/>
+      <c r="C92" s="60"/>
+      <c r="D92" s="60"/>
+      <c r="E92" s="60"/>
+      <c r="F92" s="60"/>
+      <c r="G92" s="60"/>
+      <c r="H92" s="60"/>
+      <c r="I92" s="60"/>
     </row>
     <row r="93" ht="18.75" customHeight="1">
-      <c r="A93" s="61"/>
-      <c r="B93" s="61"/>
-      <c r="C93" s="61"/>
-      <c r="D93" s="61"/>
-      <c r="E93" s="61"/>
-      <c r="F93" s="61"/>
-      <c r="G93" s="61"/>
-      <c r="H93" s="61"/>
-      <c r="I93" s="61"/>
+      <c r="A93" s="60"/>
+      <c r="B93" s="60"/>
+      <c r="C93" s="60"/>
+      <c r="D93" s="60"/>
+      <c r="E93" s="60"/>
+      <c r="F93" s="60"/>
+      <c r="G93" s="60"/>
+      <c r="H93" s="60"/>
+      <c r="I93" s="60"/>
     </row>
     <row r="94" ht="18.75" customHeight="1">
-      <c r="A94" s="61"/>
-      <c r="B94" s="61"/>
-      <c r="C94" s="61"/>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="61"/>
-      <c r="I94" s="61"/>
+      <c r="A94" s="60"/>
+      <c r="B94" s="60"/>
+      <c r="C94" s="60"/>
+      <c r="D94" s="60"/>
+      <c r="E94" s="60"/>
+      <c r="F94" s="60"/>
+      <c r="G94" s="60"/>
+      <c r="H94" s="60"/>
+      <c r="I94" s="60"/>
     </row>
     <row r="95" ht="18.75" customHeight="1">
-      <c r="A95" s="61"/>
-      <c r="B95" s="61"/>
-      <c r="C95" s="61"/>
-      <c r="D95" s="61"/>
-      <c r="E95" s="61"/>
-      <c r="F95" s="61"/>
-      <c r="G95" s="61"/>
-      <c r="H95" s="61"/>
-      <c r="I95" s="61"/>
+      <c r="A95" s="60"/>
+      <c r="B95" s="60"/>
+      <c r="C95" s="60"/>
+      <c r="D95" s="60"/>
+      <c r="E95" s="60"/>
+      <c r="F95" s="60"/>
+      <c r="G95" s="60"/>
+      <c r="H95" s="60"/>
+      <c r="I95" s="60"/>
     </row>
     <row r="96" ht="18.75" customHeight="1">
-      <c r="A96" s="61"/>
-      <c r="B96" s="61"/>
-      <c r="C96" s="61"/>
-      <c r="D96" s="61"/>
-      <c r="E96" s="61"/>
-      <c r="F96" s="61"/>
-      <c r="G96" s="61"/>
-      <c r="H96" s="61"/>
-      <c r="I96" s="61"/>
+      <c r="A96" s="60"/>
+      <c r="B96" s="60"/>
+      <c r="C96" s="60"/>
+      <c r="D96" s="60"/>
+      <c r="E96" s="60"/>
+      <c r="F96" s="60"/>
+      <c r="G96" s="60"/>
+      <c r="H96" s="60"/>
+      <c r="I96" s="60"/>
     </row>
     <row r="97" ht="18.75" customHeight="1">
-      <c r="A97" s="61"/>
-      <c r="B97" s="61"/>
-      <c r="C97" s="61"/>
-      <c r="D97" s="61"/>
-      <c r="E97" s="61"/>
-      <c r="F97" s="61"/>
-      <c r="G97" s="61"/>
-      <c r="H97" s="61"/>
-      <c r="I97" s="61"/>
+      <c r="A97" s="60"/>
+      <c r="B97" s="60"/>
+      <c r="C97" s="60"/>
+      <c r="D97" s="60"/>
+      <c r="E97" s="60"/>
+      <c r="F97" s="60"/>
+      <c r="G97" s="60"/>
+      <c r="H97" s="60"/>
+      <c r="I97" s="60"/>
     </row>
     <row r="98" ht="18.75" customHeight="1">
-      <c r="A98" s="61"/>
-      <c r="B98" s="61"/>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
-      <c r="E98" s="61"/>
-      <c r="F98" s="61"/>
-      <c r="G98" s="61"/>
-      <c r="H98" s="61"/>
-      <c r="I98" s="61"/>
+      <c r="A98" s="60"/>
+      <c r="B98" s="60"/>
+      <c r="C98" s="60"/>
+      <c r="D98" s="60"/>
+      <c r="E98" s="60"/>
+      <c r="F98" s="60"/>
+      <c r="G98" s="60"/>
+      <c r="H98" s="60"/>
+      <c r="I98" s="60"/>
     </row>
     <row r="99" ht="18.75" customHeight="1">
-      <c r="A99" s="61"/>
-      <c r="B99" s="61"/>
-      <c r="C99" s="61"/>
-      <c r="D99" s="61"/>
-      <c r="E99" s="61"/>
-      <c r="F99" s="61"/>
-      <c r="G99" s="61"/>
-      <c r="H99" s="61"/>
-      <c r="I99" s="61"/>
+      <c r="A99" s="60"/>
+      <c r="B99" s="60"/>
+      <c r="C99" s="60"/>
+      <c r="D99" s="60"/>
+      <c r="E99" s="60"/>
+      <c r="F99" s="60"/>
+      <c r="G99" s="60"/>
+      <c r="H99" s="60"/>
+      <c r="I99" s="60"/>
     </row>
     <row r="100" ht="18.75" customHeight="1">
-      <c r="A100" s="61"/>
-      <c r="B100" s="61"/>
-      <c r="C100" s="61"/>
-      <c r="D100" s="61"/>
-      <c r="E100" s="61"/>
-      <c r="F100" s="61"/>
-      <c r="G100" s="61"/>
-      <c r="H100" s="61"/>
-      <c r="I100" s="61"/>
+      <c r="A100" s="60"/>
+      <c r="B100" s="60"/>
+      <c r="C100" s="60"/>
+      <c r="D100" s="60"/>
+      <c r="E100" s="60"/>
+      <c r="F100" s="60"/>
+      <c r="G100" s="60"/>
+      <c r="H100" s="60"/>
+      <c r="I100" s="60"/>
     </row>
   </sheetData>
   <mergeCells count="27">
@@ -13820,1137 +13842,1137 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="56" t="s">
-        <v>1035</v>
-      </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
+      <c r="A1" s="55" t="s">
+        <v>1037</v>
+      </c>
+      <c r="C1" s="56"/>
+      <c r="D1" s="57"/>
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="57"/>
+      <c r="H1" s="57"/>
+      <c r="I1" s="57"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="56" t="s">
-        <v>1036</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>1037</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
+      <c r="A2" s="55" t="s">
+        <v>1038</v>
+      </c>
+      <c r="B2" s="55" t="s">
+        <v>1039</v>
+      </c>
+      <c r="C2" s="57"/>
+      <c r="D2" s="57"/>
+      <c r="E2" s="57"/>
+      <c r="F2" s="57"/>
+      <c r="G2" s="57"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="58" t="s">
-        <v>1038</v>
-      </c>
-      <c r="B3" s="58" t="s">
-        <v>1039</v>
-      </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
+      <c r="A3" s="57" t="s">
+        <v>1040</v>
+      </c>
+      <c r="B3" s="57" t="s">
+        <v>1041</v>
+      </c>
+      <c r="C3" s="57"/>
+      <c r="D3" s="57"/>
+      <c r="E3" s="57"/>
+      <c r="F3" s="57"/>
+      <c r="G3" s="57"/>
+      <c r="H3" s="57"/>
+      <c r="I3" s="57"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="58" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B4" s="58" t="s">
-        <v>1040</v>
-      </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
+      <c r="A4" s="57" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B4" s="57" t="s">
+        <v>1042</v>
+      </c>
+      <c r="C4" s="57"/>
+      <c r="D4" s="57"/>
+      <c r="E4" s="57"/>
+      <c r="F4" s="57"/>
+      <c r="G4" s="57"/>
+      <c r="H4" s="57"/>
+      <c r="I4" s="57"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="58" t="s">
-        <v>1041</v>
-      </c>
-      <c r="B5" s="58" t="s">
-        <v>1042</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
+      <c r="A5" s="57" t="s">
+        <v>1043</v>
+      </c>
+      <c r="B5" s="57" t="s">
+        <v>1044</v>
+      </c>
+      <c r="C5" s="57"/>
+      <c r="D5" s="57"/>
+      <c r="E5" s="57"/>
+      <c r="F5" s="57"/>
+      <c r="G5" s="57"/>
+      <c r="H5" s="57"/>
+      <c r="I5" s="57"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="58" t="s">
-        <v>1042</v>
-      </c>
-      <c r="B6" s="58" t="s">
+      <c r="A6" s="57" t="s">
+        <v>1044</v>
+      </c>
+      <c r="B6" s="57" t="s">
         <v>369</v>
       </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
+      <c r="C6" s="57"/>
+      <c r="D6" s="57"/>
+      <c r="E6" s="57"/>
+      <c r="F6" s="57"/>
+      <c r="G6" s="57"/>
+      <c r="H6" s="57"/>
+      <c r="I6" s="57"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="58" t="s">
-        <v>1043</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
+      <c r="A7" s="57" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B7" s="57" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C7" s="57"/>
+      <c r="D7" s="57"/>
+      <c r="E7" s="57"/>
+      <c r="F7" s="57"/>
+      <c r="G7" s="57"/>
+      <c r="H7" s="57"/>
+      <c r="I7" s="57"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="58" t="s">
-        <v>1044</v>
-      </c>
-      <c r="B8" s="58" t="s">
-        <v>1044</v>
-      </c>
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
+      <c r="A8" s="57" t="s">
+        <v>1046</v>
+      </c>
+      <c r="B8" s="57" t="s">
+        <v>1046</v>
+      </c>
+      <c r="C8" s="57"/>
+      <c r="D8" s="57"/>
+      <c r="E8" s="57"/>
+      <c r="F8" s="57"/>
+      <c r="G8" s="57"/>
+      <c r="H8" s="57"/>
+      <c r="I8" s="57"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="58" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>1045</v>
-      </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
+      <c r="A9" s="57" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B9" s="57" t="s">
+        <v>1047</v>
+      </c>
+      <c r="C9" s="57"/>
+      <c r="D9" s="57"/>
+      <c r="E9" s="57"/>
+      <c r="F9" s="57"/>
+      <c r="G9" s="57"/>
+      <c r="H9" s="57"/>
+      <c r="I9" s="57"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="58"/>
-      <c r="B10" s="58"/>
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="57"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="57"/>
+      <c r="E10" s="57"/>
+      <c r="F10" s="57"/>
+      <c r="G10" s="57"/>
+      <c r="H10" s="57"/>
+      <c r="I10" s="57"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="57"/>
+      <c r="E11" s="57"/>
+      <c r="F11" s="57"/>
+      <c r="G11" s="57"/>
+      <c r="H11" s="57"/>
+      <c r="I11" s="57"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="58"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
+      <c r="A12" s="57"/>
+      <c r="B12" s="57"/>
+      <c r="C12" s="57"/>
+      <c r="D12" s="57"/>
+      <c r="E12" s="57"/>
+      <c r="F12" s="57"/>
+      <c r="G12" s="57"/>
+      <c r="H12" s="57"/>
+      <c r="I12" s="57"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="58"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
+      <c r="A13" s="57"/>
+      <c r="B13" s="57"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="57"/>
+      <c r="E13" s="57"/>
+      <c r="F13" s="57"/>
+      <c r="G13" s="57"/>
+      <c r="H13" s="57"/>
+      <c r="I13" s="57"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="57"/>
+      <c r="C14" s="57"/>
+      <c r="D14" s="57"/>
+      <c r="E14" s="57"/>
+      <c r="F14" s="57"/>
+      <c r="G14" s="57"/>
+      <c r="H14" s="57"/>
+      <c r="I14" s="57"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
+      <c r="A15" s="57"/>
+      <c r="B15" s="57"/>
+      <c r="C15" s="57"/>
+      <c r="D15" s="57"/>
+      <c r="E15" s="57"/>
+      <c r="F15" s="57"/>
+      <c r="G15" s="57"/>
+      <c r="H15" s="57"/>
+      <c r="I15" s="57"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
+      <c r="A16" s="57"/>
+      <c r="B16" s="57"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="57"/>
+      <c r="E16" s="57"/>
+      <c r="F16" s="57"/>
+      <c r="G16" s="57"/>
+      <c r="H16" s="57"/>
+      <c r="I16" s="57"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="58"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
+      <c r="A17" s="57"/>
+      <c r="B17" s="57"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="57"/>
+      <c r="E17" s="57"/>
+      <c r="F17" s="57"/>
+      <c r="G17" s="57"/>
+      <c r="H17" s="57"/>
+      <c r="I17" s="57"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="58"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
+      <c r="A18" s="57"/>
+      <c r="B18" s="57"/>
+      <c r="C18" s="57"/>
+      <c r="D18" s="57"/>
+      <c r="E18" s="57"/>
+      <c r="F18" s="57"/>
+      <c r="G18" s="57"/>
+      <c r="H18" s="57"/>
+      <c r="I18" s="57"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="58"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
+      <c r="A19" s="57"/>
+      <c r="B19" s="57"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="57"/>
+      <c r="E19" s="57"/>
+      <c r="F19" s="57"/>
+      <c r="G19" s="57"/>
+      <c r="H19" s="57"/>
+      <c r="I19" s="57"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="58"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="57"/>
+      <c r="C20" s="57"/>
+      <c r="D20" s="57"/>
+      <c r="E20" s="57"/>
+      <c r="F20" s="57"/>
+      <c r="G20" s="57"/>
+      <c r="H20" s="57"/>
+      <c r="I20" s="57"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="58"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
+      <c r="A21" s="57"/>
+      <c r="B21" s="57"/>
+      <c r="C21" s="57"/>
+      <c r="D21" s="57"/>
+      <c r="E21" s="57"/>
+      <c r="F21" s="57"/>
+      <c r="G21" s="57"/>
+      <c r="H21" s="57"/>
+      <c r="I21" s="57"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="58"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
+      <c r="A22" s="57"/>
+      <c r="B22" s="57"/>
+      <c r="C22" s="57"/>
+      <c r="D22" s="57"/>
+      <c r="E22" s="57"/>
+      <c r="F22" s="57"/>
+      <c r="G22" s="57"/>
+      <c r="H22" s="57"/>
+      <c r="I22" s="57"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="58"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="57"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="57"/>
+      <c r="E23" s="57"/>
+      <c r="F23" s="57"/>
+      <c r="G23" s="57"/>
+      <c r="H23" s="57"/>
+      <c r="I23" s="57"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="58"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="57"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="57"/>
+      <c r="E24" s="57"/>
+      <c r="F24" s="57"/>
+      <c r="G24" s="57"/>
+      <c r="H24" s="57"/>
+      <c r="I24" s="57"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="58"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
+      <c r="A25" s="57"/>
+      <c r="B25" s="57"/>
+      <c r="C25" s="57"/>
+      <c r="D25" s="57"/>
+      <c r="E25" s="57"/>
+      <c r="F25" s="57"/>
+      <c r="G25" s="57"/>
+      <c r="H25" s="57"/>
+      <c r="I25" s="57"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="58"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
+      <c r="A26" s="57"/>
+      <c r="B26" s="57"/>
+      <c r="C26" s="57"/>
+      <c r="D26" s="57"/>
+      <c r="E26" s="57"/>
+      <c r="F26" s="57"/>
+      <c r="G26" s="57"/>
+      <c r="H26" s="57"/>
+      <c r="I26" s="57"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="58"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
+      <c r="A27" s="57"/>
+      <c r="B27" s="57"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="57"/>
+      <c r="E27" s="57"/>
+      <c r="F27" s="57"/>
+      <c r="G27" s="57"/>
+      <c r="H27" s="57"/>
+      <c r="I27" s="57"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="58"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
+      <c r="A28" s="57"/>
+      <c r="B28" s="57"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="57"/>
+      <c r="E28" s="57"/>
+      <c r="F28" s="57"/>
+      <c r="G28" s="57"/>
+      <c r="H28" s="57"/>
+      <c r="I28" s="57"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="58"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
+      <c r="A29" s="57"/>
+      <c r="B29" s="57"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="57"/>
+      <c r="E29" s="57"/>
+      <c r="F29" s="57"/>
+      <c r="G29" s="57"/>
+      <c r="H29" s="57"/>
+      <c r="I29" s="57"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="58"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
+      <c r="A30" s="57"/>
+      <c r="B30" s="57"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="57"/>
+      <c r="E30" s="57"/>
+      <c r="F30" s="57"/>
+      <c r="G30" s="57"/>
+      <c r="H30" s="57"/>
+      <c r="I30" s="57"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="58"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
+      <c r="A31" s="57"/>
+      <c r="B31" s="57"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="57"/>
+      <c r="E31" s="57"/>
+      <c r="F31" s="57"/>
+      <c r="G31" s="57"/>
+      <c r="H31" s="57"/>
+      <c r="I31" s="57"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="58"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="58"/>
+      <c r="A32" s="57"/>
+      <c r="B32" s="57"/>
+      <c r="C32" s="57"/>
+      <c r="D32" s="57"/>
+      <c r="E32" s="57"/>
+      <c r="F32" s="57"/>
+      <c r="G32" s="57"/>
+      <c r="H32" s="57"/>
+      <c r="I32" s="57"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="58"/>
-      <c r="B33" s="58"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
+      <c r="A33" s="57"/>
+      <c r="B33" s="57"/>
+      <c r="C33" s="57"/>
+      <c r="D33" s="57"/>
+      <c r="E33" s="57"/>
+      <c r="F33" s="57"/>
+      <c r="G33" s="57"/>
+      <c r="H33" s="57"/>
+      <c r="I33" s="57"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="58"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="58"/>
+      <c r="A34" s="57"/>
+      <c r="B34" s="57"/>
+      <c r="C34" s="57"/>
+      <c r="D34" s="57"/>
+      <c r="E34" s="57"/>
+      <c r="F34" s="57"/>
+      <c r="G34" s="57"/>
+      <c r="H34" s="57"/>
+      <c r="I34" s="57"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
+      <c r="A35" s="57"/>
+      <c r="B35" s="57"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="57"/>
+      <c r="E35" s="57"/>
+      <c r="F35" s="57"/>
+      <c r="G35" s="57"/>
+      <c r="H35" s="57"/>
+      <c r="I35" s="57"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="58"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="58"/>
+      <c r="A36" s="57"/>
+      <c r="B36" s="57"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="57"/>
+      <c r="E36" s="57"/>
+      <c r="F36" s="57"/>
+      <c r="G36" s="57"/>
+      <c r="H36" s="57"/>
+      <c r="I36" s="57"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="58"/>
-      <c r="B37" s="58"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="58"/>
-      <c r="I37" s="58"/>
+      <c r="A37" s="57"/>
+      <c r="B37" s="57"/>
+      <c r="C37" s="57"/>
+      <c r="D37" s="57"/>
+      <c r="E37" s="57"/>
+      <c r="F37" s="57"/>
+      <c r="G37" s="57"/>
+      <c r="H37" s="57"/>
+      <c r="I37" s="57"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="58"/>
-      <c r="B38" s="58"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
+      <c r="A38" s="57"/>
+      <c r="B38" s="57"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="57"/>
+      <c r="E38" s="57"/>
+      <c r="F38" s="57"/>
+      <c r="G38" s="57"/>
+      <c r="H38" s="57"/>
+      <c r="I38" s="57"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="58"/>
-      <c r="B39" s="58"/>
-      <c r="C39" s="58"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="58"/>
+      <c r="A39" s="57"/>
+      <c r="B39" s="57"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="57"/>
+      <c r="E39" s="57"/>
+      <c r="F39" s="57"/>
+      <c r="G39" s="57"/>
+      <c r="H39" s="57"/>
+      <c r="I39" s="57"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="58"/>
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
+      <c r="A40" s="57"/>
+      <c r="B40" s="57"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="57"/>
+      <c r="E40" s="57"/>
+      <c r="F40" s="57"/>
+      <c r="G40" s="57"/>
+      <c r="H40" s="57"/>
+      <c r="I40" s="57"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="58"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="57"/>
+      <c r="E41" s="57"/>
+      <c r="F41" s="57"/>
+      <c r="G41" s="57"/>
+      <c r="H41" s="57"/>
+      <c r="I41" s="57"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="58"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="57"/>
+      <c r="E42" s="57"/>
+      <c r="F42" s="57"/>
+      <c r="G42" s="57"/>
+      <c r="H42" s="57"/>
+      <c r="I42" s="57"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
+      <c r="A43" s="57"/>
+      <c r="B43" s="57"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="57"/>
+      <c r="E43" s="57"/>
+      <c r="F43" s="57"/>
+      <c r="G43" s="57"/>
+      <c r="H43" s="57"/>
+      <c r="I43" s="57"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="58"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="57"/>
+      <c r="E44" s="57"/>
+      <c r="F44" s="57"/>
+      <c r="G44" s="57"/>
+      <c r="H44" s="57"/>
+      <c r="I44" s="57"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="58"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="57"/>
+      <c r="E45" s="57"/>
+      <c r="F45" s="57"/>
+      <c r="G45" s="57"/>
+      <c r="H45" s="57"/>
+      <c r="I45" s="57"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
+      <c r="C46" s="57"/>
+      <c r="D46" s="57"/>
+      <c r="E46" s="57"/>
+      <c r="F46" s="57"/>
+      <c r="G46" s="57"/>
+      <c r="H46" s="57"/>
+      <c r="I46" s="57"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="57"/>
+      <c r="E47" s="57"/>
+      <c r="F47" s="57"/>
+      <c r="G47" s="57"/>
+      <c r="H47" s="57"/>
+      <c r="I47" s="57"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="57"/>
+      <c r="E48" s="57"/>
+      <c r="F48" s="57"/>
+      <c r="G48" s="57"/>
+      <c r="H48" s="57"/>
+      <c r="I48" s="57"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" s="58"/>
-      <c r="B49" s="58"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="58"/>
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
+      <c r="C49" s="57"/>
+      <c r="D49" s="57"/>
+      <c r="E49" s="57"/>
+      <c r="F49" s="57"/>
+      <c r="G49" s="57"/>
+      <c r="H49" s="57"/>
+      <c r="I49" s="57"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="A50" s="58"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
+      <c r="C50" s="57"/>
+      <c r="D50" s="57"/>
+      <c r="E50" s="57"/>
+      <c r="F50" s="57"/>
+      <c r="G50" s="57"/>
+      <c r="H50" s="57"/>
+      <c r="I50" s="57"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
-      <c r="A51" s="58"/>
-      <c r="B51" s="58"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="58"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="57"/>
+      <c r="C51" s="57"/>
+      <c r="D51" s="57"/>
+      <c r="E51" s="57"/>
+      <c r="F51" s="57"/>
+      <c r="G51" s="57"/>
+      <c r="H51" s="57"/>
+      <c r="I51" s="57"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
-      <c r="A52" s="58"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="58"/>
-      <c r="I52" s="58"/>
+      <c r="A52" s="57"/>
+      <c r="B52" s="57"/>
+      <c r="C52" s="57"/>
+      <c r="D52" s="57"/>
+      <c r="E52" s="57"/>
+      <c r="F52" s="57"/>
+      <c r="G52" s="57"/>
+      <c r="H52" s="57"/>
+      <c r="I52" s="57"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
-      <c r="A53" s="58"/>
-      <c r="B53" s="58"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="58"/>
-      <c r="I53" s="58"/>
+      <c r="A53" s="57"/>
+      <c r="B53" s="57"/>
+      <c r="C53" s="57"/>
+      <c r="D53" s="57"/>
+      <c r="E53" s="57"/>
+      <c r="F53" s="57"/>
+      <c r="G53" s="57"/>
+      <c r="H53" s="57"/>
+      <c r="I53" s="57"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" s="58"/>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="58"/>
-      <c r="I54" s="58"/>
+      <c r="A54" s="57"/>
+      <c r="B54" s="57"/>
+      <c r="C54" s="57"/>
+      <c r="D54" s="57"/>
+      <c r="E54" s="57"/>
+      <c r="F54" s="57"/>
+      <c r="G54" s="57"/>
+      <c r="H54" s="57"/>
+      <c r="I54" s="57"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
-      <c r="A55" s="58"/>
-      <c r="B55" s="58"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="58"/>
-      <c r="F55" s="58"/>
-      <c r="G55" s="58"/>
-      <c r="H55" s="58"/>
-      <c r="I55" s="58"/>
+      <c r="A55" s="57"/>
+      <c r="B55" s="57"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="57"/>
+      <c r="E55" s="57"/>
+      <c r="F55" s="57"/>
+      <c r="G55" s="57"/>
+      <c r="H55" s="57"/>
+      <c r="I55" s="57"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
-      <c r="A56" s="58"/>
-      <c r="B56" s="58"/>
-      <c r="C56" s="58"/>
-      <c r="D56" s="58"/>
-      <c r="E56" s="58"/>
-      <c r="F56" s="58"/>
-      <c r="G56" s="58"/>
-      <c r="H56" s="58"/>
-      <c r="I56" s="58"/>
+      <c r="A56" s="57"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="57"/>
+      <c r="D56" s="57"/>
+      <c r="E56" s="57"/>
+      <c r="F56" s="57"/>
+      <c r="G56" s="57"/>
+      <c r="H56" s="57"/>
+      <c r="I56" s="57"/>
     </row>
     <row r="57" ht="18.75" customHeight="1">
-      <c r="A57" s="58"/>
-      <c r="B57" s="58"/>
-      <c r="C57" s="58"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="58"/>
-      <c r="F57" s="58"/>
-      <c r="G57" s="58"/>
-      <c r="H57" s="58"/>
-      <c r="I57" s="58"/>
+      <c r="A57" s="57"/>
+      <c r="B57" s="57"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="57"/>
+      <c r="E57" s="57"/>
+      <c r="F57" s="57"/>
+      <c r="G57" s="57"/>
+      <c r="H57" s="57"/>
+      <c r="I57" s="57"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
-      <c r="A58" s="58"/>
-      <c r="B58" s="58"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="58"/>
-      <c r="F58" s="58"/>
-      <c r="G58" s="58"/>
-      <c r="H58" s="58"/>
-      <c r="I58" s="58"/>
+      <c r="A58" s="57"/>
+      <c r="B58" s="57"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="57"/>
+      <c r="E58" s="57"/>
+      <c r="F58" s="57"/>
+      <c r="G58" s="57"/>
+      <c r="H58" s="57"/>
+      <c r="I58" s="57"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
-      <c r="A59" s="58"/>
-      <c r="B59" s="58"/>
-      <c r="C59" s="58"/>
-      <c r="D59" s="58"/>
-      <c r="E59" s="58"/>
-      <c r="F59" s="58"/>
-      <c r="G59" s="58"/>
-      <c r="H59" s="58"/>
-      <c r="I59" s="58"/>
+      <c r="A59" s="57"/>
+      <c r="B59" s="57"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="57"/>
+      <c r="E59" s="57"/>
+      <c r="F59" s="57"/>
+      <c r="G59" s="57"/>
+      <c r="H59" s="57"/>
+      <c r="I59" s="57"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
-      <c r="A60" s="58"/>
-      <c r="B60" s="58"/>
-      <c r="C60" s="58"/>
-      <c r="D60" s="58"/>
-      <c r="E60" s="58"/>
-      <c r="F60" s="58"/>
-      <c r="G60" s="58"/>
-      <c r="H60" s="58"/>
-      <c r="I60" s="58"/>
+      <c r="A60" s="57"/>
+      <c r="B60" s="57"/>
+      <c r="C60" s="57"/>
+      <c r="D60" s="57"/>
+      <c r="E60" s="57"/>
+      <c r="F60" s="57"/>
+      <c r="G60" s="57"/>
+      <c r="H60" s="57"/>
+      <c r="I60" s="57"/>
     </row>
     <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" s="58"/>
-      <c r="B61" s="58"/>
-      <c r="C61" s="58"/>
-      <c r="D61" s="58"/>
-      <c r="E61" s="58"/>
-      <c r="F61" s="58"/>
-      <c r="G61" s="58"/>
-      <c r="H61" s="58"/>
-      <c r="I61" s="58"/>
+      <c r="A61" s="57"/>
+      <c r="B61" s="57"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="57"/>
+      <c r="E61" s="57"/>
+      <c r="F61" s="57"/>
+      <c r="G61" s="57"/>
+      <c r="H61" s="57"/>
+      <c r="I61" s="57"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
-      <c r="A62" s="58"/>
-      <c r="B62" s="58"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="58"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="58"/>
-      <c r="I62" s="58"/>
+      <c r="A62" s="57"/>
+      <c r="B62" s="57"/>
+      <c r="C62" s="57"/>
+      <c r="D62" s="57"/>
+      <c r="E62" s="57"/>
+      <c r="F62" s="57"/>
+      <c r="G62" s="57"/>
+      <c r="H62" s="57"/>
+      <c r="I62" s="57"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
-      <c r="A63" s="58"/>
-      <c r="B63" s="58"/>
-      <c r="C63" s="58"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="58"/>
-      <c r="F63" s="58"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="58"/>
-      <c r="I63" s="58"/>
+      <c r="A63" s="57"/>
+      <c r="B63" s="57"/>
+      <c r="C63" s="57"/>
+      <c r="D63" s="57"/>
+      <c r="E63" s="57"/>
+      <c r="F63" s="57"/>
+      <c r="G63" s="57"/>
+      <c r="H63" s="57"/>
+      <c r="I63" s="57"/>
     </row>
     <row r="64" ht="18.75" customHeight="1">
-      <c r="A64" s="58"/>
-      <c r="B64" s="58"/>
-      <c r="C64" s="58"/>
-      <c r="D64" s="58"/>
-      <c r="E64" s="58"/>
-      <c r="F64" s="58"/>
-      <c r="G64" s="58"/>
-      <c r="H64" s="58"/>
-      <c r="I64" s="58"/>
+      <c r="A64" s="57"/>
+      <c r="B64" s="57"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="57"/>
+      <c r="E64" s="57"/>
+      <c r="F64" s="57"/>
+      <c r="G64" s="57"/>
+      <c r="H64" s="57"/>
+      <c r="I64" s="57"/>
     </row>
     <row r="65" ht="18.75" customHeight="1">
-      <c r="A65" s="58"/>
-      <c r="B65" s="58"/>
-      <c r="C65" s="58"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="58"/>
-      <c r="I65" s="58"/>
+      <c r="A65" s="57"/>
+      <c r="B65" s="57"/>
+      <c r="C65" s="57"/>
+      <c r="D65" s="57"/>
+      <c r="E65" s="57"/>
+      <c r="F65" s="57"/>
+      <c r="G65" s="57"/>
+      <c r="H65" s="57"/>
+      <c r="I65" s="57"/>
     </row>
     <row r="66" ht="18.75" customHeight="1">
-      <c r="A66" s="58"/>
-      <c r="B66" s="58"/>
-      <c r="C66" s="58"/>
-      <c r="D66" s="58"/>
-      <c r="E66" s="58"/>
-      <c r="F66" s="58"/>
-      <c r="G66" s="58"/>
-      <c r="H66" s="58"/>
-      <c r="I66" s="58"/>
+      <c r="A66" s="57"/>
+      <c r="B66" s="57"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="57"/>
+      <c r="E66" s="57"/>
+      <c r="F66" s="57"/>
+      <c r="G66" s="57"/>
+      <c r="H66" s="57"/>
+      <c r="I66" s="57"/>
     </row>
     <row r="67" ht="18.75" customHeight="1">
-      <c r="A67" s="58"/>
-      <c r="B67" s="58"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="58"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58"/>
-      <c r="I67" s="58"/>
+      <c r="A67" s="57"/>
+      <c r="B67" s="57"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="57"/>
+      <c r="E67" s="57"/>
+      <c r="F67" s="57"/>
+      <c r="G67" s="57"/>
+      <c r="H67" s="57"/>
+      <c r="I67" s="57"/>
     </row>
     <row r="68" ht="18.75" customHeight="1">
-      <c r="A68" s="58"/>
-      <c r="B68" s="58"/>
-      <c r="C68" s="58"/>
-      <c r="D68" s="58"/>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58"/>
-      <c r="I68" s="58"/>
+      <c r="A68" s="57"/>
+      <c r="B68" s="57"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="57"/>
+      <c r="E68" s="57"/>
+      <c r="F68" s="57"/>
+      <c r="G68" s="57"/>
+      <c r="H68" s="57"/>
+      <c r="I68" s="57"/>
     </row>
     <row r="69" ht="18.75" customHeight="1">
-      <c r="A69" s="58"/>
-      <c r="B69" s="58"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="58"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="58"/>
-      <c r="I69" s="58"/>
+      <c r="A69" s="57"/>
+      <c r="B69" s="57"/>
+      <c r="C69" s="57"/>
+      <c r="D69" s="57"/>
+      <c r="E69" s="57"/>
+      <c r="F69" s="57"/>
+      <c r="G69" s="57"/>
+      <c r="H69" s="57"/>
+      <c r="I69" s="57"/>
     </row>
     <row r="70" ht="18.75" customHeight="1">
-      <c r="A70" s="58"/>
-      <c r="B70" s="58"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="58"/>
-      <c r="E70" s="58"/>
-      <c r="F70" s="58"/>
-      <c r="G70" s="58"/>
-      <c r="H70" s="58"/>
-      <c r="I70" s="58"/>
+      <c r="A70" s="57"/>
+      <c r="B70" s="57"/>
+      <c r="C70" s="57"/>
+      <c r="D70" s="57"/>
+      <c r="E70" s="57"/>
+      <c r="F70" s="57"/>
+      <c r="G70" s="57"/>
+      <c r="H70" s="57"/>
+      <c r="I70" s="57"/>
     </row>
     <row r="71" ht="18.75" customHeight="1">
-      <c r="A71" s="58"/>
-      <c r="B71" s="58"/>
-      <c r="C71" s="58"/>
-      <c r="D71" s="58"/>
-      <c r="E71" s="58"/>
-      <c r="F71" s="58"/>
-      <c r="G71" s="58"/>
-      <c r="H71" s="58"/>
-      <c r="I71" s="58"/>
+      <c r="A71" s="57"/>
+      <c r="B71" s="57"/>
+      <c r="C71" s="57"/>
+      <c r="D71" s="57"/>
+      <c r="E71" s="57"/>
+      <c r="F71" s="57"/>
+      <c r="G71" s="57"/>
+      <c r="H71" s="57"/>
+      <c r="I71" s="57"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
-      <c r="A72" s="58"/>
-      <c r="B72" s="58"/>
-      <c r="C72" s="58"/>
-      <c r="D72" s="58"/>
-      <c r="E72" s="58"/>
-      <c r="F72" s="58"/>
-      <c r="G72" s="58"/>
-      <c r="H72" s="58"/>
-      <c r="I72" s="58"/>
+      <c r="A72" s="57"/>
+      <c r="B72" s="57"/>
+      <c r="C72" s="57"/>
+      <c r="D72" s="57"/>
+      <c r="E72" s="57"/>
+      <c r="F72" s="57"/>
+      <c r="G72" s="57"/>
+      <c r="H72" s="57"/>
+      <c r="I72" s="57"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
-      <c r="A73" s="58"/>
-      <c r="B73" s="58"/>
-      <c r="C73" s="58"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="58"/>
-      <c r="I73" s="58"/>
+      <c r="A73" s="57"/>
+      <c r="B73" s="57"/>
+      <c r="C73" s="57"/>
+      <c r="D73" s="57"/>
+      <c r="E73" s="57"/>
+      <c r="F73" s="57"/>
+      <c r="G73" s="57"/>
+      <c r="H73" s="57"/>
+      <c r="I73" s="57"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
-      <c r="A74" s="58"/>
-      <c r="B74" s="58"/>
-      <c r="C74" s="58"/>
-      <c r="D74" s="58"/>
-      <c r="E74" s="58"/>
-      <c r="F74" s="58"/>
-      <c r="G74" s="58"/>
-      <c r="H74" s="58"/>
-      <c r="I74" s="58"/>
+      <c r="A74" s="57"/>
+      <c r="B74" s="57"/>
+      <c r="C74" s="57"/>
+      <c r="D74" s="57"/>
+      <c r="E74" s="57"/>
+      <c r="F74" s="57"/>
+      <c r="G74" s="57"/>
+      <c r="H74" s="57"/>
+      <c r="I74" s="57"/>
     </row>
     <row r="75" ht="18.75" customHeight="1">
-      <c r="A75" s="58"/>
-      <c r="B75" s="58"/>
-      <c r="C75" s="58"/>
-      <c r="D75" s="58"/>
-      <c r="E75" s="58"/>
-      <c r="F75" s="58"/>
-      <c r="G75" s="58"/>
-      <c r="H75" s="58"/>
-      <c r="I75" s="58"/>
+      <c r="A75" s="57"/>
+      <c r="B75" s="57"/>
+      <c r="C75" s="57"/>
+      <c r="D75" s="57"/>
+      <c r="E75" s="57"/>
+      <c r="F75" s="57"/>
+      <c r="G75" s="57"/>
+      <c r="H75" s="57"/>
+      <c r="I75" s="57"/>
     </row>
     <row r="76" ht="18.75" customHeight="1">
-      <c r="A76" s="58"/>
-      <c r="B76" s="58"/>
-      <c r="C76" s="58"/>
-      <c r="D76" s="58"/>
-      <c r="E76" s="58"/>
-      <c r="F76" s="58"/>
-      <c r="G76" s="58"/>
-      <c r="H76" s="58"/>
-      <c r="I76" s="58"/>
+      <c r="A76" s="57"/>
+      <c r="B76" s="57"/>
+      <c r="C76" s="57"/>
+      <c r="D76" s="57"/>
+      <c r="E76" s="57"/>
+      <c r="F76" s="57"/>
+      <c r="G76" s="57"/>
+      <c r="H76" s="57"/>
+      <c r="I76" s="57"/>
     </row>
     <row r="77" ht="18.75" customHeight="1">
-      <c r="A77" s="58"/>
-      <c r="B77" s="58"/>
-      <c r="C77" s="58"/>
-      <c r="D77" s="58"/>
-      <c r="E77" s="58"/>
-      <c r="F77" s="58"/>
-      <c r="G77" s="58"/>
-      <c r="H77" s="58"/>
-      <c r="I77" s="58"/>
+      <c r="A77" s="57"/>
+      <c r="B77" s="57"/>
+      <c r="C77" s="57"/>
+      <c r="D77" s="57"/>
+      <c r="E77" s="57"/>
+      <c r="F77" s="57"/>
+      <c r="G77" s="57"/>
+      <c r="H77" s="57"/>
+      <c r="I77" s="57"/>
     </row>
     <row r="78" ht="18.75" customHeight="1">
-      <c r="A78" s="58"/>
-      <c r="B78" s="58"/>
-      <c r="C78" s="58"/>
-      <c r="D78" s="58"/>
-      <c r="E78" s="58"/>
-      <c r="F78" s="58"/>
-      <c r="G78" s="58"/>
-      <c r="H78" s="58"/>
-      <c r="I78" s="58"/>
+      <c r="A78" s="57"/>
+      <c r="B78" s="57"/>
+      <c r="C78" s="57"/>
+      <c r="D78" s="57"/>
+      <c r="E78" s="57"/>
+      <c r="F78" s="57"/>
+      <c r="G78" s="57"/>
+      <c r="H78" s="57"/>
+      <c r="I78" s="57"/>
     </row>
     <row r="79" ht="18.75" customHeight="1">
-      <c r="A79" s="58"/>
-      <c r="B79" s="58"/>
-      <c r="C79" s="58"/>
-      <c r="D79" s="58"/>
-      <c r="E79" s="58"/>
-      <c r="F79" s="58"/>
-      <c r="G79" s="58"/>
-      <c r="H79" s="58"/>
-      <c r="I79" s="58"/>
+      <c r="A79" s="57"/>
+      <c r="B79" s="57"/>
+      <c r="C79" s="57"/>
+      <c r="D79" s="57"/>
+      <c r="E79" s="57"/>
+      <c r="F79" s="57"/>
+      <c r="G79" s="57"/>
+      <c r="H79" s="57"/>
+      <c r="I79" s="57"/>
     </row>
     <row r="80" ht="18.75" customHeight="1">
-      <c r="A80" s="58"/>
-      <c r="B80" s="58"/>
-      <c r="C80" s="58"/>
-      <c r="D80" s="58"/>
-      <c r="E80" s="58"/>
-      <c r="F80" s="58"/>
-      <c r="G80" s="58"/>
-      <c r="H80" s="58"/>
-      <c r="I80" s="58"/>
+      <c r="A80" s="57"/>
+      <c r="B80" s="57"/>
+      <c r="C80" s="57"/>
+      <c r="D80" s="57"/>
+      <c r="E80" s="57"/>
+      <c r="F80" s="57"/>
+      <c r="G80" s="57"/>
+      <c r="H80" s="57"/>
+      <c r="I80" s="57"/>
     </row>
     <row r="81" ht="18.75" customHeight="1">
-      <c r="A81" s="58"/>
-      <c r="B81" s="58"/>
-      <c r="C81" s="58"/>
-      <c r="D81" s="58"/>
-      <c r="E81" s="58"/>
-      <c r="F81" s="58"/>
-      <c r="G81" s="58"/>
-      <c r="H81" s="58"/>
-      <c r="I81" s="58"/>
+      <c r="A81" s="57"/>
+      <c r="B81" s="57"/>
+      <c r="C81" s="57"/>
+      <c r="D81" s="57"/>
+      <c r="E81" s="57"/>
+      <c r="F81" s="57"/>
+      <c r="G81" s="57"/>
+      <c r="H81" s="57"/>
+      <c r="I81" s="57"/>
     </row>
     <row r="82" ht="18.75" customHeight="1">
-      <c r="A82" s="58"/>
-      <c r="B82" s="58"/>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58"/>
-      <c r="E82" s="58"/>
-      <c r="F82" s="58"/>
-      <c r="G82" s="58"/>
-      <c r="H82" s="58"/>
-      <c r="I82" s="58"/>
+      <c r="A82" s="57"/>
+      <c r="B82" s="57"/>
+      <c r="C82" s="57"/>
+      <c r="D82" s="57"/>
+      <c r="E82" s="57"/>
+      <c r="F82" s="57"/>
+      <c r="G82" s="57"/>
+      <c r="H82" s="57"/>
+      <c r="I82" s="57"/>
     </row>
     <row r="83" ht="18.75" customHeight="1">
-      <c r="A83" s="58"/>
-      <c r="B83" s="58"/>
-      <c r="C83" s="58"/>
-      <c r="D83" s="58"/>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58"/>
-      <c r="G83" s="58"/>
-      <c r="H83" s="58"/>
-      <c r="I83" s="58"/>
+      <c r="A83" s="57"/>
+      <c r="B83" s="57"/>
+      <c r="C83" s="57"/>
+      <c r="D83" s="57"/>
+      <c r="E83" s="57"/>
+      <c r="F83" s="57"/>
+      <c r="G83" s="57"/>
+      <c r="H83" s="57"/>
+      <c r="I83" s="57"/>
     </row>
     <row r="84" ht="18.75" customHeight="1">
-      <c r="A84" s="58"/>
-      <c r="B84" s="58"/>
-      <c r="C84" s="58"/>
-      <c r="D84" s="58"/>
-      <c r="E84" s="58"/>
-      <c r="F84" s="58"/>
-      <c r="G84" s="58"/>
-      <c r="H84" s="58"/>
-      <c r="I84" s="58"/>
+      <c r="A84" s="57"/>
+      <c r="B84" s="57"/>
+      <c r="C84" s="57"/>
+      <c r="D84" s="57"/>
+      <c r="E84" s="57"/>
+      <c r="F84" s="57"/>
+      <c r="G84" s="57"/>
+      <c r="H84" s="57"/>
+      <c r="I84" s="57"/>
     </row>
     <row r="85" ht="18.75" customHeight="1">
-      <c r="A85" s="58"/>
-      <c r="B85" s="58"/>
-      <c r="C85" s="58"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="58"/>
-      <c r="F85" s="58"/>
-      <c r="G85" s="58"/>
-      <c r="H85" s="58"/>
-      <c r="I85" s="58"/>
+      <c r="A85" s="57"/>
+      <c r="B85" s="57"/>
+      <c r="C85" s="57"/>
+      <c r="D85" s="57"/>
+      <c r="E85" s="57"/>
+      <c r="F85" s="57"/>
+      <c r="G85" s="57"/>
+      <c r="H85" s="57"/>
+      <c r="I85" s="57"/>
     </row>
     <row r="86" ht="18.75" customHeight="1">
-      <c r="A86" s="58"/>
-      <c r="B86" s="58"/>
-      <c r="C86" s="58"/>
-      <c r="D86" s="58"/>
-      <c r="E86" s="58"/>
-      <c r="F86" s="58"/>
-      <c r="G86" s="58"/>
-      <c r="H86" s="58"/>
-      <c r="I86" s="58"/>
+      <c r="A86" s="57"/>
+      <c r="B86" s="57"/>
+      <c r="C86" s="57"/>
+      <c r="D86" s="57"/>
+      <c r="E86" s="57"/>
+      <c r="F86" s="57"/>
+      <c r="G86" s="57"/>
+      <c r="H86" s="57"/>
+      <c r="I86" s="57"/>
     </row>
     <row r="87" ht="18.75" customHeight="1">
-      <c r="A87" s="58"/>
-      <c r="B87" s="58"/>
-      <c r="C87" s="58"/>
-      <c r="D87" s="58"/>
-      <c r="E87" s="58"/>
-      <c r="F87" s="58"/>
-      <c r="G87" s="58"/>
-      <c r="H87" s="58"/>
-      <c r="I87" s="58"/>
+      <c r="A87" s="57"/>
+      <c r="B87" s="57"/>
+      <c r="C87" s="57"/>
+      <c r="D87" s="57"/>
+      <c r="E87" s="57"/>
+      <c r="F87" s="57"/>
+      <c r="G87" s="57"/>
+      <c r="H87" s="57"/>
+      <c r="I87" s="57"/>
     </row>
     <row r="88" ht="18.75" customHeight="1">
-      <c r="A88" s="58"/>
-      <c r="B88" s="58"/>
-      <c r="C88" s="58"/>
-      <c r="D88" s="58"/>
-      <c r="E88" s="58"/>
-      <c r="F88" s="58"/>
-      <c r="G88" s="58"/>
-      <c r="H88" s="58"/>
-      <c r="I88" s="58"/>
+      <c r="A88" s="57"/>
+      <c r="B88" s="57"/>
+      <c r="C88" s="57"/>
+      <c r="D88" s="57"/>
+      <c r="E88" s="57"/>
+      <c r="F88" s="57"/>
+      <c r="G88" s="57"/>
+      <c r="H88" s="57"/>
+      <c r="I88" s="57"/>
     </row>
     <row r="89" ht="18.75" customHeight="1">
-      <c r="A89" s="58"/>
-      <c r="B89" s="58"/>
-      <c r="C89" s="58"/>
-      <c r="D89" s="58"/>
-      <c r="E89" s="58"/>
-      <c r="F89" s="58"/>
-      <c r="G89" s="58"/>
-      <c r="H89" s="58"/>
-      <c r="I89" s="58"/>
+      <c r="A89" s="57"/>
+      <c r="B89" s="57"/>
+      <c r="C89" s="57"/>
+      <c r="D89" s="57"/>
+      <c r="E89" s="57"/>
+      <c r="F89" s="57"/>
+      <c r="G89" s="57"/>
+      <c r="H89" s="57"/>
+      <c r="I89" s="57"/>
     </row>
     <row r="90" ht="18.75" customHeight="1">
-      <c r="A90" s="58"/>
-      <c r="B90" s="58"/>
-      <c r="C90" s="58"/>
-      <c r="D90" s="58"/>
-      <c r="E90" s="58"/>
-      <c r="F90" s="58"/>
-      <c r="G90" s="58"/>
-      <c r="H90" s="58"/>
-      <c r="I90" s="58"/>
+      <c r="A90" s="57"/>
+      <c r="B90" s="57"/>
+      <c r="C90" s="57"/>
+      <c r="D90" s="57"/>
+      <c r="E90" s="57"/>
+      <c r="F90" s="57"/>
+      <c r="G90" s="57"/>
+      <c r="H90" s="57"/>
+      <c r="I90" s="57"/>
     </row>
     <row r="91" ht="18.75" customHeight="1">
-      <c r="A91" s="58"/>
-      <c r="B91" s="58"/>
-      <c r="C91" s="58"/>
-      <c r="D91" s="58"/>
-      <c r="E91" s="58"/>
-      <c r="F91" s="58"/>
-      <c r="G91" s="58"/>
-      <c r="H91" s="58"/>
-      <c r="I91" s="58"/>
+      <c r="A91" s="57"/>
+      <c r="B91" s="57"/>
+      <c r="C91" s="57"/>
+      <c r="D91" s="57"/>
+      <c r="E91" s="57"/>
+      <c r="F91" s="57"/>
+      <c r="G91" s="57"/>
+      <c r="H91" s="57"/>
+      <c r="I91" s="57"/>
     </row>
     <row r="92" ht="18.75" customHeight="1">
-      <c r="A92" s="58"/>
-      <c r="B92" s="58"/>
-      <c r="C92" s="58"/>
-      <c r="D92" s="58"/>
-      <c r="E92" s="58"/>
-      <c r="F92" s="58"/>
-      <c r="G92" s="58"/>
-      <c r="H92" s="58"/>
-      <c r="I92" s="58"/>
+      <c r="A92" s="57"/>
+      <c r="B92" s="57"/>
+      <c r="C92" s="57"/>
+      <c r="D92" s="57"/>
+      <c r="E92" s="57"/>
+      <c r="F92" s="57"/>
+      <c r="G92" s="57"/>
+      <c r="H92" s="57"/>
+      <c r="I92" s="57"/>
     </row>
     <row r="93" ht="18.75" customHeight="1">
-      <c r="A93" s="58"/>
-      <c r="B93" s="58"/>
-      <c r="C93" s="58"/>
-      <c r="D93" s="58"/>
-      <c r="E93" s="58"/>
-      <c r="F93" s="58"/>
-      <c r="G93" s="58"/>
-      <c r="H93" s="58"/>
-      <c r="I93" s="58"/>
+      <c r="A93" s="57"/>
+      <c r="B93" s="57"/>
+      <c r="C93" s="57"/>
+      <c r="D93" s="57"/>
+      <c r="E93" s="57"/>
+      <c r="F93" s="57"/>
+      <c r="G93" s="57"/>
+      <c r="H93" s="57"/>
+      <c r="I93" s="57"/>
     </row>
     <row r="94" ht="18.75" customHeight="1">
-      <c r="A94" s="58"/>
-      <c r="B94" s="58"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="58"/>
-      <c r="E94" s="58"/>
-      <c r="F94" s="58"/>
-      <c r="G94" s="58"/>
-      <c r="H94" s="58"/>
-      <c r="I94" s="58"/>
+      <c r="A94" s="57"/>
+      <c r="B94" s="57"/>
+      <c r="C94" s="57"/>
+      <c r="D94" s="57"/>
+      <c r="E94" s="57"/>
+      <c r="F94" s="57"/>
+      <c r="G94" s="57"/>
+      <c r="H94" s="57"/>
+      <c r="I94" s="57"/>
     </row>
     <row r="95" ht="18.75" customHeight="1">
-      <c r="A95" s="58"/>
-      <c r="B95" s="58"/>
-      <c r="C95" s="58"/>
-      <c r="D95" s="58"/>
-      <c r="E95" s="58"/>
-      <c r="F95" s="58"/>
-      <c r="G95" s="58"/>
-      <c r="H95" s="58"/>
-      <c r="I95" s="58"/>
+      <c r="A95" s="57"/>
+      <c r="B95" s="57"/>
+      <c r="C95" s="57"/>
+      <c r="D95" s="57"/>
+      <c r="E95" s="57"/>
+      <c r="F95" s="57"/>
+      <c r="G95" s="57"/>
+      <c r="H95" s="57"/>
+      <c r="I95" s="57"/>
     </row>
     <row r="96" ht="18.75" customHeight="1">
-      <c r="A96" s="58"/>
-      <c r="B96" s="58"/>
-      <c r="C96" s="58"/>
-      <c r="D96" s="58"/>
-      <c r="E96" s="58"/>
-      <c r="F96" s="58"/>
-      <c r="G96" s="58"/>
-      <c r="H96" s="58"/>
-      <c r="I96" s="58"/>
+      <c r="A96" s="57"/>
+      <c r="B96" s="57"/>
+      <c r="C96" s="57"/>
+      <c r="D96" s="57"/>
+      <c r="E96" s="57"/>
+      <c r="F96" s="57"/>
+      <c r="G96" s="57"/>
+      <c r="H96" s="57"/>
+      <c r="I96" s="57"/>
     </row>
     <row r="97" ht="18.75" customHeight="1">
-      <c r="A97" s="58"/>
-      <c r="B97" s="58"/>
-      <c r="C97" s="58"/>
-      <c r="D97" s="58"/>
-      <c r="E97" s="58"/>
-      <c r="F97" s="58"/>
-      <c r="G97" s="58"/>
-      <c r="H97" s="58"/>
-      <c r="I97" s="58"/>
+      <c r="A97" s="57"/>
+      <c r="B97" s="57"/>
+      <c r="C97" s="57"/>
+      <c r="D97" s="57"/>
+      <c r="E97" s="57"/>
+      <c r="F97" s="57"/>
+      <c r="G97" s="57"/>
+      <c r="H97" s="57"/>
+      <c r="I97" s="57"/>
     </row>
     <row r="98" ht="18.75" customHeight="1">
-      <c r="A98" s="58"/>
-      <c r="B98" s="58"/>
-      <c r="C98" s="58"/>
-      <c r="D98" s="58"/>
-      <c r="E98" s="58"/>
-      <c r="F98" s="58"/>
-      <c r="G98" s="58"/>
-      <c r="H98" s="58"/>
-      <c r="I98" s="58"/>
+      <c r="A98" s="57"/>
+      <c r="B98" s="57"/>
+      <c r="C98" s="57"/>
+      <c r="D98" s="57"/>
+      <c r="E98" s="57"/>
+      <c r="F98" s="57"/>
+      <c r="G98" s="57"/>
+      <c r="H98" s="57"/>
+      <c r="I98" s="57"/>
     </row>
     <row r="99" ht="18.75" customHeight="1">
-      <c r="A99" s="58"/>
-      <c r="B99" s="58"/>
-      <c r="C99" s="58"/>
-      <c r="D99" s="58"/>
-      <c r="E99" s="58"/>
-      <c r="F99" s="58"/>
-      <c r="G99" s="58"/>
-      <c r="H99" s="58"/>
-      <c r="I99" s="58"/>
+      <c r="A99" s="57"/>
+      <c r="B99" s="57"/>
+      <c r="C99" s="57"/>
+      <c r="D99" s="57"/>
+      <c r="E99" s="57"/>
+      <c r="F99" s="57"/>
+      <c r="G99" s="57"/>
+      <c r="H99" s="57"/>
+      <c r="I99" s="57"/>
     </row>
     <row r="100" ht="18.75" customHeight="1">
-      <c r="A100" s="58"/>
-      <c r="B100" s="58"/>
-      <c r="C100" s="58"/>
-      <c r="D100" s="58"/>
-      <c r="E100" s="58"/>
-      <c r="F100" s="58"/>
-      <c r="G100" s="58"/>
-      <c r="H100" s="58"/>
-      <c r="I100" s="58"/>
+      <c r="A100" s="57"/>
+      <c r="B100" s="57"/>
+      <c r="C100" s="57"/>
+      <c r="D100" s="57"/>
+      <c r="E100" s="57"/>
+      <c r="F100" s="57"/>
+      <c r="G100" s="57"/>
+      <c r="H100" s="57"/>
+      <c r="I100" s="57"/>
     </row>
   </sheetData>
   <mergeCells count="1">

--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -3531,7 +3531,7 @@
     <t>v</t>
   </si>
   <si>
-    <t>/v/</t>
+    <t>/ʋ/</t>
   </si>
   <si>
     <t>hv</t>
@@ -16631,7 +16631,7 @@
       <c r="A35" s="73" t="s">
         <v>1170</v>
       </c>
-      <c r="B35" s="73" t="s">
+      <c r="B35" s="59" t="s">
         <v>1171</v>
       </c>
       <c r="C35" s="72"/>

--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -9,14 +9,14 @@
     <sheet state="visible" name="Pronunciation" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$475</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$477</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1736" uniqueCount="1178">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="1182">
   <si>
     <t>Word</t>
   </si>
@@ -1800,6 +1800,12 @@
     <t>room</t>
   </si>
   <si>
+    <t>virtend</t>
+  </si>
+  <si>
+    <t>rotten, foul</t>
+  </si>
+  <si>
     <t>rulingene</t>
   </si>
   <si>
@@ -2661,6 +2667,9 @@
     <t>to rot</t>
   </si>
   <si>
+    <t>verten</t>
+  </si>
+  <si>
     <t>daven</t>
   </si>
   <si>
@@ -3336,55 +3345,58 @@
     <t>i-shift</t>
   </si>
   <si>
-    <t>a, æ</t>
+    <t>a, æ, ø</t>
   </si>
   <si>
     <t>e</t>
   </si>
   <si>
+    <t>å, o</t>
+  </si>
+  <si>
+    <t>ø</t>
+  </si>
+  <si>
+    <t>y</t>
+  </si>
+  <si>
+    <t>u</t>
+  </si>
+  <si>
+    <t>ai, ei, y, oy, øy</t>
+  </si>
+  <si>
+    <t>uneffected</t>
+  </si>
+  <si>
+    <t>monophthongs</t>
+  </si>
+  <si>
+    <t>diphthongs</t>
+  </si>
+  <si>
+    <t>letter</t>
+  </si>
+  <si>
+    <t>ipa</t>
+  </si>
+  <si>
+    <t>a</t>
+  </si>
+  <si>
+    <t>ai</t>
+  </si>
+  <si>
+    <t>/æiː/</t>
+  </si>
+  <si>
+    <t>æ</t>
+  </si>
+  <si>
+    <t>/æ/</t>
+  </si>
+  <si>
     <t>ei</t>
-  </si>
-  <si>
-    <t>å, o</t>
-  </si>
-  <si>
-    <t>ø</t>
-  </si>
-  <si>
-    <t>ei, i</t>
-  </si>
-  <si>
-    <t>y</t>
-  </si>
-  <si>
-    <t>u</t>
-  </si>
-  <si>
-    <t>monophthongs</t>
-  </si>
-  <si>
-    <t>diphthongs</t>
-  </si>
-  <si>
-    <t>letter</t>
-  </si>
-  <si>
-    <t>ipa</t>
-  </si>
-  <si>
-    <t>a</t>
-  </si>
-  <si>
-    <t>ai</t>
-  </si>
-  <si>
-    <t>/æiː/</t>
-  </si>
-  <si>
-    <t>æ</t>
-  </si>
-  <si>
-    <t>/æ/</t>
   </si>
   <si>
     <t>/ɛiː/</t>
@@ -4009,7 +4021,7 @@
     <xf borderId="6" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -4148,8 +4160,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C475" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$475"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C477" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$477"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Type" id="2"/>
@@ -4479,7 +4491,7 @@
         <v>25</v>
       </c>
       <c r="H4" s="21" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C475, REGEXMATCH(C2:C475, I3)), 2, TRUE)"),"ibyrten")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C477, REGEXMATCH(C2:C477, I3)), 2, TRUE)"),"ibyrten")</f>
         <v>ibyrten</v>
       </c>
       <c r="I4" s="4" t="str">
@@ -9264,10 +9276,10 @@
       <c r="A247" s="15" t="s">
         <v>594</v>
       </c>
-      <c r="B247" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C247" s="17" t="s">
+      <c r="B247" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C247" s="24" t="s">
         <v>595</v>
       </c>
       <c r="D247" s="4"/>
@@ -9283,10 +9295,10 @@
       <c r="A248" s="10" t="s">
         <v>596</v>
       </c>
-      <c r="B248" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C248" s="12" t="s">
+      <c r="B248" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C248" s="20" t="s">
         <v>597</v>
       </c>
       <c r="D248" s="4"/>
@@ -9302,8 +9314,8 @@
       <c r="A249" s="15" t="s">
         <v>598</v>
       </c>
-      <c r="B249" s="35" t="s">
-        <v>9</v>
+      <c r="B249" s="16" t="s">
+        <v>68</v>
       </c>
       <c r="C249" s="24" t="s">
         <v>599</v>
@@ -9321,7 +9333,7 @@
       <c r="A250" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="B250" s="51" t="s">
+      <c r="B250" s="26" t="s">
         <v>9</v>
       </c>
       <c r="C250" s="12" t="s">
@@ -9340,10 +9352,10 @@
       <c r="A251" s="15" t="s">
         <v>602</v>
       </c>
-      <c r="B251" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C251" s="17" t="s">
+      <c r="B251" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C251" s="24" t="s">
         <v>603</v>
       </c>
       <c r="D251" s="4"/>
@@ -9359,10 +9371,10 @@
       <c r="A252" s="10" t="s">
         <v>604</v>
       </c>
-      <c r="B252" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C252" s="12" t="s">
+      <c r="B252" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C252" s="20" t="s">
         <v>605</v>
       </c>
       <c r="D252" s="4"/>
@@ -9378,8 +9390,8 @@
       <c r="A253" s="15" t="s">
         <v>606</v>
       </c>
-      <c r="B253" s="16" t="s">
-        <v>68</v>
+      <c r="B253" s="35" t="s">
+        <v>9</v>
       </c>
       <c r="C253" s="24" t="s">
         <v>607</v>
@@ -9394,13 +9406,13 @@
       <c r="K253" s="9"/>
     </row>
     <row r="254" ht="15.75" customHeight="1">
-      <c r="A254" s="39" t="s">
+      <c r="A254" s="10" t="s">
         <v>608</v>
       </c>
-      <c r="B254" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="C254" s="40" t="s">
+      <c r="B254" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C254" s="12" t="s">
         <v>609</v>
       </c>
       <c r="D254" s="4"/>
@@ -9413,13 +9425,13 @@
       <c r="K254" s="9"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="15" t="s">
+      <c r="A255" s="34" t="s">
         <v>610</v>
       </c>
       <c r="B255" s="35" t="s">
         <v>361</v>
       </c>
-      <c r="C255" s="24" t="s">
+      <c r="C255" s="36" t="s">
         <v>611</v>
       </c>
       <c r="D255" s="4"/>
@@ -9432,13 +9444,13 @@
       <c r="K255" s="9"/>
     </row>
     <row r="256" ht="15.75" customHeight="1">
-      <c r="A256" s="39" t="s">
+      <c r="A256" s="10" t="s">
         <v>612</v>
       </c>
       <c r="B256" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="C256" s="40" t="s">
+      <c r="C256" s="12" t="s">
         <v>613</v>
       </c>
       <c r="D256" s="4"/>
@@ -9451,13 +9463,13 @@
       <c r="K256" s="9"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="15" t="s">
+      <c r="A257" s="34" t="s">
         <v>614</v>
       </c>
-      <c r="B257" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C257" s="24" t="s">
+      <c r="B257" s="35" t="s">
+        <v>361</v>
+      </c>
+      <c r="C257" s="36" t="s">
         <v>615</v>
       </c>
       <c r="D257" s="4"/>
@@ -9473,7 +9485,7 @@
       <c r="A258" s="10" t="s">
         <v>616</v>
       </c>
-      <c r="B258" s="51" t="s">
+      <c r="B258" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C258" s="12" t="s">
@@ -9492,8 +9504,8 @@
       <c r="A259" s="15" t="s">
         <v>618</v>
       </c>
-      <c r="B259" s="16" t="s">
-        <v>68</v>
+      <c r="B259" s="50" t="s">
+        <v>9</v>
       </c>
       <c r="C259" s="24" t="s">
         <v>619</v>
@@ -9511,10 +9523,10 @@
       <c r="A260" s="10" t="s">
         <v>620</v>
       </c>
-      <c r="B260" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C260" s="20" t="s">
+      <c r="B260" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C260" s="12" t="s">
         <v>621</v>
       </c>
       <c r="D260" s="4"/>
@@ -9527,11 +9539,11 @@
       <c r="K260" s="9"/>
     </row>
     <row r="261" ht="15.75" customHeight="1">
-      <c r="A261" s="25" t="s">
+      <c r="A261" s="15" t="s">
         <v>622</v>
       </c>
-      <c r="B261" s="16" t="s">
-        <v>285</v>
+      <c r="B261" s="50" t="s">
+        <v>9</v>
       </c>
       <c r="C261" s="17" t="s">
         <v>623</v>
@@ -9546,11 +9558,11 @@
       <c r="K261" s="9"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="10" t="s">
+      <c r="A262" s="22" t="s">
         <v>624</v>
       </c>
-      <c r="B262" s="51" t="s">
-        <v>9</v>
+      <c r="B262" s="11" t="s">
+        <v>285</v>
       </c>
       <c r="C262" s="20" t="s">
         <v>625</v>
@@ -9565,13 +9577,13 @@
       <c r="K262" s="9"/>
     </row>
     <row r="263" ht="15.75" customHeight="1">
-      <c r="A263" s="34" t="s">
+      <c r="A263" s="15" t="s">
         <v>626</v>
       </c>
       <c r="B263" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C263" s="36" t="s">
+      <c r="C263" s="17" t="s">
         <v>627</v>
       </c>
       <c r="D263" s="4"/>
@@ -9584,13 +9596,13 @@
       <c r="K263" s="9"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="10" t="s">
+      <c r="A264" s="39" t="s">
         <v>628</v>
       </c>
-      <c r="B264" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C264" s="12" t="s">
+      <c r="B264" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C264" s="40" t="s">
         <v>629</v>
       </c>
       <c r="D264" s="4"/>
@@ -9603,13 +9615,13 @@
       <c r="K264" s="9"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="34" t="s">
+      <c r="A265" s="15" t="s">
         <v>630</v>
       </c>
-      <c r="B265" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C265" s="36" t="s">
+      <c r="B265" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C265" s="24" t="s">
         <v>631</v>
       </c>
       <c r="D265" s="4"/>
@@ -9622,13 +9634,13 @@
       <c r="K265" s="9"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="10" t="s">
+      <c r="A266" s="39" t="s">
         <v>632</v>
       </c>
       <c r="B266" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C266" s="20" t="s">
+      <c r="C266" s="40" t="s">
         <v>633</v>
       </c>
       <c r="D266" s="4"/>
@@ -9641,13 +9653,13 @@
       <c r="K266" s="9"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="34" t="s">
+      <c r="A267" s="15" t="s">
         <v>634</v>
       </c>
-      <c r="B267" s="35" t="s">
-        <v>83</v>
-      </c>
-      <c r="C267" s="36" t="s">
+      <c r="B267" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C267" s="17" t="s">
         <v>635</v>
       </c>
       <c r="D267" s="4"/>
@@ -9660,13 +9672,13 @@
       <c r="K267" s="9"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="10" t="s">
+      <c r="A268" s="39" t="s">
         <v>636</v>
       </c>
-      <c r="B268" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C268" s="12" t="s">
+      <c r="B268" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="C268" s="40" t="s">
         <v>637</v>
       </c>
       <c r="D268" s="4"/>
@@ -9683,7 +9695,7 @@
         <v>638</v>
       </c>
       <c r="B269" s="16" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C269" s="24" t="s">
         <v>639</v>
@@ -9701,7 +9713,7 @@
       <c r="A270" s="10" t="s">
         <v>640</v>
       </c>
-      <c r="B270" s="51" t="s">
+      <c r="B270" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C270" s="12" t="s">
@@ -9720,7 +9732,7 @@
       <c r="A271" s="15" t="s">
         <v>642</v>
       </c>
-      <c r="B271" s="16" t="s">
+      <c r="B271" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C271" s="24" t="s">
@@ -9739,7 +9751,7 @@
       <c r="A272" s="10" t="s">
         <v>644</v>
       </c>
-      <c r="B272" s="51" t="s">
+      <c r="B272" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C272" s="12" t="s">
@@ -9758,7 +9770,7 @@
       <c r="A273" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="B273" s="16" t="s">
+      <c r="B273" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C273" s="24" t="s">
@@ -9793,13 +9805,13 @@
       <c r="K274" s="9"/>
     </row>
     <row r="275" ht="15.75" customHeight="1">
-      <c r="A275" s="34" t="s">
+      <c r="A275" s="15" t="s">
         <v>650</v>
       </c>
-      <c r="B275" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C275" s="36" t="s">
+      <c r="B275" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C275" s="24" t="s">
         <v>651</v>
       </c>
       <c r="D275" s="4"/>
@@ -9812,13 +9824,13 @@
       <c r="K275" s="9"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="10" t="s">
+      <c r="A276" s="39" t="s">
         <v>652</v>
       </c>
       <c r="B276" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C276" s="12" t="s">
+      <c r="C276" s="40" t="s">
         <v>653</v>
       </c>
       <c r="D276" s="4"/>
@@ -9850,11 +9862,11 @@
       <c r="K277" s="9"/>
     </row>
     <row r="278" ht="15.75" customHeight="1">
-      <c r="A278" s="22" t="s">
+      <c r="A278" s="10" t="s">
         <v>656</v>
       </c>
-      <c r="B278" s="11" t="s">
-        <v>68</v>
+      <c r="B278" s="51" t="s">
+        <v>9</v>
       </c>
       <c r="C278" s="12" t="s">
         <v>657</v>
@@ -9869,11 +9881,11 @@
       <c r="K278" s="9"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="15" t="s">
+      <c r="A279" s="25" t="s">
         <v>658</v>
       </c>
-      <c r="B279" s="50" t="s">
-        <v>9</v>
+      <c r="B279" s="16" t="s">
+        <v>68</v>
       </c>
       <c r="C279" s="24" t="s">
         <v>659</v>
@@ -9910,10 +9922,10 @@
       <c r="A281" s="15" t="s">
         <v>662</v>
       </c>
-      <c r="B281" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C281" s="17" t="s">
+      <c r="B281" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C281" s="24" t="s">
         <v>663</v>
       </c>
       <c r="D281" s="4"/>
@@ -9930,7 +9942,7 @@
         <v>664</v>
       </c>
       <c r="B282" s="11" t="s">
-        <v>361</v>
+        <v>285</v>
       </c>
       <c r="C282" s="20" t="s">
         <v>665</v>
@@ -9949,9 +9961,9 @@
         <v>666</v>
       </c>
       <c r="B283" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C283" s="24" t="s">
+        <v>361</v>
+      </c>
+      <c r="C283" s="17" t="s">
         <v>667</v>
       </c>
       <c r="D283" s="4"/>
@@ -9967,10 +9979,10 @@
       <c r="A284" s="10" t="s">
         <v>668</v>
       </c>
-      <c r="B284" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C284" s="20" t="s">
+      <c r="B284" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C284" s="12" t="s">
         <v>669</v>
       </c>
       <c r="D284" s="4"/>
@@ -9983,7 +9995,7 @@
       <c r="K284" s="9"/>
     </row>
     <row r="285" ht="15.75" customHeight="1">
-      <c r="A285" s="25" t="s">
+      <c r="A285" s="15" t="s">
         <v>670</v>
       </c>
       <c r="B285" s="50" t="s">
@@ -10002,13 +10014,13 @@
       <c r="K285" s="9"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="10" t="s">
+      <c r="A286" s="22" t="s">
         <v>672</v>
       </c>
       <c r="B286" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C286" s="12" t="s">
+      <c r="C286" s="20" t="s">
         <v>673</v>
       </c>
       <c r="D286" s="4"/>
@@ -10024,7 +10036,7 @@
       <c r="A287" s="15" t="s">
         <v>674</v>
       </c>
-      <c r="B287" s="16" t="s">
+      <c r="B287" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C287" s="24" t="s">
@@ -10040,13 +10052,13 @@
       <c r="K287" s="9"/>
     </row>
     <row r="288" ht="15.75" customHeight="1">
-      <c r="A288" s="22" t="s">
+      <c r="A288" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="B288" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C288" s="20" t="s">
+      <c r="B288" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C288" s="12" t="s">
         <v>677</v>
       </c>
       <c r="D288" s="4"/>
@@ -10059,13 +10071,13 @@
       <c r="K288" s="9"/>
     </row>
     <row r="289" ht="15.75" customHeight="1">
-      <c r="A289" s="15" t="s">
+      <c r="A289" s="25" t="s">
         <v>678</v>
       </c>
-      <c r="B289" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C289" s="24" t="s">
+      <c r="B289" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C289" s="17" t="s">
         <v>679</v>
       </c>
       <c r="D289" s="4"/>
@@ -10082,9 +10094,9 @@
         <v>680</v>
       </c>
       <c r="B290" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C290" s="20" t="s">
+        <v>83</v>
+      </c>
+      <c r="C290" s="12" t="s">
         <v>681</v>
       </c>
       <c r="D290" s="4"/>
@@ -10097,13 +10109,13 @@
       <c r="K290" s="9"/>
     </row>
     <row r="291" ht="15.75" customHeight="1">
-      <c r="A291" s="34" t="s">
+      <c r="A291" s="15" t="s">
         <v>682</v>
       </c>
-      <c r="B291" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="C291" s="36" t="s">
+      <c r="B291" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C291" s="17" t="s">
         <v>683</v>
       </c>
       <c r="D291" s="4"/>
@@ -10116,13 +10128,13 @@
       <c r="K291" s="9"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="10" t="s">
+      <c r="A292" s="39" t="s">
         <v>684</v>
       </c>
       <c r="B292" s="26" t="s">
         <v>361</v>
       </c>
-      <c r="C292" s="12" t="s">
+      <c r="C292" s="40" t="s">
         <v>685</v>
       </c>
       <c r="D292" s="4"/>
@@ -10173,13 +10185,13 @@
       <c r="K294" s="9"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="34" t="s">
+      <c r="A295" s="15" t="s">
         <v>690</v>
       </c>
       <c r="B295" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C295" s="36" t="s">
+        <v>361</v>
+      </c>
+      <c r="C295" s="24" t="s">
         <v>691</v>
       </c>
       <c r="D295" s="4"/>
@@ -10192,13 +10204,13 @@
       <c r="K295" s="9"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="10" t="s">
+      <c r="A296" s="39" t="s">
         <v>692</v>
       </c>
-      <c r="B296" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C296" s="12" t="s">
+      <c r="B296" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C296" s="40" t="s">
         <v>693</v>
       </c>
       <c r="D296" s="4"/>
@@ -10211,13 +10223,13 @@
       <c r="K296" s="9"/>
     </row>
     <row r="297" ht="15.75" customHeight="1">
-      <c r="A297" s="34" t="s">
+      <c r="A297" s="15" t="s">
         <v>694</v>
       </c>
-      <c r="B297" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C297" s="36" t="s">
+      <c r="B297" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C297" s="24" t="s">
         <v>695</v>
       </c>
       <c r="D297" s="4"/>
@@ -10234,7 +10246,7 @@
         <v>696</v>
       </c>
       <c r="B298" s="26" t="s">
-        <v>361</v>
+        <v>68</v>
       </c>
       <c r="C298" s="40" t="s">
         <v>697</v>
@@ -10268,13 +10280,13 @@
       <c r="K299" s="9"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="10" t="s">
+      <c r="A300" s="39" t="s">
         <v>700</v>
       </c>
-      <c r="B300" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="C300" s="20" t="s">
+      <c r="B300" s="26" t="s">
+        <v>361</v>
+      </c>
+      <c r="C300" s="40" t="s">
         <v>701</v>
       </c>
       <c r="D300" s="4"/>
@@ -10309,10 +10321,10 @@
       <c r="A302" s="10" t="s">
         <v>704</v>
       </c>
-      <c r="B302" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C302" s="12" t="s">
+      <c r="B302" s="11" t="s">
+        <v>285</v>
+      </c>
+      <c r="C302" s="20" t="s">
         <v>705</v>
       </c>
       <c r="D302" s="4"/>
@@ -10325,13 +10337,13 @@
       <c r="K302" s="9"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="45" t="s">
+      <c r="A303" s="15" t="s">
         <v>706</v>
       </c>
-      <c r="B303" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C303" s="49" t="s">
+      <c r="B303" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C303" s="24" t="s">
         <v>707</v>
       </c>
       <c r="D303" s="4"/>
@@ -10344,13 +10356,13 @@
       <c r="K303" s="9"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="10" t="s">
+      <c r="A304" s="41" t="s">
         <v>708</v>
       </c>
       <c r="B304" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C304" s="12" t="s">
+      <c r="C304" s="42" t="s">
         <v>709</v>
       </c>
       <c r="D304" s="4"/>
@@ -10382,7 +10394,7 @@
       <c r="K305" s="9"/>
     </row>
     <row r="306" ht="15.75" customHeight="1">
-      <c r="A306" s="39" t="s">
+      <c r="A306" s="10" t="s">
         <v>712</v>
       </c>
       <c r="B306" s="11" t="s">
@@ -10420,13 +10432,13 @@
       <c r="K307" s="9"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="10" t="s">
+      <c r="A308" s="39" t="s">
         <v>716</v>
       </c>
       <c r="B308" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C308" s="20" t="s">
+      <c r="C308" s="12" t="s">
         <v>717</v>
       </c>
       <c r="D308" s="4"/>
@@ -10445,7 +10457,7 @@
       <c r="B309" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C309" s="24" t="s">
+      <c r="C309" s="17" t="s">
         <v>719</v>
       </c>
       <c r="D309" s="4"/>
@@ -10462,7 +10474,7 @@
         <v>720</v>
       </c>
       <c r="B310" s="11" t="s">
-        <v>406</v>
+        <v>48</v>
       </c>
       <c r="C310" s="12" t="s">
         <v>721</v>
@@ -10481,7 +10493,7 @@
         <v>722</v>
       </c>
       <c r="B311" s="16" t="s">
-        <v>48</v>
+        <v>406</v>
       </c>
       <c r="C311" s="24" t="s">
         <v>723</v>
@@ -10496,13 +10508,13 @@
       <c r="K311" s="9"/>
     </row>
     <row r="312" ht="15.75" customHeight="1">
-      <c r="A312" s="39" t="s">
+      <c r="A312" s="10" t="s">
         <v>724</v>
       </c>
       <c r="B312" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C312" s="40" t="s">
+      <c r="C312" s="12" t="s">
         <v>725</v>
       </c>
       <c r="D312" s="4"/>
@@ -10534,13 +10546,13 @@
       <c r="K313" s="9"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="10" t="s">
+      <c r="A314" s="39" t="s">
         <v>728</v>
       </c>
       <c r="B314" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C314" s="20" t="s">
+      <c r="C314" s="40" t="s">
         <v>729</v>
       </c>
       <c r="D314" s="4"/>
@@ -10572,13 +10584,13 @@
       <c r="K315" s="9"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="39" t="s">
+      <c r="A316" s="10" t="s">
         <v>732</v>
       </c>
       <c r="B316" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C316" s="40" t="s">
+      <c r="C316" s="20" t="s">
         <v>733</v>
       </c>
       <c r="D316" s="4"/>
@@ -10591,13 +10603,13 @@
       <c r="K316" s="9"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="15" t="s">
+      <c r="A317" s="34" t="s">
         <v>734</v>
       </c>
       <c r="B317" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C317" s="24" t="s">
+      <c r="C317" s="36" t="s">
         <v>735</v>
       </c>
       <c r="D317" s="4"/>
@@ -10610,13 +10622,13 @@
       <c r="K317" s="9"/>
     </row>
     <row r="318" ht="15.75" customHeight="1">
-      <c r="A318" s="39" t="s">
+      <c r="A318" s="10" t="s">
         <v>736</v>
       </c>
       <c r="B318" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C318" s="40" t="s">
+      <c r="C318" s="12" t="s">
         <v>737</v>
       </c>
       <c r="D318" s="4"/>
@@ -10648,13 +10660,13 @@
       <c r="K319" s="9"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="10" t="s">
+      <c r="A320" s="39" t="s">
         <v>740</v>
       </c>
       <c r="B320" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C320" s="12" t="s">
+      <c r="C320" s="40" t="s">
         <v>741</v>
       </c>
       <c r="D320" s="4"/>
@@ -10686,13 +10698,13 @@
       <c r="K321" s="9"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="39" t="s">
+      <c r="A322" s="10" t="s">
         <v>744</v>
       </c>
       <c r="B322" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C322" s="40" t="s">
+      <c r="C322" s="12" t="s">
         <v>745</v>
       </c>
       <c r="D322" s="4"/>
@@ -10724,13 +10736,13 @@
       <c r="K323" s="9"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="10" t="s">
+      <c r="A324" s="39" t="s">
         <v>748</v>
       </c>
       <c r="B324" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C324" s="12" t="s">
+      <c r="C324" s="40" t="s">
         <v>749</v>
       </c>
       <c r="D324" s="4"/>
@@ -10743,13 +10755,13 @@
       <c r="K324" s="9"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="34" t="s">
+      <c r="A325" s="15" t="s">
         <v>750</v>
       </c>
       <c r="B325" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C325" s="36" t="s">
+      <c r="C325" s="24" t="s">
         <v>751</v>
       </c>
       <c r="D325" s="4"/>
@@ -10781,13 +10793,13 @@
       <c r="K326" s="9"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="15" t="s">
+      <c r="A327" s="34" t="s">
         <v>754</v>
       </c>
       <c r="B327" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C327" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C327" s="36" t="s">
         <v>755</v>
       </c>
       <c r="D327" s="4"/>
@@ -10804,9 +10816,9 @@
         <v>756</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C328" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C328" s="12" t="s">
         <v>757</v>
       </c>
       <c r="D328" s="4"/>
@@ -10819,7 +10831,7 @@
       <c r="K328" s="9"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="34" t="s">
+      <c r="A329" s="15" t="s">
         <v>758</v>
       </c>
       <c r="B329" s="16" t="s">
@@ -10838,7 +10850,7 @@
       <c r="K329" s="9"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="10" t="s">
+      <c r="A330" s="39" t="s">
         <v>760</v>
       </c>
       <c r="B330" s="11" t="s">
@@ -10857,13 +10869,13 @@
       <c r="K330" s="9"/>
     </row>
     <row r="331" ht="15.75" customHeight="1">
-      <c r="A331" s="34" t="s">
+      <c r="A331" s="15" t="s">
         <v>762</v>
       </c>
       <c r="B331" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C331" s="36" t="s">
+      <c r="C331" s="17" t="s">
         <v>763</v>
       </c>
       <c r="D331" s="4"/>
@@ -10876,14 +10888,14 @@
       <c r="K331" s="9"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="10" t="s">
+      <c r="A332" s="39" t="s">
         <v>764</v>
       </c>
       <c r="B332" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C332" s="12" t="s">
-        <v>763</v>
+      <c r="C332" s="40" t="s">
+        <v>765</v>
       </c>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
@@ -10896,13 +10908,13 @@
     </row>
     <row r="333" ht="15.75" customHeight="1">
       <c r="A333" s="15" t="s">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="B333" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C333" s="17" t="s">
-        <v>766</v>
+      <c r="C333" s="24" t="s">
+        <v>765</v>
       </c>
       <c r="D333" s="4"/>
       <c r="E333" s="4"/>
@@ -10939,7 +10951,7 @@
       <c r="B335" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C335" s="24" t="s">
+      <c r="C335" s="17" t="s">
         <v>770</v>
       </c>
       <c r="D335" s="4"/>
@@ -10952,13 +10964,13 @@
       <c r="K335" s="9"/>
     </row>
     <row r="336" ht="15.75" customHeight="1">
-      <c r="A336" s="39" t="s">
+      <c r="A336" s="10" t="s">
         <v>771</v>
       </c>
       <c r="B336" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C336" s="40" t="s">
+      <c r="C336" s="12" t="s">
         <v>772</v>
       </c>
       <c r="D336" s="4"/>
@@ -10990,13 +11002,13 @@
       <c r="K337" s="9"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="10" t="s">
+      <c r="A338" s="39" t="s">
         <v>775</v>
       </c>
       <c r="B338" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C338" s="12" t="s">
+      <c r="C338" s="40" t="s">
         <v>776</v>
       </c>
       <c r="D338" s="4"/>
@@ -11009,13 +11021,13 @@
       <c r="K338" s="9"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="34" t="s">
+      <c r="A339" s="15" t="s">
         <v>777</v>
       </c>
       <c r="B339" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C339" s="36" t="s">
+      <c r="C339" s="24" t="s">
         <v>778</v>
       </c>
       <c r="D339" s="4"/>
@@ -11028,13 +11040,13 @@
       <c r="K339" s="9"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="10" t="s">
+      <c r="A340" s="39" t="s">
         <v>779</v>
       </c>
       <c r="B340" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C340" s="20" t="s">
+      <c r="C340" s="40" t="s">
         <v>780</v>
       </c>
       <c r="D340" s="4"/>
@@ -11053,7 +11065,7 @@
       <c r="B341" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C341" s="24" t="s">
+      <c r="C341" s="17" t="s">
         <v>782</v>
       </c>
       <c r="D341" s="4"/>
@@ -11091,7 +11103,7 @@
       <c r="B343" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C343" s="17" t="s">
+      <c r="C343" s="24" t="s">
         <v>786</v>
       </c>
       <c r="D343" s="4"/>
@@ -11110,7 +11122,7 @@
       <c r="B344" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C344" s="12" t="s">
+      <c r="C344" s="20" t="s">
         <v>788</v>
       </c>
       <c r="D344" s="4"/>
@@ -11129,7 +11141,7 @@
       <c r="B345" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C345" s="17" t="s">
+      <c r="C345" s="24" t="s">
         <v>790</v>
       </c>
       <c r="D345" s="4"/>
@@ -11205,7 +11217,7 @@
       <c r="B349" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C349" s="24" t="s">
+      <c r="C349" s="17" t="s">
         <v>798</v>
       </c>
       <c r="D349" s="4"/>
@@ -11218,13 +11230,13 @@
       <c r="K349" s="9"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="41" t="s">
+      <c r="A350" s="10" t="s">
         <v>799</v>
       </c>
       <c r="B350" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C350" s="48" t="s">
+      <c r="C350" s="12" t="s">
         <v>800</v>
       </c>
       <c r="D350" s="4"/>
@@ -11237,13 +11249,13 @@
       <c r="K350" s="9"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="15" t="s">
+      <c r="A351" s="45" t="s">
         <v>801</v>
       </c>
       <c r="B351" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C351" s="17" t="s">
+      <c r="C351" s="46" t="s">
         <v>802</v>
       </c>
       <c r="D351" s="4"/>
@@ -11294,13 +11306,13 @@
       <c r="K353" s="9"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="39" t="s">
+      <c r="A354" s="10" t="s">
         <v>807</v>
       </c>
       <c r="B354" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C354" s="40" t="s">
+      <c r="C354" s="20" t="s">
         <v>808</v>
       </c>
       <c r="D354" s="4"/>
@@ -11313,13 +11325,13 @@
       <c r="K354" s="9"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="15" t="s">
+      <c r="A355" s="34" t="s">
         <v>809</v>
       </c>
       <c r="B355" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C355" s="17" t="s">
+      <c r="C355" s="36" t="s">
         <v>810</v>
       </c>
       <c r="D355" s="4"/>
@@ -11338,7 +11350,7 @@
       <c r="B356" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C356" s="12" t="s">
+      <c r="C356" s="20" t="s">
         <v>812</v>
       </c>
       <c r="D356" s="4"/>
@@ -11395,7 +11407,7 @@
       <c r="B359" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C359" s="17" t="s">
+      <c r="C359" s="24" t="s">
         <v>818</v>
       </c>
       <c r="D359" s="4"/>
@@ -11408,13 +11420,13 @@
       <c r="K359" s="9"/>
     </row>
     <row r="360" ht="15.75" customHeight="1">
-      <c r="A360" s="41" t="s">
+      <c r="A360" s="10" t="s">
         <v>819</v>
       </c>
       <c r="B360" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C360" s="48" t="s">
+      <c r="C360" s="20" t="s">
         <v>820</v>
       </c>
       <c r="D360" s="4"/>
@@ -11427,13 +11439,13 @@
       <c r="K360" s="9"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="15" t="s">
+      <c r="A361" s="45" t="s">
         <v>821</v>
       </c>
       <c r="B361" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C361" s="17" t="s">
+      <c r="C361" s="46" t="s">
         <v>822</v>
       </c>
       <c r="D361" s="4"/>
@@ -11503,13 +11515,13 @@
       <c r="K364" s="9"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="45" t="s">
+      <c r="A365" s="15" t="s">
         <v>829</v>
       </c>
       <c r="B365" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C365" s="49" t="s">
+      <c r="C365" s="17" t="s">
         <v>830</v>
       </c>
       <c r="D365" s="4"/>
@@ -11522,13 +11534,13 @@
       <c r="K365" s="9"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="10" t="s">
+      <c r="A366" s="41" t="s">
         <v>831</v>
       </c>
       <c r="B366" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C366" s="20" t="s">
+      <c r="C366" s="42" t="s">
         <v>832</v>
       </c>
       <c r="D366" s="4"/>
@@ -11541,13 +11553,13 @@
       <c r="K366" s="9"/>
     </row>
     <row r="367" ht="15.75" customHeight="1">
-      <c r="A367" s="34" t="s">
+      <c r="A367" s="15" t="s">
         <v>833</v>
       </c>
       <c r="B367" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C367" s="36" t="s">
+      <c r="C367" s="17" t="s">
         <v>834</v>
       </c>
       <c r="D367" s="4"/>
@@ -11579,13 +11591,13 @@
       <c r="K368" s="9"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="15" t="s">
+      <c r="A369" s="34" t="s">
         <v>837</v>
       </c>
       <c r="B369" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C369" s="24" t="s">
+      <c r="C369" s="36" t="s">
         <v>838</v>
       </c>
       <c r="D369" s="4"/>
@@ -11598,13 +11610,13 @@
       <c r="K369" s="9"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="39" t="s">
+      <c r="A370" s="10" t="s">
         <v>839</v>
       </c>
       <c r="B370" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C370" s="40" t="s">
+      <c r="C370" s="12" t="s">
         <v>840</v>
       </c>
       <c r="D370" s="4"/>
@@ -11623,7 +11635,7 @@
       <c r="B371" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C371" s="52" t="s">
+      <c r="C371" s="36" t="s">
         <v>842</v>
       </c>
       <c r="D371" s="4"/>
@@ -11642,7 +11654,7 @@
       <c r="B372" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C372" s="40" t="s">
+      <c r="C372" s="52" t="s">
         <v>844</v>
       </c>
       <c r="D372" s="4"/>
@@ -11655,13 +11667,13 @@
       <c r="K372" s="9"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="15" t="s">
+      <c r="A373" s="34" t="s">
         <v>845</v>
       </c>
       <c r="B373" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C373" s="24" t="s">
+      <c r="C373" s="36" t="s">
         <v>846</v>
       </c>
       <c r="D373" s="4"/>
@@ -11775,7 +11787,7 @@
       <c r="B379" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C379" s="17" t="s">
+      <c r="C379" s="24" t="s">
         <v>858</v>
       </c>
       <c r="D379" s="4"/>
@@ -11794,7 +11806,7 @@
       <c r="B380" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C380" s="12" t="s">
+      <c r="C380" s="20" t="s">
         <v>860</v>
       </c>
       <c r="D380" s="4"/>
@@ -11851,7 +11863,7 @@
       <c r="B383" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C383" s="17" t="s">
+      <c r="C383" s="24" t="s">
         <v>866</v>
       </c>
       <c r="D383" s="4"/>
@@ -11870,7 +11882,7 @@
       <c r="B384" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C384" s="12" t="s">
+      <c r="C384" s="20" t="s">
         <v>868</v>
       </c>
       <c r="D384" s="4"/>
@@ -11908,7 +11920,7 @@
       <c r="B386" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C386" s="20" t="s">
+      <c r="C386" s="12" t="s">
         <v>872</v>
       </c>
       <c r="D386" s="4"/>
@@ -11946,7 +11958,7 @@
       <c r="B388" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C388" s="12" t="s">
+      <c r="C388" s="20" t="s">
         <v>876</v>
       </c>
       <c r="D388" s="4"/>
@@ -11959,13 +11971,13 @@
       <c r="K388" s="9"/>
     </row>
     <row r="389" ht="15.75" customHeight="1">
-      <c r="A389" s="34" t="s">
+      <c r="A389" s="15" t="s">
         <v>877</v>
       </c>
       <c r="B389" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C389" s="36" t="s">
+      <c r="C389" s="24" t="s">
         <v>878</v>
       </c>
       <c r="D389" s="4"/>
@@ -11978,13 +11990,13 @@
       <c r="K389" s="9"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="10" t="s">
+      <c r="A390" s="39" t="s">
         <v>879</v>
       </c>
       <c r="B390" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C390" s="20" t="s">
+      <c r="C390" s="40" t="s">
         <v>880</v>
       </c>
       <c r="D390" s="4"/>
@@ -11997,13 +12009,13 @@
       <c r="K390" s="9"/>
     </row>
     <row r="391" ht="15.75" customHeight="1">
-      <c r="A391" s="45" t="s">
+      <c r="A391" s="15" t="s">
         <v>881</v>
       </c>
       <c r="B391" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C391" s="46" t="s">
+      <c r="C391" s="17" t="s">
         <v>882</v>
       </c>
       <c r="D391" s="4"/>
@@ -12023,7 +12035,7 @@
         <v>48</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>884</v>
+        <v>882</v>
       </c>
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
@@ -12035,14 +12047,14 @@
       <c r="K392" s="9"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="15" t="s">
-        <v>885</v>
+      <c r="A393" s="45" t="s">
+        <v>884</v>
       </c>
       <c r="B393" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C393" s="17" t="s">
-        <v>886</v>
+      <c r="C393" s="46" t="s">
+        <v>885</v>
       </c>
       <c r="D393" s="4"/>
       <c r="E393" s="4"/>
@@ -12054,14 +12066,14 @@
       <c r="K393" s="9"/>
     </row>
     <row r="394" ht="15.75" customHeight="1">
-      <c r="A394" s="41" t="s">
-        <v>887</v>
+      <c r="A394" s="10" t="s">
+        <v>886</v>
       </c>
       <c r="B394" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C394" s="42" t="s">
-        <v>888</v>
+      <c r="C394" s="12" t="s">
+        <v>887</v>
       </c>
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
@@ -12074,13 +12086,13 @@
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="15" t="s">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="B395" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C395" s="24" t="s">
-        <v>890</v>
+      <c r="C395" s="17" t="s">
+        <v>889</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -12092,14 +12104,14 @@
       <c r="K395" s="9"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="10" t="s">
-        <v>891</v>
+      <c r="A396" s="41" t="s">
+        <v>890</v>
       </c>
       <c r="B396" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C396" s="20" t="s">
-        <v>892</v>
+      <c r="C396" s="42" t="s">
+        <v>891</v>
       </c>
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
@@ -12112,13 +12124,13 @@
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="15" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="B397" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C397" s="17" t="s">
-        <v>894</v>
+      <c r="C397" s="24" t="s">
+        <v>893</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
@@ -12131,13 +12143,13 @@
     </row>
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="10" t="s">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="B398" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C398" s="12" t="s">
-        <v>896</v>
+      <c r="C398" s="20" t="s">
+        <v>895</v>
       </c>
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
@@ -12150,13 +12162,13 @@
     </row>
     <row r="399" ht="15.75" customHeight="1">
       <c r="A399" s="15" t="s">
-        <v>897</v>
+        <v>896</v>
       </c>
       <c r="B399" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C399" s="17" t="s">
-        <v>898</v>
+        <v>897</v>
       </c>
       <c r="D399" s="4"/>
       <c r="E399" s="4"/>
@@ -12169,13 +12181,13 @@
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="10" t="s">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="B400" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C400" s="12" t="s">
-        <v>900</v>
+        <v>899</v>
       </c>
       <c r="D400" s="4"/>
       <c r="E400" s="4"/>
@@ -12188,13 +12200,13 @@
     </row>
     <row r="401" ht="15.75" customHeight="1">
       <c r="A401" s="15" t="s">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="B401" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C401" s="24" t="s">
-        <v>902</v>
+      <c r="C401" s="17" t="s">
+        <v>901</v>
       </c>
       <c r="D401" s="4"/>
       <c r="E401" s="4"/>
@@ -12207,13 +12219,13 @@
     </row>
     <row r="402" ht="15.75" customHeight="1">
       <c r="A402" s="10" t="s">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="B402" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C402" s="20" t="s">
-        <v>904</v>
+      <c r="C402" s="12" t="s">
+        <v>903</v>
       </c>
       <c r="D402" s="4"/>
       <c r="E402" s="4"/>
@@ -12226,13 +12238,13 @@
     </row>
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="15" t="s">
-        <v>905</v>
+        <v>904</v>
       </c>
       <c r="B403" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C403" s="24" t="s">
-        <v>906</v>
+        <v>905</v>
       </c>
       <c r="D403" s="4"/>
       <c r="E403" s="4"/>
@@ -12245,13 +12257,13 @@
     </row>
     <row r="404" ht="15.75" customHeight="1">
       <c r="A404" s="10" t="s">
-        <v>907</v>
+        <v>906</v>
       </c>
       <c r="B404" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C404" s="12" t="s">
-        <v>908</v>
+      <c r="C404" s="20" t="s">
+        <v>907</v>
       </c>
       <c r="D404" s="4"/>
       <c r="E404" s="4"/>
@@ -12264,13 +12276,13 @@
     </row>
     <row r="405" ht="15.75" customHeight="1">
       <c r="A405" s="15" t="s">
-        <v>909</v>
+        <v>908</v>
       </c>
       <c r="B405" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C405" s="24" t="s">
-        <v>910</v>
+        <v>909</v>
       </c>
       <c r="D405" s="4"/>
       <c r="E405" s="4"/>
@@ -12283,13 +12295,13 @@
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="10" t="s">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="B406" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C406" s="20" t="s">
-        <v>912</v>
+      <c r="C406" s="12" t="s">
+        <v>911</v>
       </c>
       <c r="D406" s="4"/>
       <c r="E406" s="4"/>
@@ -12302,13 +12314,13 @@
     </row>
     <row r="407" ht="15.75" customHeight="1">
       <c r="A407" s="15" t="s">
-        <v>913</v>
+        <v>912</v>
       </c>
       <c r="B407" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C407" s="24" t="s">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="D407" s="4"/>
       <c r="E407" s="4"/>
@@ -12321,13 +12333,13 @@
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="10" t="s">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="B408" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C408" s="12" t="s">
-        <v>916</v>
+      <c r="C408" s="20" t="s">
+        <v>915</v>
       </c>
       <c r="D408" s="4"/>
       <c r="E408" s="4"/>
@@ -12340,13 +12352,13 @@
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="15" t="s">
-        <v>917</v>
+        <v>916</v>
       </c>
       <c r="B409" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C409" s="17" t="s">
-        <v>918</v>
+      <c r="C409" s="24" t="s">
+        <v>917</v>
       </c>
       <c r="D409" s="4"/>
       <c r="E409" s="4"/>
@@ -12359,13 +12371,13 @@
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="10" t="s">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="B410" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C410" s="20" t="s">
-        <v>920</v>
+      <c r="C410" s="12" t="s">
+        <v>919</v>
       </c>
       <c r="D410" s="4"/>
       <c r="E410" s="4"/>
@@ -12377,14 +12389,14 @@
       <c r="K410" s="9"/>
     </row>
     <row r="411" ht="15.75" customHeight="1">
-      <c r="A411" s="34" t="s">
-        <v>921</v>
+      <c r="A411" s="15" t="s">
+        <v>920</v>
       </c>
       <c r="B411" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C411" s="36" t="s">
-        <v>922</v>
+      <c r="C411" s="17" t="s">
+        <v>921</v>
       </c>
       <c r="D411" s="4"/>
       <c r="E411" s="4"/>
@@ -12397,13 +12409,13 @@
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="10" t="s">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="B412" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C412" s="12" t="s">
-        <v>924</v>
+      <c r="C412" s="20" t="s">
+        <v>923</v>
       </c>
       <c r="D412" s="4"/>
       <c r="E412" s="4"/>
@@ -12415,14 +12427,14 @@
       <c r="K412" s="9"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="15" t="s">
-        <v>925</v>
+      <c r="A413" s="34" t="s">
+        <v>924</v>
       </c>
       <c r="B413" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C413" s="24" t="s">
-        <v>926</v>
+      <c r="C413" s="36" t="s">
+        <v>925</v>
       </c>
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
@@ -12435,13 +12447,13 @@
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="10" t="s">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C414" s="20" t="s">
-        <v>928</v>
+      <c r="C414" s="12" t="s">
+        <v>927</v>
       </c>
       <c r="D414" s="4"/>
       <c r="E414" s="4"/>
@@ -12454,13 +12466,13 @@
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="15" t="s">
-        <v>929</v>
+        <v>928</v>
       </c>
       <c r="B415" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C415" s="24" t="s">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="D415" s="4"/>
       <c r="E415" s="4"/>
@@ -12473,13 +12485,13 @@
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="10" t="s">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="B416" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C416" s="20" t="s">
-        <v>932</v>
+        <v>931</v>
       </c>
       <c r="D416" s="4"/>
       <c r="E416" s="4"/>
@@ -12492,13 +12504,13 @@
     </row>
     <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="15" t="s">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="B417" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C417" s="24" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D417" s="4"/>
       <c r="E417" s="4"/>
@@ -12511,13 +12523,13 @@
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="10" t="s">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="B418" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C418" s="12" t="s">
-        <v>936</v>
+      <c r="C418" s="20" t="s">
+        <v>935</v>
       </c>
       <c r="D418" s="4"/>
       <c r="E418" s="4"/>
@@ -12530,13 +12542,13 @@
     </row>
     <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="15" t="s">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="B419" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C419" s="17" t="s">
-        <v>938</v>
+      <c r="C419" s="24" t="s">
+        <v>937</v>
       </c>
       <c r="D419" s="4"/>
       <c r="E419" s="4"/>
@@ -12549,13 +12561,13 @@
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="10" t="s">
-        <v>939</v>
+        <v>938</v>
       </c>
       <c r="B420" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C420" s="20" t="s">
-        <v>940</v>
+      <c r="C420" s="12" t="s">
+        <v>939</v>
       </c>
       <c r="D420" s="4"/>
       <c r="E420" s="4"/>
@@ -12568,13 +12580,13 @@
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="15" t="s">
-        <v>941</v>
+        <v>940</v>
       </c>
       <c r="B421" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C421" s="17" t="s">
-        <v>942</v>
+        <v>941</v>
       </c>
       <c r="D421" s="4"/>
       <c r="E421" s="4"/>
@@ -12587,13 +12599,13 @@
     </row>
     <row r="422" ht="15.75" customHeight="1">
       <c r="A422" s="10" t="s">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="B422" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C422" s="20" t="s">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D422" s="4"/>
       <c r="E422" s="4"/>
@@ -12606,13 +12618,13 @@
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="15" t="s">
-        <v>945</v>
+        <v>944</v>
       </c>
       <c r="B423" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C423" s="17" t="s">
-        <v>946</v>
+        <v>945</v>
       </c>
       <c r="D423" s="4"/>
       <c r="E423" s="4"/>
@@ -12625,13 +12637,13 @@
     </row>
     <row r="424" ht="15.75" customHeight="1">
       <c r="A424" s="10" t="s">
-        <v>947</v>
+        <v>946</v>
       </c>
       <c r="B424" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C424" s="12" t="s">
-        <v>948</v>
+      <c r="C424" s="20" t="s">
+        <v>947</v>
       </c>
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
@@ -12643,14 +12655,14 @@
       <c r="K424" s="9"/>
     </row>
     <row r="425" ht="15.75" customHeight="1">
-      <c r="A425" s="34" t="s">
-        <v>949</v>
+      <c r="A425" s="15" t="s">
+        <v>948</v>
       </c>
       <c r="B425" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C425" s="36" t="s">
-        <v>950</v>
+      <c r="C425" s="17" t="s">
+        <v>949</v>
       </c>
       <c r="D425" s="4"/>
       <c r="E425" s="4"/>
@@ -12662,14 +12674,14 @@
       <c r="K425" s="9"/>
     </row>
     <row r="426" ht="15.75" customHeight="1">
-      <c r="A426" s="39" t="s">
-        <v>951</v>
+      <c r="A426" s="10" t="s">
+        <v>950</v>
       </c>
       <c r="B426" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C426" s="40" t="s">
-        <v>952</v>
+      <c r="C426" s="12" t="s">
+        <v>951</v>
       </c>
       <c r="D426" s="4"/>
       <c r="E426" s="4"/>
@@ -12681,14 +12693,14 @@
       <c r="K426" s="9"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="15" t="s">
-        <v>953</v>
+      <c r="A427" s="34" t="s">
+        <v>952</v>
       </c>
       <c r="B427" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C427" s="17" t="s">
-        <v>954</v>
+      <c r="C427" s="36" t="s">
+        <v>953</v>
       </c>
       <c r="D427" s="4"/>
       <c r="E427" s="4"/>
@@ -12700,14 +12712,14 @@
       <c r="K427" s="9"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="10" t="s">
+      <c r="A428" s="39" t="s">
+        <v>954</v>
+      </c>
+      <c r="B428" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C428" s="40" t="s">
         <v>955</v>
-      </c>
-      <c r="B428" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C428" s="12" t="s">
-        <v>956</v>
       </c>
       <c r="D428" s="4"/>
       <c r="E428" s="4"/>
@@ -12720,12 +12732,12 @@
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="15" t="s">
-        <v>957</v>
+        <v>956</v>
       </c>
       <c r="B429" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C429" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C429" s="17" t="s">
         <v>957</v>
       </c>
       <c r="D429" s="4"/>
@@ -12738,13 +12750,13 @@
       <c r="K429" s="9"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="39" t="s">
+      <c r="A430" s="10" t="s">
         <v>958</v>
       </c>
-      <c r="B430" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C430" s="40" t="s">
+      <c r="B430" s="11" t="s">
+        <v>53</v>
+      </c>
+      <c r="C430" s="12" t="s">
         <v>959</v>
       </c>
       <c r="D430" s="4"/>
@@ -12757,14 +12769,14 @@
       <c r="K430" s="9"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="25" t="s">
+      <c r="A431" s="15" t="s">
         <v>960</v>
       </c>
-      <c r="B431" s="50" t="s">
+      <c r="B431" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C431" s="24" t="s">
-        <v>961</v>
+        <v>960</v>
       </c>
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
@@ -12776,14 +12788,14 @@
       <c r="K431" s="9"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="10" t="s">
+      <c r="A432" s="39" t="s">
+        <v>961</v>
+      </c>
+      <c r="B432" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C432" s="40" t="s">
         <v>962</v>
-      </c>
-      <c r="B432" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C432" s="12" t="s">
-        <v>963</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -12795,10 +12807,10 @@
       <c r="K432" s="9"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="15" t="s">
-        <v>964</v>
-      </c>
-      <c r="B433" s="16" t="s">
+      <c r="A433" s="25" t="s">
+        <v>963</v>
+      </c>
+      <c r="B433" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C433" s="24" t="s">
@@ -12814,13 +12826,13 @@
       <c r="K433" s="9"/>
     </row>
     <row r="434" ht="15.75" customHeight="1">
-      <c r="A434" s="39" t="s">
+      <c r="A434" s="10" t="s">
         <v>965</v>
       </c>
       <c r="B434" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C434" s="40" t="s">
+      <c r="C434" s="12" t="s">
         <v>966</v>
       </c>
       <c r="D434" s="4"/>
@@ -12833,14 +12845,14 @@
       <c r="K434" s="9"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="25" t="s">
+      <c r="A435" s="15" t="s">
         <v>967</v>
       </c>
       <c r="B435" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C435" s="17" t="s">
-        <v>968</v>
+        <v>9</v>
+      </c>
+      <c r="C435" s="24" t="s">
+        <v>967</v>
       </c>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
@@ -12853,13 +12865,13 @@
     </row>
     <row r="436" ht="15.75" customHeight="1">
       <c r="A436" s="39" t="s">
+        <v>968</v>
+      </c>
+      <c r="B436" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C436" s="40" t="s">
         <v>969</v>
-      </c>
-      <c r="B436" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="C436" s="20" t="s">
-        <v>970</v>
       </c>
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
@@ -12871,14 +12883,14 @@
       <c r="K436" s="9"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="45" t="s">
+      <c r="A437" s="25" t="s">
+        <v>970</v>
+      </c>
+      <c r="B437" s="16" t="s">
+        <v>285</v>
+      </c>
+      <c r="C437" s="17" t="s">
         <v>971</v>
-      </c>
-      <c r="B437" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="C437" s="49" t="s">
-        <v>972</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
@@ -12890,14 +12902,14 @@
       <c r="K437" s="9"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="10" t="s">
+      <c r="A438" s="39" t="s">
+        <v>972</v>
+      </c>
+      <c r="B438" s="26" t="s">
+        <v>58</v>
+      </c>
+      <c r="C438" s="20" t="s">
         <v>973</v>
-      </c>
-      <c r="B438" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C438" s="12" t="s">
-        <v>974</v>
       </c>
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
@@ -12909,14 +12921,14 @@
       <c r="K438" s="9"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="15" t="s">
+      <c r="A439" s="45" t="s">
+        <v>974</v>
+      </c>
+      <c r="B439" s="16" t="s">
+        <v>298</v>
+      </c>
+      <c r="C439" s="49" t="s">
         <v>975</v>
-      </c>
-      <c r="B439" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C439" s="24" t="s">
-        <v>976</v>
       </c>
       <c r="D439" s="4"/>
       <c r="E439" s="4"/>
@@ -12929,13 +12941,13 @@
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="10" t="s">
+        <v>976</v>
+      </c>
+      <c r="B440" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C440" s="12" t="s">
         <v>977</v>
-      </c>
-      <c r="B440" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C440" s="12" t="s">
-        <v>978</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4"/>
@@ -12948,13 +12960,13 @@
     </row>
     <row r="441" ht="15.75" customHeight="1">
       <c r="A441" s="15" t="s">
+        <v>978</v>
+      </c>
+      <c r="B441" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C441" s="24" t="s">
         <v>979</v>
-      </c>
-      <c r="B441" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C441" s="24" t="s">
-        <v>980</v>
       </c>
       <c r="D441" s="4"/>
       <c r="E441" s="4"/>
@@ -12967,13 +12979,13 @@
     </row>
     <row r="442" ht="15.75" customHeight="1">
       <c r="A442" s="10" t="s">
+        <v>980</v>
+      </c>
+      <c r="B442" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C442" s="12" t="s">
         <v>981</v>
-      </c>
-      <c r="B442" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C442" s="20" t="s">
-        <v>982</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4"/>
@@ -12986,13 +12998,13 @@
     </row>
     <row r="443" ht="15.75" customHeight="1">
       <c r="A443" s="15" t="s">
+        <v>982</v>
+      </c>
+      <c r="B443" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C443" s="24" t="s">
         <v>983</v>
-      </c>
-      <c r="B443" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="C443" s="24" t="s">
-        <v>984</v>
       </c>
       <c r="D443" s="4"/>
       <c r="E443" s="4"/>
@@ -13005,13 +13017,13 @@
     </row>
     <row r="444" ht="15.75" customHeight="1">
       <c r="A444" s="10" t="s">
+        <v>984</v>
+      </c>
+      <c r="B444" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C444" s="20" t="s">
         <v>985</v>
-      </c>
-      <c r="B444" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="C444" s="12" t="s">
-        <v>986</v>
       </c>
       <c r="D444" s="4"/>
       <c r="E444" s="4"/>
@@ -13024,13 +13036,13 @@
     </row>
     <row r="445" ht="15.75" customHeight="1">
       <c r="A445" s="15" t="s">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="B445" s="16" t="s">
         <v>361</v>
       </c>
       <c r="C445" s="24" t="s">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="D445" s="4"/>
       <c r="E445" s="4"/>
@@ -13043,13 +13055,13 @@
     </row>
     <row r="446" ht="15.75" customHeight="1">
       <c r="A446" s="10" t="s">
+        <v>988</v>
+      </c>
+      <c r="B446" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="C446" s="12" t="s">
         <v>989</v>
-      </c>
-      <c r="B446" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C446" s="12" t="s">
-        <v>990</v>
       </c>
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
@@ -13062,13 +13074,13 @@
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="15" t="s">
+        <v>990</v>
+      </c>
+      <c r="B447" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="C447" s="24" t="s">
         <v>991</v>
-      </c>
-      <c r="B447" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C447" s="24" t="s">
-        <v>992</v>
       </c>
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
@@ -13081,13 +13093,13 @@
     </row>
     <row r="448" ht="15.75" customHeight="1">
       <c r="A448" s="10" t="s">
+        <v>992</v>
+      </c>
+      <c r="B448" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C448" s="12" t="s">
         <v>993</v>
-      </c>
-      <c r="B448" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C448" s="12" t="s">
-        <v>994</v>
       </c>
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
@@ -13100,13 +13112,13 @@
     </row>
     <row r="449" ht="15.75" customHeight="1">
       <c r="A449" s="15" t="s">
+        <v>994</v>
+      </c>
+      <c r="B449" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C449" s="24" t="s">
         <v>995</v>
-      </c>
-      <c r="B449" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C449" s="24" t="s">
-        <v>996</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4"/>
@@ -13119,13 +13131,13 @@
     </row>
     <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="10" t="s">
+        <v>996</v>
+      </c>
+      <c r="B450" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C450" s="12" t="s">
         <v>997</v>
-      </c>
-      <c r="B450" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C450" s="20" t="s">
-        <v>998</v>
       </c>
       <c r="D450" s="4"/>
       <c r="E450" s="4"/>
@@ -13137,14 +13149,14 @@
       <c r="K450" s="9"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="25" t="s">
+      <c r="A451" s="15" t="s">
+        <v>998</v>
+      </c>
+      <c r="B451" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C451" s="24" t="s">
         <v>999</v>
-      </c>
-      <c r="B451" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C451" s="17" t="s">
-        <v>1000</v>
       </c>
       <c r="D451" s="4"/>
       <c r="E451" s="4"/>
@@ -13157,13 +13169,13 @@
     </row>
     <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="10" t="s">
+        <v>1000</v>
+      </c>
+      <c r="B452" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C452" s="20" t="s">
         <v>1001</v>
-      </c>
-      <c r="B452" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C452" s="12" t="s">
-        <v>1002</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
@@ -13175,14 +13187,14 @@
       <c r="K452" s="9"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="15" t="s">
+      <c r="A453" s="25" t="s">
+        <v>1002</v>
+      </c>
+      <c r="B453" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C453" s="17" t="s">
         <v>1003</v>
-      </c>
-      <c r="B453" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C453" s="24" t="s">
-        <v>1004</v>
       </c>
       <c r="D453" s="4"/>
       <c r="E453" s="4"/>
@@ -13195,13 +13207,13 @@
     </row>
     <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="10" t="s">
+        <v>1004</v>
+      </c>
+      <c r="B454" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C454" s="12" t="s">
         <v>1005</v>
-      </c>
-      <c r="B454" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C454" s="12" t="s">
-        <v>1006</v>
       </c>
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
@@ -13214,13 +13226,13 @@
     </row>
     <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="15" t="s">
+        <v>1006</v>
+      </c>
+      <c r="B455" s="16" t="s">
+        <v>48</v>
+      </c>
+      <c r="C455" s="24" t="s">
         <v>1007</v>
-      </c>
-      <c r="B455" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C455" s="17" t="s">
-        <v>1008</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
@@ -13233,13 +13245,13 @@
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="10" t="s">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="B456" s="11" t="s">
         <v>83</v>
       </c>
       <c r="C456" s="12" t="s">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
@@ -13251,14 +13263,14 @@
       <c r="K456" s="9"/>
     </row>
     <row r="457" ht="15.75" customHeight="1">
-      <c r="A457" s="34" t="s">
-        <v>1011</v>
+      <c r="A457" s="15" t="s">
+        <v>1010</v>
       </c>
       <c r="B457" s="16" t="s">
         <v>83</v>
       </c>
-      <c r="C457" s="36" t="s">
-        <v>1012</v>
+      <c r="C457" s="17" t="s">
+        <v>1011</v>
       </c>
       <c r="D457" s="4"/>
       <c r="E457" s="4"/>
@@ -13271,13 +13283,13 @@
     </row>
     <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="10" t="s">
+        <v>1012</v>
+      </c>
+      <c r="B458" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C458" s="12" t="s">
         <v>1013</v>
-      </c>
-      <c r="B458" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C458" s="20" t="s">
-        <v>1014</v>
       </c>
       <c r="D458" s="4"/>
       <c r="E458" s="4"/>
@@ -13290,13 +13302,13 @@
     </row>
     <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="34" t="s">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="B459" s="16" t="s">
         <v>83</v>
       </c>
       <c r="C459" s="36" t="s">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="D459" s="4"/>
       <c r="E459" s="4"/>
@@ -13308,13 +13320,13 @@
       <c r="K459" s="9"/>
     </row>
     <row r="460" ht="15.75" customHeight="1">
-      <c r="A460" s="39" t="s">
-        <v>985</v>
+      <c r="A460" s="10" t="s">
+        <v>1016</v>
       </c>
       <c r="B460" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C460" s="40" t="s">
+        <v>68</v>
+      </c>
+      <c r="C460" s="20" t="s">
         <v>1017</v>
       </c>
       <c r="D460" s="4"/>
@@ -13327,13 +13339,13 @@
       <c r="K460" s="9"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="15" t="s">
+      <c r="A461" s="34" t="s">
         <v>1018</v>
       </c>
-      <c r="B461" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C461" s="24" t="s">
+      <c r="B461" s="16" t="s">
+        <v>83</v>
+      </c>
+      <c r="C461" s="36" t="s">
         <v>1019</v>
       </c>
       <c r="D461" s="4"/>
@@ -13346,14 +13358,14 @@
       <c r="K461" s="9"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="10" t="s">
+      <c r="A462" s="39" t="s">
+        <v>988</v>
+      </c>
+      <c r="B462" s="11" t="s">
+        <v>83</v>
+      </c>
+      <c r="C462" s="40" t="s">
         <v>1020</v>
-      </c>
-      <c r="B462" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C462" s="20" t="s">
-        <v>1021</v>
       </c>
       <c r="D462" s="4"/>
       <c r="E462" s="4"/>
@@ -13365,14 +13377,14 @@
       <c r="K462" s="9"/>
     </row>
     <row r="463" ht="15.75" customHeight="1">
-      <c r="A463" s="34" t="s">
+      <c r="A463" s="15" t="s">
+        <v>1021</v>
+      </c>
+      <c r="B463" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C463" s="24" t="s">
         <v>1022</v>
-      </c>
-      <c r="B463" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C463" s="36" t="s">
-        <v>1023</v>
       </c>
       <c r="D463" s="4"/>
       <c r="E463" s="4"/>
@@ -13384,14 +13396,14 @@
       <c r="K463" s="9"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="39" t="s">
+      <c r="A464" s="10" t="s">
+        <v>1023</v>
+      </c>
+      <c r="B464" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C464" s="20" t="s">
         <v>1024</v>
-      </c>
-      <c r="B464" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C464" s="40" t="s">
-        <v>1025</v>
       </c>
       <c r="D464" s="4"/>
       <c r="E464" s="4"/>
@@ -13403,14 +13415,14 @@
       <c r="K464" s="9"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="15" t="s">
+      <c r="A465" s="34" t="s">
+        <v>1025</v>
+      </c>
+      <c r="B465" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C465" s="36" t="s">
         <v>1026</v>
-      </c>
-      <c r="B465" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C465" s="24" t="s">
-        <v>1027</v>
       </c>
       <c r="D465" s="4"/>
       <c r="E465" s="4"/>
@@ -13422,14 +13434,14 @@
       <c r="K465" s="9"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="10" t="s">
+      <c r="A466" s="39" t="s">
+        <v>1027</v>
+      </c>
+      <c r="B466" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C466" s="40" t="s">
         <v>1028</v>
-      </c>
-      <c r="B466" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C466" s="12" t="s">
-        <v>1029</v>
       </c>
       <c r="D466" s="4"/>
       <c r="E466" s="4"/>
@@ -13442,13 +13454,13 @@
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="15" t="s">
+        <v>1029</v>
+      </c>
+      <c r="B467" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C467" s="24" t="s">
         <v>1030</v>
-      </c>
-      <c r="B467" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C467" s="24" t="s">
-        <v>1031</v>
       </c>
       <c r="D467" s="4"/>
       <c r="E467" s="4"/>
@@ -13460,14 +13472,14 @@
       <c r="K467" s="9"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="22" t="s">
+      <c r="A468" s="10" t="s">
+        <v>1031</v>
+      </c>
+      <c r="B468" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C468" s="12" t="s">
         <v>1032</v>
-      </c>
-      <c r="B468" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C468" s="20" t="s">
-        <v>1033</v>
       </c>
       <c r="D468" s="4"/>
       <c r="E468" s="4"/>
@@ -13480,13 +13492,13 @@
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="15" t="s">
+        <v>1033</v>
+      </c>
+      <c r="B469" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C469" s="24" t="s">
         <v>1034</v>
-      </c>
-      <c r="B469" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C469" s="24" t="s">
-        <v>1035</v>
       </c>
       <c r="D469" s="4"/>
       <c r="E469" s="4"/>
@@ -13498,14 +13510,14 @@
       <c r="K469" s="9"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="10" t="s">
+      <c r="A470" s="22" t="s">
+        <v>1035</v>
+      </c>
+      <c r="B470" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C470" s="20" t="s">
         <v>1036</v>
-      </c>
-      <c r="B470" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C470" s="12" t="s">
-        <v>1037</v>
       </c>
       <c r="D470" s="4"/>
       <c r="E470" s="4"/>
@@ -13517,14 +13529,14 @@
       <c r="K470" s="9"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="53" t="s">
+      <c r="A471" s="15" t="s">
+        <v>1037</v>
+      </c>
+      <c r="B471" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C471" s="24" t="s">
         <v>1038</v>
-      </c>
-      <c r="B471" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C471" s="46" t="s">
-        <v>1039</v>
       </c>
       <c r="D471" s="4"/>
       <c r="E471" s="4"/>
@@ -13537,13 +13549,13 @@
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="10" t="s">
+        <v>1039</v>
+      </c>
+      <c r="B472" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C472" s="12" t="s">
         <v>1040</v>
-      </c>
-      <c r="B472" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="C472" s="12" t="s">
-        <v>1041</v>
       </c>
       <c r="D472" s="4"/>
       <c r="E472" s="4"/>
@@ -13555,14 +13567,14 @@
       <c r="K472" s="9"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="15" t="s">
+      <c r="A473" s="53" t="s">
+        <v>1041</v>
+      </c>
+      <c r="B473" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="C473" s="46" t="s">
         <v>1042</v>
-      </c>
-      <c r="B473" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="C473" s="24" t="s">
-        <v>1043</v>
       </c>
       <c r="D473" s="4"/>
       <c r="E473" s="4"/>
@@ -13575,13 +13587,13 @@
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="10" t="s">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="B474" s="11" t="s">
         <v>361</v>
       </c>
       <c r="C474" s="12" t="s">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D474" s="4"/>
       <c r="E474" s="4"/>
@@ -13593,14 +13605,14 @@
       <c r="K474" s="9"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="54" t="s">
+      <c r="A475" s="15" t="s">
+        <v>1045</v>
+      </c>
+      <c r="B475" s="16" t="s">
+        <v>361</v>
+      </c>
+      <c r="C475" s="24" t="s">
         <v>1046</v>
-      </c>
-      <c r="B475" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C475" s="56" t="s">
-        <v>1047</v>
       </c>
       <c r="D475" s="4"/>
       <c r="E475" s="4"/>
@@ -13611,9 +13623,47 @@
       <c r="J475" s="9"/>
       <c r="K475" s="9"/>
     </row>
+    <row r="476" ht="15.75" customHeight="1">
+      <c r="A476" s="10" t="s">
+        <v>1047</v>
+      </c>
+      <c r="B476" s="11" t="s">
+        <v>361</v>
+      </c>
+      <c r="C476" s="12" t="s">
+        <v>1048</v>
+      </c>
+      <c r="D476" s="4"/>
+      <c r="E476" s="4"/>
+      <c r="F476" s="4"/>
+      <c r="G476" s="4"/>
+      <c r="H476" s="4"/>
+      <c r="I476" s="4"/>
+      <c r="J476" s="9"/>
+      <c r="K476" s="9"/>
+    </row>
+    <row r="477" ht="15.75" customHeight="1">
+      <c r="A477" s="54" t="s">
+        <v>1049</v>
+      </c>
+      <c r="B477" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C477" s="56" t="s">
+        <v>1050</v>
+      </c>
+      <c r="D477" s="4"/>
+      <c r="E477" s="4"/>
+      <c r="F477" s="4"/>
+      <c r="G477" s="4"/>
+      <c r="H477" s="4"/>
+      <c r="I477" s="4"/>
+      <c r="J477" s="9"/>
+      <c r="K477" s="9"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B475">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B477">
       <formula1>"adjective,adjective-adverb,adverb,auxiliary,conjunction,interjection,noun,numeral,preposition,pronoun,verb"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13639,10 +13689,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>1048</v>
+        <v>1051</v>
       </c>
       <c r="D1" s="57" t="s">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="G1" s="58"/>
       <c r="H1" s="58"/>
@@ -13650,16 +13700,16 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>891</v>
+        <v>894</v>
       </c>
       <c r="G2" s="58"/>
       <c r="H2" s="58"/>
@@ -13670,13 +13720,13 @@
         <v>113</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D3" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="G3" s="58"/>
       <c r="H3" s="58"/>
@@ -13685,17 +13735,17 @@
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="60"/>
       <c r="B4" s="61" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D4" s="60"/>
       <c r="E4" s="61" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="G4" s="58"/>
       <c r="H4" s="58"/>
@@ -13703,22 +13753,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="57" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>1059</v>
+        <v>1062</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>1060</v>
+        <v>1063</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="58"/>
@@ -13726,22 +13776,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="57" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1062</v>
+        <v>1065</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1064</v>
+        <v>1067</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1065</v>
+        <v>1068</v>
       </c>
       <c r="G6" s="58"/>
       <c r="H6" s="58"/>
@@ -13749,33 +13799,33 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="57" t="s">
-        <v>1066</v>
+        <v>1069</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>1067</v>
+        <v>1070</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>1068</v>
+        <v>1071</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="57" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="G8" s="57" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>875</v>
+        <v>877</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -13783,108 +13833,108 @@
         <v>113</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E9" s="59" t="s">
-        <v>1069</v>
+        <v>1072</v>
       </c>
       <c r="G9" s="57" t="s">
         <v>113</v>
       </c>
       <c r="H9" s="59" t="s">
-        <v>1070</v>
+        <v>1073</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="60"/>
       <c r="B10" s="61" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D10" s="60"/>
       <c r="E10" s="61" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="F10" s="61" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="G10" s="60"/>
       <c r="H10" s="61" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="I10" s="61" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="57" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="C11" s="59" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E11" s="59" t="s">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>1072</v>
+        <v>1075</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>1073</v>
+        <v>1076</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>1074</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="57" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1075</v>
+        <v>1078</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1077</v>
+        <v>1080</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1078</v>
+        <v>1081</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>1080</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="57" t="s">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="G13" s="58"/>
       <c r="H13" s="58"/>
@@ -13892,16 +13942,16 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="57" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1051</v>
+        <v>1054</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>775</v>
+        <v>777</v>
       </c>
       <c r="G14" s="58"/>
       <c r="H14" s="58"/>
@@ -13912,13 +13962,13 @@
         <v>113</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>1052</v>
+        <v>1055</v>
       </c>
       <c r="D15" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E15" s="59" t="s">
-        <v>1083</v>
+        <v>1086</v>
       </c>
       <c r="G15" s="58"/>
       <c r="H15" s="58"/>
@@ -13927,17 +13977,17 @@
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="60"/>
       <c r="B16" s="61" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="D16" s="60"/>
       <c r="E16" s="61" t="s">
-        <v>1054</v>
+        <v>1057</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>1055</v>
+        <v>1058</v>
       </c>
       <c r="G16" s="58"/>
       <c r="H16" s="58"/>
@@ -13945,22 +13995,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="57" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>1057</v>
+        <v>1060</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>1056</v>
+        <v>1059</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>1084</v>
+        <v>1087</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>1085</v>
+        <v>1088</v>
       </c>
       <c r="G17" s="58"/>
       <c r="H17" s="58"/>
@@ -13968,22 +14018,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="57" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1086</v>
+        <v>1089</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1076</v>
+        <v>1079</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>1061</v>
+        <v>1064</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>1087</v>
+        <v>1090</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>1088</v>
+        <v>1091</v>
       </c>
       <c r="G18" s="58"/>
       <c r="H18" s="58"/>
@@ -14002,13 +14052,13 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>1089</v>
+        <v>1092</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>1090</v>
+        <v>1093</v>
       </c>
       <c r="D20" s="64" t="s">
-        <v>1091</v>
+        <v>1094</v>
       </c>
       <c r="F20" s="62"/>
       <c r="G20" s="62"/>
@@ -14017,16 +14067,16 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="B21" s="65" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="D21" s="65" t="s">
-        <v>1092</v>
+        <v>1095</v>
       </c>
       <c r="E21" s="65" t="s">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="F21" s="62"/>
       <c r="G21" s="62"/>
@@ -14035,19 +14085,19 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="66" t="s">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="B22" s="59" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="F22" s="62"/>
       <c r="G22" s="62"/>
@@ -14056,19 +14106,19 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="64" t="s">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>1099</v>
+        <v>1102</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>1101</v>
+        <v>1104</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="F23" s="62"/>
       <c r="G23" s="62"/>
@@ -14962,7 +15012,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>1103</v>
+        <v>1106</v>
       </c>
       <c r="C1" s="58"/>
       <c r="D1" s="59"/>
@@ -14974,10 +15024,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>1104</v>
+        <v>1107</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1105</v>
+        <v>1108</v>
       </c>
       <c r="C2" s="59"/>
       <c r="D2" s="59"/>
@@ -14989,10 +15039,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="59" t="s">
-        <v>1106</v>
+        <v>1109</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="C3" s="59"/>
       <c r="D3" s="59"/>
@@ -15004,10 +15054,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="59" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>1108</v>
+        <v>397</v>
       </c>
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
@@ -15019,10 +15069,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="59" t="s">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="C5" s="59"/>
       <c r="D5" s="59"/>
@@ -15034,10 +15084,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="59" t="s">
-        <v>1110</v>
+        <v>397</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>397</v>
+        <v>1113</v>
       </c>
       <c r="C6" s="59"/>
       <c r="D6" s="59"/>
@@ -15049,7 +15099,7 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="59" t="s">
-        <v>1111</v>
+        <v>1114</v>
       </c>
       <c r="B7" s="59" t="s">
         <v>1112</v>
@@ -15063,12 +15113,6 @@
       <c r="I7" s="59"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="59" t="s">
-        <v>1112</v>
-      </c>
-      <c r="B8" s="59" t="s">
-        <v>1112</v>
-      </c>
       <c r="C8" s="59"/>
       <c r="D8" s="59"/>
       <c r="E8" s="59"/>
@@ -15079,10 +15123,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="59" t="s">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1113</v>
+        <v>1116</v>
       </c>
       <c r="C9" s="59"/>
       <c r="D9" s="59"/>
@@ -15093,8 +15137,6 @@
       <c r="I9" s="59"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
       <c r="C10" s="59"/>
       <c r="D10" s="59"/>
       <c r="E10" s="59"/>
@@ -16113,62 +16155,62 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="69" t="s">
-        <v>1114</v>
+        <v>1117</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="71" t="s">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="H1" s="72"/>
       <c r="I1" s="72"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="71" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C2" s="72"/>
       <c r="D2" s="71" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="E2" s="71" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="H2" s="72"/>
       <c r="I2" s="72"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="73" t="s">
-        <v>1118</v>
+        <v>1121</v>
       </c>
       <c r="B3" s="59" t="s">
         <v>131</v>
       </c>
       <c r="C3" s="73"/>
       <c r="D3" s="59" t="s">
-        <v>1119</v>
+        <v>1122</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>1120</v>
+        <v>1123</v>
       </c>
       <c r="H3" s="72"/>
       <c r="I3" s="72"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="59" t="s">
-        <v>1121</v>
+        <v>1124</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>1122</v>
+        <v>1125</v>
       </c>
       <c r="C4" s="73"/>
       <c r="D4" s="73" t="s">
-        <v>1108</v>
+        <v>1126</v>
       </c>
       <c r="E4" s="73" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="73"/>
@@ -16184,10 +16226,10 @@
       </c>
       <c r="C5" s="73"/>
       <c r="D5" s="59" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="F5" s="73"/>
       <c r="G5" s="73"/>
@@ -16196,17 +16238,17 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="73" t="s">
-        <v>1107</v>
+        <v>1110</v>
       </c>
       <c r="B6" s="73" t="s">
         <v>144</v>
       </c>
       <c r="C6" s="73"/>
       <c r="D6" s="59" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="F6" s="73"/>
       <c r="G6" s="73"/>
@@ -16222,10 +16264,10 @@
       </c>
       <c r="C7" s="73"/>
       <c r="D7" s="59" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E7" s="59" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="F7" s="73"/>
       <c r="G7" s="73"/>
@@ -16234,17 +16276,17 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="73" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>152</v>
       </c>
       <c r="C8" s="73"/>
       <c r="D8" s="59" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="F8" s="73"/>
       <c r="G8" s="73"/>
@@ -16253,10 +16295,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="59" t="s">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="C9" s="73"/>
       <c r="D9" s="73"/>
@@ -16268,7 +16310,7 @@
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="73" t="s">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>156</v>
@@ -16283,7 +16325,7 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="73" t="s">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="B11" s="59" t="s">
         <v>162</v>
@@ -16320,7 +16362,7 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="C14" s="72"/>
       <c r="D14" s="72"/>
@@ -16332,10 +16374,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="71" t="s">
-        <v>1116</v>
+        <v>1119</v>
       </c>
       <c r="B15" s="71" t="s">
-        <v>1117</v>
+        <v>1120</v>
       </c>
       <c r="C15" s="72"/>
       <c r="D15" s="72"/>
@@ -16347,10 +16389,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="73" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="B16" s="73" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="C16" s="72"/>
       <c r="D16" s="72"/>
@@ -16362,10 +16404,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="73" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="B17" s="73" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="C17" s="72"/>
       <c r="D17" s="72"/>
@@ -16377,10 +16419,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="73" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="B18" s="73" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="C18" s="72"/>
       <c r="D18" s="72"/>
@@ -16392,10 +16434,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="73" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="B19" s="73" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="C19" s="72"/>
       <c r="D19" s="72"/>
@@ -16407,10 +16449,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="59" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="B20" s="73" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="C20" s="72"/>
       <c r="D20" s="72"/>
@@ -16422,10 +16464,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="59" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="B21" s="73" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="C21" s="72"/>
       <c r="D21" s="72"/>
@@ -16437,10 +16479,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="59" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="C22" s="72"/>
       <c r="D22" s="72"/>
@@ -16452,10 +16494,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="59" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="B23" s="73" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="C23" s="72"/>
       <c r="D23" s="72"/>
@@ -16467,7 +16509,7 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="59" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="C24" s="72"/>
       <c r="D24" s="72"/>
@@ -16479,10 +16521,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="73" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="B25" s="73" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C25" s="72"/>
       <c r="D25" s="72"/>
@@ -16494,10 +16536,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="73" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="B26" s="73" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="C26" s="72"/>
       <c r="D26" s="72"/>
@@ -16509,10 +16551,10 @@
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="73" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="B27" s="73" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="C27" s="72"/>
       <c r="D27" s="72"/>
@@ -16524,10 +16566,10 @@
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="73" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="B28" s="73" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="C28" s="72"/>
       <c r="D28" s="72"/>
@@ -16539,10 +16581,10 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="73" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="B29" s="73" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="C29" s="72"/>
       <c r="D29" s="72"/>
@@ -16554,10 +16596,10 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="73" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="B30" s="73" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="C30" s="72"/>
       <c r="D30" s="72"/>
@@ -16569,10 +16611,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="73" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="B31" s="73" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="C31" s="72"/>
       <c r="D31" s="72"/>
@@ -16584,7 +16626,7 @@
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="73" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="B32" s="73" t="s">
         <v>174</v>
@@ -16599,10 +16641,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="73" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="B33" s="73" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="C33" s="72"/>
       <c r="D33" s="72"/>
@@ -16614,10 +16656,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="73" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="B34" s="73" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="C34" s="72"/>
       <c r="D34" s="72"/>
@@ -16629,10 +16671,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="73" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="B35" s="59" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="C35" s="72"/>
       <c r="D35" s="72"/>
@@ -16644,10 +16686,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="73" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="B36" s="59" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="C36" s="72"/>
       <c r="D36" s="72"/>
@@ -16659,10 +16701,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="73" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="B37" s="73" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="C37" s="72"/>
       <c r="D37" s="72"/>
@@ -16674,10 +16716,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="73" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="B38" s="73" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="C38" s="72"/>
       <c r="D38" s="72"/>

--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -9,14 +9,14 @@
     <sheet state="visible" name="Pronunciation" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$477</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$480</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1740" uniqueCount="1182">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="1188">
   <si>
     <t>Word</t>
   </si>
@@ -264,6 +264,18 @@
     <t>an axe (weapon)</t>
   </si>
   <si>
+    <t>eldre (2)</t>
+  </si>
+  <si>
+    <t>an elder, an elderly person</t>
+  </si>
+  <si>
+    <t>definitive -en</t>
+  </si>
+  <si>
+    <t>add -en to word. if ends with -e, use -n. if ends with other vowel, add -nen</t>
+  </si>
+  <si>
     <t>ok</t>
   </si>
   <si>
@@ -273,10 +285,10 @@
     <t>and</t>
   </si>
   <si>
-    <t>definitive -en</t>
-  </si>
-  <si>
-    <t>add -en to word. if ends with -e, use -n. if ends with other vowel, add -nen</t>
+    <t>plural -ir</t>
+  </si>
+  <si>
+    <t>add -ir to word. if ends with -e, remove the -e and add -ir. if ends with other vowel, add -nir</t>
   </si>
   <si>
     <t>ange</t>
@@ -285,10 +297,10 @@
     <t>angry (adjective)</t>
   </si>
   <si>
-    <t>plural -ir</t>
-  </si>
-  <si>
-    <t>add -ir to word. if ends with -e, remove the -e and add -ir. if ends with other vowel, add -nir</t>
+    <t>past tense -de</t>
+  </si>
+  <si>
+    <t>remove -en, then add -de. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and double the consonant | gjårken =&gt; gjårkde | akresten =&gt; akreisdde | hæsten =&gt; hesdde (-ten is replaced with -den)</t>
   </si>
   <si>
     <t>klæddvin</t>
@@ -297,10 +309,10 @@
     <t>any cloth attire, or apparel; clothing</t>
   </si>
   <si>
-    <t>past tense -de</t>
-  </si>
-  <si>
-    <t>remove -en, then add -de. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and double the consonant | gjårken =&gt; gjårkde | akresten =&gt; akreisdde | hæsten =&gt; hesdde (-ten is replaced with -den)</t>
+    <t>present tense -ete</t>
+  </si>
+  <si>
+    <t>remove -en</t>
   </si>
   <si>
     <t>antul</t>
@@ -309,10 +321,10 @@
     <t>any type of armor</t>
   </si>
   <si>
-    <t>present tense -ete</t>
-  </si>
-  <si>
-    <t>remove -en</t>
+    <t>past participle -den, -edet</t>
+  </si>
+  <si>
+    <t>remove -en, then add -den. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and add -ende | gjårken =&gt; gjårkden | akresten =&gt; akreistende | hæsten =&gt; hestende  (-ten is replaced with -den)</t>
   </si>
   <si>
     <t>borg</t>
@@ -321,10 +333,10 @@
     <t>any type of fortified structure, mostly used to refer castles</t>
   </si>
   <si>
-    <t>past participle -den, -edet</t>
-  </si>
-  <si>
-    <t>remove -en, then add -den. if after removing the ending, and it ends with two different consonants (or -t or -d) (excluding consonants are r, n, m, and l), apply i shift and add -ende | gjårken =&gt; gjårkden | akresten =&gt; akreistende | hæsten =&gt; hestende  (-ten is replaced with -den)</t>
+    <t>present participle -inde</t>
+  </si>
+  <si>
+    <t>remove -en, then add -inde</t>
   </si>
   <si>
     <t>mirste</t>
@@ -333,10 +345,10 @@
     <t>any type of metal</t>
   </si>
   <si>
-    <t>present participle -inde</t>
-  </si>
-  <si>
-    <t>remove -en, then add -inde</t>
+    <t>noun form of verb -inge</t>
+  </si>
+  <si>
+    <t>remove -en, then add -inge</t>
   </si>
   <si>
     <t>nem</t>
@@ -345,10 +357,10 @@
     <t>any, some</t>
   </si>
   <si>
-    <t>noun form of verb -inge</t>
-  </si>
-  <si>
-    <t>remove -en, then add -inge</t>
+    <t>imperative</t>
+  </si>
+  <si>
+    <t>remove the -n</t>
   </si>
   <si>
     <t>blogvir</t>
@@ -357,10 +369,10 @@
     <t>around</t>
   </si>
   <si>
-    <t>imperative</t>
-  </si>
-  <si>
-    <t>remove the -n</t>
+    <t>likeness -lik</t>
+  </si>
+  <si>
+    <t>add -lik</t>
   </si>
   <si>
     <t>å</t>
@@ -369,10 +381,13 @@
     <t>at</t>
   </si>
   <si>
-    <t>likeness -lik</t>
-  </si>
-  <si>
-    <t>add -lik</t>
+    <t>Pronunciation</t>
+  </si>
+  <si>
+    <t>Sound</t>
+  </si>
+  <si>
+    <t>Special</t>
   </si>
   <si>
     <t>væg</t>
@@ -381,13 +396,10 @@
     <t>away</t>
   </si>
   <si>
-    <t>Pronunciation</t>
-  </si>
-  <si>
-    <t>Sound</t>
-  </si>
-  <si>
-    <t>Special</t>
+    <t>VOWELS</t>
+  </si>
+  <si>
+    <t>A Å Æ E I O Ø U Y</t>
   </si>
   <si>
     <t>lybe</t>
@@ -396,10 +408,10 @@
     <t>baby</t>
   </si>
   <si>
-    <t>VOWELS</t>
-  </si>
-  <si>
-    <t>A Å Æ E I O Ø U Y</t>
+    <t>A</t>
+  </si>
+  <si>
+    <t>/a/</t>
   </si>
   <si>
     <t>dym</t>
@@ -408,10 +420,10 @@
     <t>bad</t>
   </si>
   <si>
-    <t>A</t>
-  </si>
-  <si>
-    <t>/a/</t>
+    <t>Å</t>
+  </si>
+  <si>
+    <t>/ɒ/</t>
   </si>
   <si>
     <t>bal</t>
@@ -420,10 +432,10 @@
     <t>ball, sphere</t>
   </si>
   <si>
-    <t>Å</t>
-  </si>
-  <si>
-    <t>/ɒ/</t>
+    <t>Æ</t>
+  </si>
+  <si>
+    <t>/aː/</t>
   </si>
   <si>
     <t>kåf</t>
@@ -435,10 +447,10 @@
     <t>bark (dog)</t>
   </si>
   <si>
-    <t>Æ</t>
-  </si>
-  <si>
-    <t>/aː/</t>
+    <t>E</t>
+  </si>
+  <si>
+    <t>/ɛ/</t>
   </si>
   <si>
     <t>bavked</t>
@@ -447,10 +459,10 @@
     <t>bastard (insult)</t>
   </si>
   <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>/ɛ/</t>
+    <t>I</t>
+  </si>
+  <si>
+    <t>/ɪ/</t>
   </si>
   <si>
     <t>bagt</t>
@@ -459,10 +471,10 @@
     <t>battle, or any large-scale fight</t>
   </si>
   <si>
-    <t>I</t>
-  </si>
-  <si>
-    <t>/ɪ/</t>
+    <t>O</t>
+  </si>
+  <si>
+    <t>/ɔ/</t>
   </si>
   <si>
     <t>dul</t>
@@ -471,10 +483,10 @@
     <t>bean</t>
   </si>
   <si>
-    <t>O</t>
-  </si>
-  <si>
-    <t>/ɔ/</t>
+    <t>U</t>
+  </si>
+  <si>
+    <t>/u/</t>
   </si>
   <si>
     <t>byr</t>
@@ -483,28 +495,28 @@
     <t>bear</t>
   </si>
   <si>
-    <t>U</t>
-  </si>
-  <si>
-    <t>/u/</t>
-  </si>
-  <si>
     <t>kødde</t>
   </si>
   <si>
     <t>bed</t>
   </si>
   <si>
+    <t>Y</t>
+  </si>
+  <si>
+    <t>/i/</t>
+  </si>
+  <si>
     <t>glof</t>
   </si>
   <si>
     <t>being fat</t>
   </si>
   <si>
-    <t>Y</t>
-  </si>
-  <si>
-    <t>/i/</t>
+    <t>EA</t>
+  </si>
+  <si>
+    <t>/aːɒː/</t>
   </si>
   <si>
     <t>tuvig</t>
@@ -513,10 +525,10 @@
     <t>being heavy</t>
   </si>
   <si>
-    <t>EA</t>
-  </si>
-  <si>
-    <t>/aːɒː/</t>
+    <t>EO</t>
+  </si>
+  <si>
+    <t>/ɛoː/</t>
   </si>
   <si>
     <t>berre</t>
@@ -525,10 +537,10 @@
     <t>berry</t>
   </si>
   <si>
-    <t>EO</t>
-  </si>
-  <si>
-    <t>/ɛoː/</t>
+    <t>R</t>
+  </si>
+  <si>
+    <t>/r/</t>
   </si>
   <si>
     <t>bag</t>
@@ -537,10 +549,10 @@
     <t>big, vast, massive, or great</t>
   </si>
   <si>
-    <t>R</t>
-  </si>
-  <si>
-    <t>/r/</t>
+    <t>L when its after the vowel in a syllable</t>
+  </si>
+  <si>
+    <t>/l̪/</t>
   </si>
   <si>
     <t>årke</t>
@@ -549,12 +561,6 @@
     <t>bird</t>
   </si>
   <si>
-    <t>L when its after the vowel in a syllable</t>
-  </si>
-  <si>
-    <t>/l̪/</t>
-  </si>
-  <si>
     <t>blæke</t>
   </si>
   <si>
@@ -573,13 +579,16 @@
     <t>blood</t>
   </si>
   <si>
+    <t>adjectives go before nouns</t>
+  </si>
+  <si>
     <t>blor</t>
   </si>
   <si>
     <t>blue</t>
   </si>
   <si>
-    <t>adjectives go before nouns</t>
+    <t>adverbs go after verbs</t>
   </si>
   <si>
     <t>skått</t>
@@ -588,25 +597,28 @@
     <t>boat</t>
   </si>
   <si>
-    <t>adverbs go after verbs</t>
-  </si>
-  <si>
     <t>bok</t>
   </si>
   <si>
     <t>book</t>
   </si>
   <si>
+    <t>question example</t>
+  </si>
+  <si>
+    <t>vil du som matig?</t>
+  </si>
+  <si>
     <t>flaske</t>
   </si>
   <si>
     <t>bottle</t>
   </si>
   <si>
-    <t>question example</t>
-  </si>
-  <si>
-    <t>vil du som matig?</t>
+    <t>auxiliary example</t>
+  </si>
+  <si>
+    <t>eg vil eten som matig.</t>
   </si>
   <si>
     <t>buv</t>
@@ -615,12 +627,6 @@
     <t>bow (weapon)</t>
   </si>
   <si>
-    <t>auxiliary example</t>
-  </si>
-  <si>
-    <t>eg vil eten som matig.</t>
-  </si>
-  <si>
     <t>gutte</t>
   </si>
   <si>
@@ -1605,6 +1611,12 @@
     <t>old</t>
   </si>
   <si>
+    <t>eldre (1)</t>
+  </si>
+  <si>
+    <t>old, elderly</t>
+  </si>
+  <si>
     <t>ep</t>
   </si>
   <si>
@@ -1786,6 +1798,12 @@
   </si>
   <si>
     <t>right (direction)</t>
+  </si>
+  <si>
+    <t>ringe</t>
+  </si>
+  <si>
+    <t>ring</t>
   </si>
   <si>
     <t>elve</t>
@@ -3827,10 +3845,10 @@
         <color rgb="FF284E3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3838,13 +3856,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3852,13 +3870,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
         <color rgb="FF284E3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3967,6 +3985,18 @@
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment vertical="center"/>
     </xf>
+    <xf borderId="5" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    </xf>
     <xf borderId="8" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -3976,55 +4006,43 @@
     <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="5" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="5" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="7" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="10" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
+    <xf borderId="6" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="9" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="6" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
-    </xf>
-    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -4160,8 +4178,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C477" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$477"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C480" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$480"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Type" id="2"/>
@@ -4491,7 +4509,7 @@
         <v>25</v>
       </c>
       <c r="H4" s="21" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C477, REGEXMATCH(C2:C477, I3)), 2, TRUE)"),"ibyrten")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C480, REGEXMATCH(C2:C480, I3)), 2, TRUE)"),"ibyrten")</f>
         <v>ibyrten</v>
       </c>
       <c r="I4" s="4" t="str">
@@ -4839,18 +4857,18 @@
         <v>82</v>
       </c>
       <c r="B19" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C19" s="24" t="s">
         <v>83</v>
-      </c>
-      <c r="C19" s="17" t="s">
-        <v>84</v>
       </c>
       <c r="D19" s="4"/>
       <c r="E19" s="30" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F19" s="31"/>
       <c r="G19" s="30" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="H19" s="4"/>
       <c r="I19" s="4"/>
@@ -4859,12 +4877,12 @@
     </row>
     <row r="20" ht="15.75" customHeight="1">
       <c r="A20" s="10" t="s">
+        <v>86</v>
+      </c>
+      <c r="B20" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="B20" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C20" s="12" t="s">
+      <c r="C20" s="20" t="s">
         <v>88</v>
       </c>
       <c r="D20" s="4"/>
@@ -4885,7 +4903,7 @@
         <v>91</v>
       </c>
       <c r="B21" s="16" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C21" s="24" t="s">
         <v>92</v>
@@ -4904,13 +4922,13 @@
       <c r="K21" s="9"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="22" t="s">
+      <c r="A22" s="10" t="s">
         <v>95</v>
       </c>
       <c r="B22" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C22" s="20" t="s">
+      <c r="C22" s="12" t="s">
         <v>96</v>
       </c>
       <c r="D22" s="4"/>
@@ -4927,7 +4945,7 @@
       <c r="K22" s="9"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="15" t="s">
+      <c r="A23" s="25" t="s">
         <v>99</v>
       </c>
       <c r="B23" s="16" t="s">
@@ -4973,13 +4991,13 @@
       <c r="K24" s="9"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="34" t="s">
+      <c r="A25" s="15" t="s">
         <v>107</v>
       </c>
-      <c r="B25" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C25" s="36" t="s">
+      <c r="B25" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C25" s="17" t="s">
         <v>108</v>
       </c>
       <c r="D25" s="4"/>
@@ -4996,13 +5014,13 @@
       <c r="K25" s="9"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="22" t="s">
+      <c r="A26" s="34" t="s">
         <v>111</v>
       </c>
-      <c r="B26" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C26" s="20" t="s">
+      <c r="B26" s="26" t="s">
+        <v>68</v>
+      </c>
+      <c r="C26" s="35" t="s">
         <v>112</v>
       </c>
       <c r="D26" s="4"/>
@@ -5019,13 +5037,13 @@
       <c r="K26" s="9"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="34" t="s">
+      <c r="A27" s="25" t="s">
         <v>115</v>
       </c>
-      <c r="B27" s="35" t="s">
-        <v>53</v>
-      </c>
-      <c r="C27" s="36" t="s">
+      <c r="B27" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C27" s="17" t="s">
         <v>116</v>
       </c>
       <c r="D27" s="4"/>
@@ -5042,23 +5060,23 @@
       <c r="K27" s="9"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="10" t="s">
+      <c r="A28" s="34" t="s">
         <v>119</v>
       </c>
-      <c r="B28" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C28" s="20" t="s">
+      <c r="B28" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C28" s="35" t="s">
         <v>120</v>
       </c>
       <c r="D28" s="4"/>
-      <c r="E28" s="37" t="s">
+      <c r="E28" s="36" t="s">
         <v>121</v>
       </c>
-      <c r="F28" s="37" t="s">
+      <c r="F28" s="36" t="s">
         <v>122</v>
       </c>
-      <c r="G28" s="37" t="s">
+      <c r="G28" s="36" t="s">
         <v>123</v>
       </c>
       <c r="H28" s="4"/>
@@ -5067,13 +5085,13 @@
       <c r="K28" s="9"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="34" t="s">
+      <c r="A29" s="15" t="s">
         <v>124</v>
       </c>
-      <c r="B29" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C29" s="36" t="s">
+      <c r="B29" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="C29" s="17" t="s">
         <v>125</v>
       </c>
       <c r="D29" s="4"/>
@@ -5090,13 +5108,13 @@
       <c r="K29" s="9"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="10" t="s">
+      <c r="A30" s="34" t="s">
         <v>128</v>
       </c>
-      <c r="B30" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C30" s="12" t="s">
+      <c r="B30" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C30" s="35" t="s">
         <v>129</v>
       </c>
       <c r="D30" s="4"/>
@@ -5117,7 +5135,7 @@
         <v>132</v>
       </c>
       <c r="B31" s="16" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C31" s="24" t="s">
         <v>133</v>
@@ -5140,17 +5158,17 @@
         <v>136</v>
       </c>
       <c r="B32" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C32" s="12" t="s">
         <v>137</v>
-      </c>
-      <c r="C32" s="12" t="s">
-        <v>138</v>
       </c>
       <c r="D32" s="4"/>
       <c r="E32" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="F32" s="30" t="s">
         <v>139</v>
-      </c>
-      <c r="F32" s="30" t="s">
-        <v>140</v>
       </c>
       <c r="G32" s="31"/>
       <c r="H32" s="4"/>
@@ -5160,10 +5178,10 @@
     </row>
     <row r="33" ht="15.75" customHeight="1">
       <c r="A33" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="B33" s="16" t="s">
         <v>141</v>
-      </c>
-      <c r="B33" s="16" t="s">
-        <v>9</v>
       </c>
       <c r="C33" s="24" t="s">
         <v>142</v>
@@ -5182,13 +5200,13 @@
       <c r="K33" s="9"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="22" t="s">
+      <c r="A34" s="10" t="s">
         <v>145</v>
       </c>
       <c r="B34" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C34" s="20" t="s">
+      <c r="C34" s="12" t="s">
         <v>146</v>
       </c>
       <c r="D34" s="4"/>
@@ -5205,13 +5223,13 @@
       <c r="K34" s="9"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="15" t="s">
+      <c r="A35" s="25" t="s">
         <v>149</v>
       </c>
       <c r="B35" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C35" s="24" t="s">
+      <c r="C35" s="17" t="s">
         <v>150</v>
       </c>
       <c r="D35" s="4"/>
@@ -5228,13 +5246,13 @@
       <c r="K35" s="9"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="22" t="s">
+      <c r="A36" s="10" t="s">
         <v>153</v>
       </c>
       <c r="B36" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C36" s="20" t="s">
+      <c r="C36" s="12" t="s">
         <v>154</v>
       </c>
       <c r="D36" s="4"/>
@@ -5251,18 +5269,18 @@
       <c r="K36" s="9"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="15" t="s">
+      <c r="A37" s="25" t="s">
         <v>157</v>
       </c>
       <c r="B37" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C37" s="24" t="s">
+      <c r="C37" s="17" t="s">
         <v>158</v>
       </c>
       <c r="D37" s="4"/>
-      <c r="E37" s="38"/>
-      <c r="F37" s="38"/>
+      <c r="E37" s="37"/>
+      <c r="F37" s="37"/>
       <c r="G37" s="4"/>
       <c r="H37" s="4"/>
       <c r="I37" s="4"/>
@@ -5270,20 +5288,20 @@
       <c r="K37" s="9"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="22" t="s">
+      <c r="A38" s="10" t="s">
         <v>159</v>
       </c>
       <c r="B38" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C38" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C38" s="12" t="s">
         <v>160</v>
       </c>
       <c r="D38" s="4"/>
-      <c r="E38" s="38" t="s">
+      <c r="E38" s="37" t="s">
         <v>161</v>
       </c>
-      <c r="F38" s="38" t="s">
+      <c r="F38" s="37" t="s">
         <v>162</v>
       </c>
       <c r="G38" s="4"/>
@@ -5293,7 +5311,7 @@
       <c r="K38" s="9"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="15" t="s">
+      <c r="A39" s="25" t="s">
         <v>163</v>
       </c>
       <c r="B39" s="16" t="s">
@@ -5303,10 +5321,10 @@
         <v>164</v>
       </c>
       <c r="D39" s="4"/>
-      <c r="E39" s="38" t="s">
+      <c r="E39" s="37" t="s">
         <v>165</v>
       </c>
-      <c r="F39" s="38" t="s">
+      <c r="F39" s="37" t="s">
         <v>166</v>
       </c>
       <c r="G39" s="4"/>
@@ -5320,16 +5338,16 @@
         <v>167</v>
       </c>
       <c r="B40" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C40" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C40" s="20" t="s">
         <v>168</v>
       </c>
       <c r="D40" s="4"/>
-      <c r="E40" s="38" t="s">
+      <c r="E40" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="F40" s="38" t="s">
+      <c r="F40" s="37" t="s">
         <v>170</v>
       </c>
       <c r="G40" s="4"/>
@@ -5339,43 +5357,43 @@
       <c r="K40" s="9"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="25" t="s">
+      <c r="A41" s="15" t="s">
         <v>171</v>
       </c>
       <c r="B41" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C41" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C41" s="24" t="s">
         <v>172</v>
       </c>
       <c r="D41" s="4"/>
-      <c r="E41" s="38" t="s">
+      <c r="E41" s="37" t="s">
         <v>173</v>
       </c>
-      <c r="F41" s="38" t="s">
+      <c r="F41" s="37" t="s">
         <v>174</v>
       </c>
-      <c r="G41" s="38"/>
+      <c r="G41" s="37"/>
       <c r="H41" s="4"/>
       <c r="I41" s="4"/>
       <c r="J41" s="9"/>
       <c r="K41" s="9"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="10" t="s">
+      <c r="A42" s="22" t="s">
         <v>175</v>
       </c>
       <c r="B42" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C42" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C42" s="20" t="s">
         <v>176</v>
       </c>
       <c r="D42" s="4"/>
-      <c r="E42" s="38" t="s">
+      <c r="E42" s="37" t="s">
         <v>177</v>
       </c>
-      <c r="F42" s="38" t="s">
+      <c r="F42" s="37" t="s">
         <v>178</v>
       </c>
       <c r="G42" s="4"/>
@@ -5389,7 +5407,7 @@
         <v>179</v>
       </c>
       <c r="B43" s="16" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C43" s="24" t="s">
         <v>180</v>
@@ -5408,7 +5426,7 @@
         <v>181</v>
       </c>
       <c r="B44" s="11" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>182</v>
@@ -5429,7 +5447,7 @@
       <c r="B45" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C45" s="17" t="s">
+      <c r="C45" s="24" t="s">
         <v>184</v>
       </c>
       <c r="D45" s="4"/>
@@ -5442,17 +5460,17 @@
       <c r="K45" s="9"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="39" t="s">
+      <c r="A46" s="10" t="s">
         <v>185</v>
       </c>
-      <c r="B46" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C46" s="40" t="s">
+      <c r="B46" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C46" s="20" t="s">
         <v>186</v>
       </c>
       <c r="D46" s="4"/>
-      <c r="E46" s="38" t="s">
+      <c r="E46" s="37" t="s">
         <v>187</v>
       </c>
       <c r="F46" s="4"/>
@@ -5463,17 +5481,17 @@
       <c r="K46" s="9"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="15" t="s">
+      <c r="A47" s="38" t="s">
         <v>188</v>
       </c>
-      <c r="B47" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C47" s="24" t="s">
+      <c r="B47" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C47" s="40" t="s">
         <v>189</v>
       </c>
       <c r="D47" s="4"/>
-      <c r="E47" s="38" t="s">
+      <c r="E47" s="37" t="s">
         <v>190</v>
       </c>
       <c r="F47" s="4"/>
@@ -5513,11 +5531,11 @@
         <v>194</v>
       </c>
       <c r="D49" s="4"/>
-      <c r="E49" s="38" t="s">
+      <c r="E49" s="37" t="s">
         <v>195</v>
       </c>
       <c r="F49" s="4"/>
-      <c r="G49" s="38" t="s">
+      <c r="G49" s="37" t="s">
         <v>196</v>
       </c>
       <c r="H49" s="4"/>
@@ -5536,11 +5554,11 @@
         <v>198</v>
       </c>
       <c r="D50" s="4"/>
-      <c r="E50" s="38" t="s">
+      <c r="E50" s="37" t="s">
         <v>199</v>
       </c>
       <c r="F50" s="4"/>
-      <c r="G50" s="38" t="s">
+      <c r="G50" s="37" t="s">
         <v>200</v>
       </c>
       <c r="H50" s="4"/>
@@ -5572,7 +5590,7 @@
         <v>203</v>
       </c>
       <c r="B52" s="11" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C52" s="12" t="s">
         <v>204</v>
@@ -5591,9 +5609,9 @@
         <v>205</v>
       </c>
       <c r="B53" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C53" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C53" s="24" t="s">
         <v>206</v>
       </c>
       <c r="D53" s="4"/>
@@ -5610,9 +5628,9 @@
         <v>207</v>
       </c>
       <c r="B54" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C54" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C54" s="20" t="s">
         <v>208</v>
       </c>
       <c r="D54" s="4"/>
@@ -5629,9 +5647,9 @@
         <v>209</v>
       </c>
       <c r="B55" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C55" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C55" s="24" t="s">
         <v>210</v>
       </c>
       <c r="D55" s="4"/>
@@ -5648,9 +5666,9 @@
         <v>211</v>
       </c>
       <c r="B56" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C56" s="12" t="s">
+        <v>87</v>
+      </c>
+      <c r="C56" s="20" t="s">
         <v>212</v>
       </c>
       <c r="D56" s="4"/>
@@ -5758,13 +5776,13 @@
       <c r="K61" s="9"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="39" t="s">
+      <c r="A62" s="10" t="s">
         <v>223</v>
       </c>
       <c r="B62" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C62" s="40" t="s">
+      <c r="C62" s="12" t="s">
         <v>224</v>
       </c>
       <c r="D62" s="4"/>
@@ -5777,13 +5795,13 @@
       <c r="K62" s="9"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="15" t="s">
+      <c r="A63" s="38" t="s">
         <v>225</v>
       </c>
       <c r="B63" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C63" s="17" t="s">
+      <c r="C63" s="40" t="s">
         <v>226</v>
       </c>
       <c r="D63" s="4"/>
@@ -5800,9 +5818,9 @@
         <v>227</v>
       </c>
       <c r="B64" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C64" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C64" s="20" t="s">
         <v>228</v>
       </c>
       <c r="D64" s="4"/>
@@ -5819,7 +5837,7 @@
         <v>229</v>
       </c>
       <c r="B65" s="16" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C65" s="24" t="s">
         <v>230</v>
@@ -5872,13 +5890,13 @@
       <c r="K67" s="9"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="41" t="s">
+      <c r="A68" s="10" t="s">
         <v>235</v>
       </c>
       <c r="B68" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C68" s="42" t="s">
+        <v>9</v>
+      </c>
+      <c r="C68" s="12" t="s">
         <v>236</v>
       </c>
       <c r="D68" s="4"/>
@@ -5891,13 +5909,13 @@
       <c r="K68" s="9"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="15" t="s">
+      <c r="A69" s="41" t="s">
         <v>237</v>
       </c>
       <c r="B69" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C69" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C69" s="42" t="s">
         <v>238</v>
       </c>
       <c r="D69" s="4"/>
@@ -5910,13 +5928,13 @@
       <c r="K69" s="9"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="39" t="s">
+      <c r="A70" s="10" t="s">
         <v>239</v>
       </c>
       <c r="B70" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C70" s="40" t="s">
+      <c r="C70" s="12" t="s">
         <v>240</v>
       </c>
       <c r="D70" s="4"/>
@@ -5929,13 +5947,13 @@
       <c r="K70" s="9"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="34" t="s">
+      <c r="A71" s="38" t="s">
         <v>241</v>
       </c>
       <c r="B71" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C71" s="36" t="s">
+      <c r="C71" s="40" t="s">
         <v>242</v>
       </c>
       <c r="D71" s="4"/>
@@ -5948,13 +5966,13 @@
       <c r="K71" s="9"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="10" t="s">
+      <c r="A72" s="34" t="s">
         <v>243</v>
       </c>
       <c r="B72" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C72" s="43" t="s">
+      <c r="C72" s="35" t="s">
         <v>244</v>
       </c>
       <c r="D72" s="4"/>
@@ -5971,9 +5989,9 @@
         <v>245</v>
       </c>
       <c r="B73" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C73" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C73" s="43" t="s">
         <v>246</v>
       </c>
       <c r="D73" s="4"/>
@@ -5992,7 +6010,7 @@
       <c r="B74" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C74" s="43" t="s">
+      <c r="C74" s="12" t="s">
         <v>248</v>
       </c>
       <c r="D74" s="4"/>
@@ -6009,9 +6027,9 @@
         <v>249</v>
       </c>
       <c r="B75" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C75" s="44" t="s">
+        <v>68</v>
+      </c>
+      <c r="C75" s="43" t="s">
         <v>250</v>
       </c>
       <c r="D75" s="4"/>
@@ -6030,7 +6048,7 @@
       <c r="B76" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C76" s="12" t="s">
+      <c r="C76" s="44" t="s">
         <v>252</v>
       </c>
       <c r="D76" s="4"/>
@@ -6047,7 +6065,7 @@
         <v>253</v>
       </c>
       <c r="B77" s="16" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C77" s="24" t="s">
         <v>254</v>
@@ -6066,9 +6084,9 @@
         <v>255</v>
       </c>
       <c r="B78" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C78" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C78" s="12" t="s">
         <v>256</v>
       </c>
       <c r="D78" s="4"/>
@@ -6100,13 +6118,13 @@
       <c r="K79" s="9"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="39" t="s">
+      <c r="A80" s="10" t="s">
         <v>259</v>
       </c>
       <c r="B80" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C80" s="40" t="s">
+      <c r="C80" s="20" t="s">
         <v>260</v>
       </c>
       <c r="D80" s="4"/>
@@ -6119,13 +6137,13 @@
       <c r="K80" s="9"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="15" t="s">
+      <c r="A81" s="38" t="s">
         <v>261</v>
       </c>
       <c r="B81" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C81" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C81" s="40" t="s">
         <v>262</v>
       </c>
       <c r="D81" s="4"/>
@@ -6142,7 +6160,7 @@
         <v>263</v>
       </c>
       <c r="B82" s="11" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C82" s="12" t="s">
         <v>264</v>
@@ -6161,9 +6179,9 @@
         <v>265</v>
       </c>
       <c r="B83" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C83" s="44" t="s">
+        <v>9</v>
+      </c>
+      <c r="C83" s="24" t="s">
         <v>266</v>
       </c>
       <c r="D83" s="4"/>
@@ -6182,7 +6200,7 @@
       <c r="B84" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C84" s="12" t="s">
+      <c r="C84" s="44" t="s">
         <v>268</v>
       </c>
       <c r="D84" s="4"/>
@@ -6195,11 +6213,11 @@
       <c r="K84" s="9"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="25" t="s">
+      <c r="A85" s="15" t="s">
         <v>269</v>
       </c>
       <c r="B85" s="16" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C85" s="24" t="s">
         <v>270</v>
@@ -6214,7 +6232,7 @@
       <c r="K85" s="9"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="10" t="s">
+      <c r="A86" s="22" t="s">
         <v>271</v>
       </c>
       <c r="B86" s="11" t="s">
@@ -6271,13 +6289,13 @@
       <c r="K88" s="9"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="34" t="s">
+      <c r="A89" s="15" t="s">
         <v>277</v>
       </c>
       <c r="B89" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C89" s="36" t="s">
+      <c r="C89" s="24" t="s">
         <v>278</v>
       </c>
       <c r="D89" s="4"/>
@@ -6290,13 +6308,13 @@
       <c r="K89" s="9"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="22" t="s">
+      <c r="A90" s="34" t="s">
         <v>279</v>
       </c>
       <c r="B90" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C90" s="12" t="s">
+      <c r="C90" s="35" t="s">
         <v>280</v>
       </c>
       <c r="D90" s="4"/>
@@ -6309,13 +6327,13 @@
       <c r="K90" s="9"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="15" t="s">
+      <c r="A91" s="25" t="s">
         <v>281</v>
       </c>
       <c r="B91" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C91" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C91" s="24" t="s">
         <v>282</v>
       </c>
       <c r="D91" s="4"/>
@@ -6328,14 +6346,14 @@
       <c r="K91" s="9"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="39" t="s">
-        <v>247</v>
+      <c r="A92" s="10" t="s">
+        <v>283</v>
       </c>
       <c r="B92" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C92" s="40" t="s">
-        <v>283</v>
+        <v>68</v>
+      </c>
+      <c r="C92" s="20" t="s">
+        <v>284</v>
       </c>
       <c r="D92" s="4"/>
       <c r="E92" s="4"/>
@@ -6347,14 +6365,14 @@
       <c r="K92" s="9"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="15" t="s">
-        <v>284</v>
+      <c r="A93" s="38" t="s">
+        <v>249</v>
       </c>
       <c r="B93" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C93" s="40" t="s">
         <v>285</v>
-      </c>
-      <c r="C93" s="17" t="s">
-        <v>286</v>
       </c>
       <c r="D93" s="4"/>
       <c r="E93" s="4"/>
@@ -6367,10 +6385,10 @@
     </row>
     <row r="94" ht="15.75" customHeight="1">
       <c r="A94" s="10" t="s">
+        <v>286</v>
+      </c>
+      <c r="B94" s="11" t="s">
         <v>287</v>
-      </c>
-      <c r="B94" s="11" t="s">
-        <v>285</v>
       </c>
       <c r="C94" s="20" t="s">
         <v>288</v>
@@ -6389,7 +6407,7 @@
         <v>289</v>
       </c>
       <c r="B95" s="16" t="s">
-        <v>68</v>
+        <v>287</v>
       </c>
       <c r="C95" s="17" t="s">
         <v>290</v>
@@ -6423,13 +6441,13 @@
       <c r="K96" s="9"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="34" t="s">
+      <c r="A97" s="15" t="s">
         <v>293</v>
       </c>
-      <c r="B97" s="35" t="s">
-        <v>137</v>
-      </c>
-      <c r="C97" s="36" t="s">
+      <c r="B97" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C97" s="17" t="s">
         <v>294</v>
       </c>
       <c r="D97" s="4"/>
@@ -6442,13 +6460,13 @@
       <c r="K97" s="9"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="10" t="s">
+      <c r="A98" s="34" t="s">
         <v>295</v>
       </c>
-      <c r="B98" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C98" s="12" t="s">
+      <c r="B98" s="26" t="s">
+        <v>141</v>
+      </c>
+      <c r="C98" s="35" t="s">
         <v>296</v>
       </c>
       <c r="D98" s="4"/>
@@ -6465,10 +6483,10 @@
         <v>297</v>
       </c>
       <c r="B99" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C99" s="24" t="s">
         <v>298</v>
-      </c>
-      <c r="C99" s="17" t="s">
-        <v>299</v>
       </c>
       <c r="D99" s="4"/>
       <c r="E99" s="4"/>
@@ -6480,13 +6498,13 @@
       <c r="K99" s="9"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="41" t="s">
+      <c r="A100" s="10" t="s">
+        <v>299</v>
+      </c>
+      <c r="B100" s="11" t="s">
         <v>300</v>
       </c>
-      <c r="B100" s="11" t="s">
-        <v>298</v>
-      </c>
-      <c r="C100" s="42" t="s">
+      <c r="C100" s="20" t="s">
         <v>301</v>
       </c>
       <c r="D100" s="4"/>
@@ -6499,13 +6517,13 @@
       <c r="K100" s="9"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="15" t="s">
+      <c r="A101" s="41" t="s">
         <v>302</v>
       </c>
       <c r="B101" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C101" s="24" t="s">
+        <v>300</v>
+      </c>
+      <c r="C101" s="42" t="s">
         <v>303</v>
       </c>
       <c r="D101" s="4"/>
@@ -6579,9 +6597,9 @@
         <v>310</v>
       </c>
       <c r="B105" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C105" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C105" s="24" t="s">
         <v>311</v>
       </c>
       <c r="D105" s="4"/>
@@ -6598,9 +6616,9 @@
         <v>312</v>
       </c>
       <c r="B106" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C106" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C106" s="20" t="s">
         <v>313</v>
       </c>
       <c r="D106" s="4"/>
@@ -6613,7 +6631,7 @@
       <c r="K106" s="9"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="34" t="s">
+      <c r="A107" s="15" t="s">
         <v>314</v>
       </c>
       <c r="B107" s="16" t="s">
@@ -6632,7 +6650,7 @@
       <c r="K107" s="9"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="10" t="s">
+      <c r="A108" s="34" t="s">
         <v>316</v>
       </c>
       <c r="B108" s="11" t="s">
@@ -6651,13 +6669,13 @@
       <c r="K108" s="9"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="25" t="s">
+      <c r="A109" s="15" t="s">
         <v>318</v>
       </c>
       <c r="B109" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C109" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C109" s="24" t="s">
         <v>319</v>
       </c>
       <c r="D109" s="4"/>
@@ -6670,13 +6688,13 @@
       <c r="K109" s="9"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="10" t="s">
+      <c r="A110" s="22" t="s">
         <v>320</v>
       </c>
       <c r="B110" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C110" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C110" s="20" t="s">
         <v>321</v>
       </c>
       <c r="D110" s="4"/>
@@ -6708,13 +6726,13 @@
       <c r="K111" s="9"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="39" t="s">
+      <c r="A112" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="B112" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C112" s="40" t="s">
+      <c r="B112" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C112" s="12" t="s">
         <v>325</v>
       </c>
       <c r="D112" s="4"/>
@@ -6727,13 +6745,13 @@
       <c r="K112" s="9"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="15" t="s">
+      <c r="A113" s="38" t="s">
         <v>326</v>
       </c>
-      <c r="B113" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C113" s="24" t="s">
+      <c r="B113" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C113" s="40" t="s">
         <v>327</v>
       </c>
       <c r="D113" s="4"/>
@@ -6803,13 +6821,13 @@
       <c r="K116" s="9"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="34" t="s">
+      <c r="A117" s="15" t="s">
         <v>334</v>
       </c>
       <c r="B117" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C117" s="36" t="s">
+      <c r="C117" s="24" t="s">
         <v>335</v>
       </c>
       <c r="D117" s="4"/>
@@ -6822,13 +6840,13 @@
       <c r="K117" s="9"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="10" t="s">
+      <c r="A118" s="34" t="s">
         <v>336</v>
       </c>
       <c r="B118" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C118" s="12" t="s">
+      <c r="C118" s="35" t="s">
         <v>337</v>
       </c>
       <c r="D118" s="4"/>
@@ -6866,7 +6884,7 @@
       <c r="B120" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C120" s="20" t="s">
+      <c r="C120" s="12" t="s">
         <v>341</v>
       </c>
       <c r="D120" s="4"/>
@@ -6883,9 +6901,9 @@
         <v>342</v>
       </c>
       <c r="B121" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C121" s="24" t="s">
+        <v>9</v>
+      </c>
+      <c r="C121" s="17" t="s">
         <v>343</v>
       </c>
       <c r="D121" s="4"/>
@@ -6902,7 +6920,7 @@
         <v>344</v>
       </c>
       <c r="B122" s="11" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C122" s="12" t="s">
         <v>345</v>
@@ -6923,7 +6941,7 @@
       <c r="B123" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C123" s="17" t="s">
+      <c r="C123" s="24" t="s">
         <v>347</v>
       </c>
       <c r="D123" s="4"/>
@@ -6940,7 +6958,7 @@
         <v>348</v>
       </c>
       <c r="B124" s="11" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C124" s="20" t="s">
         <v>349</v>
@@ -6978,9 +6996,9 @@
         <v>352</v>
       </c>
       <c r="B126" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C126" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C126" s="20" t="s">
         <v>353</v>
       </c>
       <c r="D126" s="4"/>
@@ -7012,13 +7030,13 @@
       <c r="K127" s="9"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="39" t="s">
+      <c r="A128" s="10" t="s">
         <v>356</v>
       </c>
       <c r="B128" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C128" s="40" t="s">
+      <c r="C128" s="12" t="s">
         <v>357</v>
       </c>
       <c r="D128" s="4"/>
@@ -7031,13 +7049,13 @@
       <c r="K128" s="9"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="15" t="s">
+      <c r="A129" s="38" t="s">
         <v>358</v>
       </c>
       <c r="B129" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C129" s="24" t="s">
+      <c r="C129" s="40" t="s">
         <v>359</v>
       </c>
       <c r="D129" s="4"/>
@@ -7050,14 +7068,14 @@
       <c r="K129" s="9"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="39" t="s">
+      <c r="A130" s="10" t="s">
         <v>360</v>
       </c>
-      <c r="B130" s="26" t="s">
+      <c r="B130" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C130" s="12" t="s">
         <v>361</v>
-      </c>
-      <c r="C130" s="40" t="s">
-        <v>362</v>
       </c>
       <c r="D130" s="4"/>
       <c r="E130" s="4"/>
@@ -7069,13 +7087,13 @@
       <c r="K130" s="9"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="45" t="s">
+      <c r="A131" s="38" t="s">
+        <v>362</v>
+      </c>
+      <c r="B131" s="39" t="s">
         <v>363</v>
       </c>
-      <c r="B131" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="C131" s="46" t="s">
+      <c r="C131" s="40" t="s">
         <v>364</v>
       </c>
       <c r="D131" s="4"/>
@@ -7088,13 +7106,13 @@
       <c r="K131" s="9"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="10" t="s">
+      <c r="A132" s="45" t="s">
         <v>365</v>
       </c>
       <c r="B132" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="C132" s="40" t="s">
+        <v>363</v>
+      </c>
+      <c r="C132" s="46" t="s">
         <v>366</v>
       </c>
       <c r="D132" s="4"/>
@@ -7110,10 +7128,10 @@
       <c r="A133" s="15" t="s">
         <v>367</v>
       </c>
-      <c r="B133" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C133" s="17" t="s">
+      <c r="B133" s="39" t="s">
+        <v>363</v>
+      </c>
+      <c r="C133" s="40" t="s">
         <v>368</v>
       </c>
       <c r="D133" s="4"/>
@@ -7126,13 +7144,13 @@
       <c r="K133" s="9"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="39" t="s">
+      <c r="A134" s="10" t="s">
         <v>369</v>
       </c>
-      <c r="B134" s="26" t="s">
-        <v>137</v>
-      </c>
-      <c r="C134" s="40" t="s">
+      <c r="B134" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C134" s="20" t="s">
         <v>370</v>
       </c>
       <c r="D134" s="4"/>
@@ -7145,13 +7163,13 @@
       <c r="K134" s="9"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="15" t="s">
+      <c r="A135" s="38" t="s">
         <v>371</v>
       </c>
-      <c r="B135" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C135" s="17" t="s">
+      <c r="B135" s="39" t="s">
+        <v>141</v>
+      </c>
+      <c r="C135" s="40" t="s">
         <v>372</v>
       </c>
       <c r="D135" s="4"/>
@@ -7168,9 +7186,9 @@
         <v>373</v>
       </c>
       <c r="B136" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C136" s="12" t="s">
+        <v>58</v>
+      </c>
+      <c r="C136" s="20" t="s">
         <v>374</v>
       </c>
       <c r="D136" s="4"/>
@@ -7206,7 +7224,7 @@
         <v>377</v>
       </c>
       <c r="B138" s="11" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C138" s="12" t="s">
         <v>378</v>
@@ -7225,7 +7243,7 @@
         <v>379</v>
       </c>
       <c r="B139" s="16" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C139" s="24" t="s">
         <v>380</v>
@@ -7244,7 +7262,7 @@
         <v>381</v>
       </c>
       <c r="B140" s="11" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="C140" s="12" t="s">
         <v>382</v>
@@ -7259,13 +7277,13 @@
       <c r="K140" s="9"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="25" t="s">
+      <c r="A141" s="15" t="s">
         <v>383</v>
       </c>
       <c r="B141" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C141" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C141" s="24" t="s">
         <v>384</v>
       </c>
       <c r="D141" s="4"/>
@@ -7278,13 +7296,13 @@
       <c r="K141" s="9"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="39" t="s">
+      <c r="A142" s="22" t="s">
         <v>385</v>
       </c>
-      <c r="B142" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C142" s="40" t="s">
+      <c r="B142" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C142" s="20" t="s">
         <v>386</v>
       </c>
       <c r="D142" s="4"/>
@@ -7297,13 +7315,13 @@
       <c r="K142" s="9"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="15" t="s">
+      <c r="A143" s="38" t="s">
         <v>387</v>
       </c>
-      <c r="B143" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="C143" s="24" t="s">
+      <c r="B143" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C143" s="40" t="s">
         <v>388</v>
       </c>
       <c r="D143" s="4"/>
@@ -7316,13 +7334,13 @@
       <c r="K143" s="9"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="47" t="s">
+      <c r="A144" s="10" t="s">
         <v>389</v>
       </c>
       <c r="B144" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="C144" s="48" t="s">
+        <v>363</v>
+      </c>
+      <c r="C144" s="12" t="s">
         <v>390</v>
       </c>
       <c r="D144" s="4"/>
@@ -7335,13 +7353,13 @@
       <c r="K144" s="9"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="15" t="s">
+      <c r="A145" s="47" t="s">
         <v>391</v>
       </c>
-      <c r="B145" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="C145" s="24" t="s">
+      <c r="B145" s="39" t="s">
+        <v>363</v>
+      </c>
+      <c r="C145" s="48" t="s">
         <v>392</v>
       </c>
       <c r="D145" s="4"/>
@@ -7357,10 +7375,10 @@
       <c r="A146" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="B146" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C146" s="20" t="s">
+      <c r="B146" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="C146" s="12" t="s">
         <v>394</v>
       </c>
       <c r="D146" s="4"/>
@@ -7377,7 +7395,7 @@
         <v>395</v>
       </c>
       <c r="B147" s="16" t="s">
-        <v>83</v>
+        <v>9</v>
       </c>
       <c r="C147" s="17" t="s">
         <v>396</v>
@@ -7396,7 +7414,7 @@
         <v>397</v>
       </c>
       <c r="B148" s="11" t="s">
-        <v>53</v>
+        <v>87</v>
       </c>
       <c r="C148" s="20" t="s">
         <v>398</v>
@@ -7411,13 +7429,13 @@
       <c r="K148" s="9"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="45" t="s">
+      <c r="A149" s="15" t="s">
         <v>399</v>
       </c>
       <c r="B149" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C149" s="49" t="s">
+        <v>53</v>
+      </c>
+      <c r="C149" s="17" t="s">
         <v>400</v>
       </c>
       <c r="D149" s="4"/>
@@ -7430,13 +7448,13 @@
       <c r="K149" s="9"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="10" t="s">
+      <c r="A150" s="45" t="s">
         <v>401</v>
       </c>
       <c r="B150" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C150" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C150" s="49" t="s">
         <v>402</v>
       </c>
       <c r="D150" s="4"/>
@@ -7455,7 +7473,7 @@
       <c r="B151" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C151" s="17" t="s">
+      <c r="C151" s="24" t="s">
         <v>404</v>
       </c>
       <c r="D151" s="4"/>
@@ -7472,10 +7490,10 @@
         <v>405</v>
       </c>
       <c r="B152" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C152" s="20" t="s">
         <v>406</v>
-      </c>
-      <c r="C152" s="12" t="s">
-        <v>407</v>
       </c>
       <c r="D152" s="4"/>
       <c r="E152" s="4"/>
@@ -7488,10 +7506,10 @@
     </row>
     <row r="153" ht="15.75" customHeight="1">
       <c r="A153" s="15" t="s">
+        <v>407</v>
+      </c>
+      <c r="B153" s="16" t="s">
         <v>408</v>
-      </c>
-      <c r="B153" s="16" t="s">
-        <v>9</v>
       </c>
       <c r="C153" s="24" t="s">
         <v>409</v>
@@ -7512,7 +7530,7 @@
       <c r="B154" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C154" s="20" t="s">
+      <c r="C154" s="12" t="s">
         <v>411</v>
       </c>
       <c r="D154" s="4"/>
@@ -7525,13 +7543,13 @@
       <c r="K154" s="9"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="34" t="s">
+      <c r="A155" s="15" t="s">
         <v>412</v>
       </c>
-      <c r="B155" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C155" s="36" t="s">
+      <c r="B155" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C155" s="17" t="s">
         <v>413</v>
       </c>
       <c r="D155" s="4"/>
@@ -7544,13 +7562,13 @@
       <c r="K155" s="9"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="10" t="s">
+      <c r="A156" s="34" t="s">
         <v>414</v>
       </c>
       <c r="B156" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C156" s="12" t="s">
+      <c r="C156" s="35" t="s">
         <v>415</v>
       </c>
       <c r="D156" s="4"/>
@@ -7566,7 +7584,7 @@
       <c r="A157" s="15" t="s">
         <v>416</v>
       </c>
-      <c r="B157" s="35" t="s">
+      <c r="B157" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C157" s="24" t="s">
@@ -7604,7 +7622,7 @@
       <c r="A159" s="15" t="s">
         <v>420</v>
       </c>
-      <c r="B159" s="35" t="s">
+      <c r="B159" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C159" s="24" t="s">
@@ -7639,13 +7657,13 @@
       <c r="K160" s="9"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="34" t="s">
+      <c r="A161" s="15" t="s">
         <v>424</v>
       </c>
-      <c r="B161" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C161" s="36" t="s">
+      <c r="B161" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C161" s="24" t="s">
         <v>425</v>
       </c>
       <c r="D161" s="4"/>
@@ -7658,13 +7676,13 @@
       <c r="K161" s="9"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="10" t="s">
+      <c r="A162" s="34" t="s">
         <v>426</v>
       </c>
       <c r="B162" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C162" s="12" t="s">
+      <c r="C162" s="35" t="s">
         <v>427</v>
       </c>
       <c r="D162" s="4"/>
@@ -7680,7 +7698,7 @@
       <c r="A163" s="15" t="s">
         <v>428</v>
       </c>
-      <c r="B163" s="35" t="s">
+      <c r="B163" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C163" s="24" t="s">
@@ -7699,10 +7717,10 @@
       <c r="A164" s="10" t="s">
         <v>430</v>
       </c>
-      <c r="B164" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C164" s="20" t="s">
+      <c r="B164" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C164" s="12" t="s">
         <v>431</v>
       </c>
       <c r="D164" s="4"/>
@@ -7715,13 +7733,13 @@
       <c r="K164" s="9"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="25" t="s">
+      <c r="A165" s="15" t="s">
         <v>432</v>
       </c>
-      <c r="B165" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C165" s="24" t="s">
+      <c r="B165" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C165" s="17" t="s">
         <v>433</v>
       </c>
       <c r="D165" s="4"/>
@@ -7734,10 +7752,10 @@
       <c r="K165" s="9"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="10" t="s">
+      <c r="A166" s="22" t="s">
         <v>434</v>
       </c>
-      <c r="B166" s="11" t="s">
+      <c r="B166" s="26" t="s">
         <v>9</v>
       </c>
       <c r="C166" s="12" t="s">
@@ -7757,7 +7775,7 @@
         <v>436</v>
       </c>
       <c r="B167" s="16" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C167" s="24" t="s">
         <v>437</v>
@@ -7775,8 +7793,8 @@
       <c r="A168" s="10" t="s">
         <v>438</v>
       </c>
-      <c r="B168" s="26" t="s">
-        <v>9</v>
+      <c r="B168" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="C168" s="12" t="s">
         <v>439</v>
@@ -7794,7 +7812,7 @@
       <c r="A169" s="15" t="s">
         <v>440</v>
       </c>
-      <c r="B169" s="50" t="s">
+      <c r="B169" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C169" s="24" t="s">
@@ -7813,10 +7831,10 @@
       <c r="A170" s="10" t="s">
         <v>442</v>
       </c>
-      <c r="B170" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C170" s="20" t="s">
+      <c r="B170" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C170" s="12" t="s">
         <v>443</v>
       </c>
       <c r="D170" s="4"/>
@@ -7829,13 +7847,13 @@
       <c r="K170" s="9"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="34" t="s">
+      <c r="A171" s="15" t="s">
         <v>444</v>
       </c>
-      <c r="B171" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C171" s="36" t="s">
+      <c r="B171" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C171" s="17" t="s">
         <v>445</v>
       </c>
       <c r="D171" s="4"/>
@@ -7848,13 +7866,13 @@
       <c r="K171" s="9"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="10" t="s">
+      <c r="A172" s="34" t="s">
         <v>446</v>
       </c>
       <c r="B172" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C172" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C172" s="35" t="s">
         <v>447</v>
       </c>
       <c r="D172" s="4"/>
@@ -7867,13 +7885,13 @@
       <c r="K172" s="9"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="34" t="s">
+      <c r="A173" s="15" t="s">
         <v>448</v>
       </c>
-      <c r="B173" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C173" s="36" t="s">
+      <c r="B173" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C173" s="24" t="s">
         <v>449</v>
       </c>
       <c r="D173" s="4"/>
@@ -7886,13 +7904,13 @@
       <c r="K173" s="9"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="10" t="s">
+      <c r="A174" s="34" t="s">
         <v>450</v>
       </c>
       <c r="B174" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C174" s="12" t="s">
+      <c r="C174" s="35" t="s">
         <v>451</v>
       </c>
       <c r="D174" s="4"/>
@@ -7908,7 +7926,7 @@
       <c r="A175" s="15" t="s">
         <v>452</v>
       </c>
-      <c r="B175" s="50" t="s">
+      <c r="B175" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C175" s="24" t="s">
@@ -7927,7 +7945,7 @@
       <c r="A176" s="10" t="s">
         <v>454</v>
       </c>
-      <c r="B176" s="26" t="s">
+      <c r="B176" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C176" s="12" t="s">
@@ -7946,8 +7964,8 @@
       <c r="A177" s="15" t="s">
         <v>456</v>
       </c>
-      <c r="B177" s="16" t="s">
-        <v>68</v>
+      <c r="B177" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="C177" s="24" t="s">
         <v>457</v>
@@ -7965,8 +7983,8 @@
       <c r="A178" s="10" t="s">
         <v>458</v>
       </c>
-      <c r="B178" s="26" t="s">
-        <v>9</v>
+      <c r="B178" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C178" s="12" t="s">
         <v>459</v>
@@ -7984,10 +8002,10 @@
       <c r="A179" s="15" t="s">
         <v>460</v>
       </c>
-      <c r="B179" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="C179" s="17" t="s">
+      <c r="B179" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C179" s="24" t="s">
         <v>461</v>
       </c>
       <c r="D179" s="4"/>
@@ -8000,11 +8018,11 @@
       <c r="K179" s="9"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="22" t="s">
+      <c r="A180" s="10" t="s">
         <v>462</v>
       </c>
-      <c r="B180" s="26" t="s">
-        <v>9</v>
+      <c r="B180" s="11" t="s">
+        <v>300</v>
       </c>
       <c r="C180" s="20" t="s">
         <v>463</v>
@@ -8019,11 +8037,11 @@
       <c r="K180" s="9"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="15" t="s">
+      <c r="A181" s="25" t="s">
         <v>464</v>
       </c>
-      <c r="B181" s="16" t="s">
-        <v>58</v>
+      <c r="B181" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="C181" s="17" t="s">
         <v>465</v>
@@ -8041,8 +8059,8 @@
       <c r="A182" s="10" t="s">
         <v>466</v>
       </c>
-      <c r="B182" s="26" t="s">
-        <v>9</v>
+      <c r="B182" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="C182" s="20" t="s">
         <v>467</v>
@@ -8060,10 +8078,10 @@
       <c r="A183" s="15" t="s">
         <v>468</v>
       </c>
-      <c r="B183" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C183" s="24" t="s">
+      <c r="B183" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C183" s="17" t="s">
         <v>469</v>
       </c>
       <c r="D183" s="4"/>
@@ -8079,7 +8097,7 @@
       <c r="A184" s="10" t="s">
         <v>470</v>
       </c>
-      <c r="B184" s="51" t="s">
+      <c r="B184" s="26" t="s">
         <v>9</v>
       </c>
       <c r="C184" s="12" t="s">
@@ -8098,8 +8116,8 @@
       <c r="A185" s="15" t="s">
         <v>472</v>
       </c>
-      <c r="B185" s="16" t="s">
-        <v>137</v>
+      <c r="B185" s="51" t="s">
+        <v>9</v>
       </c>
       <c r="C185" s="24" t="s">
         <v>473</v>
@@ -8114,13 +8132,13 @@
       <c r="K185" s="9"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="39" t="s">
+      <c r="A186" s="10" t="s">
         <v>474</v>
       </c>
-      <c r="B186" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C186" s="40" t="s">
+      <c r="B186" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C186" s="12" t="s">
         <v>475</v>
       </c>
       <c r="D186" s="4"/>
@@ -8133,13 +8151,13 @@
       <c r="K186" s="9"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="15" t="s">
+      <c r="A187" s="38" t="s">
         <v>476</v>
       </c>
-      <c r="B187" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C187" s="17" t="s">
+      <c r="B187" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C187" s="40" t="s">
         <v>477</v>
       </c>
       <c r="D187" s="4"/>
@@ -8152,13 +8170,13 @@
       <c r="K187" s="9"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="39" t="s">
+      <c r="A188" s="10" t="s">
         <v>478</v>
       </c>
-      <c r="B188" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C188" s="40" t="s">
+      <c r="B188" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C188" s="20" t="s">
         <v>479</v>
       </c>
       <c r="D188" s="4"/>
@@ -8171,13 +8189,13 @@
       <c r="K188" s="9"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="15" t="s">
+      <c r="A189" s="38" t="s">
         <v>480</v>
       </c>
-      <c r="B189" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C189" s="24" t="s">
+      <c r="B189" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C189" s="40" t="s">
         <v>481</v>
       </c>
       <c r="D189" s="4"/>
@@ -8212,7 +8230,7 @@
       <c r="A191" s="15" t="s">
         <v>484</v>
       </c>
-      <c r="B191" s="50" t="s">
+      <c r="B191" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C191" s="24" t="s">
@@ -8231,10 +8249,10 @@
       <c r="A192" s="10" t="s">
         <v>486</v>
       </c>
-      <c r="B192" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C192" s="20" t="s">
+      <c r="B192" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C192" s="12" t="s">
         <v>487</v>
       </c>
       <c r="D192" s="4"/>
@@ -8253,7 +8271,7 @@
       <c r="B193" s="16" t="s">
         <v>68</v>
       </c>
-      <c r="C193" s="24" t="s">
+      <c r="C193" s="17" t="s">
         <v>489</v>
       </c>
       <c r="D193" s="4"/>
@@ -8266,13 +8284,13 @@
       <c r="K193" s="9"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="39" t="s">
+      <c r="A194" s="10" t="s">
         <v>490</v>
       </c>
-      <c r="B194" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C194" s="40" t="s">
+      <c r="B194" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C194" s="12" t="s">
         <v>491</v>
       </c>
       <c r="D194" s="4"/>
@@ -8285,13 +8303,13 @@
       <c r="K194" s="9"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="25" t="s">
+      <c r="A195" s="38" t="s">
         <v>492</v>
       </c>
-      <c r="B195" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C195" s="24" t="s">
+      <c r="B195" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C195" s="40" t="s">
         <v>493</v>
       </c>
       <c r="D195" s="4"/>
@@ -8304,10 +8322,10 @@
       <c r="K195" s="9"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="10" t="s">
+      <c r="A196" s="22" t="s">
         <v>494</v>
       </c>
-      <c r="B196" s="11" t="s">
+      <c r="B196" s="26" t="s">
         <v>9</v>
       </c>
       <c r="C196" s="12" t="s">
@@ -8323,13 +8341,13 @@
       <c r="K196" s="9"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="25" t="s">
+      <c r="A197" s="15" t="s">
         <v>496</v>
       </c>
       <c r="B197" s="16" t="s">
-        <v>406</v>
-      </c>
-      <c r="C197" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C197" s="24" t="s">
         <v>497</v>
       </c>
       <c r="D197" s="4"/>
@@ -8342,13 +8360,13 @@
       <c r="K197" s="9"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="10" t="s">
+      <c r="A198" s="22" t="s">
         <v>498</v>
       </c>
-      <c r="B198" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C198" s="12" t="s">
+      <c r="B198" s="11" t="s">
+        <v>408</v>
+      </c>
+      <c r="C198" s="20" t="s">
         <v>499</v>
       </c>
       <c r="D198" s="4"/>
@@ -8364,10 +8382,10 @@
       <c r="A199" s="15" t="s">
         <v>500</v>
       </c>
-      <c r="B199" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="C199" s="17" t="s">
+      <c r="B199" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C199" s="24" t="s">
         <v>501</v>
       </c>
       <c r="D199" s="4"/>
@@ -8384,7 +8402,7 @@
         <v>502</v>
       </c>
       <c r="B200" s="11" t="s">
-        <v>58</v>
+        <v>300</v>
       </c>
       <c r="C200" s="20" t="s">
         <v>503</v>
@@ -8403,9 +8421,9 @@
         <v>504</v>
       </c>
       <c r="B201" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C201" s="24" t="s">
+        <v>58</v>
+      </c>
+      <c r="C201" s="17" t="s">
         <v>505</v>
       </c>
       <c r="D201" s="4"/>
@@ -8421,8 +8439,8 @@
       <c r="A202" s="10" t="s">
         <v>506</v>
       </c>
-      <c r="B202" s="26" t="s">
-        <v>9</v>
+      <c r="B202" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C202" s="12" t="s">
         <v>507</v>
@@ -8437,13 +8455,13 @@
       <c r="K202" s="9"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="25" t="s">
+      <c r="A203" s="15" t="s">
         <v>508</v>
       </c>
-      <c r="B203" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C203" s="17" t="s">
+      <c r="B203" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C203" s="24" t="s">
         <v>509</v>
       </c>
       <c r="D203" s="4"/>
@@ -8456,13 +8474,13 @@
       <c r="K203" s="9"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="41" t="s">
+      <c r="A204" s="22" t="s">
         <v>510</v>
       </c>
-      <c r="B204" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="C204" s="48" t="s">
+      <c r="B204" s="11" t="s">
+        <v>287</v>
+      </c>
+      <c r="C204" s="20" t="s">
         <v>511</v>
       </c>
       <c r="D204" s="4"/>
@@ -8475,13 +8493,13 @@
       <c r="K204" s="9"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="34" t="s">
+      <c r="A205" s="41" t="s">
         <v>512</v>
       </c>
-      <c r="B205" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C205" s="36" t="s">
+      <c r="B205" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C205" s="48" t="s">
         <v>513</v>
       </c>
       <c r="D205" s="4"/>
@@ -8494,13 +8512,13 @@
       <c r="K205" s="9"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="39" t="s">
+      <c r="A206" s="34" t="s">
         <v>514</v>
       </c>
       <c r="B206" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C206" s="40" t="s">
+      <c r="C206" s="35" t="s">
         <v>515</v>
       </c>
       <c r="D206" s="4"/>
@@ -8513,13 +8531,13 @@
       <c r="K206" s="9"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="45" t="s">
+      <c r="A207" s="38" t="s">
         <v>516</v>
       </c>
-      <c r="B207" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C207" s="46" t="s">
+      <c r="B207" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C207" s="40" t="s">
         <v>517</v>
       </c>
       <c r="D207" s="4"/>
@@ -8532,13 +8550,13 @@
       <c r="K207" s="9"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="10" t="s">
+      <c r="A208" s="45" t="s">
         <v>518</v>
       </c>
-      <c r="B208" s="26" t="s">
+      <c r="B208" s="11" t="s">
         <v>58</v>
       </c>
-      <c r="C208" s="12" t="s">
+      <c r="C208" s="46" t="s">
         <v>519</v>
       </c>
       <c r="D208" s="4"/>
@@ -8551,13 +8569,13 @@
       <c r="K208" s="9"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="34" t="s">
+      <c r="A209" s="15" t="s">
         <v>520</v>
       </c>
-      <c r="B209" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C209" s="36" t="s">
+      <c r="B209" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C209" s="24" t="s">
         <v>521</v>
       </c>
       <c r="D209" s="4"/>
@@ -8570,13 +8588,13 @@
       <c r="K209" s="9"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="10" t="s">
+      <c r="A210" s="34" t="s">
         <v>522</v>
       </c>
-      <c r="B210" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C210" s="12" t="s">
+      <c r="B210" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C210" s="35" t="s">
         <v>523</v>
       </c>
       <c r="D210" s="4"/>
@@ -8593,9 +8611,9 @@
         <v>524</v>
       </c>
       <c r="B211" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C211" s="17" t="s">
+        <v>53</v>
+      </c>
+      <c r="C211" s="24" t="s">
         <v>525</v>
       </c>
       <c r="D211" s="4"/>
@@ -8608,14 +8626,14 @@
       <c r="K211" s="9"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="39" t="s">
+      <c r="A212" s="10" t="s">
         <v>526</v>
       </c>
-      <c r="B212" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C212" s="12" t="s">
-        <v>526</v>
+      <c r="B212" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C212" s="20" t="s">
+        <v>527</v>
       </c>
       <c r="D212" s="4"/>
       <c r="E212" s="4"/>
@@ -8627,11 +8645,11 @@
       <c r="K212" s="9"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="25" t="s">
-        <v>527</v>
-      </c>
-      <c r="B213" s="16" t="s">
-        <v>68</v>
+      <c r="A213" s="38" t="s">
+        <v>528</v>
+      </c>
+      <c r="B213" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="C213" s="24" t="s">
         <v>528</v>
@@ -8646,13 +8664,13 @@
       <c r="K213" s="9"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="10" t="s">
+      <c r="A214" s="22" t="s">
         <v>529</v>
       </c>
       <c r="B214" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C214" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C214" s="12" t="s">
         <v>530</v>
       </c>
       <c r="D214" s="4"/>
@@ -8669,9 +8687,9 @@
         <v>531</v>
       </c>
       <c r="B215" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C215" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C215" s="24" t="s">
         <v>532</v>
       </c>
       <c r="D215" s="4"/>
@@ -8687,8 +8705,8 @@
       <c r="A216" s="10" t="s">
         <v>533</v>
       </c>
-      <c r="B216" s="26" t="s">
-        <v>9</v>
+      <c r="B216" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="C216" s="20" t="s">
         <v>534</v>
@@ -8706,8 +8724,8 @@
       <c r="A217" s="15" t="s">
         <v>535</v>
       </c>
-      <c r="B217" s="35" t="s">
-        <v>9</v>
+      <c r="B217" s="16" t="s">
+        <v>287</v>
       </c>
       <c r="C217" s="17" t="s">
         <v>536</v>
@@ -8744,7 +8762,7 @@
       <c r="A219" s="15" t="s">
         <v>539</v>
       </c>
-      <c r="B219" s="35" t="s">
+      <c r="B219" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C219" s="17" t="s">
@@ -8779,13 +8797,13 @@
       <c r="K220" s="9"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="A221" s="34" t="s">
+      <c r="A221" s="15" t="s">
         <v>543</v>
       </c>
-      <c r="B221" s="35" t="s">
-        <v>298</v>
-      </c>
-      <c r="C221" s="36" t="s">
+      <c r="B221" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C221" s="17" t="s">
         <v>544</v>
       </c>
       <c r="D221" s="4"/>
@@ -8801,8 +8819,8 @@
       <c r="A222" s="10" t="s">
         <v>545</v>
       </c>
-      <c r="B222" s="11" t="s">
-        <v>58</v>
+      <c r="B222" s="26" t="s">
+        <v>9</v>
       </c>
       <c r="C222" s="20" t="s">
         <v>546</v>
@@ -8817,13 +8835,13 @@
       <c r="K222" s="9"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="A223" s="15" t="s">
+      <c r="A223" s="38" t="s">
         <v>547</v>
       </c>
-      <c r="B223" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C223" s="17" t="s">
+      <c r="B223" s="39" t="s">
+        <v>300</v>
+      </c>
+      <c r="C223" s="40" t="s">
         <v>548</v>
       </c>
       <c r="D223" s="4"/>
@@ -8840,7 +8858,7 @@
         <v>549</v>
       </c>
       <c r="B224" s="11" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="C224" s="20" t="s">
         <v>550</v>
@@ -8859,9 +8877,9 @@
         <v>551</v>
       </c>
       <c r="B225" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C225" s="24" t="s">
+        <v>87</v>
+      </c>
+      <c r="C225" s="17" t="s">
         <v>552</v>
       </c>
       <c r="D225" s="4"/>
@@ -8874,11 +8892,11 @@
       <c r="K225" s="9"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="A226" s="22" t="s">
+      <c r="A226" s="10" t="s">
         <v>553</v>
       </c>
       <c r="B226" s="11" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C226" s="20" t="s">
         <v>554</v>
@@ -8893,13 +8911,13 @@
       <c r="K226" s="9"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="A227" s="25" t="s">
+      <c r="A227" s="15" t="s">
         <v>555</v>
       </c>
       <c r="B227" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C227" s="17" t="s">
+        <v>68</v>
+      </c>
+      <c r="C227" s="24" t="s">
         <v>556</v>
       </c>
       <c r="D227" s="4"/>
@@ -8912,11 +8930,11 @@
       <c r="K227" s="9"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="A228" s="10" t="s">
+      <c r="A228" s="22" t="s">
         <v>557</v>
       </c>
       <c r="B228" s="11" t="s">
-        <v>9</v>
+        <v>58</v>
       </c>
       <c r="C228" s="20" t="s">
         <v>558</v>
@@ -8931,13 +8949,13 @@
       <c r="K228" s="9"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="A229" s="34" t="s">
+      <c r="A229" s="25" t="s">
         <v>559</v>
       </c>
-      <c r="B229" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C229" s="36" t="s">
+      <c r="B229" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C229" s="17" t="s">
         <v>560</v>
       </c>
       <c r="D229" s="4"/>
@@ -8954,9 +8972,9 @@
         <v>561</v>
       </c>
       <c r="B230" s="11" t="s">
-        <v>58</v>
-      </c>
-      <c r="C230" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C230" s="20" t="s">
         <v>562</v>
       </c>
       <c r="D230" s="4"/>
@@ -8969,13 +8987,13 @@
       <c r="K230" s="9"/>
     </row>
     <row r="231" ht="15.75" customHeight="1">
-      <c r="A231" s="15" t="s">
+      <c r="A231" s="38" t="s">
         <v>563</v>
       </c>
-      <c r="B231" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C231" s="24" t="s">
+      <c r="B231" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C231" s="40" t="s">
         <v>564</v>
       </c>
       <c r="D231" s="4"/>
@@ -8988,13 +9006,13 @@
       <c r="K231" s="9"/>
     </row>
     <row r="232" ht="15.75" customHeight="1">
-      <c r="A232" s="39" t="s">
+      <c r="A232" s="10" t="s">
         <v>565</v>
       </c>
-      <c r="B232" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C232" s="40" t="s">
+      <c r="B232" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C232" s="12" t="s">
         <v>566</v>
       </c>
       <c r="D232" s="4"/>
@@ -9007,13 +9025,13 @@
       <c r="K232" s="9"/>
     </row>
     <row r="233" ht="15.75" customHeight="1">
-      <c r="A233" s="34" t="s">
+      <c r="A233" s="15" t="s">
         <v>567</v>
       </c>
-      <c r="B233" s="35" t="s">
-        <v>68</v>
-      </c>
-      <c r="C233" s="36" t="s">
+      <c r="B233" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C233" s="24" t="s">
         <v>568</v>
       </c>
       <c r="D233" s="4"/>
@@ -9026,13 +9044,13 @@
       <c r="K233" s="9"/>
     </row>
     <row r="234" ht="15.75" customHeight="1">
-      <c r="A234" s="10" t="s">
+      <c r="A234" s="34" t="s">
         <v>569</v>
       </c>
-      <c r="B234" s="11" t="s">
-        <v>137</v>
-      </c>
-      <c r="C234" s="12" t="s">
+      <c r="B234" s="26" t="s">
+        <v>9</v>
+      </c>
+      <c r="C234" s="35" t="s">
         <v>570</v>
       </c>
       <c r="D234" s="4"/>
@@ -9045,14 +9063,14 @@
       <c r="K234" s="9"/>
     </row>
     <row r="235" ht="15.75" customHeight="1">
-      <c r="A235" s="15" t="s">
-        <v>508</v>
-      </c>
-      <c r="B235" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C235" s="24" t="s">
+      <c r="A235" s="38" t="s">
         <v>571</v>
+      </c>
+      <c r="B235" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C235" s="40" t="s">
+        <v>572</v>
       </c>
       <c r="D235" s="4"/>
       <c r="E235" s="4"/>
@@ -9064,14 +9082,14 @@
       <c r="K235" s="9"/>
     </row>
     <row r="236" ht="15.75" customHeight="1">
-      <c r="A236" s="39" t="s">
-        <v>572</v>
-      </c>
-      <c r="B236" s="26" t="s">
-        <v>9</v>
-      </c>
-      <c r="C236" s="40" t="s">
+      <c r="A236" s="10" t="s">
         <v>573</v>
+      </c>
+      <c r="B236" s="11" t="s">
+        <v>141</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>574</v>
       </c>
       <c r="D236" s="4"/>
       <c r="E236" s="4"/>
@@ -9084,9 +9102,9 @@
     </row>
     <row r="237" ht="15.75" customHeight="1">
       <c r="A237" s="15" t="s">
-        <v>574</v>
-      </c>
-      <c r="B237" s="35" t="s">
+        <v>510</v>
+      </c>
+      <c r="B237" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C237" s="24" t="s">
@@ -9102,13 +9120,13 @@
       <c r="K237" s="9"/>
     </row>
     <row r="238" ht="15.75" customHeight="1">
-      <c r="A238" s="10" t="s">
+      <c r="A238" s="34" t="s">
         <v>576</v>
       </c>
       <c r="B238" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C238" s="12" t="s">
+        <v>9</v>
+      </c>
+      <c r="C238" s="35" t="s">
         <v>577</v>
       </c>
       <c r="D238" s="4"/>
@@ -9121,10 +9139,10 @@
       <c r="K238" s="9"/>
     </row>
     <row r="239" ht="15.75" customHeight="1">
-      <c r="A239" s="25" t="s">
+      <c r="A239" s="15" t="s">
         <v>578</v>
       </c>
-      <c r="B239" s="35" t="s">
+      <c r="B239" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C239" s="24" t="s">
@@ -9143,10 +9161,10 @@
       <c r="A240" s="10" t="s">
         <v>580</v>
       </c>
-      <c r="B240" s="11" t="s">
+      <c r="B240" s="26" t="s">
         <v>68</v>
       </c>
-      <c r="C240" s="20" t="s">
+      <c r="C240" s="12" t="s">
         <v>581</v>
       </c>
       <c r="D240" s="4"/>
@@ -9159,13 +9177,13 @@
       <c r="K240" s="9"/>
     </row>
     <row r="241" ht="15.75" customHeight="1">
-      <c r="A241" s="15" t="s">
+      <c r="A241" s="25" t="s">
         <v>582</v>
       </c>
-      <c r="B241" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C241" s="17" t="s">
+      <c r="B241" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C241" s="24" t="s">
         <v>583</v>
       </c>
       <c r="D241" s="4"/>
@@ -9184,7 +9202,7 @@
       <c r="B242" s="11" t="s">
         <v>68</v>
       </c>
-      <c r="C242" s="12" t="s">
+      <c r="C242" s="20" t="s">
         <v>585</v>
       </c>
       <c r="D242" s="4"/>
@@ -9220,7 +9238,7 @@
         <v>588</v>
       </c>
       <c r="B244" s="11" t="s">
-        <v>58</v>
+        <v>68</v>
       </c>
       <c r="C244" s="12" t="s">
         <v>589</v>
@@ -9235,13 +9253,13 @@
       <c r="K244" s="9"/>
     </row>
     <row r="245" ht="15.75" customHeight="1">
-      <c r="A245" s="34" t="s">
+      <c r="A245" s="15" t="s">
         <v>590</v>
       </c>
-      <c r="B245" s="35" t="s">
-        <v>9</v>
-      </c>
-      <c r="C245" s="36" t="s">
+      <c r="B245" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C245" s="17" t="s">
         <v>591</v>
       </c>
       <c r="D245" s="4"/>
@@ -9254,11 +9272,11 @@
       <c r="K245" s="9"/>
     </row>
     <row r="246" ht="15.75" customHeight="1">
-      <c r="A246" s="22" t="s">
+      <c r="A246" s="10" t="s">
         <v>592</v>
       </c>
-      <c r="B246" s="26" t="s">
-        <v>9</v>
+      <c r="B246" s="11" t="s">
+        <v>58</v>
       </c>
       <c r="C246" s="12" t="s">
         <v>593</v>
@@ -9277,7 +9295,7 @@
         <v>594</v>
       </c>
       <c r="B247" s="16" t="s">
-        <v>68</v>
+        <v>9</v>
       </c>
       <c r="C247" s="24" t="s">
         <v>595</v>
@@ -9292,13 +9310,13 @@
       <c r="K247" s="9"/>
     </row>
     <row r="248" ht="15.75" customHeight="1">
-      <c r="A248" s="10" t="s">
+      <c r="A248" s="34" t="s">
         <v>596</v>
       </c>
       <c r="B248" s="26" t="s">
         <v>9</v>
       </c>
-      <c r="C248" s="20" t="s">
+      <c r="C248" s="35" t="s">
         <v>597</v>
       </c>
       <c r="D248" s="4"/>
@@ -9311,11 +9329,11 @@
       <c r="K248" s="9"/>
     </row>
     <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="15" t="s">
+      <c r="A249" s="25" t="s">
         <v>598</v>
       </c>
-      <c r="B249" s="16" t="s">
-        <v>68</v>
+      <c r="B249" s="39" t="s">
+        <v>9</v>
       </c>
       <c r="C249" s="24" t="s">
         <v>599</v>
@@ -9333,8 +9351,8 @@
       <c r="A250" s="10" t="s">
         <v>600</v>
       </c>
-      <c r="B250" s="26" t="s">
-        <v>9</v>
+      <c r="B250" s="11" t="s">
+        <v>68</v>
       </c>
       <c r="C250" s="12" t="s">
         <v>601</v>
@@ -9352,10 +9370,10 @@
       <c r="A251" s="15" t="s">
         <v>602</v>
       </c>
-      <c r="B251" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C251" s="24" t="s">
+      <c r="B251" s="39" t="s">
+        <v>9</v>
+      </c>
+      <c r="C251" s="17" t="s">
         <v>603</v>
       </c>
       <c r="D251" s="4"/>
@@ -9372,9 +9390,9 @@
         <v>604</v>
       </c>
       <c r="B252" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="C252" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C252" s="12" t="s">
         <v>605</v>
       </c>
       <c r="D252" s="4"/>
@@ -9390,7 +9408,7 @@
       <c r="A253" s="15" t="s">
         <v>606</v>
       </c>
-      <c r="B253" s="35" t="s">
+      <c r="B253" s="39" t="s">
         <v>9</v>
       </c>
       <c r="C253" s="24" t="s">
@@ -9409,8 +9427,8 @@
       <c r="A254" s="10" t="s">
         <v>608</v>
       </c>
-      <c r="B254" s="11" t="s">
-        <v>68</v>
+      <c r="B254" s="50" t="s">
+        <v>9</v>
       </c>
       <c r="C254" s="12" t="s">
         <v>609</v>
@@ -9425,13 +9443,13 @@
       <c r="K254" s="9"/>
     </row>
     <row r="255" ht="15.75" customHeight="1">
-      <c r="A255" s="34" t="s">
+      <c r="A255" s="15" t="s">
         <v>610</v>
       </c>
-      <c r="B255" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="C255" s="36" t="s">
+      <c r="B255" s="16" t="s">
+        <v>287</v>
+      </c>
+      <c r="C255" s="17" t="s">
         <v>611</v>
       </c>
       <c r="D255" s="4"/>
@@ -9448,7 +9466,7 @@
         <v>612</v>
       </c>
       <c r="B256" s="26" t="s">
-        <v>361</v>
+        <v>9</v>
       </c>
       <c r="C256" s="12" t="s">
         <v>613</v>
@@ -9463,13 +9481,13 @@
       <c r="K256" s="9"/>
     </row>
     <row r="257" ht="15.75" customHeight="1">
-      <c r="A257" s="34" t="s">
+      <c r="A257" s="15" t="s">
         <v>614</v>
       </c>
-      <c r="B257" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="C257" s="36" t="s">
+      <c r="B257" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C257" s="24" t="s">
         <v>615</v>
       </c>
       <c r="D257" s="4"/>
@@ -9482,13 +9500,13 @@
       <c r="K257" s="9"/>
     </row>
     <row r="258" ht="15.75" customHeight="1">
-      <c r="A258" s="10" t="s">
+      <c r="A258" s="34" t="s">
         <v>616</v>
       </c>
-      <c r="B258" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C258" s="12" t="s">
+      <c r="B258" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="C258" s="35" t="s">
         <v>617</v>
       </c>
       <c r="D258" s="4"/>
@@ -9504,8 +9522,8 @@
       <c r="A259" s="15" t="s">
         <v>618</v>
       </c>
-      <c r="B259" s="50" t="s">
-        <v>9</v>
+      <c r="B259" s="39" t="s">
+        <v>363</v>
       </c>
       <c r="C259" s="24" t="s">
         <v>619</v>
@@ -9520,13 +9538,13 @@
       <c r="K259" s="9"/>
     </row>
     <row r="260" ht="15.75" customHeight="1">
-      <c r="A260" s="10" t="s">
+      <c r="A260" s="34" t="s">
         <v>620</v>
       </c>
-      <c r="B260" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C260" s="12" t="s">
+      <c r="B260" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="C260" s="35" t="s">
         <v>621</v>
       </c>
       <c r="D260" s="4"/>
@@ -9542,10 +9560,10 @@
       <c r="A261" s="15" t="s">
         <v>622</v>
       </c>
-      <c r="B261" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C261" s="17" t="s">
+      <c r="B261" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C261" s="24" t="s">
         <v>623</v>
       </c>
       <c r="D261" s="4"/>
@@ -9558,13 +9576,13 @@
       <c r="K261" s="9"/>
     </row>
     <row r="262" ht="15.75" customHeight="1">
-      <c r="A262" s="22" t="s">
+      <c r="A262" s="10" t="s">
         <v>624</v>
       </c>
-      <c r="B262" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="C262" s="20" t="s">
+      <c r="B262" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C262" s="12" t="s">
         <v>625</v>
       </c>
       <c r="D262" s="4"/>
@@ -9580,10 +9598,10 @@
       <c r="A263" s="15" t="s">
         <v>626</v>
       </c>
-      <c r="B263" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C263" s="17" t="s">
+      <c r="B263" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C263" s="24" t="s">
         <v>627</v>
       </c>
       <c r="D263" s="4"/>
@@ -9596,13 +9614,13 @@
       <c r="K263" s="9"/>
     </row>
     <row r="264" ht="15.75" customHeight="1">
-      <c r="A264" s="39" t="s">
+      <c r="A264" s="10" t="s">
         <v>628</v>
       </c>
-      <c r="B264" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C264" s="40" t="s">
+      <c r="B264" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C264" s="20" t="s">
         <v>629</v>
       </c>
       <c r="D264" s="4"/>
@@ -9615,13 +9633,13 @@
       <c r="K264" s="9"/>
     </row>
     <row r="265" ht="15.75" customHeight="1">
-      <c r="A265" s="15" t="s">
+      <c r="A265" s="25" t="s">
         <v>630</v>
       </c>
       <c r="B265" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C265" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="C265" s="17" t="s">
         <v>631</v>
       </c>
       <c r="D265" s="4"/>
@@ -9634,13 +9652,13 @@
       <c r="K265" s="9"/>
     </row>
     <row r="266" ht="15.75" customHeight="1">
-      <c r="A266" s="39" t="s">
+      <c r="A266" s="10" t="s">
         <v>632</v>
       </c>
-      <c r="B266" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C266" s="40" t="s">
+      <c r="B266" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C266" s="20" t="s">
         <v>633</v>
       </c>
       <c r="D266" s="4"/>
@@ -9653,13 +9671,13 @@
       <c r="K266" s="9"/>
     </row>
     <row r="267" ht="15.75" customHeight="1">
-      <c r="A267" s="15" t="s">
+      <c r="A267" s="38" t="s">
         <v>634</v>
       </c>
-      <c r="B267" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C267" s="17" t="s">
+      <c r="B267" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C267" s="40" t="s">
         <v>635</v>
       </c>
       <c r="D267" s="4"/>
@@ -9672,13 +9690,13 @@
       <c r="K267" s="9"/>
     </row>
     <row r="268" ht="15.75" customHeight="1">
-      <c r="A268" s="39" t="s">
+      <c r="A268" s="10" t="s">
         <v>636</v>
       </c>
-      <c r="B268" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="C268" s="40" t="s">
+      <c r="B268" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C268" s="12" t="s">
         <v>637</v>
       </c>
       <c r="D268" s="4"/>
@@ -9691,13 +9709,13 @@
       <c r="K268" s="9"/>
     </row>
     <row r="269" ht="15.75" customHeight="1">
-      <c r="A269" s="15" t="s">
+      <c r="A269" s="38" t="s">
         <v>638</v>
       </c>
-      <c r="B269" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C269" s="24" t="s">
+      <c r="B269" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C269" s="40" t="s">
         <v>639</v>
       </c>
       <c r="D269" s="4"/>
@@ -9713,10 +9731,10 @@
       <c r="A270" s="10" t="s">
         <v>640</v>
       </c>
-      <c r="B270" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C270" s="12" t="s">
+      <c r="B270" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C270" s="20" t="s">
         <v>641</v>
       </c>
       <c r="D270" s="4"/>
@@ -9729,13 +9747,13 @@
       <c r="K270" s="9"/>
     </row>
     <row r="271" ht="15.75" customHeight="1">
-      <c r="A271" s="15" t="s">
+      <c r="A271" s="38" t="s">
         <v>642</v>
       </c>
-      <c r="B271" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C271" s="24" t="s">
+      <c r="B271" s="39" t="s">
+        <v>87</v>
+      </c>
+      <c r="C271" s="40" t="s">
         <v>643</v>
       </c>
       <c r="D271" s="4"/>
@@ -9752,7 +9770,7 @@
         <v>644</v>
       </c>
       <c r="B272" s="11" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C272" s="12" t="s">
         <v>645</v>
@@ -9770,7 +9788,7 @@
       <c r="A273" s="15" t="s">
         <v>646</v>
       </c>
-      <c r="B273" s="50" t="s">
+      <c r="B273" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C273" s="24" t="s">
@@ -9789,7 +9807,7 @@
       <c r="A274" s="10" t="s">
         <v>648</v>
       </c>
-      <c r="B274" s="11" t="s">
+      <c r="B274" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C274" s="12" t="s">
@@ -9824,13 +9842,13 @@
       <c r="K275" s="9"/>
     </row>
     <row r="276" ht="15.75" customHeight="1">
-      <c r="A276" s="39" t="s">
+      <c r="A276" s="10" t="s">
         <v>652</v>
       </c>
-      <c r="B276" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C276" s="40" t="s">
+      <c r="B276" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C276" s="12" t="s">
         <v>653</v>
       </c>
       <c r="D276" s="4"/>
@@ -9846,7 +9864,7 @@
       <c r="A277" s="15" t="s">
         <v>654</v>
       </c>
-      <c r="B277" s="50" t="s">
+      <c r="B277" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C277" s="24" t="s">
@@ -9865,7 +9883,7 @@
       <c r="A278" s="10" t="s">
         <v>656</v>
       </c>
-      <c r="B278" s="51" t="s">
+      <c r="B278" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C278" s="12" t="s">
@@ -9881,13 +9899,13 @@
       <c r="K278" s="9"/>
     </row>
     <row r="279" ht="15.75" customHeight="1">
-      <c r="A279" s="25" t="s">
+      <c r="A279" s="38" t="s">
         <v>658</v>
       </c>
-      <c r="B279" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C279" s="24" t="s">
+      <c r="B279" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C279" s="40" t="s">
         <v>659</v>
       </c>
       <c r="D279" s="4"/>
@@ -9903,7 +9921,7 @@
       <c r="A280" s="10" t="s">
         <v>660</v>
       </c>
-      <c r="B280" s="51" t="s">
+      <c r="B280" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C280" s="12" t="s">
@@ -9922,7 +9940,7 @@
       <c r="A281" s="15" t="s">
         <v>662</v>
       </c>
-      <c r="B281" s="50" t="s">
+      <c r="B281" s="51" t="s">
         <v>9</v>
       </c>
       <c r="C281" s="24" t="s">
@@ -9938,13 +9956,13 @@
       <c r="K281" s="9"/>
     </row>
     <row r="282" ht="15.75" customHeight="1">
-      <c r="A282" s="10" t="s">
+      <c r="A282" s="22" t="s">
         <v>664</v>
       </c>
       <c r="B282" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="C282" s="20" t="s">
+        <v>68</v>
+      </c>
+      <c r="C282" s="12" t="s">
         <v>665</v>
       </c>
       <c r="D282" s="4"/>
@@ -9960,10 +9978,10 @@
       <c r="A283" s="15" t="s">
         <v>666</v>
       </c>
-      <c r="B283" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="C283" s="17" t="s">
+      <c r="B283" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C283" s="24" t="s">
         <v>667</v>
       </c>
       <c r="D283" s="4"/>
@@ -9979,7 +9997,7 @@
       <c r="A284" s="10" t="s">
         <v>668</v>
       </c>
-      <c r="B284" s="11" t="s">
+      <c r="B284" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C284" s="12" t="s">
@@ -9998,8 +10016,8 @@
       <c r="A285" s="15" t="s">
         <v>670</v>
       </c>
-      <c r="B285" s="50" t="s">
-        <v>9</v>
+      <c r="B285" s="16" t="s">
+        <v>287</v>
       </c>
       <c r="C285" s="17" t="s">
         <v>671</v>
@@ -10014,11 +10032,11 @@
       <c r="K285" s="9"/>
     </row>
     <row r="286" ht="15.75" customHeight="1">
-      <c r="A286" s="22" t="s">
+      <c r="A286" s="10" t="s">
         <v>672</v>
       </c>
-      <c r="B286" s="51" t="s">
-        <v>9</v>
+      <c r="B286" s="11" t="s">
+        <v>363</v>
       </c>
       <c r="C286" s="20" t="s">
         <v>673</v>
@@ -10036,7 +10054,7 @@
       <c r="A287" s="15" t="s">
         <v>674</v>
       </c>
-      <c r="B287" s="50" t="s">
+      <c r="B287" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C287" s="24" t="s">
@@ -10055,10 +10073,10 @@
       <c r="A288" s="10" t="s">
         <v>676</v>
       </c>
-      <c r="B288" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C288" s="12" t="s">
+      <c r="B288" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C288" s="20" t="s">
         <v>677</v>
       </c>
       <c r="D288" s="4"/>
@@ -10074,7 +10092,7 @@
       <c r="A289" s="25" t="s">
         <v>678</v>
       </c>
-      <c r="B289" s="50" t="s">
+      <c r="B289" s="51" t="s">
         <v>9</v>
       </c>
       <c r="C289" s="17" t="s">
@@ -10093,8 +10111,8 @@
       <c r="A290" s="10" t="s">
         <v>680</v>
       </c>
-      <c r="B290" s="11" t="s">
-        <v>83</v>
+      <c r="B290" s="50" t="s">
+        <v>9</v>
       </c>
       <c r="C290" s="12" t="s">
         <v>681</v>
@@ -10113,9 +10131,9 @@
         <v>682</v>
       </c>
       <c r="B291" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C291" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C291" s="24" t="s">
         <v>683</v>
       </c>
       <c r="D291" s="4"/>
@@ -10128,13 +10146,13 @@
       <c r="K291" s="9"/>
     </row>
     <row r="292" ht="15.75" customHeight="1">
-      <c r="A292" s="39" t="s">
+      <c r="A292" s="22" t="s">
         <v>684</v>
       </c>
-      <c r="B292" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="C292" s="40" t="s">
+      <c r="B292" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C292" s="20" t="s">
         <v>685</v>
       </c>
       <c r="D292" s="4"/>
@@ -10150,8 +10168,8 @@
       <c r="A293" s="15" t="s">
         <v>686</v>
       </c>
-      <c r="B293" s="35" t="s">
-        <v>361</v>
+      <c r="B293" s="16" t="s">
+        <v>87</v>
       </c>
       <c r="C293" s="24" t="s">
         <v>687</v>
@@ -10169,10 +10187,10 @@
       <c r="A294" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="B294" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="C294" s="12" t="s">
+      <c r="B294" s="11" t="s">
+        <v>58</v>
+      </c>
+      <c r="C294" s="20" t="s">
         <v>689</v>
       </c>
       <c r="D294" s="4"/>
@@ -10185,13 +10203,13 @@
       <c r="K294" s="9"/>
     </row>
     <row r="295" ht="15.75" customHeight="1">
-      <c r="A295" s="15" t="s">
+      <c r="A295" s="38" t="s">
         <v>690</v>
       </c>
-      <c r="B295" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="C295" s="24" t="s">
+      <c r="B295" s="39" t="s">
+        <v>363</v>
+      </c>
+      <c r="C295" s="40" t="s">
         <v>691</v>
       </c>
       <c r="D295" s="4"/>
@@ -10204,13 +10222,13 @@
       <c r="K295" s="9"/>
     </row>
     <row r="296" ht="15.75" customHeight="1">
-      <c r="A296" s="39" t="s">
+      <c r="A296" s="10" t="s">
         <v>692</v>
       </c>
       <c r="B296" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C296" s="40" t="s">
+        <v>363</v>
+      </c>
+      <c r="C296" s="12" t="s">
         <v>693</v>
       </c>
       <c r="D296" s="4"/>
@@ -10226,8 +10244,8 @@
       <c r="A297" s="15" t="s">
         <v>694</v>
       </c>
-      <c r="B297" s="50" t="s">
-        <v>9</v>
+      <c r="B297" s="39" t="s">
+        <v>363</v>
       </c>
       <c r="C297" s="24" t="s">
         <v>695</v>
@@ -10242,13 +10260,13 @@
       <c r="K297" s="9"/>
     </row>
     <row r="298" ht="15.75" customHeight="1">
-      <c r="A298" s="39" t="s">
+      <c r="A298" s="10" t="s">
         <v>696</v>
       </c>
       <c r="B298" s="26" t="s">
-        <v>68</v>
-      </c>
-      <c r="C298" s="40" t="s">
+        <v>363</v>
+      </c>
+      <c r="C298" s="12" t="s">
         <v>697</v>
       </c>
       <c r="D298" s="4"/>
@@ -10261,13 +10279,13 @@
       <c r="K298" s="9"/>
     </row>
     <row r="299" ht="15.75" customHeight="1">
-      <c r="A299" s="34" t="s">
+      <c r="A299" s="38" t="s">
         <v>698</v>
       </c>
-      <c r="B299" s="35" t="s">
-        <v>361</v>
-      </c>
-      <c r="C299" s="36" t="s">
+      <c r="B299" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C299" s="40" t="s">
         <v>699</v>
       </c>
       <c r="D299" s="4"/>
@@ -10280,13 +10298,13 @@
       <c r="K299" s="9"/>
     </row>
     <row r="300" ht="15.75" customHeight="1">
-      <c r="A300" s="39" t="s">
+      <c r="A300" s="10" t="s">
         <v>700</v>
       </c>
-      <c r="B300" s="26" t="s">
-        <v>361</v>
-      </c>
-      <c r="C300" s="40" t="s">
+      <c r="B300" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C300" s="12" t="s">
         <v>701</v>
       </c>
       <c r="D300" s="4"/>
@@ -10299,13 +10317,13 @@
       <c r="K300" s="9"/>
     </row>
     <row r="301" ht="15.75" customHeight="1">
-      <c r="A301" s="15" t="s">
+      <c r="A301" s="38" t="s">
         <v>702</v>
       </c>
-      <c r="B301" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C301" s="17" t="s">
+      <c r="B301" s="39" t="s">
+        <v>68</v>
+      </c>
+      <c r="C301" s="40" t="s">
         <v>703</v>
       </c>
       <c r="D301" s="4"/>
@@ -10318,13 +10336,13 @@
       <c r="K301" s="9"/>
     </row>
     <row r="302" ht="15.75" customHeight="1">
-      <c r="A302" s="10" t="s">
+      <c r="A302" s="34" t="s">
         <v>704</v>
       </c>
-      <c r="B302" s="11" t="s">
-        <v>285</v>
-      </c>
-      <c r="C302" s="20" t="s">
+      <c r="B302" s="26" t="s">
+        <v>363</v>
+      </c>
+      <c r="C302" s="35" t="s">
         <v>705</v>
       </c>
       <c r="D302" s="4"/>
@@ -10337,13 +10355,13 @@
       <c r="K302" s="9"/>
     </row>
     <row r="303" ht="15.75" customHeight="1">
-      <c r="A303" s="15" t="s">
+      <c r="A303" s="38" t="s">
         <v>706</v>
       </c>
-      <c r="B303" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C303" s="24" t="s">
+      <c r="B303" s="39" t="s">
+        <v>363</v>
+      </c>
+      <c r="C303" s="40" t="s">
         <v>707</v>
       </c>
       <c r="D303" s="4"/>
@@ -10356,13 +10374,13 @@
       <c r="K303" s="9"/>
     </row>
     <row r="304" ht="15.75" customHeight="1">
-      <c r="A304" s="41" t="s">
+      <c r="A304" s="10" t="s">
         <v>708</v>
       </c>
       <c r="B304" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C304" s="42" t="s">
+        <v>287</v>
+      </c>
+      <c r="C304" s="20" t="s">
         <v>709</v>
       </c>
       <c r="D304" s="4"/>
@@ -10379,9 +10397,9 @@
         <v>710</v>
       </c>
       <c r="B305" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C305" s="24" t="s">
+        <v>287</v>
+      </c>
+      <c r="C305" s="17" t="s">
         <v>711</v>
       </c>
       <c r="D305" s="4"/>
@@ -10397,8 +10415,8 @@
       <c r="A306" s="10" t="s">
         <v>712</v>
       </c>
-      <c r="B306" s="11" t="s">
-        <v>48</v>
+      <c r="B306" s="50" t="s">
+        <v>9</v>
       </c>
       <c r="C306" s="12" t="s">
         <v>713</v>
@@ -10413,13 +10431,13 @@
       <c r="K306" s="9"/>
     </row>
     <row r="307" ht="15.75" customHeight="1">
-      <c r="A307" s="34" t="s">
+      <c r="A307" s="41" t="s">
         <v>714</v>
       </c>
       <c r="B307" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C307" s="24" t="s">
+      <c r="C307" s="42" t="s">
         <v>715</v>
       </c>
       <c r="D307" s="4"/>
@@ -10432,7 +10450,7 @@
       <c r="K307" s="9"/>
     </row>
     <row r="308" ht="15.75" customHeight="1">
-      <c r="A308" s="39" t="s">
+      <c r="A308" s="10" t="s">
         <v>716</v>
       </c>
       <c r="B308" s="11" t="s">
@@ -10457,7 +10475,7 @@
       <c r="B309" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C309" s="17" t="s">
+      <c r="C309" s="24" t="s">
         <v>719</v>
       </c>
       <c r="D309" s="4"/>
@@ -10470,7 +10488,7 @@
       <c r="K309" s="9"/>
     </row>
     <row r="310" ht="15.75" customHeight="1">
-      <c r="A310" s="10" t="s">
+      <c r="A310" s="34" t="s">
         <v>720</v>
       </c>
       <c r="B310" s="11" t="s">
@@ -10489,11 +10507,11 @@
       <c r="K310" s="9"/>
     </row>
     <row r="311" ht="15.75" customHeight="1">
-      <c r="A311" s="15" t="s">
+      <c r="A311" s="38" t="s">
         <v>722</v>
       </c>
       <c r="B311" s="16" t="s">
-        <v>406</v>
+        <v>48</v>
       </c>
       <c r="C311" s="24" t="s">
         <v>723</v>
@@ -10514,7 +10532,7 @@
       <c r="B312" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C312" s="12" t="s">
+      <c r="C312" s="20" t="s">
         <v>725</v>
       </c>
       <c r="D312" s="4"/>
@@ -10527,13 +10545,13 @@
       <c r="K312" s="9"/>
     </row>
     <row r="313" ht="15.75" customHeight="1">
-      <c r="A313" s="34" t="s">
+      <c r="A313" s="15" t="s">
         <v>726</v>
       </c>
       <c r="B313" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C313" s="36" t="s">
+      <c r="C313" s="24" t="s">
         <v>727</v>
       </c>
       <c r="D313" s="4"/>
@@ -10546,13 +10564,13 @@
       <c r="K313" s="9"/>
     </row>
     <row r="314" ht="15.75" customHeight="1">
-      <c r="A314" s="39" t="s">
+      <c r="A314" s="10" t="s">
         <v>728</v>
       </c>
       <c r="B314" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C314" s="40" t="s">
+        <v>408</v>
+      </c>
+      <c r="C314" s="12" t="s">
         <v>729</v>
       </c>
       <c r="D314" s="4"/>
@@ -10571,7 +10589,7 @@
       <c r="B315" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C315" s="17" t="s">
+      <c r="C315" s="24" t="s">
         <v>731</v>
       </c>
       <c r="D315" s="4"/>
@@ -10584,13 +10602,13 @@
       <c r="K315" s="9"/>
     </row>
     <row r="316" ht="15.75" customHeight="1">
-      <c r="A316" s="10" t="s">
+      <c r="A316" s="34" t="s">
         <v>732</v>
       </c>
       <c r="B316" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C316" s="20" t="s">
+      <c r="C316" s="35" t="s">
         <v>733</v>
       </c>
       <c r="D316" s="4"/>
@@ -10603,13 +10621,13 @@
       <c r="K316" s="9"/>
     </row>
     <row r="317" ht="15.75" customHeight="1">
-      <c r="A317" s="34" t="s">
+      <c r="A317" s="38" t="s">
         <v>734</v>
       </c>
       <c r="B317" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C317" s="36" t="s">
+      <c r="C317" s="40" t="s">
         <v>735</v>
       </c>
       <c r="D317" s="4"/>
@@ -10628,7 +10646,7 @@
       <c r="B318" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C318" s="12" t="s">
+      <c r="C318" s="20" t="s">
         <v>737</v>
       </c>
       <c r="D318" s="4"/>
@@ -10641,13 +10659,13 @@
       <c r="K318" s="9"/>
     </row>
     <row r="319" ht="15.75" customHeight="1">
-      <c r="A319" s="34" t="s">
+      <c r="A319" s="15" t="s">
         <v>738</v>
       </c>
       <c r="B319" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C319" s="36" t="s">
+      <c r="C319" s="17" t="s">
         <v>739</v>
       </c>
       <c r="D319" s="4"/>
@@ -10660,13 +10678,13 @@
       <c r="K319" s="9"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="39" t="s">
+      <c r="A320" s="34" t="s">
         <v>740</v>
       </c>
       <c r="B320" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C320" s="40" t="s">
+      <c r="C320" s="35" t="s">
         <v>741</v>
       </c>
       <c r="D320" s="4"/>
@@ -10698,13 +10716,13 @@
       <c r="K321" s="9"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="10" t="s">
+      <c r="A322" s="34" t="s">
         <v>744</v>
       </c>
       <c r="B322" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C322" s="12" t="s">
+      <c r="C322" s="35" t="s">
         <v>745</v>
       </c>
       <c r="D322" s="4"/>
@@ -10717,13 +10735,13 @@
       <c r="K322" s="9"/>
     </row>
     <row r="323" ht="15.75" customHeight="1">
-      <c r="A323" s="34" t="s">
+      <c r="A323" s="38" t="s">
         <v>746</v>
       </c>
       <c r="B323" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C323" s="36" t="s">
+      <c r="C323" s="40" t="s">
         <v>747</v>
       </c>
       <c r="D323" s="4"/>
@@ -10736,13 +10754,13 @@
       <c r="K323" s="9"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="39" t="s">
+      <c r="A324" s="10" t="s">
         <v>748</v>
       </c>
       <c r="B324" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C324" s="40" t="s">
+      <c r="C324" s="12" t="s">
         <v>749</v>
       </c>
       <c r="D324" s="4"/>
@@ -10774,13 +10792,13 @@
       <c r="K325" s="9"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="39" t="s">
+      <c r="A326" s="34" t="s">
         <v>752</v>
       </c>
       <c r="B326" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C326" s="40" t="s">
+      <c r="C326" s="35" t="s">
         <v>753</v>
       </c>
       <c r="D326" s="4"/>
@@ -10793,13 +10811,13 @@
       <c r="K326" s="9"/>
     </row>
     <row r="327" ht="15.75" customHeight="1">
-      <c r="A327" s="34" t="s">
+      <c r="A327" s="38" t="s">
         <v>754</v>
       </c>
       <c r="B327" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C327" s="36" t="s">
+      <c r="C327" s="40" t="s">
         <v>755</v>
       </c>
       <c r="D327" s="4"/>
@@ -10816,7 +10834,7 @@
         <v>756</v>
       </c>
       <c r="B328" s="11" t="s">
-        <v>9</v>
+        <v>48</v>
       </c>
       <c r="C328" s="12" t="s">
         <v>757</v>
@@ -10831,13 +10849,13 @@
       <c r="K328" s="9"/>
     </row>
     <row r="329" ht="15.75" customHeight="1">
-      <c r="A329" s="15" t="s">
+      <c r="A329" s="38" t="s">
         <v>758</v>
       </c>
       <c r="B329" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C329" s="17" t="s">
+      <c r="C329" s="40" t="s">
         <v>759</v>
       </c>
       <c r="D329" s="4"/>
@@ -10850,13 +10868,13 @@
       <c r="K329" s="9"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="39" t="s">
+      <c r="A330" s="34" t="s">
         <v>760</v>
       </c>
       <c r="B330" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C330" s="20" t="s">
+      <c r="C330" s="35" t="s">
         <v>761</v>
       </c>
       <c r="D330" s="4"/>
@@ -10873,9 +10891,9 @@
         <v>762</v>
       </c>
       <c r="B331" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C331" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C331" s="24" t="s">
         <v>763</v>
       </c>
       <c r="D331" s="4"/>
@@ -10888,13 +10906,13 @@
       <c r="K331" s="9"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="39" t="s">
+      <c r="A332" s="10" t="s">
         <v>764</v>
       </c>
       <c r="B332" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C332" s="40" t="s">
+      <c r="C332" s="20" t="s">
         <v>765</v>
       </c>
       <c r="D332" s="4"/>
@@ -10907,14 +10925,14 @@
       <c r="K332" s="9"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="15" t="s">
+      <c r="A333" s="38" t="s">
         <v>766</v>
       </c>
       <c r="B333" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C333" s="24" t="s">
-        <v>765</v>
+      <c r="C333" s="17" t="s">
+        <v>767</v>
       </c>
       <c r="D333" s="4"/>
       <c r="E333" s="4"/>
@@ -10927,13 +10945,13 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="10" t="s">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="B334" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C334" s="20" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
@@ -10945,14 +10963,14 @@
       <c r="K334" s="9"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="15" t="s">
-        <v>769</v>
+      <c r="A335" s="38" t="s">
+        <v>770</v>
       </c>
       <c r="B335" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C335" s="17" t="s">
-        <v>770</v>
+      <c r="C335" s="40" t="s">
+        <v>771</v>
       </c>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
@@ -10965,13 +10983,13 @@
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="10" t="s">
-        <v>771</v>
+        <v>772</v>
       </c>
       <c r="B336" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C336" s="12" t="s">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D336" s="4"/>
       <c r="E336" s="4"/>
@@ -10983,13 +11001,13 @@
       <c r="K336" s="9"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="34" t="s">
+      <c r="A337" s="15" t="s">
         <v>773</v>
       </c>
       <c r="B337" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C337" s="36" t="s">
+      <c r="C337" s="17" t="s">
         <v>774</v>
       </c>
       <c r="D337" s="4"/>
@@ -11002,13 +11020,13 @@
       <c r="K337" s="9"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="39" t="s">
+      <c r="A338" s="10" t="s">
         <v>775</v>
       </c>
       <c r="B338" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C338" s="40" t="s">
+      <c r="C338" s="20" t="s">
         <v>776</v>
       </c>
       <c r="D338" s="4"/>
@@ -11040,13 +11058,13 @@
       <c r="K339" s="9"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="39" t="s">
+      <c r="A340" s="34" t="s">
         <v>779</v>
       </c>
       <c r="B340" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C340" s="40" t="s">
+      <c r="C340" s="35" t="s">
         <v>780</v>
       </c>
       <c r="D340" s="4"/>
@@ -11059,13 +11077,13 @@
       <c r="K340" s="9"/>
     </row>
     <row r="341" ht="15.75" customHeight="1">
-      <c r="A341" s="15" t="s">
+      <c r="A341" s="38" t="s">
         <v>781</v>
       </c>
       <c r="B341" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C341" s="17" t="s">
+      <c r="C341" s="40" t="s">
         <v>782</v>
       </c>
       <c r="D341" s="4"/>
@@ -11097,13 +11115,13 @@
       <c r="K342" s="9"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="15" t="s">
+      <c r="A343" s="38" t="s">
         <v>785</v>
       </c>
       <c r="B343" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C343" s="24" t="s">
+      <c r="C343" s="40" t="s">
         <v>786</v>
       </c>
       <c r="D343" s="4"/>
@@ -11160,7 +11178,7 @@
       <c r="B346" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C346" s="20" t="s">
+      <c r="C346" s="12" t="s">
         <v>792</v>
       </c>
       <c r="D346" s="4"/>
@@ -11198,7 +11216,7 @@
       <c r="B348" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C348" s="20" t="s">
+      <c r="C348" s="12" t="s">
         <v>796</v>
       </c>
       <c r="D348" s="4"/>
@@ -11236,7 +11254,7 @@
       <c r="B350" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C350" s="12" t="s">
+      <c r="C350" s="20" t="s">
         <v>800</v>
       </c>
       <c r="D350" s="4"/>
@@ -11249,13 +11267,13 @@
       <c r="K350" s="9"/>
     </row>
     <row r="351" ht="15.75" customHeight="1">
-      <c r="A351" s="45" t="s">
+      <c r="A351" s="15" t="s">
         <v>801</v>
       </c>
       <c r="B351" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C351" s="46" t="s">
+      <c r="C351" s="17" t="s">
         <v>802</v>
       </c>
       <c r="D351" s="4"/>
@@ -11293,7 +11311,7 @@
       <c r="B353" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C353" s="17" t="s">
+      <c r="C353" s="24" t="s">
         <v>806</v>
       </c>
       <c r="D353" s="4"/>
@@ -11306,13 +11324,13 @@
       <c r="K353" s="9"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="10" t="s">
+      <c r="A354" s="45" t="s">
         <v>807</v>
       </c>
       <c r="B354" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C354" s="20" t="s">
+      <c r="C354" s="46" t="s">
         <v>808</v>
       </c>
       <c r="D354" s="4"/>
@@ -11325,13 +11343,13 @@
       <c r="K354" s="9"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="34" t="s">
+      <c r="A355" s="15" t="s">
         <v>809</v>
       </c>
       <c r="B355" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C355" s="36" t="s">
+      <c r="C355" s="17" t="s">
         <v>810</v>
       </c>
       <c r="D355" s="4"/>
@@ -11369,7 +11387,7 @@
       <c r="B357" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C357" s="24" t="s">
+      <c r="C357" s="17" t="s">
         <v>814</v>
       </c>
       <c r="D357" s="4"/>
@@ -11382,13 +11400,13 @@
       <c r="K357" s="9"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="10" t="s">
+      <c r="A358" s="34" t="s">
         <v>815</v>
       </c>
       <c r="B358" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C358" s="12" t="s">
+      <c r="C358" s="35" t="s">
         <v>816</v>
       </c>
       <c r="D358" s="4"/>
@@ -11407,7 +11425,7 @@
       <c r="B359" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C359" s="24" t="s">
+      <c r="C359" s="17" t="s">
         <v>818</v>
       </c>
       <c r="D359" s="4"/>
@@ -11426,7 +11444,7 @@
       <c r="B360" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C360" s="20" t="s">
+      <c r="C360" s="12" t="s">
         <v>820</v>
       </c>
       <c r="D360" s="4"/>
@@ -11439,13 +11457,13 @@
       <c r="K360" s="9"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="45" t="s">
+      <c r="A361" s="15" t="s">
         <v>821</v>
       </c>
       <c r="B361" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C361" s="46" t="s">
+      <c r="C361" s="24" t="s">
         <v>822</v>
       </c>
       <c r="D361" s="4"/>
@@ -11464,7 +11482,7 @@
       <c r="B362" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C362" s="20" t="s">
+      <c r="C362" s="12" t="s">
         <v>824</v>
       </c>
       <c r="D362" s="4"/>
@@ -11496,13 +11514,13 @@
       <c r="K363" s="9"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="10" t="s">
+      <c r="A364" s="45" t="s">
         <v>827</v>
       </c>
       <c r="B364" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C364" s="20" t="s">
+      <c r="C364" s="46" t="s">
         <v>828</v>
       </c>
       <c r="D364" s="4"/>
@@ -11534,13 +11552,13 @@
       <c r="K365" s="9"/>
     </row>
     <row r="366" ht="15.75" customHeight="1">
-      <c r="A366" s="41" t="s">
+      <c r="A366" s="10" t="s">
         <v>831</v>
       </c>
       <c r="B366" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C366" s="42" t="s">
+      <c r="C366" s="20" t="s">
         <v>832</v>
       </c>
       <c r="D366" s="4"/>
@@ -11572,13 +11590,13 @@
       <c r="K367" s="9"/>
     </row>
     <row r="368" ht="15.75" customHeight="1">
-      <c r="A368" s="39" t="s">
+      <c r="A368" s="10" t="s">
         <v>835</v>
       </c>
       <c r="B368" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C368" s="40" t="s">
+      <c r="C368" s="20" t="s">
         <v>836</v>
       </c>
       <c r="D368" s="4"/>
@@ -11591,13 +11609,13 @@
       <c r="K368" s="9"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="34" t="s">
+      <c r="A369" s="41" t="s">
         <v>837</v>
       </c>
       <c r="B369" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C369" s="36" t="s">
+      <c r="C369" s="42" t="s">
         <v>838</v>
       </c>
       <c r="D369" s="4"/>
@@ -11616,7 +11634,7 @@
       <c r="B370" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C370" s="12" t="s">
+      <c r="C370" s="20" t="s">
         <v>840</v>
       </c>
       <c r="D370" s="4"/>
@@ -11629,13 +11647,13 @@
       <c r="K370" s="9"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="34" t="s">
+      <c r="A371" s="38" t="s">
         <v>841</v>
       </c>
       <c r="B371" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C371" s="36" t="s">
+      <c r="C371" s="40" t="s">
         <v>842</v>
       </c>
       <c r="D371" s="4"/>
@@ -11648,13 +11666,13 @@
       <c r="K371" s="9"/>
     </row>
     <row r="372" ht="15.75" customHeight="1">
-      <c r="A372" s="39" t="s">
+      <c r="A372" s="34" t="s">
         <v>843</v>
       </c>
       <c r="B372" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C372" s="52" t="s">
+      <c r="C372" s="35" t="s">
         <v>844</v>
       </c>
       <c r="D372" s="4"/>
@@ -11667,13 +11685,13 @@
       <c r="K372" s="9"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="34" t="s">
+      <c r="A373" s="15" t="s">
         <v>845</v>
       </c>
       <c r="B373" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C373" s="36" t="s">
+      <c r="C373" s="24" t="s">
         <v>846</v>
       </c>
       <c r="D373" s="4"/>
@@ -11686,13 +11704,13 @@
       <c r="K373" s="9"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="10" t="s">
+      <c r="A374" s="34" t="s">
         <v>847</v>
       </c>
       <c r="B374" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C374" s="12" t="s">
+      <c r="C374" s="35" t="s">
         <v>848</v>
       </c>
       <c r="D374" s="4"/>
@@ -11705,13 +11723,13 @@
       <c r="K374" s="9"/>
     </row>
     <row r="375" ht="15.75" customHeight="1">
-      <c r="A375" s="15" t="s">
+      <c r="A375" s="38" t="s">
         <v>849</v>
       </c>
       <c r="B375" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C375" s="24" t="s">
+      <c r="C375" s="52" t="s">
         <v>850</v>
       </c>
       <c r="D375" s="4"/>
@@ -11724,13 +11742,13 @@
       <c r="K375" s="9"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="10" t="s">
+      <c r="A376" s="34" t="s">
         <v>851</v>
       </c>
       <c r="B376" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C376" s="12" t="s">
+      <c r="C376" s="35" t="s">
         <v>852</v>
       </c>
       <c r="D376" s="4"/>
@@ -11806,7 +11824,7 @@
       <c r="B380" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C380" s="20" t="s">
+      <c r="C380" s="12" t="s">
         <v>860</v>
       </c>
       <c r="D380" s="4"/>
@@ -11863,7 +11881,7 @@
       <c r="B383" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C383" s="24" t="s">
+      <c r="C383" s="17" t="s">
         <v>866</v>
       </c>
       <c r="D383" s="4"/>
@@ -11882,7 +11900,7 @@
       <c r="B384" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C384" s="20" t="s">
+      <c r="C384" s="12" t="s">
         <v>868</v>
       </c>
       <c r="D384" s="4"/>
@@ -11958,7 +11976,7 @@
       <c r="B388" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C388" s="20" t="s">
+      <c r="C388" s="12" t="s">
         <v>876</v>
       </c>
       <c r="D388" s="4"/>
@@ -11990,13 +12008,13 @@
       <c r="K389" s="9"/>
     </row>
     <row r="390" ht="15.75" customHeight="1">
-      <c r="A390" s="39" t="s">
+      <c r="A390" s="10" t="s">
         <v>879</v>
       </c>
       <c r="B390" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C390" s="40" t="s">
+      <c r="C390" s="20" t="s">
         <v>880</v>
       </c>
       <c r="D390" s="4"/>
@@ -12035,7 +12053,7 @@
         <v>48</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>882</v>
+        <v>884</v>
       </c>
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
@@ -12047,14 +12065,14 @@
       <c r="K392" s="9"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="45" t="s">
-        <v>884</v>
+      <c r="A393" s="38" t="s">
+        <v>885</v>
       </c>
       <c r="B393" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C393" s="46" t="s">
-        <v>885</v>
+      <c r="C393" s="40" t="s">
+        <v>886</v>
       </c>
       <c r="D393" s="4"/>
       <c r="E393" s="4"/>
@@ -12067,13 +12085,13 @@
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="10" t="s">
-        <v>886</v>
+        <v>887</v>
       </c>
       <c r="B394" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C394" s="12" t="s">
-        <v>887</v>
+      <c r="C394" s="20" t="s">
+        <v>888</v>
       </c>
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
@@ -12086,13 +12104,13 @@
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="15" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="B395" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C395" s="17" t="s">
-        <v>889</v>
+      <c r="C395" s="24" t="s">
+        <v>888</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -12104,13 +12122,13 @@
       <c r="K395" s="9"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="41" t="s">
+      <c r="A396" s="45" t="s">
         <v>890</v>
       </c>
       <c r="B396" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C396" s="42" t="s">
+      <c r="C396" s="46" t="s">
         <v>891</v>
       </c>
       <c r="D396" s="4"/>
@@ -12161,13 +12179,13 @@
       <c r="K398" s="9"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="15" t="s">
+      <c r="A399" s="41" t="s">
         <v>896</v>
       </c>
       <c r="B399" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C399" s="17" t="s">
+      <c r="C399" s="42" t="s">
         <v>897</v>
       </c>
       <c r="D399" s="4"/>
@@ -12224,7 +12242,7 @@
       <c r="B402" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C402" s="12" t="s">
+      <c r="C402" s="20" t="s">
         <v>903</v>
       </c>
       <c r="D402" s="4"/>
@@ -12319,7 +12337,7 @@
       <c r="B407" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C407" s="24" t="s">
+      <c r="C407" s="17" t="s">
         <v>913</v>
       </c>
       <c r="D407" s="4"/>
@@ -12338,7 +12356,7 @@
       <c r="B408" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C408" s="20" t="s">
+      <c r="C408" s="12" t="s">
         <v>915</v>
       </c>
       <c r="D408" s="4"/>
@@ -12414,7 +12432,7 @@
       <c r="B412" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C412" s="20" t="s">
+      <c r="C412" s="12" t="s">
         <v>923</v>
       </c>
       <c r="D412" s="4"/>
@@ -12427,13 +12445,13 @@
       <c r="K412" s="9"/>
     </row>
     <row r="413" ht="15.75" customHeight="1">
-      <c r="A413" s="34" t="s">
+      <c r="A413" s="15" t="s">
         <v>924</v>
       </c>
       <c r="B413" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C413" s="36" t="s">
+      <c r="C413" s="24" t="s">
         <v>925</v>
       </c>
       <c r="D413" s="4"/>
@@ -12452,7 +12470,7 @@
       <c r="B414" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C414" s="12" t="s">
+      <c r="C414" s="20" t="s">
         <v>927</v>
       </c>
       <c r="D414" s="4"/>
@@ -12471,7 +12489,7 @@
       <c r="B415" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C415" s="24" t="s">
+      <c r="C415" s="17" t="s">
         <v>929</v>
       </c>
       <c r="D415" s="4"/>
@@ -12484,13 +12502,13 @@
       <c r="K415" s="9"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="10" t="s">
+      <c r="A416" s="34" t="s">
         <v>930</v>
       </c>
       <c r="B416" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C416" s="20" t="s">
+      <c r="C416" s="35" t="s">
         <v>931</v>
       </c>
       <c r="D416" s="4"/>
@@ -12528,7 +12546,7 @@
       <c r="B418" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C418" s="20" t="s">
+      <c r="C418" s="12" t="s">
         <v>935</v>
       </c>
       <c r="D418" s="4"/>
@@ -12547,7 +12565,7 @@
       <c r="B419" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C419" s="24" t="s">
+      <c r="C419" s="17" t="s">
         <v>937</v>
       </c>
       <c r="D419" s="4"/>
@@ -12604,7 +12622,7 @@
       <c r="B422" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C422" s="20" t="s">
+      <c r="C422" s="12" t="s">
         <v>943</v>
       </c>
       <c r="D422" s="4"/>
@@ -12623,7 +12641,7 @@
       <c r="B423" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C423" s="17" t="s">
+      <c r="C423" s="24" t="s">
         <v>945</v>
       </c>
       <c r="D423" s="4"/>
@@ -12680,7 +12698,7 @@
       <c r="B426" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C426" s="12" t="s">
+      <c r="C426" s="20" t="s">
         <v>951</v>
       </c>
       <c r="D426" s="4"/>
@@ -12693,13 +12711,13 @@
       <c r="K426" s="9"/>
     </row>
     <row r="427" ht="15.75" customHeight="1">
-      <c r="A427" s="34" t="s">
+      <c r="A427" s="15" t="s">
         <v>952</v>
       </c>
       <c r="B427" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C427" s="36" t="s">
+      <c r="C427" s="17" t="s">
         <v>953</v>
       </c>
       <c r="D427" s="4"/>
@@ -12712,13 +12730,13 @@
       <c r="K427" s="9"/>
     </row>
     <row r="428" ht="15.75" customHeight="1">
-      <c r="A428" s="39" t="s">
+      <c r="A428" s="10" t="s">
         <v>954</v>
       </c>
       <c r="B428" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C428" s="40" t="s">
+      <c r="C428" s="20" t="s">
         <v>955</v>
       </c>
       <c r="D428" s="4"/>
@@ -12737,7 +12755,7 @@
       <c r="B429" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C429" s="17" t="s">
+      <c r="C429" s="24" t="s">
         <v>957</v>
       </c>
       <c r="D429" s="4"/>
@@ -12750,13 +12768,13 @@
       <c r="K429" s="9"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="10" t="s">
+      <c r="A430" s="34" t="s">
         <v>958</v>
       </c>
       <c r="B430" s="11" t="s">
-        <v>53</v>
-      </c>
-      <c r="C430" s="12" t="s">
+        <v>48</v>
+      </c>
+      <c r="C430" s="35" t="s">
         <v>959</v>
       </c>
       <c r="D430" s="4"/>
@@ -12769,14 +12787,14 @@
       <c r="K430" s="9"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="15" t="s">
+      <c r="A431" s="38" t="s">
         <v>960</v>
       </c>
       <c r="B431" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C431" s="24" t="s">
-        <v>960</v>
+        <v>48</v>
+      </c>
+      <c r="C431" s="40" t="s">
+        <v>961</v>
       </c>
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
@@ -12788,14 +12806,14 @@
       <c r="K431" s="9"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="39" t="s">
-        <v>961</v>
-      </c>
-      <c r="B432" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C432" s="40" t="s">
+      <c r="A432" s="10" t="s">
         <v>962</v>
+      </c>
+      <c r="B432" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C432" s="20" t="s">
+        <v>963</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -12807,14 +12825,14 @@
       <c r="K432" s="9"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="25" t="s">
-        <v>963</v>
-      </c>
-      <c r="B433" s="50" t="s">
-        <v>9</v>
+      <c r="A433" s="15" t="s">
+        <v>964</v>
+      </c>
+      <c r="B433" s="16" t="s">
+        <v>53</v>
       </c>
       <c r="C433" s="24" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -12827,9 +12845,9 @@
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="10" t="s">
-        <v>965</v>
-      </c>
-      <c r="B434" s="51" t="s">
+        <v>966</v>
+      </c>
+      <c r="B434" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C434" s="12" t="s">
@@ -12845,14 +12863,14 @@
       <c r="K434" s="9"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="15" t="s">
+      <c r="A435" s="38" t="s">
         <v>967</v>
       </c>
-      <c r="B435" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C435" s="24" t="s">
-        <v>967</v>
+      <c r="B435" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C435" s="40" t="s">
+        <v>968</v>
       </c>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
@@ -12864,14 +12882,14 @@
       <c r="K435" s="9"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="39" t="s">
-        <v>968</v>
-      </c>
-      <c r="B436" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C436" s="40" t="s">
+      <c r="A436" s="22" t="s">
         <v>969</v>
+      </c>
+      <c r="B436" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C436" s="12" t="s">
+        <v>970</v>
       </c>
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
@@ -12883,14 +12901,14 @@
       <c r="K436" s="9"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="25" t="s">
-        <v>970</v>
-      </c>
-      <c r="B437" s="16" t="s">
-        <v>285</v>
-      </c>
-      <c r="C437" s="17" t="s">
+      <c r="A437" s="15" t="s">
         <v>971</v>
+      </c>
+      <c r="B437" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C437" s="24" t="s">
+        <v>972</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
@@ -12902,13 +12920,13 @@
       <c r="K437" s="9"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="39" t="s">
-        <v>972</v>
-      </c>
-      <c r="B438" s="26" t="s">
-        <v>58</v>
-      </c>
-      <c r="C438" s="20" t="s">
+      <c r="A438" s="10" t="s">
+        <v>973</v>
+      </c>
+      <c r="B438" s="11" t="s">
+        <v>9</v>
+      </c>
+      <c r="C438" s="12" t="s">
         <v>973</v>
       </c>
       <c r="D438" s="4"/>
@@ -12921,13 +12939,13 @@
       <c r="K438" s="9"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="45" t="s">
+      <c r="A439" s="38" t="s">
         <v>974</v>
       </c>
-      <c r="B439" s="16" t="s">
-        <v>298</v>
-      </c>
-      <c r="C439" s="49" t="s">
+      <c r="B439" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C439" s="40" t="s">
         <v>975</v>
       </c>
       <c r="D439" s="4"/>
@@ -12940,13 +12958,13 @@
       <c r="K439" s="9"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="10" t="s">
+      <c r="A440" s="22" t="s">
         <v>976</v>
       </c>
       <c r="B440" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C440" s="12" t="s">
+        <v>287</v>
+      </c>
+      <c r="C440" s="20" t="s">
         <v>977</v>
       </c>
       <c r="D440" s="4"/>
@@ -12959,13 +12977,13 @@
       <c r="K440" s="9"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="15" t="s">
+      <c r="A441" s="38" t="s">
         <v>978</v>
       </c>
-      <c r="B441" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C441" s="24" t="s">
+      <c r="B441" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C441" s="17" t="s">
         <v>979</v>
       </c>
       <c r="D441" s="4"/>
@@ -12978,13 +12996,13 @@
       <c r="K441" s="9"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="10" t="s">
+      <c r="A442" s="45" t="s">
         <v>980</v>
       </c>
-      <c r="B442" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C442" s="12" t="s">
+      <c r="B442" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C442" s="49" t="s">
         <v>981</v>
       </c>
       <c r="D442" s="4"/>
@@ -13001,7 +13019,7 @@
         <v>982</v>
       </c>
       <c r="B443" s="16" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C443" s="24" t="s">
         <v>983</v>
@@ -13019,10 +13037,10 @@
       <c r="A444" s="10" t="s">
         <v>984</v>
       </c>
-      <c r="B444" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C444" s="20" t="s">
+      <c r="B444" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C444" s="12" t="s">
         <v>985</v>
       </c>
       <c r="D444" s="4"/>
@@ -13038,8 +13056,8 @@
       <c r="A445" s="15" t="s">
         <v>986</v>
       </c>
-      <c r="B445" s="16" t="s">
-        <v>361</v>
+      <c r="B445" s="51" t="s">
+        <v>9</v>
       </c>
       <c r="C445" s="24" t="s">
         <v>987</v>
@@ -13058,7 +13076,7 @@
         <v>988</v>
       </c>
       <c r="B446" s="11" t="s">
-        <v>361</v>
+        <v>9</v>
       </c>
       <c r="C446" s="12" t="s">
         <v>989</v>
@@ -13076,10 +13094,10 @@
       <c r="A447" s="15" t="s">
         <v>990</v>
       </c>
-      <c r="B447" s="16" t="s">
-        <v>361</v>
-      </c>
-      <c r="C447" s="24" t="s">
+      <c r="B447" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C447" s="17" t="s">
         <v>991</v>
       </c>
       <c r="D447" s="4"/>
@@ -13096,7 +13114,7 @@
         <v>992</v>
       </c>
       <c r="B448" s="11" t="s">
-        <v>68</v>
+        <v>363</v>
       </c>
       <c r="C448" s="12" t="s">
         <v>993</v>
@@ -13115,7 +13133,7 @@
         <v>994</v>
       </c>
       <c r="B449" s="16" t="s">
-        <v>9</v>
+        <v>363</v>
       </c>
       <c r="C449" s="24" t="s">
         <v>995</v>
@@ -13134,7 +13152,7 @@
         <v>996</v>
       </c>
       <c r="B450" s="11" t="s">
-        <v>9</v>
+        <v>363</v>
       </c>
       <c r="C450" s="12" t="s">
         <v>997</v>
@@ -13153,7 +13171,7 @@
         <v>998</v>
       </c>
       <c r="B451" s="16" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C451" s="24" t="s">
         <v>999</v>
@@ -13172,9 +13190,9 @@
         <v>1000</v>
       </c>
       <c r="B452" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C452" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C452" s="12" t="s">
         <v>1001</v>
       </c>
       <c r="D452" s="4"/>
@@ -13187,13 +13205,13 @@
       <c r="K452" s="9"/>
     </row>
     <row r="453" ht="15.75" customHeight="1">
-      <c r="A453" s="25" t="s">
+      <c r="A453" s="15" t="s">
         <v>1002</v>
       </c>
       <c r="B453" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C453" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C453" s="24" t="s">
         <v>1003</v>
       </c>
       <c r="D453" s="4"/>
@@ -13210,7 +13228,7 @@
         <v>1004</v>
       </c>
       <c r="B454" s="11" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C454" s="12" t="s">
         <v>1005</v>
@@ -13229,9 +13247,9 @@
         <v>1006</v>
       </c>
       <c r="B455" s="16" t="s">
-        <v>48</v>
-      </c>
-      <c r="C455" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C455" s="17" t="s">
         <v>1007</v>
       </c>
       <c r="D455" s="4"/>
@@ -13244,13 +13262,13 @@
       <c r="K455" s="9"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="10" t="s">
+      <c r="A456" s="22" t="s">
         <v>1008</v>
       </c>
       <c r="B456" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C456" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C456" s="20" t="s">
         <v>1009</v>
       </c>
       <c r="D456" s="4"/>
@@ -13267,9 +13285,9 @@
         <v>1010</v>
       </c>
       <c r="B457" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C457" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="C457" s="24" t="s">
         <v>1011</v>
       </c>
       <c r="D457" s="4"/>
@@ -13286,7 +13304,7 @@
         <v>1012</v>
       </c>
       <c r="B458" s="11" t="s">
-        <v>83</v>
+        <v>48</v>
       </c>
       <c r="C458" s="12" t="s">
         <v>1013</v>
@@ -13301,13 +13319,13 @@
       <c r="K458" s="9"/>
     </row>
     <row r="459" ht="15.75" customHeight="1">
-      <c r="A459" s="34" t="s">
+      <c r="A459" s="15" t="s">
         <v>1014</v>
       </c>
       <c r="B459" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C459" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C459" s="24" t="s">
         <v>1015</v>
       </c>
       <c r="D459" s="4"/>
@@ -13324,7 +13342,7 @@
         <v>1016</v>
       </c>
       <c r="B460" s="11" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="C460" s="20" t="s">
         <v>1017</v>
@@ -13339,13 +13357,13 @@
       <c r="K460" s="9"/>
     </row>
     <row r="461" ht="15.75" customHeight="1">
-      <c r="A461" s="34" t="s">
+      <c r="A461" s="15" t="s">
         <v>1018</v>
       </c>
       <c r="B461" s="16" t="s">
-        <v>83</v>
-      </c>
-      <c r="C461" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C461" s="24" t="s">
         <v>1019</v>
       </c>
       <c r="D461" s="4"/>
@@ -13358,14 +13376,14 @@
       <c r="K461" s="9"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="39" t="s">
-        <v>988</v>
+      <c r="A462" s="34" t="s">
+        <v>1020</v>
       </c>
       <c r="B462" s="11" t="s">
-        <v>83</v>
-      </c>
-      <c r="C462" s="40" t="s">
-        <v>1020</v>
+        <v>87</v>
+      </c>
+      <c r="C462" s="35" t="s">
+        <v>1021</v>
       </c>
       <c r="D462" s="4"/>
       <c r="E462" s="4"/>
@@ -13378,13 +13396,13 @@
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="15" t="s">
-        <v>1021</v>
-      </c>
-      <c r="B463" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C463" s="24" t="s">
         <v>1022</v>
+      </c>
+      <c r="B463" s="16" t="s">
+        <v>68</v>
+      </c>
+      <c r="C463" s="17" t="s">
+        <v>1023</v>
       </c>
       <c r="D463" s="4"/>
       <c r="E463" s="4"/>
@@ -13396,14 +13414,14 @@
       <c r="K463" s="9"/>
     </row>
     <row r="464" ht="15.75" customHeight="1">
-      <c r="A464" s="10" t="s">
-        <v>1023</v>
+      <c r="A464" s="34" t="s">
+        <v>1024</v>
       </c>
       <c r="B464" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C464" s="20" t="s">
-        <v>1024</v>
+        <v>87</v>
+      </c>
+      <c r="C464" s="35" t="s">
+        <v>1025</v>
       </c>
       <c r="D464" s="4"/>
       <c r="E464" s="4"/>
@@ -13415,13 +13433,13 @@
       <c r="K464" s="9"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="34" t="s">
-        <v>1025</v>
+      <c r="A465" s="38" t="s">
+        <v>994</v>
       </c>
       <c r="B465" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C465" s="36" t="s">
+        <v>87</v>
+      </c>
+      <c r="C465" s="40" t="s">
         <v>1026</v>
       </c>
       <c r="D465" s="4"/>
@@ -13434,13 +13452,13 @@
       <c r="K465" s="9"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="39" t="s">
+      <c r="A466" s="10" t="s">
         <v>1027</v>
       </c>
-      <c r="B466" s="26" t="s">
-        <v>53</v>
-      </c>
-      <c r="C466" s="40" t="s">
+      <c r="B466" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C466" s="12" t="s">
         <v>1028</v>
       </c>
       <c r="D466" s="4"/>
@@ -13459,7 +13477,7 @@
       <c r="B467" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C467" s="24" t="s">
+      <c r="C467" s="17" t="s">
         <v>1030</v>
       </c>
       <c r="D467" s="4"/>
@@ -13472,13 +13490,13 @@
       <c r="K467" s="9"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="10" t="s">
+      <c r="A468" s="34" t="s">
         <v>1031</v>
       </c>
       <c r="B468" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C468" s="12" t="s">
+      <c r="C468" s="35" t="s">
         <v>1032</v>
       </c>
       <c r="D468" s="4"/>
@@ -13491,13 +13509,13 @@
       <c r="K468" s="9"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="15" t="s">
+      <c r="A469" s="38" t="s">
         <v>1033</v>
       </c>
-      <c r="B469" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C469" s="24" t="s">
+      <c r="B469" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C469" s="40" t="s">
         <v>1034</v>
       </c>
       <c r="D469" s="4"/>
@@ -13510,13 +13528,13 @@
       <c r="K469" s="9"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="22" t="s">
+      <c r="A470" s="10" t="s">
         <v>1035</v>
       </c>
       <c r="B470" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C470" s="20" t="s">
+      <c r="C470" s="12" t="s">
         <v>1036</v>
       </c>
       <c r="D470" s="4"/>
@@ -13567,13 +13585,13 @@
       <c r="K472" s="9"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="53" t="s">
+      <c r="A473" s="25" t="s">
         <v>1041</v>
       </c>
       <c r="B473" s="16" t="s">
-        <v>137</v>
-      </c>
-      <c r="C473" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C473" s="17" t="s">
         <v>1042</v>
       </c>
       <c r="D473" s="4"/>
@@ -13590,7 +13608,7 @@
         <v>1043</v>
       </c>
       <c r="B474" s="11" t="s">
-        <v>361</v>
+        <v>9</v>
       </c>
       <c r="C474" s="12" t="s">
         <v>1044</v>
@@ -13609,7 +13627,7 @@
         <v>1045</v>
       </c>
       <c r="B475" s="16" t="s">
-        <v>361</v>
+        <v>9</v>
       </c>
       <c r="C475" s="24" t="s">
         <v>1046</v>
@@ -13624,13 +13642,13 @@
       <c r="K475" s="9"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="10" t="s">
+      <c r="A476" s="53" t="s">
         <v>1047</v>
       </c>
       <c r="B476" s="11" t="s">
-        <v>361</v>
-      </c>
-      <c r="C476" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C476" s="46" t="s">
         <v>1048</v>
       </c>
       <c r="D476" s="4"/>
@@ -13643,13 +13661,13 @@
       <c r="K476" s="9"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="54" t="s">
+      <c r="A477" s="15" t="s">
         <v>1049</v>
       </c>
-      <c r="B477" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C477" s="56" t="s">
+      <c r="B477" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="C477" s="24" t="s">
         <v>1050</v>
       </c>
       <c r="D477" s="4"/>
@@ -13661,9 +13679,66 @@
       <c r="J477" s="9"/>
       <c r="K477" s="9"/>
     </row>
+    <row r="478" ht="15.75" customHeight="1">
+      <c r="A478" s="10" t="s">
+        <v>1051</v>
+      </c>
+      <c r="B478" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="C478" s="12" t="s">
+        <v>1052</v>
+      </c>
+      <c r="D478" s="4"/>
+      <c r="E478" s="4"/>
+      <c r="F478" s="4"/>
+      <c r="G478" s="4"/>
+      <c r="H478" s="4"/>
+      <c r="I478" s="4"/>
+      <c r="J478" s="9"/>
+      <c r="K478" s="9"/>
+    </row>
+    <row r="479" ht="15.75" customHeight="1">
+      <c r="A479" s="15" t="s">
+        <v>1053</v>
+      </c>
+      <c r="B479" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="C479" s="24" t="s">
+        <v>1054</v>
+      </c>
+      <c r="D479" s="4"/>
+      <c r="E479" s="4"/>
+      <c r="F479" s="4"/>
+      <c r="G479" s="4"/>
+      <c r="H479" s="4"/>
+      <c r="I479" s="4"/>
+      <c r="J479" s="9"/>
+      <c r="K479" s="9"/>
+    </row>
+    <row r="480" ht="15.75" customHeight="1">
+      <c r="A480" s="54" t="s">
+        <v>1055</v>
+      </c>
+      <c r="B480" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C480" s="56" t="s">
+        <v>1056</v>
+      </c>
+      <c r="D480" s="4"/>
+      <c r="E480" s="4"/>
+      <c r="F480" s="4"/>
+      <c r="G480" s="4"/>
+      <c r="H480" s="4"/>
+      <c r="I480" s="4"/>
+      <c r="J480" s="9"/>
+      <c r="K480" s="9"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B477">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B480">
       <formula1>"adjective,adjective-adverb,adverb,auxiliary,conjunction,interjection,noun,numeral,preposition,pronoun,verb"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13689,10 +13764,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>1051</v>
+        <v>1057</v>
       </c>
       <c r="D1" s="57" t="s">
-        <v>1052</v>
+        <v>1058</v>
       </c>
       <c r="G1" s="58"/>
       <c r="H1" s="58"/>
@@ -13700,16 +13775,16 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>894</v>
+        <v>900</v>
       </c>
       <c r="G2" s="58"/>
       <c r="H2" s="58"/>
@@ -13720,13 +13795,13 @@
         <v>113</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="D3" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>1056</v>
+        <v>1062</v>
       </c>
       <c r="G3" s="58"/>
       <c r="H3" s="58"/>
@@ -13735,17 +13810,17 @@
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="60"/>
       <c r="B4" s="61" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="D4" s="60"/>
       <c r="E4" s="61" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="G4" s="58"/>
       <c r="H4" s="58"/>
@@ -13753,22 +13828,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="57" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>1063</v>
+        <v>1069</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="58"/>
@@ -13776,22 +13851,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="57" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1067</v>
+        <v>1073</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1068</v>
+        <v>1074</v>
       </c>
       <c r="G6" s="58"/>
       <c r="H6" s="58"/>
@@ -13799,33 +13874,33 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="57" t="s">
-        <v>1069</v>
+        <v>1075</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>1070</v>
+        <v>1076</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>1071</v>
+        <v>1077</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="57" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>783</v>
+        <v>789</v>
       </c>
       <c r="G8" s="57" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>877</v>
+        <v>883</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -13833,108 +13908,108 @@
         <v>113</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E9" s="59" t="s">
-        <v>1072</v>
+        <v>1078</v>
       </c>
       <c r="G9" s="57" t="s">
         <v>113</v>
       </c>
       <c r="H9" s="59" t="s">
-        <v>1073</v>
+        <v>1079</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="60"/>
       <c r="B10" s="61" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="D10" s="60"/>
       <c r="E10" s="61" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="F10" s="61" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="G10" s="60"/>
       <c r="H10" s="61" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="I10" s="61" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="57" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="C11" s="59" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="E11" s="59" t="s">
-        <v>1074</v>
+        <v>1080</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>1075</v>
+        <v>1081</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="57" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="57" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="G13" s="58"/>
       <c r="H13" s="58"/>
@@ -13942,16 +14017,16 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="57" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1054</v>
+        <v>1060</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>777</v>
+        <v>783</v>
       </c>
       <c r="G14" s="58"/>
       <c r="H14" s="58"/>
@@ -13962,13 +14037,13 @@
         <v>113</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>1055</v>
+        <v>1061</v>
       </c>
       <c r="D15" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E15" s="59" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="G15" s="58"/>
       <c r="H15" s="58"/>
@@ -13977,17 +14052,17 @@
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="60"/>
       <c r="B16" s="61" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="D16" s="60"/>
       <c r="E16" s="61" t="s">
-        <v>1057</v>
+        <v>1063</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>1058</v>
+        <v>1064</v>
       </c>
       <c r="G16" s="58"/>
       <c r="H16" s="58"/>
@@ -13995,22 +14070,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="57" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>1060</v>
+        <v>1066</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>1061</v>
+        <v>1067</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>1059</v>
+        <v>1065</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="G17" s="58"/>
       <c r="H17" s="58"/>
@@ -14018,22 +14093,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="57" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="G18" s="58"/>
       <c r="H18" s="58"/>
@@ -14052,13 +14127,13 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="D20" s="64" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="F20" s="62"/>
       <c r="G20" s="62"/>
@@ -14067,16 +14142,16 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="B21" s="65" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="D21" s="65" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="E21" s="65" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
       <c r="F21" s="62"/>
       <c r="G21" s="62"/>
@@ -14085,19 +14160,19 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="66" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="B22" s="59" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="F22" s="62"/>
       <c r="G22" s="62"/>
@@ -14106,19 +14181,19 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="64" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="F23" s="62"/>
       <c r="G23" s="62"/>
@@ -15012,7 +15087,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="C1" s="58"/>
       <c r="D1" s="59"/>
@@ -15024,10 +15099,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
       <c r="C2" s="59"/>
       <c r="D2" s="59"/>
@@ -15039,10 +15114,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="59" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="C3" s="59"/>
       <c r="D3" s="59"/>
@@ -15054,10 +15129,10 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="59" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="C4" s="59"/>
       <c r="D4" s="59"/>
@@ -15069,10 +15144,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="59" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="C5" s="59"/>
       <c r="D5" s="59"/>
@@ -15084,10 +15159,10 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="59" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="C6" s="59"/>
       <c r="D6" s="59"/>
@@ -15099,10 +15174,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="59" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="C7" s="59"/>
       <c r="D7" s="59"/>
@@ -15123,10 +15198,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="59" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="C9" s="59"/>
       <c r="D9" s="59"/>
@@ -16155,62 +16230,62 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="69" t="s">
-        <v>1117</v>
+        <v>1123</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="71" t="s">
-        <v>1118</v>
+        <v>1124</v>
       </c>
       <c r="H1" s="72"/>
       <c r="I1" s="72"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="71" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="C2" s="72"/>
       <c r="D2" s="71" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="E2" s="71" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="H2" s="72"/>
       <c r="I2" s="72"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="73" t="s">
-        <v>1121</v>
+        <v>1127</v>
       </c>
       <c r="B3" s="59" t="s">
         <v>131</v>
       </c>
       <c r="C3" s="73"/>
       <c r="D3" s="59" t="s">
-        <v>1122</v>
+        <v>1128</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>1123</v>
+        <v>1129</v>
       </c>
       <c r="H3" s="72"/>
       <c r="I3" s="72"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="59" t="s">
-        <v>1124</v>
+        <v>1130</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>1125</v>
+        <v>1131</v>
       </c>
       <c r="C4" s="73"/>
       <c r="D4" s="73" t="s">
-        <v>1126</v>
+        <v>1132</v>
       </c>
       <c r="E4" s="73" t="s">
-        <v>1127</v>
+        <v>1133</v>
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="73"/>
@@ -16219,17 +16294,17 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="59" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="B5" s="59" t="s">
         <v>135</v>
       </c>
       <c r="C5" s="73"/>
       <c r="D5" s="59" t="s">
-        <v>1128</v>
+        <v>1134</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>1129</v>
+        <v>1135</v>
       </c>
       <c r="F5" s="73"/>
       <c r="G5" s="73"/>
@@ -16238,17 +16313,17 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="73" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="B6" s="73" t="s">
         <v>144</v>
       </c>
       <c r="C6" s="73"/>
       <c r="D6" s="59" t="s">
-        <v>1130</v>
+        <v>1136</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1131</v>
+        <v>1137</v>
       </c>
       <c r="F6" s="73"/>
       <c r="G6" s="73"/>
@@ -16257,17 +16332,17 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="73" t="s">
-        <v>397</v>
+        <v>399</v>
       </c>
       <c r="B7" s="73" t="s">
         <v>148</v>
       </c>
       <c r="C7" s="73"/>
       <c r="D7" s="59" t="s">
-        <v>1132</v>
+        <v>1138</v>
       </c>
       <c r="E7" s="59" t="s">
-        <v>1133</v>
+        <v>1139</v>
       </c>
       <c r="F7" s="73"/>
       <c r="G7" s="73"/>
@@ -16276,17 +16351,17 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="73" t="s">
-        <v>1134</v>
+        <v>1140</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>152</v>
       </c>
       <c r="C8" s="73"/>
       <c r="D8" s="59" t="s">
-        <v>1135</v>
+        <v>1141</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1136</v>
+        <v>1142</v>
       </c>
       <c r="F8" s="73"/>
       <c r="G8" s="73"/>
@@ -16295,10 +16370,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="59" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1137</v>
+        <v>1143</v>
       </c>
       <c r="C9" s="73"/>
       <c r="D9" s="73"/>
@@ -16310,7 +16385,7 @@
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="73" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>156</v>
@@ -16325,7 +16400,7 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="73" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="B11" s="59" t="s">
         <v>162</v>
@@ -16362,7 +16437,7 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71" t="s">
-        <v>1138</v>
+        <v>1144</v>
       </c>
       <c r="C14" s="72"/>
       <c r="D14" s="72"/>
@@ -16374,10 +16449,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="71" t="s">
-        <v>1119</v>
+        <v>1125</v>
       </c>
       <c r="B15" s="71" t="s">
-        <v>1120</v>
+        <v>1126</v>
       </c>
       <c r="C15" s="72"/>
       <c r="D15" s="72"/>
@@ -16389,10 +16464,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="73" t="s">
-        <v>1139</v>
+        <v>1145</v>
       </c>
       <c r="B16" s="73" t="s">
-        <v>1140</v>
+        <v>1146</v>
       </c>
       <c r="C16" s="72"/>
       <c r="D16" s="72"/>
@@ -16404,10 +16479,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="73" t="s">
-        <v>1141</v>
+        <v>1147</v>
       </c>
       <c r="B17" s="73" t="s">
-        <v>1142</v>
+        <v>1148</v>
       </c>
       <c r="C17" s="72"/>
       <c r="D17" s="72"/>
@@ -16419,10 +16494,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="73" t="s">
-        <v>1143</v>
+        <v>1149</v>
       </c>
       <c r="B18" s="73" t="s">
-        <v>1144</v>
+        <v>1150</v>
       </c>
       <c r="C18" s="72"/>
       <c r="D18" s="72"/>
@@ -16434,10 +16509,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="73" t="s">
-        <v>1145</v>
+        <v>1151</v>
       </c>
       <c r="B19" s="73" t="s">
-        <v>1146</v>
+        <v>1152</v>
       </c>
       <c r="C19" s="72"/>
       <c r="D19" s="72"/>
@@ -16449,10 +16524,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="59" t="s">
-        <v>1147</v>
+        <v>1153</v>
       </c>
       <c r="B20" s="73" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="C20" s="72"/>
       <c r="D20" s="72"/>
@@ -16464,10 +16539,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="59" t="s">
-        <v>1149</v>
+        <v>1155</v>
       </c>
       <c r="B21" s="73" t="s">
-        <v>1148</v>
+        <v>1154</v>
       </c>
       <c r="C21" s="72"/>
       <c r="D21" s="72"/>
@@ -16479,10 +16554,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="59" t="s">
-        <v>1150</v>
+        <v>1156</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1151</v>
+        <v>1157</v>
       </c>
       <c r="C22" s="72"/>
       <c r="D22" s="72"/>
@@ -16494,10 +16569,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="59" t="s">
-        <v>1152</v>
+        <v>1158</v>
       </c>
       <c r="B23" s="73" t="s">
-        <v>1153</v>
+        <v>1159</v>
       </c>
       <c r="C23" s="72"/>
       <c r="D23" s="72"/>
@@ -16509,7 +16584,7 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="59" t="s">
-        <v>1154</v>
+        <v>1160</v>
       </c>
       <c r="C24" s="72"/>
       <c r="D24" s="72"/>
@@ -16521,10 +16596,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="73" t="s">
-        <v>1155</v>
+        <v>1161</v>
       </c>
       <c r="B25" s="73" t="s">
-        <v>1156</v>
+        <v>1162</v>
       </c>
       <c r="C25" s="72"/>
       <c r="D25" s="72"/>
@@ -16536,10 +16611,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="73" t="s">
-        <v>1157</v>
+        <v>1163</v>
       </c>
       <c r="B26" s="73" t="s">
-        <v>1158</v>
+        <v>1164</v>
       </c>
       <c r="C26" s="72"/>
       <c r="D26" s="72"/>
@@ -16551,10 +16626,10 @@
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="73" t="s">
-        <v>1159</v>
+        <v>1165</v>
       </c>
       <c r="B27" s="73" t="s">
-        <v>1160</v>
+        <v>1166</v>
       </c>
       <c r="C27" s="72"/>
       <c r="D27" s="72"/>
@@ -16566,10 +16641,10 @@
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="73" t="s">
-        <v>1161</v>
+        <v>1167</v>
       </c>
       <c r="B28" s="73" t="s">
-        <v>1162</v>
+        <v>1168</v>
       </c>
       <c r="C28" s="72"/>
       <c r="D28" s="72"/>
@@ -16581,10 +16656,10 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="73" t="s">
-        <v>1163</v>
+        <v>1169</v>
       </c>
       <c r="B29" s="73" t="s">
-        <v>1164</v>
+        <v>1170</v>
       </c>
       <c r="C29" s="72"/>
       <c r="D29" s="72"/>
@@ -16596,10 +16671,10 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="73" t="s">
-        <v>1165</v>
+        <v>1171</v>
       </c>
       <c r="B30" s="73" t="s">
-        <v>1166</v>
+        <v>1172</v>
       </c>
       <c r="C30" s="72"/>
       <c r="D30" s="72"/>
@@ -16611,10 +16686,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="73" t="s">
-        <v>1167</v>
+        <v>1173</v>
       </c>
       <c r="B31" s="73" t="s">
-        <v>1168</v>
+        <v>1174</v>
       </c>
       <c r="C31" s="72"/>
       <c r="D31" s="72"/>
@@ -16626,7 +16701,7 @@
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="73" t="s">
-        <v>1169</v>
+        <v>1175</v>
       </c>
       <c r="B32" s="73" t="s">
         <v>174</v>
@@ -16641,10 +16716,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="73" t="s">
-        <v>1170</v>
+        <v>1176</v>
       </c>
       <c r="B33" s="73" t="s">
-        <v>1171</v>
+        <v>1177</v>
       </c>
       <c r="C33" s="72"/>
       <c r="D33" s="72"/>
@@ -16656,10 +16731,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="73" t="s">
-        <v>1172</v>
+        <v>1178</v>
       </c>
       <c r="B34" s="73" t="s">
-        <v>1173</v>
+        <v>1179</v>
       </c>
       <c r="C34" s="72"/>
       <c r="D34" s="72"/>
@@ -16671,10 +16746,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="73" t="s">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B35" s="59" t="s">
-        <v>1175</v>
+        <v>1181</v>
       </c>
       <c r="C35" s="72"/>
       <c r="D35" s="72"/>
@@ -16686,10 +16761,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="73" t="s">
-        <v>1176</v>
+        <v>1182</v>
       </c>
       <c r="B36" s="59" t="s">
-        <v>1177</v>
+        <v>1183</v>
       </c>
       <c r="C36" s="72"/>
       <c r="D36" s="72"/>
@@ -16701,10 +16776,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="73" t="s">
-        <v>1178</v>
+        <v>1184</v>
       </c>
       <c r="B37" s="73" t="s">
-        <v>1179</v>
+        <v>1185</v>
       </c>
       <c r="C37" s="72"/>
       <c r="D37" s="72"/>
@@ -16716,10 +16791,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="73" t="s">
-        <v>1180</v>
+        <v>1186</v>
       </c>
       <c r="B38" s="73" t="s">
-        <v>1181</v>
+        <v>1187</v>
       </c>
       <c r="C38" s="72"/>
       <c r="D38" s="72"/>

--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -9,14 +9,14 @@
     <sheet state="visible" name="Pronunciation" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$480</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$482</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1749" uniqueCount="1188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1755" uniqueCount="1192">
   <si>
     <t>Word</t>
   </si>
@@ -2355,6 +2355,12 @@
     <t>to eat or consume, åte = past tense</t>
   </si>
   <si>
+    <t>styrken</t>
+  </si>
+  <si>
+    <t>to embolden, to become bold, to be motivated</t>
+  </si>
+  <si>
     <t>hæste-skrymen</t>
   </si>
   <si>
@@ -2635,6 +2641,12 @@
   </si>
   <si>
     <t>to proof, to test, to examinate</t>
+  </si>
+  <si>
+    <t>ralten</t>
+  </si>
+  <si>
+    <t>to rally, to motivate</t>
   </si>
   <si>
     <t>lorten</t>
@@ -4039,7 +4051,7 @@
     <xf borderId="9" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
-    <xf borderId="10" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+    <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
     <xf borderId="5" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
@@ -4178,8 +4190,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C480" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$480"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C482" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$482"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Type" id="2"/>
@@ -4509,7 +4521,7 @@
         <v>25</v>
       </c>
       <c r="H4" s="21" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C480, REGEXMATCH(C2:C480, I3)), 2, TRUE)"),"ibyrten")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C482, REGEXMATCH(C2:C482, I3)), 2, TRUE)"),"ibyrten")</f>
         <v>ibyrten</v>
       </c>
       <c r="I4" s="4" t="str">
@@ -11058,13 +11070,13 @@
       <c r="K339" s="9"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="34" t="s">
+      <c r="A340" s="10" t="s">
         <v>779</v>
       </c>
       <c r="B340" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C340" s="35" t="s">
+      <c r="C340" s="12" t="s">
         <v>780</v>
       </c>
       <c r="D340" s="4"/>
@@ -11096,13 +11108,13 @@
       <c r="K341" s="9"/>
     </row>
     <row r="342" ht="15.75" customHeight="1">
-      <c r="A342" s="10" t="s">
+      <c r="A342" s="34" t="s">
         <v>783</v>
       </c>
       <c r="B342" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C342" s="12" t="s">
+      <c r="C342" s="35" t="s">
         <v>784</v>
       </c>
       <c r="D342" s="4"/>
@@ -11115,13 +11127,13 @@
       <c r="K342" s="9"/>
     </row>
     <row r="343" ht="15.75" customHeight="1">
-      <c r="A343" s="38" t="s">
+      <c r="A343" s="15" t="s">
         <v>785</v>
       </c>
       <c r="B343" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C343" s="40" t="s">
+      <c r="C343" s="24" t="s">
         <v>786</v>
       </c>
       <c r="D343" s="4"/>
@@ -11134,13 +11146,13 @@
       <c r="K343" s="9"/>
     </row>
     <row r="344" ht="15.75" customHeight="1">
-      <c r="A344" s="10" t="s">
+      <c r="A344" s="34" t="s">
         <v>787</v>
       </c>
       <c r="B344" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C344" s="20" t="s">
+      <c r="C344" s="35" t="s">
         <v>788</v>
       </c>
       <c r="D344" s="4"/>
@@ -11159,7 +11171,7 @@
       <c r="B345" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C345" s="24" t="s">
+      <c r="C345" s="17" t="s">
         <v>790</v>
       </c>
       <c r="D345" s="4"/>
@@ -11197,7 +11209,7 @@
       <c r="B347" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C347" s="17" t="s">
+      <c r="C347" s="24" t="s">
         <v>794</v>
       </c>
       <c r="D347" s="4"/>
@@ -11216,7 +11228,7 @@
       <c r="B348" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C348" s="12" t="s">
+      <c r="C348" s="20" t="s">
         <v>796</v>
       </c>
       <c r="D348" s="4"/>
@@ -11235,7 +11247,7 @@
       <c r="B349" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C349" s="17" t="s">
+      <c r="C349" s="24" t="s">
         <v>798</v>
       </c>
       <c r="D349" s="4"/>
@@ -11311,7 +11323,7 @@
       <c r="B353" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C353" s="24" t="s">
+      <c r="C353" s="17" t="s">
         <v>806</v>
       </c>
       <c r="D353" s="4"/>
@@ -11324,13 +11336,13 @@
       <c r="K353" s="9"/>
     </row>
     <row r="354" ht="15.75" customHeight="1">
-      <c r="A354" s="45" t="s">
+      <c r="A354" s="10" t="s">
         <v>807</v>
       </c>
       <c r="B354" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C354" s="46" t="s">
+      <c r="C354" s="12" t="s">
         <v>808</v>
       </c>
       <c r="D354" s="4"/>
@@ -11343,13 +11355,13 @@
       <c r="K354" s="9"/>
     </row>
     <row r="355" ht="15.75" customHeight="1">
-      <c r="A355" s="15" t="s">
+      <c r="A355" s="41" t="s">
         <v>809</v>
       </c>
       <c r="B355" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C355" s="17" t="s">
+      <c r="C355" s="48" t="s">
         <v>810</v>
       </c>
       <c r="D355" s="4"/>
@@ -11400,13 +11412,13 @@
       <c r="K357" s="9"/>
     </row>
     <row r="358" ht="15.75" customHeight="1">
-      <c r="A358" s="34" t="s">
+      <c r="A358" s="10" t="s">
         <v>815</v>
       </c>
       <c r="B358" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C358" s="35" t="s">
+      <c r="C358" s="20" t="s">
         <v>816</v>
       </c>
       <c r="D358" s="4"/>
@@ -11419,13 +11431,13 @@
       <c r="K358" s="9"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="15" t="s">
+      <c r="A359" s="38" t="s">
         <v>817</v>
       </c>
       <c r="B359" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C359" s="17" t="s">
+      <c r="C359" s="40" t="s">
         <v>818</v>
       </c>
       <c r="D359" s="4"/>
@@ -11444,7 +11456,7 @@
       <c r="B360" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C360" s="12" t="s">
+      <c r="C360" s="20" t="s">
         <v>820</v>
       </c>
       <c r="D360" s="4"/>
@@ -11501,7 +11513,7 @@
       <c r="B363" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C363" s="17" t="s">
+      <c r="C363" s="24" t="s">
         <v>826</v>
       </c>
       <c r="D363" s="4"/>
@@ -11514,13 +11526,13 @@
       <c r="K363" s="9"/>
     </row>
     <row r="364" ht="15.75" customHeight="1">
-      <c r="A364" s="45" t="s">
+      <c r="A364" s="10" t="s">
         <v>827</v>
       </c>
       <c r="B364" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C364" s="46" t="s">
+      <c r="C364" s="20" t="s">
         <v>828</v>
       </c>
       <c r="D364" s="4"/>
@@ -11533,13 +11545,13 @@
       <c r="K364" s="9"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="15" t="s">
+      <c r="A365" s="41" t="s">
         <v>829</v>
       </c>
       <c r="B365" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C365" s="17" t="s">
+      <c r="C365" s="48" t="s">
         <v>830</v>
       </c>
       <c r="D365" s="4"/>
@@ -11609,13 +11621,13 @@
       <c r="K368" s="9"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="41" t="s">
+      <c r="A369" s="15" t="s">
         <v>837</v>
       </c>
       <c r="B369" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C369" s="42" t="s">
+      <c r="C369" s="17" t="s">
         <v>838</v>
       </c>
       <c r="D369" s="4"/>
@@ -11628,13 +11640,13 @@
       <c r="K369" s="9"/>
     </row>
     <row r="370" ht="15.75" customHeight="1">
-      <c r="A370" s="10" t="s">
+      <c r="A370" s="45" t="s">
         <v>839</v>
       </c>
       <c r="B370" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C370" s="20" t="s">
+      <c r="C370" s="49" t="s">
         <v>840</v>
       </c>
       <c r="D370" s="4"/>
@@ -11647,13 +11659,13 @@
       <c r="K370" s="9"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="38" t="s">
+      <c r="A371" s="15" t="s">
         <v>841</v>
       </c>
       <c r="B371" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C371" s="40" t="s">
+      <c r="C371" s="17" t="s">
         <v>842</v>
       </c>
       <c r="D371" s="4"/>
@@ -11685,13 +11697,13 @@
       <c r="K372" s="9"/>
     </row>
     <row r="373" ht="15.75" customHeight="1">
-      <c r="A373" s="15" t="s">
+      <c r="A373" s="38" t="s">
         <v>845</v>
       </c>
       <c r="B373" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C373" s="24" t="s">
+      <c r="C373" s="40" t="s">
         <v>846</v>
       </c>
       <c r="D373" s="4"/>
@@ -11704,13 +11716,13 @@
       <c r="K373" s="9"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="34" t="s">
+      <c r="A374" s="10" t="s">
         <v>847</v>
       </c>
       <c r="B374" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C374" s="35" t="s">
+      <c r="C374" s="12" t="s">
         <v>848</v>
       </c>
       <c r="D374" s="4"/>
@@ -11729,7 +11741,7 @@
       <c r="B375" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C375" s="52" t="s">
+      <c r="C375" s="40" t="s">
         <v>850</v>
       </c>
       <c r="D375" s="4"/>
@@ -11748,7 +11760,7 @@
       <c r="B376" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C376" s="35" t="s">
+      <c r="C376" s="52" t="s">
         <v>852</v>
       </c>
       <c r="D376" s="4"/>
@@ -11761,13 +11773,13 @@
       <c r="K376" s="9"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="15" t="s">
+      <c r="A377" s="38" t="s">
         <v>853</v>
       </c>
       <c r="B377" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C377" s="24" t="s">
+      <c r="C377" s="40" t="s">
         <v>854</v>
       </c>
       <c r="D377" s="4"/>
@@ -11881,7 +11893,7 @@
       <c r="B383" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C383" s="17" t="s">
+      <c r="C383" s="24" t="s">
         <v>866</v>
       </c>
       <c r="D383" s="4"/>
@@ -11900,7 +11912,7 @@
       <c r="B384" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C384" s="12" t="s">
+      <c r="C384" s="20" t="s">
         <v>868</v>
       </c>
       <c r="D384" s="4"/>
@@ -11957,7 +11969,7 @@
       <c r="B387" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C387" s="17" t="s">
+      <c r="C387" s="24" t="s">
         <v>874</v>
       </c>
       <c r="D387" s="4"/>
@@ -11995,7 +12007,7 @@
       <c r="B389" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C389" s="24" t="s">
+      <c r="C389" s="17" t="s">
         <v>878</v>
       </c>
       <c r="D389" s="4"/>
@@ -12014,7 +12026,7 @@
       <c r="B390" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C390" s="20" t="s">
+      <c r="C390" s="12" t="s">
         <v>880</v>
       </c>
       <c r="D390" s="4"/>
@@ -12033,7 +12045,7 @@
       <c r="B391" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C391" s="17" t="s">
+      <c r="C391" s="24" t="s">
         <v>882</v>
       </c>
       <c r="D391" s="4"/>
@@ -12052,7 +12064,7 @@
       <c r="B392" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C392" s="12" t="s">
+      <c r="C392" s="20" t="s">
         <v>884</v>
       </c>
       <c r="D392" s="4"/>
@@ -12065,13 +12077,13 @@
       <c r="K392" s="9"/>
     </row>
     <row r="393" ht="15.75" customHeight="1">
-      <c r="A393" s="38" t="s">
+      <c r="A393" s="15" t="s">
         <v>885</v>
       </c>
       <c r="B393" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C393" s="40" t="s">
+      <c r="C393" s="17" t="s">
         <v>886</v>
       </c>
       <c r="D393" s="4"/>
@@ -12090,7 +12102,7 @@
       <c r="B394" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C394" s="20" t="s">
+      <c r="C394" s="12" t="s">
         <v>888</v>
       </c>
       <c r="D394" s="4"/>
@@ -12103,14 +12115,14 @@
       <c r="K394" s="9"/>
     </row>
     <row r="395" ht="15.75" customHeight="1">
-      <c r="A395" s="15" t="s">
+      <c r="A395" s="38" t="s">
         <v>889</v>
       </c>
       <c r="B395" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C395" s="24" t="s">
-        <v>888</v>
+      <c r="C395" s="40" t="s">
+        <v>890</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -12122,14 +12134,14 @@
       <c r="K395" s="9"/>
     </row>
     <row r="396" ht="15.75" customHeight="1">
-      <c r="A396" s="45" t="s">
-        <v>890</v>
+      <c r="A396" s="10" t="s">
+        <v>891</v>
       </c>
       <c r="B396" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C396" s="46" t="s">
-        <v>891</v>
+      <c r="C396" s="20" t="s">
+        <v>892</v>
       </c>
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
@@ -12142,13 +12154,13 @@
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="15" t="s">
-        <v>892</v>
+        <v>893</v>
       </c>
       <c r="B397" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C397" s="24" t="s">
-        <v>893</v>
+        <v>892</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
@@ -12160,13 +12172,13 @@
       <c r="K397" s="9"/>
     </row>
     <row r="398" ht="15.75" customHeight="1">
-      <c r="A398" s="10" t="s">
+      <c r="A398" s="45" t="s">
         <v>894</v>
       </c>
       <c r="B398" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C398" s="20" t="s">
+      <c r="C398" s="46" t="s">
         <v>895</v>
       </c>
       <c r="D398" s="4"/>
@@ -12179,13 +12191,13 @@
       <c r="K398" s="9"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="41" t="s">
+      <c r="A399" s="15" t="s">
         <v>896</v>
       </c>
       <c r="B399" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C399" s="42" t="s">
+      <c r="C399" s="24" t="s">
         <v>897</v>
       </c>
       <c r="D399" s="4"/>
@@ -12204,7 +12216,7 @@
       <c r="B400" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C400" s="12" t="s">
+      <c r="C400" s="20" t="s">
         <v>899</v>
       </c>
       <c r="D400" s="4"/>
@@ -12217,13 +12229,13 @@
       <c r="K400" s="9"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="15" t="s">
+      <c r="A401" s="41" t="s">
         <v>900</v>
       </c>
       <c r="B401" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C401" s="17" t="s">
+      <c r="C401" s="42" t="s">
         <v>901</v>
       </c>
       <c r="D401" s="4"/>
@@ -12242,7 +12254,7 @@
       <c r="B402" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C402" s="20" t="s">
+      <c r="C402" s="12" t="s">
         <v>903</v>
       </c>
       <c r="D402" s="4"/>
@@ -12261,7 +12273,7 @@
       <c r="B403" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C403" s="24" t="s">
+      <c r="C403" s="17" t="s">
         <v>905</v>
       </c>
       <c r="D403" s="4"/>
@@ -12318,7 +12330,7 @@
       <c r="B406" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C406" s="12" t="s">
+      <c r="C406" s="20" t="s">
         <v>911</v>
       </c>
       <c r="D406" s="4"/>
@@ -12337,7 +12349,7 @@
       <c r="B407" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C407" s="17" t="s">
+      <c r="C407" s="24" t="s">
         <v>913</v>
       </c>
       <c r="D407" s="4"/>
@@ -12375,7 +12387,7 @@
       <c r="B409" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C409" s="24" t="s">
+      <c r="C409" s="17" t="s">
         <v>917</v>
       </c>
       <c r="D409" s="4"/>
@@ -12413,7 +12425,7 @@
       <c r="B411" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C411" s="17" t="s">
+      <c r="C411" s="24" t="s">
         <v>921</v>
       </c>
       <c r="D411" s="4"/>
@@ -12451,7 +12463,7 @@
       <c r="B413" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C413" s="24" t="s">
+      <c r="C413" s="17" t="s">
         <v>925</v>
       </c>
       <c r="D413" s="4"/>
@@ -12470,7 +12482,7 @@
       <c r="B414" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C414" s="20" t="s">
+      <c r="C414" s="12" t="s">
         <v>927</v>
       </c>
       <c r="D414" s="4"/>
@@ -12489,7 +12501,7 @@
       <c r="B415" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C415" s="17" t="s">
+      <c r="C415" s="24" t="s">
         <v>929</v>
       </c>
       <c r="D415" s="4"/>
@@ -12502,13 +12514,13 @@
       <c r="K415" s="9"/>
     </row>
     <row r="416" ht="15.75" customHeight="1">
-      <c r="A416" s="34" t="s">
+      <c r="A416" s="10" t="s">
         <v>930</v>
       </c>
       <c r="B416" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C416" s="35" t="s">
+      <c r="C416" s="20" t="s">
         <v>931</v>
       </c>
       <c r="D416" s="4"/>
@@ -12527,7 +12539,7 @@
       <c r="B417" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C417" s="24" t="s">
+      <c r="C417" s="17" t="s">
         <v>933</v>
       </c>
       <c r="D417" s="4"/>
@@ -12540,13 +12552,13 @@
       <c r="K417" s="9"/>
     </row>
     <row r="418" ht="15.75" customHeight="1">
-      <c r="A418" s="10" t="s">
+      <c r="A418" s="34" t="s">
         <v>934</v>
       </c>
       <c r="B418" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C418" s="12" t="s">
+      <c r="C418" s="35" t="s">
         <v>935</v>
       </c>
       <c r="D418" s="4"/>
@@ -12565,7 +12577,7 @@
       <c r="B419" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C419" s="17" t="s">
+      <c r="C419" s="24" t="s">
         <v>937</v>
       </c>
       <c r="D419" s="4"/>
@@ -12641,7 +12653,7 @@
       <c r="B423" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C423" s="24" t="s">
+      <c r="C423" s="17" t="s">
         <v>945</v>
       </c>
       <c r="D423" s="4"/>
@@ -12660,7 +12672,7 @@
       <c r="B424" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C424" s="20" t="s">
+      <c r="C424" s="12" t="s">
         <v>947</v>
       </c>
       <c r="D424" s="4"/>
@@ -12679,7 +12691,7 @@
       <c r="B425" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C425" s="17" t="s">
+      <c r="C425" s="24" t="s">
         <v>949</v>
       </c>
       <c r="D425" s="4"/>
@@ -12755,7 +12767,7 @@
       <c r="B429" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C429" s="24" t="s">
+      <c r="C429" s="17" t="s">
         <v>957</v>
       </c>
       <c r="D429" s="4"/>
@@ -12768,13 +12780,13 @@
       <c r="K429" s="9"/>
     </row>
     <row r="430" ht="15.75" customHeight="1">
-      <c r="A430" s="34" t="s">
+      <c r="A430" s="10" t="s">
         <v>958</v>
       </c>
       <c r="B430" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C430" s="35" t="s">
+      <c r="C430" s="20" t="s">
         <v>959</v>
       </c>
       <c r="D430" s="4"/>
@@ -12787,13 +12799,13 @@
       <c r="K430" s="9"/>
     </row>
     <row r="431" ht="15.75" customHeight="1">
-      <c r="A431" s="38" t="s">
+      <c r="A431" s="15" t="s">
         <v>960</v>
       </c>
       <c r="B431" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C431" s="40" t="s">
+      <c r="C431" s="24" t="s">
         <v>961</v>
       </c>
       <c r="D431" s="4"/>
@@ -12806,13 +12818,13 @@
       <c r="K431" s="9"/>
     </row>
     <row r="432" ht="15.75" customHeight="1">
-      <c r="A432" s="10" t="s">
+      <c r="A432" s="34" t="s">
         <v>962</v>
       </c>
       <c r="B432" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C432" s="20" t="s">
+      <c r="C432" s="35" t="s">
         <v>963</v>
       </c>
       <c r="D432" s="4"/>
@@ -12825,13 +12837,13 @@
       <c r="K432" s="9"/>
     </row>
     <row r="433" ht="15.75" customHeight="1">
-      <c r="A433" s="15" t="s">
+      <c r="A433" s="38" t="s">
         <v>964</v>
       </c>
       <c r="B433" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C433" s="24" t="s">
+        <v>48</v>
+      </c>
+      <c r="C433" s="40" t="s">
         <v>965</v>
       </c>
       <c r="D433" s="4"/>
@@ -12848,10 +12860,10 @@
         <v>966</v>
       </c>
       <c r="B434" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C434" s="12" t="s">
-        <v>966</v>
+        <v>48</v>
+      </c>
+      <c r="C434" s="20" t="s">
+        <v>967</v>
       </c>
       <c r="D434" s="4"/>
       <c r="E434" s="4"/>
@@ -12863,14 +12875,14 @@
       <c r="K434" s="9"/>
     </row>
     <row r="435" ht="15.75" customHeight="1">
-      <c r="A435" s="38" t="s">
-        <v>967</v>
-      </c>
-      <c r="B435" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C435" s="40" t="s">
+      <c r="A435" s="15" t="s">
         <v>968</v>
+      </c>
+      <c r="B435" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C435" s="24" t="s">
+        <v>969</v>
       </c>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
@@ -12882,10 +12894,10 @@
       <c r="K435" s="9"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="22" t="s">
-        <v>969</v>
-      </c>
-      <c r="B436" s="50" t="s">
+      <c r="A436" s="10" t="s">
+        <v>970</v>
+      </c>
+      <c r="B436" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C436" s="12" t="s">
@@ -12901,13 +12913,13 @@
       <c r="K436" s="9"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="15" t="s">
+      <c r="A437" s="38" t="s">
         <v>971</v>
       </c>
       <c r="B437" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C437" s="24" t="s">
+      <c r="C437" s="40" t="s">
         <v>972</v>
       </c>
       <c r="D437" s="4"/>
@@ -12920,14 +12932,14 @@
       <c r="K437" s="9"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="10" t="s">
+      <c r="A438" s="22" t="s">
         <v>973</v>
       </c>
-      <c r="B438" s="11" t="s">
+      <c r="B438" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C438" s="12" t="s">
-        <v>973</v>
+        <v>974</v>
       </c>
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
@@ -12939,14 +12951,14 @@
       <c r="K438" s="9"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="38" t="s">
-        <v>974</v>
+      <c r="A439" s="15" t="s">
+        <v>975</v>
       </c>
       <c r="B439" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C439" s="40" t="s">
-        <v>975</v>
+      <c r="C439" s="24" t="s">
+        <v>976</v>
       </c>
       <c r="D439" s="4"/>
       <c r="E439" s="4"/>
@@ -12958,13 +12970,13 @@
       <c r="K439" s="9"/>
     </row>
     <row r="440" ht="15.75" customHeight="1">
-      <c r="A440" s="22" t="s">
-        <v>976</v>
+      <c r="A440" s="10" t="s">
+        <v>977</v>
       </c>
       <c r="B440" s="11" t="s">
-        <v>287</v>
-      </c>
-      <c r="C440" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C440" s="12" t="s">
         <v>977</v>
       </c>
       <c r="D440" s="4"/>
@@ -12980,10 +12992,10 @@
       <c r="A441" s="38" t="s">
         <v>978</v>
       </c>
-      <c r="B441" s="39" t="s">
-        <v>58</v>
-      </c>
-      <c r="C441" s="17" t="s">
+      <c r="B441" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C441" s="40" t="s">
         <v>979</v>
       </c>
       <c r="D441" s="4"/>
@@ -12996,13 +13008,13 @@
       <c r="K441" s="9"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="45" t="s">
+      <c r="A442" s="22" t="s">
         <v>980</v>
       </c>
       <c r="B442" s="11" t="s">
-        <v>300</v>
-      </c>
-      <c r="C442" s="49" t="s">
+        <v>287</v>
+      </c>
+      <c r="C442" s="20" t="s">
         <v>981</v>
       </c>
       <c r="D442" s="4"/>
@@ -13015,13 +13027,13 @@
       <c r="K442" s="9"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="15" t="s">
+      <c r="A443" s="38" t="s">
         <v>982</v>
       </c>
-      <c r="B443" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C443" s="24" t="s">
+      <c r="B443" s="39" t="s">
+        <v>58</v>
+      </c>
+      <c r="C443" s="17" t="s">
         <v>983</v>
       </c>
       <c r="D443" s="4"/>
@@ -13034,13 +13046,13 @@
       <c r="K443" s="9"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="10" t="s">
+      <c r="A444" s="45" t="s">
         <v>984</v>
       </c>
-      <c r="B444" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C444" s="12" t="s">
+      <c r="B444" s="11" t="s">
+        <v>300</v>
+      </c>
+      <c r="C444" s="49" t="s">
         <v>985</v>
       </c>
       <c r="D444" s="4"/>
@@ -13056,8 +13068,8 @@
       <c r="A445" s="15" t="s">
         <v>986</v>
       </c>
-      <c r="B445" s="51" t="s">
-        <v>9</v>
+      <c r="B445" s="16" t="s">
+        <v>68</v>
       </c>
       <c r="C445" s="24" t="s">
         <v>987</v>
@@ -13075,7 +13087,7 @@
       <c r="A446" s="10" t="s">
         <v>988</v>
       </c>
-      <c r="B446" s="11" t="s">
+      <c r="B446" s="50" t="s">
         <v>9</v>
       </c>
       <c r="C446" s="12" t="s">
@@ -13097,7 +13109,7 @@
       <c r="B447" s="51" t="s">
         <v>9</v>
       </c>
-      <c r="C447" s="17" t="s">
+      <c r="C447" s="24" t="s">
         <v>991</v>
       </c>
       <c r="D447" s="4"/>
@@ -13114,7 +13126,7 @@
         <v>992</v>
       </c>
       <c r="B448" s="11" t="s">
-        <v>363</v>
+        <v>9</v>
       </c>
       <c r="C448" s="12" t="s">
         <v>993</v>
@@ -13132,10 +13144,10 @@
       <c r="A449" s="15" t="s">
         <v>994</v>
       </c>
-      <c r="B449" s="16" t="s">
-        <v>363</v>
-      </c>
-      <c r="C449" s="24" t="s">
+      <c r="B449" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C449" s="17" t="s">
         <v>995</v>
       </c>
       <c r="D449" s="4"/>
@@ -13171,7 +13183,7 @@
         <v>998</v>
       </c>
       <c r="B451" s="16" t="s">
-        <v>68</v>
+        <v>363</v>
       </c>
       <c r="C451" s="24" t="s">
         <v>999</v>
@@ -13190,7 +13202,7 @@
         <v>1000</v>
       </c>
       <c r="B452" s="11" t="s">
-        <v>9</v>
+        <v>363</v>
       </c>
       <c r="C452" s="12" t="s">
         <v>1001</v>
@@ -13209,7 +13221,7 @@
         <v>1002</v>
       </c>
       <c r="B453" s="16" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C453" s="24" t="s">
         <v>1003</v>
@@ -13247,9 +13259,9 @@
         <v>1006</v>
       </c>
       <c r="B455" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C455" s="17" t="s">
+        <v>9</v>
+      </c>
+      <c r="C455" s="24" t="s">
         <v>1007</v>
       </c>
       <c r="D455" s="4"/>
@@ -13262,13 +13274,13 @@
       <c r="K455" s="9"/>
     </row>
     <row r="456" ht="15.75" customHeight="1">
-      <c r="A456" s="22" t="s">
+      <c r="A456" s="10" t="s">
         <v>1008</v>
       </c>
       <c r="B456" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C456" s="20" t="s">
+        <v>9</v>
+      </c>
+      <c r="C456" s="12" t="s">
         <v>1009</v>
       </c>
       <c r="D456" s="4"/>
@@ -13285,9 +13297,9 @@
         <v>1010</v>
       </c>
       <c r="B457" s="16" t="s">
-        <v>58</v>
-      </c>
-      <c r="C457" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="C457" s="17" t="s">
         <v>1011</v>
       </c>
       <c r="D457" s="4"/>
@@ -13300,13 +13312,13 @@
       <c r="K457" s="9"/>
     </row>
     <row r="458" ht="15.75" customHeight="1">
-      <c r="A458" s="10" t="s">
+      <c r="A458" s="22" t="s">
         <v>1012</v>
       </c>
       <c r="B458" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C458" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="C458" s="20" t="s">
         <v>1013</v>
       </c>
       <c r="D458" s="4"/>
@@ -13323,7 +13335,7 @@
         <v>1014</v>
       </c>
       <c r="B459" s="16" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="C459" s="24" t="s">
         <v>1015</v>
@@ -13342,9 +13354,9 @@
         <v>1016</v>
       </c>
       <c r="B460" s="11" t="s">
-        <v>87</v>
-      </c>
-      <c r="C460" s="20" t="s">
+        <v>48</v>
+      </c>
+      <c r="C460" s="12" t="s">
         <v>1017</v>
       </c>
       <c r="D460" s="4"/>
@@ -13376,13 +13388,13 @@
       <c r="K461" s="9"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="34" t="s">
+      <c r="A462" s="10" t="s">
         <v>1020</v>
       </c>
       <c r="B462" s="11" t="s">
         <v>87</v>
       </c>
-      <c r="C462" s="35" t="s">
+      <c r="C462" s="20" t="s">
         <v>1021</v>
       </c>
       <c r="D462" s="4"/>
@@ -13399,9 +13411,9 @@
         <v>1022</v>
       </c>
       <c r="B463" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C463" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C463" s="24" t="s">
         <v>1023</v>
       </c>
       <c r="D463" s="4"/>
@@ -13433,14 +13445,14 @@
       <c r="K464" s="9"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="38" t="s">
-        <v>994</v>
+      <c r="A465" s="15" t="s">
+        <v>1026</v>
       </c>
       <c r="B465" s="16" t="s">
-        <v>87</v>
-      </c>
-      <c r="C465" s="40" t="s">
-        <v>1026</v>
+        <v>68</v>
+      </c>
+      <c r="C465" s="17" t="s">
+        <v>1027</v>
       </c>
       <c r="D465" s="4"/>
       <c r="E465" s="4"/>
@@ -13452,14 +13464,14 @@
       <c r="K465" s="9"/>
     </row>
     <row r="466" ht="15.75" customHeight="1">
-      <c r="A466" s="10" t="s">
-        <v>1027</v>
-      </c>
-      <c r="B466" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C466" s="12" t="s">
+      <c r="A466" s="34" t="s">
         <v>1028</v>
+      </c>
+      <c r="B466" s="11" t="s">
+        <v>87</v>
+      </c>
+      <c r="C466" s="35" t="s">
+        <v>1029</v>
       </c>
       <c r="D466" s="4"/>
       <c r="E466" s="4"/>
@@ -13471,13 +13483,13 @@
       <c r="K466" s="9"/>
     </row>
     <row r="467" ht="15.75" customHeight="1">
-      <c r="A467" s="15" t="s">
-        <v>1029</v>
+      <c r="A467" s="38" t="s">
+        <v>998</v>
       </c>
       <c r="B467" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C467" s="17" t="s">
+        <v>87</v>
+      </c>
+      <c r="C467" s="40" t="s">
         <v>1030</v>
       </c>
       <c r="D467" s="4"/>
@@ -13490,13 +13502,13 @@
       <c r="K467" s="9"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="34" t="s">
+      <c r="A468" s="10" t="s">
         <v>1031</v>
       </c>
-      <c r="B468" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C468" s="35" t="s">
+      <c r="B468" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C468" s="12" t="s">
         <v>1032</v>
       </c>
       <c r="D468" s="4"/>
@@ -13509,13 +13521,13 @@
       <c r="K468" s="9"/>
     </row>
     <row r="469" ht="15.75" customHeight="1">
-      <c r="A469" s="38" t="s">
+      <c r="A469" s="15" t="s">
         <v>1033</v>
       </c>
-      <c r="B469" s="39" t="s">
-        <v>53</v>
-      </c>
-      <c r="C469" s="40" t="s">
+      <c r="B469" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C469" s="17" t="s">
         <v>1034</v>
       </c>
       <c r="D469" s="4"/>
@@ -13528,13 +13540,13 @@
       <c r="K469" s="9"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="10" t="s">
+      <c r="A470" s="34" t="s">
         <v>1035</v>
       </c>
       <c r="B470" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C470" s="12" t="s">
+      <c r="C470" s="35" t="s">
         <v>1036</v>
       </c>
       <c r="D470" s="4"/>
@@ -13547,13 +13559,13 @@
       <c r="K470" s="9"/>
     </row>
     <row r="471" ht="15.75" customHeight="1">
-      <c r="A471" s="15" t="s">
+      <c r="A471" s="38" t="s">
         <v>1037</v>
       </c>
-      <c r="B471" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C471" s="24" t="s">
+      <c r="B471" s="39" t="s">
+        <v>53</v>
+      </c>
+      <c r="C471" s="40" t="s">
         <v>1038</v>
       </c>
       <c r="D471" s="4"/>
@@ -13585,13 +13597,13 @@
       <c r="K472" s="9"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="25" t="s">
+      <c r="A473" s="15" t="s">
         <v>1041</v>
       </c>
       <c r="B473" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C473" s="17" t="s">
+      <c r="C473" s="24" t="s">
         <v>1042</v>
       </c>
       <c r="D473" s="4"/>
@@ -13623,13 +13635,13 @@
       <c r="K474" s="9"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="15" t="s">
+      <c r="A475" s="25" t="s">
         <v>1045</v>
       </c>
       <c r="B475" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C475" s="24" t="s">
+      <c r="C475" s="17" t="s">
         <v>1046</v>
       </c>
       <c r="D475" s="4"/>
@@ -13642,13 +13654,13 @@
       <c r="K475" s="9"/>
     </row>
     <row r="476" ht="15.75" customHeight="1">
-      <c r="A476" s="53" t="s">
+      <c r="A476" s="10" t="s">
         <v>1047</v>
       </c>
       <c r="B476" s="11" t="s">
-        <v>141</v>
-      </c>
-      <c r="C476" s="46" t="s">
+        <v>9</v>
+      </c>
+      <c r="C476" s="12" t="s">
         <v>1048</v>
       </c>
       <c r="D476" s="4"/>
@@ -13665,7 +13677,7 @@
         <v>1049</v>
       </c>
       <c r="B477" s="16" t="s">
-        <v>363</v>
+        <v>9</v>
       </c>
       <c r="C477" s="24" t="s">
         <v>1050</v>
@@ -13680,13 +13692,13 @@
       <c r="K477" s="9"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="10" t="s">
+      <c r="A478" s="53" t="s">
         <v>1051</v>
       </c>
       <c r="B478" s="11" t="s">
-        <v>363</v>
-      </c>
-      <c r="C478" s="12" t="s">
+        <v>141</v>
+      </c>
+      <c r="C478" s="46" t="s">
         <v>1052</v>
       </c>
       <c r="D478" s="4"/>
@@ -13718,13 +13730,13 @@
       <c r="K479" s="9"/>
     </row>
     <row r="480" ht="15.75" customHeight="1">
-      <c r="A480" s="54" t="s">
+      <c r="A480" s="10" t="s">
         <v>1055</v>
       </c>
-      <c r="B480" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C480" s="56" t="s">
+      <c r="B480" s="11" t="s">
+        <v>363</v>
+      </c>
+      <c r="C480" s="12" t="s">
         <v>1056</v>
       </c>
       <c r="D480" s="4"/>
@@ -13736,9 +13748,47 @@
       <c r="J480" s="9"/>
       <c r="K480" s="9"/>
     </row>
+    <row r="481" ht="15.75" customHeight="1">
+      <c r="A481" s="15" t="s">
+        <v>1057</v>
+      </c>
+      <c r="B481" s="16" t="s">
+        <v>363</v>
+      </c>
+      <c r="C481" s="24" t="s">
+        <v>1058</v>
+      </c>
+      <c r="D481" s="4"/>
+      <c r="E481" s="4"/>
+      <c r="F481" s="4"/>
+      <c r="G481" s="4"/>
+      <c r="H481" s="4"/>
+      <c r="I481" s="4"/>
+      <c r="J481" s="9"/>
+      <c r="K481" s="9"/>
+    </row>
+    <row r="482" ht="15.75" customHeight="1">
+      <c r="A482" s="54" t="s">
+        <v>1059</v>
+      </c>
+      <c r="B482" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C482" s="56" t="s">
+        <v>1060</v>
+      </c>
+      <c r="D482" s="4"/>
+      <c r="E482" s="4"/>
+      <c r="F482" s="4"/>
+      <c r="G482" s="4"/>
+      <c r="H482" s="4"/>
+      <c r="I482" s="4"/>
+      <c r="J482" s="9"/>
+      <c r="K482" s="9"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B480">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B482">
       <formula1>"adjective,adjective-adverb,adverb,auxiliary,conjunction,interjection,noun,numeral,preposition,pronoun,verb"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13764,10 +13814,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>1057</v>
+        <v>1061</v>
       </c>
       <c r="D1" s="57" t="s">
-        <v>1058</v>
+        <v>1062</v>
       </c>
       <c r="G1" s="58"/>
       <c r="H1" s="58"/>
@@ -13775,16 +13825,16 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E2" s="59" t="s">
-        <v>900</v>
+        <v>904</v>
       </c>
       <c r="G2" s="58"/>
       <c r="H2" s="58"/>
@@ -13795,13 +13845,13 @@
         <v>113</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="D3" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>1062</v>
+        <v>1066</v>
       </c>
       <c r="G3" s="58"/>
       <c r="H3" s="58"/>
@@ -13810,17 +13860,17 @@
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="60"/>
       <c r="B4" s="61" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="D4" s="60"/>
       <c r="E4" s="61" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="G4" s="58"/>
       <c r="H4" s="58"/>
@@ -13828,22 +13878,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="57" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>1068</v>
+        <v>1072</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>1069</v>
+        <v>1073</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="58"/>
@@ -13851,22 +13901,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="57" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1071</v>
+        <v>1075</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1072</v>
+        <v>1076</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1073</v>
+        <v>1077</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1074</v>
+        <v>1078</v>
       </c>
       <c r="G6" s="58"/>
       <c r="H6" s="58"/>
@@ -13874,33 +13924,33 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="57" t="s">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>1076</v>
+        <v>1080</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>1077</v>
+        <v>1081</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="57" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>789</v>
+        <v>791</v>
       </c>
       <c r="G8" s="57" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="H8" s="59" t="s">
-        <v>883</v>
+        <v>887</v>
       </c>
     </row>
     <row r="9" ht="18.75" customHeight="1">
@@ -13908,108 +13958,108 @@
         <v>113</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E9" s="59" t="s">
-        <v>1078</v>
+        <v>1082</v>
       </c>
       <c r="G9" s="57" t="s">
         <v>113</v>
       </c>
       <c r="H9" s="59" t="s">
-        <v>1079</v>
+        <v>1083</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="60"/>
       <c r="B10" s="61" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="D10" s="60"/>
       <c r="E10" s="61" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="F10" s="61" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="G10" s="60"/>
       <c r="H10" s="61" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="I10" s="61" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="57" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C11" s="59" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="E11" s="59" t="s">
-        <v>1080</v>
+        <v>1084</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>1081</v>
+        <v>1085</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>1082</v>
+        <v>1086</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>1083</v>
+        <v>1087</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="57" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1084</v>
+        <v>1088</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1086</v>
+        <v>1090</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1087</v>
+        <v>1091</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>1088</v>
+        <v>1092</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>1089</v>
+        <v>1093</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="57" t="s">
-        <v>1090</v>
+        <v>1094</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>1091</v>
+        <v>1095</v>
       </c>
       <c r="G13" s="58"/>
       <c r="H13" s="58"/>
@@ -14017,16 +14067,16 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="57" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1060</v>
+        <v>1064</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="E14" s="59" t="s">
-        <v>783</v>
+        <v>785</v>
       </c>
       <c r="G14" s="58"/>
       <c r="H14" s="58"/>
@@ -14037,13 +14087,13 @@
         <v>113</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>1061</v>
+        <v>1065</v>
       </c>
       <c r="D15" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E15" s="59" t="s">
-        <v>1092</v>
+        <v>1096</v>
       </c>
       <c r="G15" s="58"/>
       <c r="H15" s="58"/>
@@ -14052,17 +14102,17 @@
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="60"/>
       <c r="B16" s="61" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="D16" s="60"/>
       <c r="E16" s="61" t="s">
-        <v>1063</v>
+        <v>1067</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>1064</v>
+        <v>1068</v>
       </c>
       <c r="G16" s="58"/>
       <c r="H16" s="58"/>
@@ -14070,22 +14120,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="57" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>1066</v>
+        <v>1070</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>1067</v>
+        <v>1071</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>1065</v>
+        <v>1069</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>1093</v>
+        <v>1097</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>1094</v>
+        <v>1098</v>
       </c>
       <c r="G17" s="58"/>
       <c r="H17" s="58"/>
@@ -14093,22 +14143,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="57" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1095</v>
+        <v>1099</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1085</v>
+        <v>1089</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>1070</v>
+        <v>1074</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>1096</v>
+        <v>1100</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>1097</v>
+        <v>1101</v>
       </c>
       <c r="G18" s="58"/>
       <c r="H18" s="58"/>
@@ -14127,13 +14177,13 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>1098</v>
+        <v>1102</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>1099</v>
+        <v>1103</v>
       </c>
       <c r="D20" s="64" t="s">
-        <v>1100</v>
+        <v>1104</v>
       </c>
       <c r="F20" s="62"/>
       <c r="G20" s="62"/>
@@ -14142,16 +14192,16 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="B21" s="65" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="D21" s="65" t="s">
-        <v>1101</v>
+        <v>1105</v>
       </c>
       <c r="E21" s="65" t="s">
-        <v>1102</v>
+        <v>1106</v>
       </c>
       <c r="F21" s="62"/>
       <c r="G21" s="62"/>
@@ -14160,19 +14210,19 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="66" t="s">
-        <v>1103</v>
+        <v>1107</v>
       </c>
       <c r="B22" s="59" t="s">
         <v>26</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1104</v>
+        <v>1108</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>1105</v>
+        <v>1109</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>1106</v>
+        <v>1110</v>
       </c>
       <c r="F22" s="62"/>
       <c r="G22" s="62"/>
@@ -14181,19 +14231,19 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="64" t="s">
-        <v>1107</v>
+        <v>1111</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>1108</v>
+        <v>1112</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>1109</v>
+        <v>1113</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>1110</v>
+        <v>1114</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>1111</v>
+        <v>1115</v>
       </c>
       <c r="F23" s="62"/>
       <c r="G23" s="62"/>
@@ -15087,7 +15137,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>1112</v>
+        <v>1116</v>
       </c>
       <c r="C1" s="58"/>
       <c r="D1" s="59"/>
@@ -15099,10 +15149,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>1113</v>
+        <v>1117</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1114</v>
+        <v>1118</v>
       </c>
       <c r="C2" s="59"/>
       <c r="D2" s="59"/>
@@ -15114,10 +15164,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="59" t="s">
-        <v>1115</v>
+        <v>1119</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="C3" s="59"/>
       <c r="D3" s="59"/>
@@ -15129,7 +15179,7 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="59" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="B4" s="59" t="s">
         <v>399</v>
@@ -15144,10 +15194,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="59" t="s">
-        <v>1117</v>
+        <v>1121</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="C5" s="59"/>
       <c r="D5" s="59"/>
@@ -15162,7 +15212,7 @@
         <v>399</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="C6" s="59"/>
       <c r="D6" s="59"/>
@@ -15174,10 +15224,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="59" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="C7" s="59"/>
       <c r="D7" s="59"/>
@@ -15198,10 +15248,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="59" t="s">
-        <v>1121</v>
+        <v>1125</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1122</v>
+        <v>1126</v>
       </c>
       <c r="C9" s="59"/>
       <c r="D9" s="59"/>
@@ -16230,62 +16280,62 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="69" t="s">
-        <v>1123</v>
+        <v>1127</v>
       </c>
       <c r="C1" s="70"/>
       <c r="D1" s="71" t="s">
-        <v>1124</v>
+        <v>1128</v>
       </c>
       <c r="H1" s="72"/>
       <c r="I1" s="72"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="71" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="B2" s="71" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="C2" s="72"/>
       <c r="D2" s="71" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="E2" s="71" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="H2" s="72"/>
       <c r="I2" s="72"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="73" t="s">
-        <v>1127</v>
+        <v>1131</v>
       </c>
       <c r="B3" s="59" t="s">
         <v>131</v>
       </c>
       <c r="C3" s="73"/>
       <c r="D3" s="59" t="s">
-        <v>1128</v>
+        <v>1132</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>1129</v>
+        <v>1133</v>
       </c>
       <c r="H3" s="72"/>
       <c r="I3" s="72"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="59" t="s">
-        <v>1130</v>
+        <v>1134</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>1131</v>
+        <v>1135</v>
       </c>
       <c r="C4" s="73"/>
       <c r="D4" s="73" t="s">
-        <v>1132</v>
+        <v>1136</v>
       </c>
       <c r="E4" s="73" t="s">
-        <v>1133</v>
+        <v>1137</v>
       </c>
       <c r="F4" s="73"/>
       <c r="G4" s="73"/>
@@ -16301,10 +16351,10 @@
       </c>
       <c r="C5" s="73"/>
       <c r="D5" s="59" t="s">
-        <v>1134</v>
+        <v>1138</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>1135</v>
+        <v>1139</v>
       </c>
       <c r="F5" s="73"/>
       <c r="G5" s="73"/>
@@ -16313,17 +16363,17 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="73" t="s">
-        <v>1116</v>
+        <v>1120</v>
       </c>
       <c r="B6" s="73" t="s">
         <v>144</v>
       </c>
       <c r="C6" s="73"/>
       <c r="D6" s="59" t="s">
-        <v>1136</v>
+        <v>1140</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1137</v>
+        <v>1141</v>
       </c>
       <c r="F6" s="73"/>
       <c r="G6" s="73"/>
@@ -16339,10 +16389,10 @@
       </c>
       <c r="C7" s="73"/>
       <c r="D7" s="59" t="s">
-        <v>1138</v>
+        <v>1142</v>
       </c>
       <c r="E7" s="59" t="s">
-        <v>1139</v>
+        <v>1143</v>
       </c>
       <c r="F7" s="73"/>
       <c r="G7" s="73"/>
@@ -16351,17 +16401,17 @@
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="73" t="s">
-        <v>1140</v>
+        <v>1144</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>152</v>
       </c>
       <c r="C8" s="73"/>
       <c r="D8" s="59" t="s">
-        <v>1141</v>
+        <v>1145</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1142</v>
+        <v>1146</v>
       </c>
       <c r="F8" s="73"/>
       <c r="G8" s="73"/>
@@ -16370,10 +16420,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="59" t="s">
-        <v>1118</v>
+        <v>1122</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1143</v>
+        <v>1147</v>
       </c>
       <c r="C9" s="73"/>
       <c r="D9" s="73"/>
@@ -16385,7 +16435,7 @@
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="73" t="s">
-        <v>1120</v>
+        <v>1124</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>156</v>
@@ -16400,7 +16450,7 @@
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="73" t="s">
-        <v>1119</v>
+        <v>1123</v>
       </c>
       <c r="B11" s="59" t="s">
         <v>162</v>
@@ -16437,7 +16487,7 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="71" t="s">
-        <v>1144</v>
+        <v>1148</v>
       </c>
       <c r="C14" s="72"/>
       <c r="D14" s="72"/>
@@ -16449,10 +16499,10 @@
     </row>
     <row r="15" ht="18.75" customHeight="1">
       <c r="A15" s="71" t="s">
-        <v>1125</v>
+        <v>1129</v>
       </c>
       <c r="B15" s="71" t="s">
-        <v>1126</v>
+        <v>1130</v>
       </c>
       <c r="C15" s="72"/>
       <c r="D15" s="72"/>
@@ -16464,10 +16514,10 @@
     </row>
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="73" t="s">
-        <v>1145</v>
+        <v>1149</v>
       </c>
       <c r="B16" s="73" t="s">
-        <v>1146</v>
+        <v>1150</v>
       </c>
       <c r="C16" s="72"/>
       <c r="D16" s="72"/>
@@ -16479,10 +16529,10 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="73" t="s">
-        <v>1147</v>
+        <v>1151</v>
       </c>
       <c r="B17" s="73" t="s">
-        <v>1148</v>
+        <v>1152</v>
       </c>
       <c r="C17" s="72"/>
       <c r="D17" s="72"/>
@@ -16494,10 +16544,10 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="73" t="s">
-        <v>1149</v>
+        <v>1153</v>
       </c>
       <c r="B18" s="73" t="s">
-        <v>1150</v>
+        <v>1154</v>
       </c>
       <c r="C18" s="72"/>
       <c r="D18" s="72"/>
@@ -16509,10 +16559,10 @@
     </row>
     <row r="19" ht="18.75" customHeight="1">
       <c r="A19" s="73" t="s">
-        <v>1151</v>
+        <v>1155</v>
       </c>
       <c r="B19" s="73" t="s">
-        <v>1152</v>
+        <v>1156</v>
       </c>
       <c r="C19" s="72"/>
       <c r="D19" s="72"/>
@@ -16524,10 +16574,10 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="59" t="s">
-        <v>1153</v>
+        <v>1157</v>
       </c>
       <c r="B20" s="73" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="C20" s="72"/>
       <c r="D20" s="72"/>
@@ -16539,10 +16589,10 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="59" t="s">
-        <v>1155</v>
+        <v>1159</v>
       </c>
       <c r="B21" s="73" t="s">
-        <v>1154</v>
+        <v>1158</v>
       </c>
       <c r="C21" s="72"/>
       <c r="D21" s="72"/>
@@ -16554,10 +16604,10 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="59" t="s">
-        <v>1156</v>
+        <v>1160</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1157</v>
+        <v>1161</v>
       </c>
       <c r="C22" s="72"/>
       <c r="D22" s="72"/>
@@ -16569,10 +16619,10 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="59" t="s">
-        <v>1158</v>
+        <v>1162</v>
       </c>
       <c r="B23" s="73" t="s">
-        <v>1159</v>
+        <v>1163</v>
       </c>
       <c r="C23" s="72"/>
       <c r="D23" s="72"/>
@@ -16584,7 +16634,7 @@
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="59" t="s">
-        <v>1160</v>
+        <v>1164</v>
       </c>
       <c r="C24" s="72"/>
       <c r="D24" s="72"/>
@@ -16596,10 +16646,10 @@
     </row>
     <row r="25" ht="18.75" customHeight="1">
       <c r="A25" s="73" t="s">
-        <v>1161</v>
+        <v>1165</v>
       </c>
       <c r="B25" s="73" t="s">
-        <v>1162</v>
+        <v>1166</v>
       </c>
       <c r="C25" s="72"/>
       <c r="D25" s="72"/>
@@ -16611,10 +16661,10 @@
     </row>
     <row r="26" ht="18.75" customHeight="1">
       <c r="A26" s="73" t="s">
-        <v>1163</v>
+        <v>1167</v>
       </c>
       <c r="B26" s="73" t="s">
-        <v>1164</v>
+        <v>1168</v>
       </c>
       <c r="C26" s="72"/>
       <c r="D26" s="72"/>
@@ -16626,10 +16676,10 @@
     </row>
     <row r="27" ht="18.75" customHeight="1">
       <c r="A27" s="73" t="s">
-        <v>1165</v>
+        <v>1169</v>
       </c>
       <c r="B27" s="73" t="s">
-        <v>1166</v>
+        <v>1170</v>
       </c>
       <c r="C27" s="72"/>
       <c r="D27" s="72"/>
@@ -16641,10 +16691,10 @@
     </row>
     <row r="28" ht="18.75" customHeight="1">
       <c r="A28" s="73" t="s">
-        <v>1167</v>
+        <v>1171</v>
       </c>
       <c r="B28" s="73" t="s">
-        <v>1168</v>
+        <v>1172</v>
       </c>
       <c r="C28" s="72"/>
       <c r="D28" s="72"/>
@@ -16656,10 +16706,10 @@
     </row>
     <row r="29" ht="18.75" customHeight="1">
       <c r="A29" s="73" t="s">
-        <v>1169</v>
+        <v>1173</v>
       </c>
       <c r="B29" s="73" t="s">
-        <v>1170</v>
+        <v>1174</v>
       </c>
       <c r="C29" s="72"/>
       <c r="D29" s="72"/>
@@ -16671,10 +16721,10 @@
     </row>
     <row r="30" ht="18.75" customHeight="1">
       <c r="A30" s="73" t="s">
-        <v>1171</v>
+        <v>1175</v>
       </c>
       <c r="B30" s="73" t="s">
-        <v>1172</v>
+        <v>1176</v>
       </c>
       <c r="C30" s="72"/>
       <c r="D30" s="72"/>
@@ -16686,10 +16736,10 @@
     </row>
     <row r="31" ht="18.75" customHeight="1">
       <c r="A31" s="73" t="s">
-        <v>1173</v>
+        <v>1177</v>
       </c>
       <c r="B31" s="73" t="s">
-        <v>1174</v>
+        <v>1178</v>
       </c>
       <c r="C31" s="72"/>
       <c r="D31" s="72"/>
@@ -16701,7 +16751,7 @@
     </row>
     <row r="32" ht="18.75" customHeight="1">
       <c r="A32" s="73" t="s">
-        <v>1175</v>
+        <v>1179</v>
       </c>
       <c r="B32" s="73" t="s">
         <v>174</v>
@@ -16716,10 +16766,10 @@
     </row>
     <row r="33" ht="18.75" customHeight="1">
       <c r="A33" s="73" t="s">
-        <v>1176</v>
+        <v>1180</v>
       </c>
       <c r="B33" s="73" t="s">
-        <v>1177</v>
+        <v>1181</v>
       </c>
       <c r="C33" s="72"/>
       <c r="D33" s="72"/>
@@ -16731,10 +16781,10 @@
     </row>
     <row r="34" ht="18.75" customHeight="1">
       <c r="A34" s="73" t="s">
-        <v>1178</v>
+        <v>1182</v>
       </c>
       <c r="B34" s="73" t="s">
-        <v>1179</v>
+        <v>1183</v>
       </c>
       <c r="C34" s="72"/>
       <c r="D34" s="72"/>
@@ -16746,10 +16796,10 @@
     </row>
     <row r="35" ht="18.75" customHeight="1">
       <c r="A35" s="73" t="s">
-        <v>1180</v>
+        <v>1184</v>
       </c>
       <c r="B35" s="59" t="s">
-        <v>1181</v>
+        <v>1185</v>
       </c>
       <c r="C35" s="72"/>
       <c r="D35" s="72"/>
@@ -16761,10 +16811,10 @@
     </row>
     <row r="36" ht="18.75" customHeight="1">
       <c r="A36" s="73" t="s">
-        <v>1182</v>
+        <v>1186</v>
       </c>
       <c r="B36" s="59" t="s">
-        <v>1183</v>
+        <v>1187</v>
       </c>
       <c r="C36" s="72"/>
       <c r="D36" s="72"/>
@@ -16776,10 +16826,10 @@
     </row>
     <row r="37" ht="18.75" customHeight="1">
       <c r="A37" s="73" t="s">
-        <v>1184</v>
+        <v>1188</v>
       </c>
       <c r="B37" s="73" t="s">
-        <v>1185</v>
+        <v>1189</v>
       </c>
       <c r="C37" s="72"/>
       <c r="D37" s="72"/>
@@ -16791,10 +16841,10 @@
     </row>
     <row r="38" ht="18.75" customHeight="1">
       <c r="A38" s="73" t="s">
-        <v>1186</v>
+        <v>1190</v>
       </c>
       <c r="B38" s="73" t="s">
-        <v>1187</v>
+        <v>1191</v>
       </c>
       <c r="C38" s="72"/>
       <c r="D38" s="72"/>

--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -1593,7 +1593,7 @@
     <t>av</t>
   </si>
   <si>
-    <t>of</t>
+    <t>of; done by</t>
   </si>
   <si>
     <t>åfe</t>

--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -9,14 +9,14 @@
     <sheet state="visible" name="Pronunciation" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$486</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$489</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1767" uniqueCount="1200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1207">
   <si>
     <t>Word</t>
   </si>
@@ -2238,6 +2238,15 @@
     <t>to be missing; to lack</t>
   </si>
   <si>
+    <t>til-</t>
+  </si>
+  <si>
+    <t>prefix</t>
+  </si>
+  <si>
+    <t>to become (equivalent to the -en suffix verb ending in english like "redden" or "madden")</t>
+  </si>
+  <si>
     <t>ginnen</t>
   </si>
   <si>
@@ -2391,6 +2400,12 @@
     <t>to explore</t>
   </si>
   <si>
+    <t>ei-splåken</t>
+  </si>
+  <si>
+    <t>to extinguish, to put out</t>
+  </si>
+  <si>
     <t>mørknen</t>
   </si>
   <si>
@@ -2992,6 +3007,12 @@
   </si>
   <si>
     <t>under, or below</t>
+  </si>
+  <si>
+    <t>ei-</t>
+  </si>
+  <si>
+    <t>verb negator prefix</t>
   </si>
   <si>
     <t>æg</t>
@@ -3881,10 +3902,10 @@
         <color rgb="FF284E3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3892,13 +3913,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </left>
       <right style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3906,13 +3927,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </left>
       <right style="thin">
         <color rgb="FF284E3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFFFFFFF"/>
+        <color rgb="FFF6F8F9"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3922,7 +3943,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="75">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -4078,6 +4099,9 @@
     <xf borderId="7" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
+    <xf borderId="8" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment horizontal="left" shrinkToFit="0" vertical="center" wrapText="0"/>
+    </xf>
     <xf borderId="11" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="0"/>
     </xf>
@@ -4211,8 +4235,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C486" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$486"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C489" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$489"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Type" id="2"/>
@@ -4542,7 +4566,7 @@
         <v>25</v>
       </c>
       <c r="H4" s="21" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C486, REGEXMATCH(C2:C486, I3)), 2, TRUE)"),"ibyrten")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C489, REGEXMATCH(C2:C489, I3)), 2, TRUE)"),"ibyrten")</f>
         <v>ibyrten</v>
       </c>
       <c r="I4" s="4" t="str">
@@ -10711,14 +10735,14 @@
       <c r="K319" s="9"/>
     </row>
     <row r="320" ht="15.75" customHeight="1">
-      <c r="A320" s="34" t="s">
+      <c r="A320" s="10" t="s">
         <v>740</v>
       </c>
       <c r="B320" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C320" s="35" t="s">
         <v>741</v>
+      </c>
+      <c r="C320" s="12" t="s">
+        <v>742</v>
       </c>
       <c r="D320" s="4"/>
       <c r="E320" s="4"/>
@@ -10731,13 +10755,13 @@
     </row>
     <row r="321" ht="15.75" customHeight="1">
       <c r="A321" s="40" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B321" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C321" s="41" t="s">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="D321" s="4"/>
       <c r="E321" s="4"/>
@@ -10749,14 +10773,14 @@
       <c r="K321" s="9"/>
     </row>
     <row r="322" ht="15.75" customHeight="1">
-      <c r="A322" s="10" t="s">
-        <v>744</v>
+      <c r="A322" s="34" t="s">
+        <v>745</v>
       </c>
       <c r="B322" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C322" s="20" t="s">
-        <v>745</v>
+      <c r="C322" s="35" t="s">
+        <v>746</v>
       </c>
       <c r="D322" s="4"/>
       <c r="E322" s="4"/>
@@ -10769,13 +10793,13 @@
     </row>
     <row r="323" ht="15.75" customHeight="1">
       <c r="A323" s="15" t="s">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="B323" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C323" s="17" t="s">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D323" s="4"/>
       <c r="E323" s="4"/>
@@ -10787,14 +10811,14 @@
       <c r="K323" s="9"/>
     </row>
     <row r="324" ht="15.75" customHeight="1">
-      <c r="A324" s="34" t="s">
-        <v>748</v>
+      <c r="A324" s="10" t="s">
+        <v>749</v>
       </c>
       <c r="B324" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C324" s="35" t="s">
-        <v>749</v>
+      <c r="C324" s="20" t="s">
+        <v>750</v>
       </c>
       <c r="D324" s="4"/>
       <c r="E324" s="4"/>
@@ -10806,14 +10830,14 @@
       <c r="K324" s="9"/>
     </row>
     <row r="325" ht="15.75" customHeight="1">
-      <c r="A325" s="15" t="s">
-        <v>750</v>
+      <c r="A325" s="40" t="s">
+        <v>751</v>
       </c>
       <c r="B325" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C325" s="24" t="s">
-        <v>751</v>
+      <c r="C325" s="41" t="s">
+        <v>752</v>
       </c>
       <c r="D325" s="4"/>
       <c r="E325" s="4"/>
@@ -10825,14 +10849,14 @@
       <c r="K325" s="9"/>
     </row>
     <row r="326" ht="15.75" customHeight="1">
-      <c r="A326" s="34" t="s">
-        <v>752</v>
+      <c r="A326" s="10" t="s">
+        <v>753</v>
       </c>
       <c r="B326" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C326" s="35" t="s">
-        <v>753</v>
+      <c r="C326" s="12" t="s">
+        <v>754</v>
       </c>
       <c r="D326" s="4"/>
       <c r="E326" s="4"/>
@@ -10845,13 +10869,13 @@
     </row>
     <row r="327" ht="15.75" customHeight="1">
       <c r="A327" s="40" t="s">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="B327" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C327" s="41" t="s">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="D327" s="4"/>
       <c r="E327" s="4"/>
@@ -10863,14 +10887,14 @@
       <c r="K327" s="9"/>
     </row>
     <row r="328" ht="15.75" customHeight="1">
-      <c r="A328" s="10" t="s">
-        <v>756</v>
+      <c r="A328" s="34" t="s">
+        <v>757</v>
       </c>
       <c r="B328" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C328" s="12" t="s">
-        <v>757</v>
+      <c r="C328" s="35" t="s">
+        <v>758</v>
       </c>
       <c r="D328" s="4"/>
       <c r="E328" s="4"/>
@@ -10883,13 +10907,13 @@
     </row>
     <row r="329" ht="15.75" customHeight="1">
       <c r="A329" s="15" t="s">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="B329" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C329" s="24" t="s">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="D329" s="4"/>
       <c r="E329" s="4"/>
@@ -10901,14 +10925,14 @@
       <c r="K329" s="9"/>
     </row>
     <row r="330" ht="15.75" customHeight="1">
-      <c r="A330" s="34" t="s">
-        <v>760</v>
+      <c r="A330" s="10" t="s">
+        <v>761</v>
       </c>
       <c r="B330" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C330" s="35" t="s">
-        <v>761</v>
+      <c r="C330" s="12" t="s">
+        <v>762</v>
       </c>
       <c r="D330" s="4"/>
       <c r="E330" s="4"/>
@@ -10921,13 +10945,13 @@
     </row>
     <row r="331" ht="15.75" customHeight="1">
       <c r="A331" s="40" t="s">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="B331" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C331" s="41" t="s">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D331" s="4"/>
       <c r="E331" s="4"/>
@@ -10939,14 +10963,14 @@
       <c r="K331" s="9"/>
     </row>
     <row r="332" ht="15.75" customHeight="1">
-      <c r="A332" s="10" t="s">
-        <v>764</v>
+      <c r="A332" s="34" t="s">
+        <v>765</v>
       </c>
       <c r="B332" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C332" s="12" t="s">
-        <v>765</v>
+      <c r="C332" s="35" t="s">
+        <v>766</v>
       </c>
       <c r="D332" s="4"/>
       <c r="E332" s="4"/>
@@ -10958,14 +10982,14 @@
       <c r="K332" s="9"/>
     </row>
     <row r="333" ht="15.75" customHeight="1">
-      <c r="A333" s="40" t="s">
-        <v>766</v>
+      <c r="A333" s="15" t="s">
+        <v>767</v>
       </c>
       <c r="B333" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C333" s="41" t="s">
-        <v>767</v>
+      <c r="C333" s="24" t="s">
+        <v>768</v>
       </c>
       <c r="D333" s="4"/>
       <c r="E333" s="4"/>
@@ -10978,13 +11002,13 @@
     </row>
     <row r="334" ht="15.75" customHeight="1">
       <c r="A334" s="34" t="s">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="B334" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C334" s="35" t="s">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="D334" s="4"/>
       <c r="E334" s="4"/>
@@ -10996,14 +11020,14 @@
       <c r="K334" s="9"/>
     </row>
     <row r="335" ht="15.75" customHeight="1">
-      <c r="A335" s="15" t="s">
-        <v>770</v>
+      <c r="A335" s="40" t="s">
+        <v>771</v>
       </c>
       <c r="B335" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C335" s="24" t="s">
-        <v>771</v>
+        <v>48</v>
+      </c>
+      <c r="C335" s="41" t="s">
+        <v>772</v>
       </c>
       <c r="D335" s="4"/>
       <c r="E335" s="4"/>
@@ -11016,13 +11040,13 @@
     </row>
     <row r="336" ht="15.75" customHeight="1">
       <c r="A336" s="10" t="s">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="B336" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C336" s="20" t="s">
-        <v>773</v>
+        <v>9</v>
+      </c>
+      <c r="C336" s="12" t="s">
+        <v>774</v>
       </c>
       <c r="D336" s="4"/>
       <c r="E336" s="4"/>
@@ -11034,14 +11058,14 @@
       <c r="K336" s="9"/>
     </row>
     <row r="337" ht="15.75" customHeight="1">
-      <c r="A337" s="40" t="s">
-        <v>774</v>
+      <c r="A337" s="15" t="s">
+        <v>775</v>
       </c>
       <c r="B337" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C337" s="17" t="s">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="D337" s="4"/>
       <c r="E337" s="4"/>
@@ -11053,14 +11077,14 @@
       <c r="K337" s="9"/>
     </row>
     <row r="338" ht="15.75" customHeight="1">
-      <c r="A338" s="10" t="s">
-        <v>776</v>
+      <c r="A338" s="34" t="s">
+        <v>777</v>
       </c>
       <c r="B338" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C338" s="20" t="s">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="D338" s="4"/>
       <c r="E338" s="4"/>
@@ -11072,14 +11096,14 @@
       <c r="K338" s="9"/>
     </row>
     <row r="339" ht="15.75" customHeight="1">
-      <c r="A339" s="40" t="s">
-        <v>778</v>
+      <c r="A339" s="15" t="s">
+        <v>779</v>
       </c>
       <c r="B339" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C339" s="41" t="s">
-        <v>779</v>
+      <c r="C339" s="17" t="s">
+        <v>780</v>
       </c>
       <c r="D339" s="4"/>
       <c r="E339" s="4"/>
@@ -11091,14 +11115,14 @@
       <c r="K339" s="9"/>
     </row>
     <row r="340" ht="15.75" customHeight="1">
-      <c r="A340" s="10" t="s">
-        <v>780</v>
+      <c r="A340" s="34" t="s">
+        <v>781</v>
       </c>
       <c r="B340" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C340" s="12" t="s">
-        <v>779</v>
+      <c r="C340" s="35" t="s">
+        <v>782</v>
       </c>
       <c r="D340" s="4"/>
       <c r="E340" s="4"/>
@@ -11111,12 +11135,12 @@
     </row>
     <row r="341" ht="15.75" customHeight="1">
       <c r="A341" s="15" t="s">
-        <v>781</v>
+        <v>783</v>
       </c>
       <c r="B341" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C341" s="17" t="s">
+      <c r="C341" s="24" t="s">
         <v>782</v>
       </c>
       <c r="D341" s="4"/>
@@ -11130,13 +11154,13 @@
     </row>
     <row r="342" ht="15.75" customHeight="1">
       <c r="A342" s="10" t="s">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="B342" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C342" s="20" t="s">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="D342" s="4"/>
       <c r="E342" s="4"/>
@@ -11149,13 +11173,13 @@
     </row>
     <row r="343" ht="15.75" customHeight="1">
       <c r="A343" s="15" t="s">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="B343" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C343" s="24" t="s">
-        <v>786</v>
+      <c r="C343" s="17" t="s">
+        <v>787</v>
       </c>
       <c r="D343" s="4"/>
       <c r="E343" s="4"/>
@@ -11168,13 +11192,13 @@
     </row>
     <row r="344" ht="15.75" customHeight="1">
       <c r="A344" s="10" t="s">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="B344" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C344" s="12" t="s">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D344" s="4"/>
       <c r="E344" s="4"/>
@@ -11186,14 +11210,14 @@
       <c r="K344" s="9"/>
     </row>
     <row r="345" ht="15.75" customHeight="1">
-      <c r="A345" s="40" t="s">
-        <v>789</v>
+      <c r="A345" s="15" t="s">
+        <v>790</v>
       </c>
       <c r="B345" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C345" s="41" t="s">
-        <v>790</v>
+      <c r="C345" s="24" t="s">
+        <v>791</v>
       </c>
       <c r="D345" s="4"/>
       <c r="E345" s="4"/>
@@ -11206,13 +11230,13 @@
     </row>
     <row r="346" ht="15.75" customHeight="1">
       <c r="A346" s="34" t="s">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="B346" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C346" s="35" t="s">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="D346" s="4"/>
       <c r="E346" s="4"/>
@@ -11225,13 +11249,13 @@
     </row>
     <row r="347" ht="15.75" customHeight="1">
       <c r="A347" s="15" t="s">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="B347" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C347" s="24" t="s">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="D347" s="4"/>
       <c r="E347" s="4"/>
@@ -11244,13 +11268,13 @@
     </row>
     <row r="348" ht="15.75" customHeight="1">
       <c r="A348" s="34" t="s">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="B348" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C348" s="35" t="s">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="D348" s="4"/>
       <c r="E348" s="4"/>
@@ -11263,13 +11287,13 @@
     </row>
     <row r="349" ht="15.75" customHeight="1">
       <c r="A349" s="15" t="s">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="B349" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C349" s="17" t="s">
-        <v>798</v>
+      <c r="C349" s="24" t="s">
+        <v>799</v>
       </c>
       <c r="D349" s="4"/>
       <c r="E349" s="4"/>
@@ -11281,14 +11305,14 @@
       <c r="K349" s="9"/>
     </row>
     <row r="350" ht="15.75" customHeight="1">
-      <c r="A350" s="10" t="s">
-        <v>799</v>
+      <c r="A350" s="34" t="s">
+        <v>800</v>
       </c>
       <c r="B350" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C350" s="12" t="s">
-        <v>800</v>
+      <c r="C350" s="35" t="s">
+        <v>801</v>
       </c>
       <c r="D350" s="4"/>
       <c r="E350" s="4"/>
@@ -11301,13 +11325,13 @@
     </row>
     <row r="351" ht="15.75" customHeight="1">
       <c r="A351" s="15" t="s">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="B351" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C351" s="24" t="s">
-        <v>802</v>
+      <c r="C351" s="17" t="s">
+        <v>803</v>
       </c>
       <c r="D351" s="4"/>
       <c r="E351" s="4"/>
@@ -11320,13 +11344,13 @@
     </row>
     <row r="352" ht="15.75" customHeight="1">
       <c r="A352" s="10" t="s">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="B352" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C352" s="20" t="s">
-        <v>804</v>
+      <c r="C352" s="12" t="s">
+        <v>805</v>
       </c>
       <c r="D352" s="4"/>
       <c r="E352" s="4"/>
@@ -11339,13 +11363,13 @@
     </row>
     <row r="353" ht="15.75" customHeight="1">
       <c r="A353" s="15" t="s">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="B353" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C353" s="24" t="s">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D353" s="4"/>
       <c r="E353" s="4"/>
@@ -11358,13 +11382,13 @@
     </row>
     <row r="354" ht="15.75" customHeight="1">
       <c r="A354" s="10" t="s">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="B354" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C354" s="20" t="s">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="D354" s="4"/>
       <c r="E354" s="4"/>
@@ -11377,13 +11401,13 @@
     </row>
     <row r="355" ht="15.75" customHeight="1">
       <c r="A355" s="15" t="s">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="B355" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C355" s="17" t="s">
-        <v>810</v>
+      <c r="C355" s="24" t="s">
+        <v>811</v>
       </c>
       <c r="D355" s="4"/>
       <c r="E355" s="4"/>
@@ -11396,13 +11420,13 @@
     </row>
     <row r="356" ht="15.75" customHeight="1">
       <c r="A356" s="10" t="s">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="B356" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C356" s="20" t="s">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="D356" s="4"/>
       <c r="E356" s="4"/>
@@ -11415,13 +11439,13 @@
     </row>
     <row r="357" ht="15.75" customHeight="1">
       <c r="A357" s="15" t="s">
-        <v>813</v>
+        <v>814</v>
       </c>
       <c r="B357" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C357" s="17" t="s">
-        <v>814</v>
+        <v>815</v>
       </c>
       <c r="D357" s="4"/>
       <c r="E357" s="4"/>
@@ -11434,13 +11458,13 @@
     </row>
     <row r="358" ht="15.75" customHeight="1">
       <c r="A358" s="10" t="s">
-        <v>815</v>
+        <v>816</v>
       </c>
       <c r="B358" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C358" s="12" t="s">
-        <v>816</v>
+      <c r="C358" s="20" t="s">
+        <v>817</v>
       </c>
       <c r="D358" s="4"/>
       <c r="E358" s="4"/>
@@ -11452,14 +11476,14 @@
       <c r="K358" s="9"/>
     </row>
     <row r="359" ht="15.75" customHeight="1">
-      <c r="A359" s="45" t="s">
-        <v>817</v>
+      <c r="A359" s="15" t="s">
+        <v>818</v>
       </c>
       <c r="B359" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C359" s="46" t="s">
-        <v>818</v>
+      <c r="C359" s="17" t="s">
+        <v>819</v>
       </c>
       <c r="D359" s="4"/>
       <c r="E359" s="4"/>
@@ -11472,13 +11496,13 @@
     </row>
     <row r="360" ht="15.75" customHeight="1">
       <c r="A360" s="10" t="s">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="B360" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C360" s="20" t="s">
-        <v>820</v>
+      <c r="C360" s="12" t="s">
+        <v>821</v>
       </c>
       <c r="D360" s="4"/>
       <c r="E360" s="4"/>
@@ -11490,14 +11514,14 @@
       <c r="K360" s="9"/>
     </row>
     <row r="361" ht="15.75" customHeight="1">
-      <c r="A361" s="15" t="s">
-        <v>821</v>
+      <c r="A361" s="45" t="s">
+        <v>822</v>
       </c>
       <c r="B361" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C361" s="17" t="s">
-        <v>822</v>
+      <c r="C361" s="46" t="s">
+        <v>823</v>
       </c>
       <c r="D361" s="4"/>
       <c r="E361" s="4"/>
@@ -11510,13 +11534,13 @@
     </row>
     <row r="362" ht="15.75" customHeight="1">
       <c r="A362" s="10" t="s">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="B362" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C362" s="20" t="s">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D362" s="4"/>
       <c r="E362" s="4"/>
@@ -11528,14 +11552,14 @@
       <c r="K362" s="9"/>
     </row>
     <row r="363" ht="15.75" customHeight="1">
-      <c r="A363" s="40" t="s">
-        <v>825</v>
+      <c r="A363" s="15" t="s">
+        <v>826</v>
       </c>
       <c r="B363" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C363" s="41" t="s">
-        <v>826</v>
+      <c r="C363" s="17" t="s">
+        <v>827</v>
       </c>
       <c r="D363" s="4"/>
       <c r="E363" s="4"/>
@@ -11548,13 +11572,13 @@
     </row>
     <row r="364" ht="15.75" customHeight="1">
       <c r="A364" s="10" t="s">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="B364" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C364" s="20" t="s">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="D364" s="4"/>
       <c r="E364" s="4"/>
@@ -11566,14 +11590,14 @@
       <c r="K364" s="9"/>
     </row>
     <row r="365" ht="15.75" customHeight="1">
-      <c r="A365" s="15" t="s">
-        <v>829</v>
+      <c r="A365" s="40" t="s">
+        <v>830</v>
       </c>
       <c r="B365" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C365" s="24" t="s">
-        <v>830</v>
+      <c r="C365" s="41" t="s">
+        <v>831</v>
       </c>
       <c r="D365" s="4"/>
       <c r="E365" s="4"/>
@@ -11586,13 +11610,13 @@
     </row>
     <row r="366" ht="15.75" customHeight="1">
       <c r="A366" s="10" t="s">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="B366" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C366" s="12" t="s">
-        <v>832</v>
+      <c r="C366" s="20" t="s">
+        <v>833</v>
       </c>
       <c r="D366" s="4"/>
       <c r="E366" s="4"/>
@@ -11605,13 +11629,13 @@
     </row>
     <row r="367" ht="15.75" customHeight="1">
       <c r="A367" s="15" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="B367" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C367" s="24" t="s">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="D367" s="4"/>
       <c r="E367" s="4"/>
@@ -11624,13 +11648,13 @@
     </row>
     <row r="368" ht="15.75" customHeight="1">
       <c r="A368" s="10" t="s">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="B368" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C368" s="20" t="s">
-        <v>836</v>
+      <c r="C368" s="12" t="s">
+        <v>837</v>
       </c>
       <c r="D368" s="4"/>
       <c r="E368" s="4"/>
@@ -11642,14 +11666,14 @@
       <c r="K368" s="9"/>
     </row>
     <row r="369" ht="15.75" customHeight="1">
-      <c r="A369" s="45" t="s">
-        <v>837</v>
+      <c r="A369" s="15" t="s">
+        <v>838</v>
       </c>
       <c r="B369" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C369" s="46" t="s">
-        <v>838</v>
+      <c r="C369" s="24" t="s">
+        <v>839</v>
       </c>
       <c r="D369" s="4"/>
       <c r="E369" s="4"/>
@@ -11662,13 +11686,13 @@
     </row>
     <row r="370" ht="15.75" customHeight="1">
       <c r="A370" s="10" t="s">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="B370" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C370" s="20" t="s">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="D370" s="4"/>
       <c r="E370" s="4"/>
@@ -11680,14 +11704,14 @@
       <c r="K370" s="9"/>
     </row>
     <row r="371" ht="15.75" customHeight="1">
-      <c r="A371" s="15" t="s">
-        <v>841</v>
+      <c r="A371" s="45" t="s">
+        <v>842</v>
       </c>
       <c r="B371" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C371" s="17" t="s">
-        <v>842</v>
+      <c r="C371" s="46" t="s">
+        <v>843</v>
       </c>
       <c r="D371" s="4"/>
       <c r="E371" s="4"/>
@@ -11700,13 +11724,13 @@
     </row>
     <row r="372" ht="15.75" customHeight="1">
       <c r="A372" s="10" t="s">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="B372" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C372" s="20" t="s">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="D372" s="4"/>
       <c r="E372" s="4"/>
@@ -11719,13 +11743,13 @@
     </row>
     <row r="373" ht="15.75" customHeight="1">
       <c r="A373" s="15" t="s">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="B373" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C373" s="17" t="s">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D373" s="4"/>
       <c r="E373" s="4"/>
@@ -11737,14 +11761,14 @@
       <c r="K373" s="9"/>
     </row>
     <row r="374" ht="15.75" customHeight="1">
-      <c r="A374" s="38" t="s">
-        <v>847</v>
+      <c r="A374" s="10" t="s">
+        <v>848</v>
       </c>
       <c r="B374" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C374" s="39" t="s">
-        <v>848</v>
+      <c r="C374" s="20" t="s">
+        <v>849</v>
       </c>
       <c r="D374" s="4"/>
       <c r="E374" s="4"/>
@@ -11757,13 +11781,13 @@
     </row>
     <row r="375" ht="15.75" customHeight="1">
       <c r="A375" s="15" t="s">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="B375" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C375" s="17" t="s">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="D375" s="4"/>
       <c r="E375" s="4"/>
@@ -11775,14 +11799,14 @@
       <c r="K375" s="9"/>
     </row>
     <row r="376" ht="15.75" customHeight="1">
-      <c r="A376" s="34" t="s">
-        <v>851</v>
+      <c r="A376" s="38" t="s">
+        <v>852</v>
       </c>
       <c r="B376" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C376" s="35" t="s">
-        <v>852</v>
+      <c r="C376" s="39" t="s">
+        <v>853</v>
       </c>
       <c r="D376" s="4"/>
       <c r="E376" s="4"/>
@@ -11794,14 +11818,14 @@
       <c r="K376" s="9"/>
     </row>
     <row r="377" ht="15.75" customHeight="1">
-      <c r="A377" s="40" t="s">
-        <v>853</v>
+      <c r="A377" s="15" t="s">
+        <v>854</v>
       </c>
       <c r="B377" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C377" s="41" t="s">
-        <v>854</v>
+      <c r="C377" s="17" t="s">
+        <v>855</v>
       </c>
       <c r="D377" s="4"/>
       <c r="E377" s="4"/>
@@ -11813,14 +11837,14 @@
       <c r="K377" s="9"/>
     </row>
     <row r="378" ht="15.75" customHeight="1">
-      <c r="A378" s="10" t="s">
-        <v>855</v>
+      <c r="A378" s="34" t="s">
+        <v>856</v>
       </c>
       <c r="B378" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C378" s="12" t="s">
-        <v>856</v>
+      <c r="C378" s="35" t="s">
+        <v>857</v>
       </c>
       <c r="D378" s="4"/>
       <c r="E378" s="4"/>
@@ -11833,13 +11857,13 @@
     </row>
     <row r="379" ht="15.75" customHeight="1">
       <c r="A379" s="40" t="s">
-        <v>857</v>
+        <v>858</v>
       </c>
       <c r="B379" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C379" s="41" t="s">
-        <v>858</v>
+        <v>859</v>
       </c>
       <c r="D379" s="4"/>
       <c r="E379" s="4"/>
@@ -11851,14 +11875,14 @@
       <c r="K379" s="9"/>
     </row>
     <row r="380" ht="15.75" customHeight="1">
-      <c r="A380" s="34" t="s">
-        <v>859</v>
+      <c r="A380" s="10" t="s">
+        <v>860</v>
       </c>
       <c r="B380" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C380" s="52" t="s">
-        <v>860</v>
+      <c r="C380" s="12" t="s">
+        <v>861</v>
       </c>
       <c r="D380" s="4"/>
       <c r="E380" s="4"/>
@@ -11871,13 +11895,13 @@
     </row>
     <row r="381" ht="15.75" customHeight="1">
       <c r="A381" s="40" t="s">
-        <v>861</v>
+        <v>862</v>
       </c>
       <c r="B381" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C381" s="41" t="s">
-        <v>862</v>
+        <v>863</v>
       </c>
       <c r="D381" s="4"/>
       <c r="E381" s="4"/>
@@ -11889,14 +11913,14 @@
       <c r="K381" s="9"/>
     </row>
     <row r="382" ht="15.75" customHeight="1">
-      <c r="A382" s="10" t="s">
-        <v>863</v>
+      <c r="A382" s="34" t="s">
+        <v>864</v>
       </c>
       <c r="B382" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C382" s="12" t="s">
-        <v>864</v>
+      <c r="C382" s="52" t="s">
+        <v>865</v>
       </c>
       <c r="D382" s="4"/>
       <c r="E382" s="4"/>
@@ -11908,14 +11932,14 @@
       <c r="K382" s="9"/>
     </row>
     <row r="383" ht="15.75" customHeight="1">
-      <c r="A383" s="15" t="s">
-        <v>865</v>
+      <c r="A383" s="40" t="s">
+        <v>866</v>
       </c>
       <c r="B383" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C383" s="24" t="s">
-        <v>866</v>
+      <c r="C383" s="41" t="s">
+        <v>867</v>
       </c>
       <c r="D383" s="4"/>
       <c r="E383" s="4"/>
@@ -11928,13 +11952,13 @@
     </row>
     <row r="384" ht="15.75" customHeight="1">
       <c r="A384" s="10" t="s">
-        <v>867</v>
+        <v>868</v>
       </c>
       <c r="B384" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C384" s="12" t="s">
-        <v>868</v>
+        <v>869</v>
       </c>
       <c r="D384" s="4"/>
       <c r="E384" s="4"/>
@@ -11947,13 +11971,13 @@
     </row>
     <row r="385" ht="15.75" customHeight="1">
       <c r="A385" s="15" t="s">
-        <v>869</v>
+        <v>870</v>
       </c>
       <c r="B385" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C385" s="24" t="s">
-        <v>870</v>
+        <v>871</v>
       </c>
       <c r="D385" s="4"/>
       <c r="E385" s="4"/>
@@ -11966,13 +11990,13 @@
     </row>
     <row r="386" ht="15.75" customHeight="1">
       <c r="A386" s="10" t="s">
-        <v>871</v>
+        <v>872</v>
       </c>
       <c r="B386" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C386" s="12" t="s">
-        <v>872</v>
+        <v>873</v>
       </c>
       <c r="D386" s="4"/>
       <c r="E386" s="4"/>
@@ -11985,13 +12009,13 @@
     </row>
     <row r="387" ht="15.75" customHeight="1">
       <c r="A387" s="15" t="s">
-        <v>873</v>
+        <v>874</v>
       </c>
       <c r="B387" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C387" s="24" t="s">
-        <v>874</v>
+        <v>875</v>
       </c>
       <c r="D387" s="4"/>
       <c r="E387" s="4"/>
@@ -12004,13 +12028,13 @@
     </row>
     <row r="388" ht="15.75" customHeight="1">
       <c r="A388" s="10" t="s">
-        <v>875</v>
+        <v>876</v>
       </c>
       <c r="B388" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C388" s="20" t="s">
-        <v>876</v>
+      <c r="C388" s="12" t="s">
+        <v>877</v>
       </c>
       <c r="D388" s="4"/>
       <c r="E388" s="4"/>
@@ -12023,13 +12047,13 @@
     </row>
     <row r="389" ht="15.75" customHeight="1">
       <c r="A389" s="15" t="s">
-        <v>877</v>
+        <v>878</v>
       </c>
       <c r="B389" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C389" s="24" t="s">
-        <v>878</v>
+        <v>879</v>
       </c>
       <c r="D389" s="4"/>
       <c r="E389" s="4"/>
@@ -12042,13 +12066,13 @@
     </row>
     <row r="390" ht="15.75" customHeight="1">
       <c r="A390" s="10" t="s">
-        <v>879</v>
+        <v>880</v>
       </c>
       <c r="B390" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C390" s="12" t="s">
-        <v>880</v>
+      <c r="C390" s="20" t="s">
+        <v>881</v>
       </c>
       <c r="D390" s="4"/>
       <c r="E390" s="4"/>
@@ -12061,13 +12085,13 @@
     </row>
     <row r="391" ht="15.75" customHeight="1">
       <c r="A391" s="15" t="s">
-        <v>881</v>
+        <v>882</v>
       </c>
       <c r="B391" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C391" s="24" t="s">
-        <v>882</v>
+        <v>883</v>
       </c>
       <c r="D391" s="4"/>
       <c r="E391" s="4"/>
@@ -12080,13 +12104,13 @@
     </row>
     <row r="392" ht="15.75" customHeight="1">
       <c r="A392" s="10" t="s">
-        <v>883</v>
+        <v>884</v>
       </c>
       <c r="B392" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C392" s="12" t="s">
-        <v>884</v>
+        <v>885</v>
       </c>
       <c r="D392" s="4"/>
       <c r="E392" s="4"/>
@@ -12099,13 +12123,13 @@
     </row>
     <row r="393" ht="15.75" customHeight="1">
       <c r="A393" s="15" t="s">
-        <v>885</v>
+        <v>886</v>
       </c>
       <c r="B393" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C393" s="17" t="s">
-        <v>886</v>
+      <c r="C393" s="24" t="s">
+        <v>887</v>
       </c>
       <c r="D393" s="4"/>
       <c r="E393" s="4"/>
@@ -12118,13 +12142,13 @@
     </row>
     <row r="394" ht="15.75" customHeight="1">
       <c r="A394" s="10" t="s">
-        <v>887</v>
+        <v>888</v>
       </c>
       <c r="B394" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C394" s="12" t="s">
-        <v>888</v>
+        <v>889</v>
       </c>
       <c r="D394" s="4"/>
       <c r="E394" s="4"/>
@@ -12137,13 +12161,13 @@
     </row>
     <row r="395" ht="15.75" customHeight="1">
       <c r="A395" s="15" t="s">
-        <v>889</v>
+        <v>890</v>
       </c>
       <c r="B395" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C395" s="24" t="s">
-        <v>890</v>
+      <c r="C395" s="17" t="s">
+        <v>891</v>
       </c>
       <c r="D395" s="4"/>
       <c r="E395" s="4"/>
@@ -12156,13 +12180,13 @@
     </row>
     <row r="396" ht="15.75" customHeight="1">
       <c r="A396" s="10" t="s">
-        <v>891</v>
+        <v>892</v>
       </c>
       <c r="B396" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C396" s="20" t="s">
-        <v>892</v>
+      <c r="C396" s="12" t="s">
+        <v>893</v>
       </c>
       <c r="D396" s="4"/>
       <c r="E396" s="4"/>
@@ -12175,13 +12199,13 @@
     </row>
     <row r="397" ht="15.75" customHeight="1">
       <c r="A397" s="15" t="s">
-        <v>893</v>
+        <v>894</v>
       </c>
       <c r="B397" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C397" s="17" t="s">
-        <v>894</v>
+      <c r="C397" s="24" t="s">
+        <v>895</v>
       </c>
       <c r="D397" s="4"/>
       <c r="E397" s="4"/>
@@ -12194,13 +12218,13 @@
     </row>
     <row r="398" ht="15.75" customHeight="1">
       <c r="A398" s="10" t="s">
-        <v>895</v>
+        <v>896</v>
       </c>
       <c r="B398" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C398" s="12" t="s">
-        <v>896</v>
+      <c r="C398" s="20" t="s">
+        <v>897</v>
       </c>
       <c r="D398" s="4"/>
       <c r="E398" s="4"/>
@@ -12212,14 +12236,14 @@
       <c r="K398" s="9"/>
     </row>
     <row r="399" ht="15.75" customHeight="1">
-      <c r="A399" s="40" t="s">
-        <v>897</v>
+      <c r="A399" s="15" t="s">
+        <v>898</v>
       </c>
       <c r="B399" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C399" s="41" t="s">
-        <v>898</v>
+      <c r="C399" s="17" t="s">
+        <v>899</v>
       </c>
       <c r="D399" s="4"/>
       <c r="E399" s="4"/>
@@ -12232,13 +12256,13 @@
     </row>
     <row r="400" ht="15.75" customHeight="1">
       <c r="A400" s="10" t="s">
-        <v>899</v>
+        <v>900</v>
       </c>
       <c r="B400" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C400" s="20" t="s">
-        <v>900</v>
+      <c r="C400" s="12" t="s">
+        <v>901</v>
       </c>
       <c r="D400" s="4"/>
       <c r="E400" s="4"/>
@@ -12250,14 +12274,14 @@
       <c r="K400" s="9"/>
     </row>
     <row r="401" ht="15.75" customHeight="1">
-      <c r="A401" s="15" t="s">
-        <v>901</v>
+      <c r="A401" s="40" t="s">
+        <v>902</v>
       </c>
       <c r="B401" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C401" s="24" t="s">
-        <v>900</v>
+      <c r="C401" s="41" t="s">
+        <v>903</v>
       </c>
       <c r="D401" s="4"/>
       <c r="E401" s="4"/>
@@ -12269,14 +12293,14 @@
       <c r="K401" s="9"/>
     </row>
     <row r="402" ht="15.75" customHeight="1">
-      <c r="A402" s="38" t="s">
-        <v>902</v>
+      <c r="A402" s="10" t="s">
+        <v>904</v>
       </c>
       <c r="B402" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C402" s="48" t="s">
-        <v>903</v>
+      <c r="C402" s="20" t="s">
+        <v>905</v>
       </c>
       <c r="D402" s="4"/>
       <c r="E402" s="4"/>
@@ -12289,7 +12313,7 @@
     </row>
     <row r="403" ht="15.75" customHeight="1">
       <c r="A403" s="15" t="s">
-        <v>904</v>
+        <v>906</v>
       </c>
       <c r="B403" s="16" t="s">
         <v>48</v>
@@ -12307,14 +12331,14 @@
       <c r="K403" s="9"/>
     </row>
     <row r="404" ht="15.75" customHeight="1">
-      <c r="A404" s="10" t="s">
-        <v>906</v>
+      <c r="A404" s="38" t="s">
+        <v>907</v>
       </c>
       <c r="B404" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C404" s="20" t="s">
-        <v>907</v>
+      <c r="C404" s="48" t="s">
+        <v>908</v>
       </c>
       <c r="D404" s="4"/>
       <c r="E404" s="4"/>
@@ -12326,14 +12350,14 @@
       <c r="K404" s="9"/>
     </row>
     <row r="405" ht="15.75" customHeight="1">
-      <c r="A405" s="45" t="s">
-        <v>908</v>
+      <c r="A405" s="15" t="s">
+        <v>909</v>
       </c>
       <c r="B405" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C405" s="49" t="s">
-        <v>909</v>
+      <c r="C405" s="24" t="s">
+        <v>910</v>
       </c>
       <c r="D405" s="4"/>
       <c r="E405" s="4"/>
@@ -12346,13 +12370,13 @@
     </row>
     <row r="406" ht="15.75" customHeight="1">
       <c r="A406" s="10" t="s">
-        <v>910</v>
+        <v>911</v>
       </c>
       <c r="B406" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C406" s="12" t="s">
-        <v>911</v>
+      <c r="C406" s="20" t="s">
+        <v>912</v>
       </c>
       <c r="D406" s="4"/>
       <c r="E406" s="4"/>
@@ -12364,14 +12388,14 @@
       <c r="K406" s="9"/>
     </row>
     <row r="407" ht="15.75" customHeight="1">
-      <c r="A407" s="15" t="s">
-        <v>912</v>
+      <c r="A407" s="45" t="s">
+        <v>913</v>
       </c>
       <c r="B407" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C407" s="17" t="s">
-        <v>913</v>
+      <c r="C407" s="49" t="s">
+        <v>914</v>
       </c>
       <c r="D407" s="4"/>
       <c r="E407" s="4"/>
@@ -12384,13 +12408,13 @@
     </row>
     <row r="408" ht="15.75" customHeight="1">
       <c r="A408" s="10" t="s">
-        <v>914</v>
+        <v>915</v>
       </c>
       <c r="B408" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C408" s="20" t="s">
-        <v>915</v>
+      <c r="C408" s="12" t="s">
+        <v>916</v>
       </c>
       <c r="D408" s="4"/>
       <c r="E408" s="4"/>
@@ -12403,13 +12427,13 @@
     </row>
     <row r="409" ht="15.75" customHeight="1">
       <c r="A409" s="15" t="s">
-        <v>916</v>
+        <v>917</v>
       </c>
       <c r="B409" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C409" s="24" t="s">
-        <v>917</v>
+      <c r="C409" s="17" t="s">
+        <v>918</v>
       </c>
       <c r="D409" s="4"/>
       <c r="E409" s="4"/>
@@ -12422,13 +12446,13 @@
     </row>
     <row r="410" ht="15.75" customHeight="1">
       <c r="A410" s="10" t="s">
-        <v>918</v>
+        <v>919</v>
       </c>
       <c r="B410" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C410" s="20" t="s">
-        <v>919</v>
+        <v>920</v>
       </c>
       <c r="D410" s="4"/>
       <c r="E410" s="4"/>
@@ -12441,13 +12465,13 @@
     </row>
     <row r="411" ht="15.75" customHeight="1">
       <c r="A411" s="15" t="s">
-        <v>920</v>
+        <v>921</v>
       </c>
       <c r="B411" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C411" s="24" t="s">
-        <v>921</v>
+        <v>922</v>
       </c>
       <c r="D411" s="4"/>
       <c r="E411" s="4"/>
@@ -12460,13 +12484,13 @@
     </row>
     <row r="412" ht="15.75" customHeight="1">
       <c r="A412" s="10" t="s">
-        <v>922</v>
+        <v>923</v>
       </c>
       <c r="B412" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C412" s="12" t="s">
-        <v>923</v>
+      <c r="C412" s="20" t="s">
+        <v>924</v>
       </c>
       <c r="D412" s="4"/>
       <c r="E412" s="4"/>
@@ -12479,13 +12503,13 @@
     </row>
     <row r="413" ht="15.75" customHeight="1">
       <c r="A413" s="15" t="s">
-        <v>924</v>
+        <v>925</v>
       </c>
       <c r="B413" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C413" s="17" t="s">
-        <v>925</v>
+      <c r="C413" s="24" t="s">
+        <v>926</v>
       </c>
       <c r="D413" s="4"/>
       <c r="E413" s="4"/>
@@ -12498,13 +12522,13 @@
     </row>
     <row r="414" ht="15.75" customHeight="1">
       <c r="A414" s="10" t="s">
-        <v>926</v>
+        <v>927</v>
       </c>
       <c r="B414" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C414" s="12" t="s">
-        <v>927</v>
+        <v>928</v>
       </c>
       <c r="D414" s="4"/>
       <c r="E414" s="4"/>
@@ -12517,13 +12541,13 @@
     </row>
     <row r="415" ht="15.75" customHeight="1">
       <c r="A415" s="15" t="s">
-        <v>928</v>
+        <v>929</v>
       </c>
       <c r="B415" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C415" s="24" t="s">
-        <v>929</v>
+      <c r="C415" s="17" t="s">
+        <v>930</v>
       </c>
       <c r="D415" s="4"/>
       <c r="E415" s="4"/>
@@ -12536,13 +12560,13 @@
     </row>
     <row r="416" ht="15.75" customHeight="1">
       <c r="A416" s="10" t="s">
-        <v>930</v>
+        <v>931</v>
       </c>
       <c r="B416" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C416" s="12" t="s">
-        <v>931</v>
+        <v>932</v>
       </c>
       <c r="D416" s="4"/>
       <c r="E416" s="4"/>
@@ -12555,13 +12579,13 @@
     </row>
     <row r="417" ht="15.75" customHeight="1">
       <c r="A417" s="15" t="s">
-        <v>932</v>
+        <v>933</v>
       </c>
       <c r="B417" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C417" s="17" t="s">
-        <v>933</v>
+      <c r="C417" s="24" t="s">
+        <v>934</v>
       </c>
       <c r="D417" s="4"/>
       <c r="E417" s="4"/>
@@ -12574,13 +12598,13 @@
     </row>
     <row r="418" ht="15.75" customHeight="1">
       <c r="A418" s="10" t="s">
-        <v>934</v>
+        <v>935</v>
       </c>
       <c r="B418" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C418" s="12" t="s">
-        <v>935</v>
+        <v>936</v>
       </c>
       <c r="D418" s="4"/>
       <c r="E418" s="4"/>
@@ -12593,13 +12617,13 @@
     </row>
     <row r="419" ht="15.75" customHeight="1">
       <c r="A419" s="15" t="s">
-        <v>936</v>
+        <v>937</v>
       </c>
       <c r="B419" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C419" s="24" t="s">
-        <v>937</v>
+      <c r="C419" s="17" t="s">
+        <v>938</v>
       </c>
       <c r="D419" s="4"/>
       <c r="E419" s="4"/>
@@ -12612,13 +12636,13 @@
     </row>
     <row r="420" ht="15.75" customHeight="1">
       <c r="A420" s="10" t="s">
-        <v>938</v>
+        <v>939</v>
       </c>
       <c r="B420" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C420" s="20" t="s">
-        <v>939</v>
+      <c r="C420" s="12" t="s">
+        <v>940</v>
       </c>
       <c r="D420" s="4"/>
       <c r="E420" s="4"/>
@@ -12631,13 +12655,13 @@
     </row>
     <row r="421" ht="15.75" customHeight="1">
       <c r="A421" s="15" t="s">
-        <v>940</v>
+        <v>941</v>
       </c>
       <c r="B421" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C421" s="17" t="s">
-        <v>941</v>
+      <c r="C421" s="24" t="s">
+        <v>942</v>
       </c>
       <c r="D421" s="4"/>
       <c r="E421" s="4"/>
@@ -12649,14 +12673,14 @@
       <c r="K421" s="9"/>
     </row>
     <row r="422" ht="15.75" customHeight="1">
-      <c r="A422" s="34" t="s">
-        <v>942</v>
+      <c r="A422" s="10" t="s">
+        <v>943</v>
       </c>
       <c r="B422" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C422" s="35" t="s">
-        <v>943</v>
+      <c r="C422" s="20" t="s">
+        <v>944</v>
       </c>
       <c r="D422" s="4"/>
       <c r="E422" s="4"/>
@@ -12669,13 +12693,13 @@
     </row>
     <row r="423" ht="15.75" customHeight="1">
       <c r="A423" s="15" t="s">
-        <v>944</v>
+        <v>945</v>
       </c>
       <c r="B423" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C423" s="24" t="s">
-        <v>945</v>
+      <c r="C423" s="17" t="s">
+        <v>946</v>
       </c>
       <c r="D423" s="4"/>
       <c r="E423" s="4"/>
@@ -12687,14 +12711,14 @@
       <c r="K423" s="9"/>
     </row>
     <row r="424" ht="15.75" customHeight="1">
-      <c r="A424" s="10" t="s">
-        <v>946</v>
+      <c r="A424" s="34" t="s">
+        <v>947</v>
       </c>
       <c r="B424" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C424" s="12" t="s">
-        <v>947</v>
+      <c r="C424" s="35" t="s">
+        <v>948</v>
       </c>
       <c r="D424" s="4"/>
       <c r="E424" s="4"/>
@@ -12707,13 +12731,13 @@
     </row>
     <row r="425" ht="15.75" customHeight="1">
       <c r="A425" s="15" t="s">
-        <v>948</v>
+        <v>949</v>
       </c>
       <c r="B425" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C425" s="17" t="s">
-        <v>949</v>
+      <c r="C425" s="24" t="s">
+        <v>950</v>
       </c>
       <c r="D425" s="4"/>
       <c r="E425" s="4"/>
@@ -12726,13 +12750,13 @@
     </row>
     <row r="426" ht="15.75" customHeight="1">
       <c r="A426" s="10" t="s">
-        <v>950</v>
+        <v>951</v>
       </c>
       <c r="B426" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C426" s="12" t="s">
-        <v>951</v>
+        <v>952</v>
       </c>
       <c r="D426" s="4"/>
       <c r="E426" s="4"/>
@@ -12745,13 +12769,13 @@
     </row>
     <row r="427" ht="15.75" customHeight="1">
       <c r="A427" s="15" t="s">
-        <v>952</v>
+        <v>953</v>
       </c>
       <c r="B427" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C427" s="17" t="s">
-        <v>953</v>
+        <v>954</v>
       </c>
       <c r="D427" s="4"/>
       <c r="E427" s="4"/>
@@ -12764,13 +12788,13 @@
     </row>
     <row r="428" ht="15.75" customHeight="1">
       <c r="A428" s="10" t="s">
-        <v>954</v>
+        <v>955</v>
       </c>
       <c r="B428" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C428" s="12" t="s">
-        <v>955</v>
+        <v>956</v>
       </c>
       <c r="D428" s="4"/>
       <c r="E428" s="4"/>
@@ -12783,13 +12807,13 @@
     </row>
     <row r="429" ht="15.75" customHeight="1">
       <c r="A429" s="15" t="s">
-        <v>956</v>
+        <v>957</v>
       </c>
       <c r="B429" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C429" s="24" t="s">
-        <v>957</v>
+      <c r="C429" s="17" t="s">
+        <v>958</v>
       </c>
       <c r="D429" s="4"/>
       <c r="E429" s="4"/>
@@ -12802,13 +12826,13 @@
     </row>
     <row r="430" ht="15.75" customHeight="1">
       <c r="A430" s="10" t="s">
-        <v>958</v>
+        <v>959</v>
       </c>
       <c r="B430" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C430" s="20" t="s">
-        <v>959</v>
+      <c r="C430" s="12" t="s">
+        <v>960</v>
       </c>
       <c r="D430" s="4"/>
       <c r="E430" s="4"/>
@@ -12821,13 +12845,13 @@
     </row>
     <row r="431" ht="15.75" customHeight="1">
       <c r="A431" s="15" t="s">
-        <v>960</v>
+        <v>961</v>
       </c>
       <c r="B431" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C431" s="17" t="s">
-        <v>961</v>
+      <c r="C431" s="24" t="s">
+        <v>962</v>
       </c>
       <c r="D431" s="4"/>
       <c r="E431" s="4"/>
@@ -12840,13 +12864,13 @@
     </row>
     <row r="432" ht="15.75" customHeight="1">
       <c r="A432" s="10" t="s">
-        <v>962</v>
+        <v>963</v>
       </c>
       <c r="B432" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C432" s="20" t="s">
-        <v>963</v>
+        <v>964</v>
       </c>
       <c r="D432" s="4"/>
       <c r="E432" s="4"/>
@@ -12859,13 +12883,13 @@
     </row>
     <row r="433" ht="15.75" customHeight="1">
       <c r="A433" s="15" t="s">
-        <v>964</v>
+        <v>965</v>
       </c>
       <c r="B433" s="16" t="s">
         <v>48</v>
       </c>
       <c r="C433" s="17" t="s">
-        <v>965</v>
+        <v>966</v>
       </c>
       <c r="D433" s="4"/>
       <c r="E433" s="4"/>
@@ -12878,13 +12902,13 @@
     </row>
     <row r="434" ht="15.75" customHeight="1">
       <c r="A434" s="10" t="s">
-        <v>966</v>
+        <v>967</v>
       </c>
       <c r="B434" s="11" t="s">
         <v>48</v>
       </c>
       <c r="C434" s="20" t="s">
-        <v>967</v>
+        <v>968</v>
       </c>
       <c r="D434" s="4"/>
       <c r="E434" s="4"/>
@@ -12897,13 +12921,13 @@
     </row>
     <row r="435" ht="15.75" customHeight="1">
       <c r="A435" s="15" t="s">
-        <v>968</v>
+        <v>969</v>
       </c>
       <c r="B435" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C435" s="24" t="s">
-        <v>969</v>
+      <c r="C435" s="17" t="s">
+        <v>970</v>
       </c>
       <c r="D435" s="4"/>
       <c r="E435" s="4"/>
@@ -12915,14 +12939,14 @@
       <c r="K435" s="9"/>
     </row>
     <row r="436" ht="15.75" customHeight="1">
-      <c r="A436" s="34" t="s">
-        <v>970</v>
+      <c r="A436" s="10" t="s">
+        <v>971</v>
       </c>
       <c r="B436" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C436" s="35" t="s">
-        <v>971</v>
+      <c r="C436" s="20" t="s">
+        <v>972</v>
       </c>
       <c r="D436" s="4"/>
       <c r="E436" s="4"/>
@@ -12934,14 +12958,14 @@
       <c r="K436" s="9"/>
     </row>
     <row r="437" ht="15.75" customHeight="1">
-      <c r="A437" s="40" t="s">
-        <v>972</v>
+      <c r="A437" s="15" t="s">
+        <v>973</v>
       </c>
       <c r="B437" s="16" t="s">
         <v>48</v>
       </c>
-      <c r="C437" s="41" t="s">
-        <v>973</v>
+      <c r="C437" s="24" t="s">
+        <v>974</v>
       </c>
       <c r="D437" s="4"/>
       <c r="E437" s="4"/>
@@ -12953,14 +12977,14 @@
       <c r="K437" s="9"/>
     </row>
     <row r="438" ht="15.75" customHeight="1">
-      <c r="A438" s="10" t="s">
-        <v>974</v>
+      <c r="A438" s="34" t="s">
+        <v>975</v>
       </c>
       <c r="B438" s="11" t="s">
         <v>48</v>
       </c>
-      <c r="C438" s="20" t="s">
-        <v>975</v>
+      <c r="C438" s="35" t="s">
+        <v>976</v>
       </c>
       <c r="D438" s="4"/>
       <c r="E438" s="4"/>
@@ -12972,14 +12996,14 @@
       <c r="K438" s="9"/>
     </row>
     <row r="439" ht="15.75" customHeight="1">
-      <c r="A439" s="15" t="s">
-        <v>976</v>
+      <c r="A439" s="40" t="s">
+        <v>977</v>
       </c>
       <c r="B439" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="C439" s="24" t="s">
-        <v>977</v>
+        <v>48</v>
+      </c>
+      <c r="C439" s="41" t="s">
+        <v>978</v>
       </c>
       <c r="D439" s="4"/>
       <c r="E439" s="4"/>
@@ -12992,13 +13016,13 @@
     </row>
     <row r="440" ht="15.75" customHeight="1">
       <c r="A440" s="10" t="s">
-        <v>978</v>
+        <v>979</v>
       </c>
       <c r="B440" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C440" s="12" t="s">
-        <v>978</v>
+        <v>48</v>
+      </c>
+      <c r="C440" s="20" t="s">
+        <v>980</v>
       </c>
       <c r="D440" s="4"/>
       <c r="E440" s="4"/>
@@ -13010,14 +13034,14 @@
       <c r="K440" s="9"/>
     </row>
     <row r="441" ht="15.75" customHeight="1">
-      <c r="A441" s="40" t="s">
-        <v>979</v>
-      </c>
-      <c r="B441" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C441" s="41" t="s">
-        <v>980</v>
+      <c r="A441" s="15" t="s">
+        <v>981</v>
+      </c>
+      <c r="B441" s="16" t="s">
+        <v>53</v>
+      </c>
+      <c r="C441" s="24" t="s">
+        <v>982</v>
       </c>
       <c r="D441" s="4"/>
       <c r="E441" s="4"/>
@@ -13029,14 +13053,14 @@
       <c r="K441" s="9"/>
     </row>
     <row r="442" ht="15.75" customHeight="1">
-      <c r="A442" s="22" t="s">
-        <v>981</v>
-      </c>
-      <c r="B442" s="51" t="s">
+      <c r="A442" s="10" t="s">
+        <v>983</v>
+      </c>
+      <c r="B442" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C442" s="12" t="s">
-        <v>982</v>
+        <v>983</v>
       </c>
       <c r="D442" s="4"/>
       <c r="E442" s="4"/>
@@ -13048,14 +13072,14 @@
       <c r="K442" s="9"/>
     </row>
     <row r="443" ht="15.75" customHeight="1">
-      <c r="A443" s="15" t="s">
-        <v>983</v>
+      <c r="A443" s="40" t="s">
+        <v>984</v>
       </c>
       <c r="B443" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C443" s="24" t="s">
-        <v>984</v>
+      <c r="C443" s="41" t="s">
+        <v>985</v>
       </c>
       <c r="D443" s="4"/>
       <c r="E443" s="4"/>
@@ -13067,14 +13091,14 @@
       <c r="K443" s="9"/>
     </row>
     <row r="444" ht="15.75" customHeight="1">
-      <c r="A444" s="10" t="s">
-        <v>985</v>
-      </c>
-      <c r="B444" s="11" t="s">
+      <c r="A444" s="22" t="s">
+        <v>986</v>
+      </c>
+      <c r="B444" s="51" t="s">
         <v>9</v>
       </c>
       <c r="C444" s="12" t="s">
-        <v>985</v>
+        <v>987</v>
       </c>
       <c r="D444" s="4"/>
       <c r="E444" s="4"/>
@@ -13086,14 +13110,14 @@
       <c r="K444" s="9"/>
     </row>
     <row r="445" ht="15.75" customHeight="1">
-      <c r="A445" s="40" t="s">
-        <v>986</v>
+      <c r="A445" s="15" t="s">
+        <v>988</v>
       </c>
       <c r="B445" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C445" s="41" t="s">
-        <v>987</v>
+      <c r="C445" s="24" t="s">
+        <v>989</v>
       </c>
       <c r="D445" s="4"/>
       <c r="E445" s="4"/>
@@ -13105,14 +13129,14 @@
       <c r="K445" s="9"/>
     </row>
     <row r="446" ht="15.75" customHeight="1">
-      <c r="A446" s="22" t="s">
-        <v>988</v>
+      <c r="A446" s="10" t="s">
+        <v>990</v>
       </c>
       <c r="B446" s="11" t="s">
-        <v>293</v>
-      </c>
-      <c r="C446" s="20" t="s">
-        <v>989</v>
+        <v>9</v>
+      </c>
+      <c r="C446" s="12" t="s">
+        <v>990</v>
       </c>
       <c r="D446" s="4"/>
       <c r="E446" s="4"/>
@@ -13125,13 +13149,13 @@
     </row>
     <row r="447" ht="15.75" customHeight="1">
       <c r="A447" s="40" t="s">
-        <v>990</v>
-      </c>
-      <c r="B447" s="44" t="s">
-        <v>58</v>
-      </c>
-      <c r="C447" s="17" t="s">
         <v>991</v>
+      </c>
+      <c r="B447" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C447" s="41" t="s">
+        <v>992</v>
       </c>
       <c r="D447" s="4"/>
       <c r="E447" s="4"/>
@@ -13143,14 +13167,14 @@
       <c r="K447" s="9"/>
     </row>
     <row r="448" ht="15.75" customHeight="1">
-      <c r="A448" s="38" t="s">
-        <v>992</v>
+      <c r="A448" s="22" t="s">
+        <v>993</v>
       </c>
       <c r="B448" s="11" t="s">
-        <v>306</v>
-      </c>
-      <c r="C448" s="39" t="s">
-        <v>993</v>
+        <v>293</v>
+      </c>
+      <c r="C448" s="20" t="s">
+        <v>994</v>
       </c>
       <c r="D448" s="4"/>
       <c r="E448" s="4"/>
@@ -13162,14 +13186,14 @@
       <c r="K448" s="9"/>
     </row>
     <row r="449" ht="15.75" customHeight="1">
-      <c r="A449" s="15" t="s">
-        <v>994</v>
-      </c>
-      <c r="B449" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C449" s="24" t="s">
+      <c r="A449" s="40" t="s">
         <v>995</v>
+      </c>
+      <c r="B449" s="44" t="s">
+        <v>58</v>
+      </c>
+      <c r="C449" s="17" t="s">
+        <v>996</v>
       </c>
       <c r="D449" s="4"/>
       <c r="E449" s="4"/>
@@ -13182,13 +13206,13 @@
     </row>
     <row r="450" ht="15.75" customHeight="1">
       <c r="A450" s="10" t="s">
-        <v>996</v>
-      </c>
-      <c r="B450" s="51" t="s">
-        <v>9</v>
+        <v>997</v>
+      </c>
+      <c r="B450" s="11" t="s">
+        <v>741</v>
       </c>
       <c r="C450" s="12" t="s">
-        <v>997</v>
+        <v>998</v>
       </c>
       <c r="D450" s="4"/>
       <c r="E450" s="4"/>
@@ -13200,14 +13224,14 @@
       <c r="K450" s="9"/>
     </row>
     <row r="451" ht="15.75" customHeight="1">
-      <c r="A451" s="15" t="s">
-        <v>998</v>
-      </c>
-      <c r="B451" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="C451" s="24" t="s">
+      <c r="A451" s="45" t="s">
         <v>999</v>
+      </c>
+      <c r="B451" s="16" t="s">
+        <v>306</v>
+      </c>
+      <c r="C451" s="49" t="s">
+        <v>1000</v>
       </c>
       <c r="D451" s="4"/>
       <c r="E451" s="4"/>
@@ -13220,13 +13244,13 @@
     </row>
     <row r="452" ht="15.75" customHeight="1">
       <c r="A452" s="10" t="s">
-        <v>1000</v>
+        <v>1001</v>
       </c>
       <c r="B452" s="11" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C452" s="12" t="s">
-        <v>1001</v>
+        <v>1002</v>
       </c>
       <c r="D452" s="4"/>
       <c r="E452" s="4"/>
@@ -13239,13 +13263,13 @@
     </row>
     <row r="453" ht="15.75" customHeight="1">
       <c r="A453" s="15" t="s">
-        <v>1002</v>
+        <v>1003</v>
       </c>
       <c r="B453" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="C453" s="17" t="s">
-        <v>1003</v>
+      <c r="C453" s="24" t="s">
+        <v>1004</v>
       </c>
       <c r="D453" s="4"/>
       <c r="E453" s="4"/>
@@ -13258,13 +13282,13 @@
     </row>
     <row r="454" ht="15.75" customHeight="1">
       <c r="A454" s="10" t="s">
-        <v>1004</v>
-      </c>
-      <c r="B454" s="11" t="s">
-        <v>369</v>
+        <v>1005</v>
+      </c>
+      <c r="B454" s="51" t="s">
+        <v>9</v>
       </c>
       <c r="C454" s="12" t="s">
-        <v>1005</v>
+        <v>1006</v>
       </c>
       <c r="D454" s="4"/>
       <c r="E454" s="4"/>
@@ -13277,13 +13301,13 @@
     </row>
     <row r="455" ht="15.75" customHeight="1">
       <c r="A455" s="15" t="s">
-        <v>1006</v>
+        <v>1007</v>
       </c>
       <c r="B455" s="16" t="s">
-        <v>369</v>
+        <v>9</v>
       </c>
       <c r="C455" s="24" t="s">
-        <v>1007</v>
+        <v>1008</v>
       </c>
       <c r="D455" s="4"/>
       <c r="E455" s="4"/>
@@ -13296,13 +13320,13 @@
     </row>
     <row r="456" ht="15.75" customHeight="1">
       <c r="A456" s="10" t="s">
-        <v>1008</v>
-      </c>
-      <c r="B456" s="11" t="s">
-        <v>369</v>
-      </c>
-      <c r="C456" s="12" t="s">
         <v>1009</v>
+      </c>
+      <c r="B456" s="51" t="s">
+        <v>9</v>
+      </c>
+      <c r="C456" s="20" t="s">
+        <v>1010</v>
       </c>
       <c r="D456" s="4"/>
       <c r="E456" s="4"/>
@@ -13315,13 +13339,13 @@
     </row>
     <row r="457" ht="15.75" customHeight="1">
       <c r="A457" s="15" t="s">
-        <v>1010</v>
+        <v>1011</v>
       </c>
       <c r="B457" s="16" t="s">
-        <v>68</v>
+        <v>369</v>
       </c>
       <c r="C457" s="24" t="s">
-        <v>1011</v>
+        <v>1012</v>
       </c>
       <c r="D457" s="4"/>
       <c r="E457" s="4"/>
@@ -13334,13 +13358,13 @@
     </row>
     <row r="458" ht="15.75" customHeight="1">
       <c r="A458" s="10" t="s">
-        <v>1012</v>
+        <v>1013</v>
       </c>
       <c r="B458" s="11" t="s">
-        <v>9</v>
+        <v>369</v>
       </c>
       <c r="C458" s="12" t="s">
-        <v>1013</v>
+        <v>1014</v>
       </c>
       <c r="D458" s="4"/>
       <c r="E458" s="4"/>
@@ -13353,13 +13377,13 @@
     </row>
     <row r="459" ht="15.75" customHeight="1">
       <c r="A459" s="15" t="s">
-        <v>1014</v>
+        <v>1015</v>
       </c>
       <c r="B459" s="16" t="s">
-        <v>9</v>
+        <v>369</v>
       </c>
       <c r="C459" s="24" t="s">
-        <v>1015</v>
+        <v>1016</v>
       </c>
       <c r="D459" s="4"/>
       <c r="E459" s="4"/>
@@ -13372,13 +13396,13 @@
     </row>
     <row r="460" ht="15.75" customHeight="1">
       <c r="A460" s="10" t="s">
-        <v>1016</v>
+        <v>1017</v>
       </c>
       <c r="B460" s="11" t="s">
-        <v>9</v>
+        <v>68</v>
       </c>
       <c r="C460" s="12" t="s">
-        <v>1017</v>
+        <v>1018</v>
       </c>
       <c r="D460" s="4"/>
       <c r="E460" s="4"/>
@@ -13391,13 +13415,13 @@
     </row>
     <row r="461" ht="15.75" customHeight="1">
       <c r="A461" s="15" t="s">
-        <v>1018</v>
+        <v>1019</v>
       </c>
       <c r="B461" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="C461" s="17" t="s">
-        <v>1019</v>
+        <v>9</v>
+      </c>
+      <c r="C461" s="24" t="s">
+        <v>1020</v>
       </c>
       <c r="D461" s="4"/>
       <c r="E461" s="4"/>
@@ -13409,14 +13433,14 @@
       <c r="K461" s="9"/>
     </row>
     <row r="462" ht="15.75" customHeight="1">
-      <c r="A462" s="22" t="s">
-        <v>1020</v>
+      <c r="A462" s="10" t="s">
+        <v>1021</v>
       </c>
       <c r="B462" s="11" t="s">
-        <v>68</v>
-      </c>
-      <c r="C462" s="20" t="s">
-        <v>1021</v>
+        <v>9</v>
+      </c>
+      <c r="C462" s="12" t="s">
+        <v>1022</v>
       </c>
       <c r="D462" s="4"/>
       <c r="E462" s="4"/>
@@ -13429,13 +13453,13 @@
     </row>
     <row r="463" ht="15.75" customHeight="1">
       <c r="A463" s="15" t="s">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="B463" s="16" t="s">
-        <v>58</v>
+        <v>9</v>
       </c>
       <c r="C463" s="24" t="s">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D463" s="4"/>
       <c r="E463" s="4"/>
@@ -13448,13 +13472,13 @@
     </row>
     <row r="464" ht="15.75" customHeight="1">
       <c r="A464" s="10" t="s">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="B464" s="11" t="s">
-        <v>48</v>
-      </c>
-      <c r="C464" s="12" t="s">
-        <v>1025</v>
+        <v>68</v>
+      </c>
+      <c r="C464" s="20" t="s">
+        <v>1026</v>
       </c>
       <c r="D464" s="4"/>
       <c r="E464" s="4"/>
@@ -13466,14 +13490,14 @@
       <c r="K464" s="9"/>
     </row>
     <row r="465" ht="15.75" customHeight="1">
-      <c r="A465" s="15" t="s">
-        <v>1026</v>
+      <c r="A465" s="25" t="s">
+        <v>1027</v>
       </c>
       <c r="B465" s="16" t="s">
-        <v>95</v>
-      </c>
-      <c r="C465" s="24" t="s">
-        <v>1027</v>
+        <v>68</v>
+      </c>
+      <c r="C465" s="17" t="s">
+        <v>1028</v>
       </c>
       <c r="D465" s="4"/>
       <c r="E465" s="4"/>
@@ -13486,13 +13510,13 @@
     </row>
     <row r="466" ht="15.75" customHeight="1">
       <c r="A466" s="10" t="s">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="B466" s="11" t="s">
-        <v>95</v>
-      </c>
-      <c r="C466" s="20" t="s">
-        <v>1029</v>
+        <v>58</v>
+      </c>
+      <c r="C466" s="12" t="s">
+        <v>1030</v>
       </c>
       <c r="D466" s="4"/>
       <c r="E466" s="4"/>
@@ -13505,13 +13529,13 @@
     </row>
     <row r="467" ht="15.75" customHeight="1">
       <c r="A467" s="15" t="s">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="B467" s="16" t="s">
-        <v>95</v>
+        <v>48</v>
       </c>
       <c r="C467" s="24" t="s">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D467" s="4"/>
       <c r="E467" s="4"/>
@@ -13523,14 +13547,14 @@
       <c r="K467" s="9"/>
     </row>
     <row r="468" ht="15.75" customHeight="1">
-      <c r="A468" s="34" t="s">
-        <v>1032</v>
+      <c r="A468" s="10" t="s">
+        <v>1033</v>
       </c>
       <c r="B468" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C468" s="35" t="s">
-        <v>1033</v>
+      <c r="C468" s="12" t="s">
+        <v>1034</v>
       </c>
       <c r="D468" s="4"/>
       <c r="E468" s="4"/>
@@ -13543,13 +13567,13 @@
     </row>
     <row r="469" ht="15.75" customHeight="1">
       <c r="A469" s="15" t="s">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="B469" s="16" t="s">
-        <v>68</v>
+        <v>95</v>
       </c>
       <c r="C469" s="17" t="s">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D469" s="4"/>
       <c r="E469" s="4"/>
@@ -13561,14 +13585,14 @@
       <c r="K469" s="9"/>
     </row>
     <row r="470" ht="15.75" customHeight="1">
-      <c r="A470" s="34" t="s">
-        <v>1036</v>
+      <c r="A470" s="10" t="s">
+        <v>1037</v>
       </c>
       <c r="B470" s="11" t="s">
         <v>95</v>
       </c>
-      <c r="C470" s="35" t="s">
-        <v>1037</v>
+      <c r="C470" s="12" t="s">
+        <v>1038</v>
       </c>
       <c r="D470" s="4"/>
       <c r="E470" s="4"/>
@@ -13581,13 +13605,13 @@
     </row>
     <row r="471" ht="15.75" customHeight="1">
       <c r="A471" s="40" t="s">
-        <v>1006</v>
+        <v>1039</v>
       </c>
       <c r="B471" s="16" t="s">
         <v>95</v>
       </c>
       <c r="C471" s="41" t="s">
-        <v>1038</v>
+        <v>1040</v>
       </c>
       <c r="D471" s="4"/>
       <c r="E471" s="4"/>
@@ -13600,13 +13624,13 @@
     </row>
     <row r="472" ht="15.75" customHeight="1">
       <c r="A472" s="10" t="s">
-        <v>1039</v>
-      </c>
-      <c r="B472" s="51" t="s">
-        <v>9</v>
-      </c>
-      <c r="C472" s="12" t="s">
-        <v>1040</v>
+        <v>1041</v>
+      </c>
+      <c r="B472" s="11" t="s">
+        <v>68</v>
+      </c>
+      <c r="C472" s="20" t="s">
+        <v>1042</v>
       </c>
       <c r="D472" s="4"/>
       <c r="E472" s="4"/>
@@ -13618,14 +13642,14 @@
       <c r="K472" s="9"/>
     </row>
     <row r="473" ht="15.75" customHeight="1">
-      <c r="A473" s="15" t="s">
-        <v>1041</v>
+      <c r="A473" s="40" t="s">
+        <v>1043</v>
       </c>
       <c r="B473" s="16" t="s">
-        <v>9</v>
-      </c>
-      <c r="C473" s="17" t="s">
-        <v>1042</v>
+        <v>95</v>
+      </c>
+      <c r="C473" s="41" t="s">
+        <v>1044</v>
       </c>
       <c r="D473" s="4"/>
       <c r="E473" s="4"/>
@@ -13638,13 +13662,13 @@
     </row>
     <row r="474" ht="15.75" customHeight="1">
       <c r="A474" s="34" t="s">
-        <v>1043</v>
+        <v>1013</v>
       </c>
       <c r="B474" s="11" t="s">
-        <v>9</v>
+        <v>95</v>
       </c>
       <c r="C474" s="35" t="s">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="D474" s="4"/>
       <c r="E474" s="4"/>
@@ -13656,14 +13680,14 @@
       <c r="K474" s="9"/>
     </row>
     <row r="475" ht="15.75" customHeight="1">
-      <c r="A475" s="40" t="s">
-        <v>1045</v>
-      </c>
-      <c r="B475" s="44" t="s">
-        <v>53</v>
-      </c>
-      <c r="C475" s="41" t="s">
+      <c r="A475" s="15" t="s">
         <v>1046</v>
+      </c>
+      <c r="B475" s="50" t="s">
+        <v>9</v>
+      </c>
+      <c r="C475" s="24" t="s">
+        <v>1047</v>
       </c>
       <c r="D475" s="4"/>
       <c r="E475" s="4"/>
@@ -13676,13 +13700,13 @@
     </row>
     <row r="476" ht="15.75" customHeight="1">
       <c r="A476" s="10" t="s">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="B476" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C476" s="12" t="s">
-        <v>1048</v>
+      <c r="C476" s="20" t="s">
+        <v>1049</v>
       </c>
       <c r="D476" s="4"/>
       <c r="E476" s="4"/>
@@ -13694,14 +13718,14 @@
       <c r="K476" s="9"/>
     </row>
     <row r="477" ht="15.75" customHeight="1">
-      <c r="A477" s="15" t="s">
-        <v>1049</v>
+      <c r="A477" s="40" t="s">
+        <v>1050</v>
       </c>
       <c r="B477" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C477" s="24" t="s">
-        <v>1050</v>
+      <c r="C477" s="41" t="s">
+        <v>1051</v>
       </c>
       <c r="D477" s="4"/>
       <c r="E477" s="4"/>
@@ -13713,14 +13737,14 @@
       <c r="K477" s="9"/>
     </row>
     <row r="478" ht="15.75" customHeight="1">
-      <c r="A478" s="10" t="s">
-        <v>1051</v>
-      </c>
-      <c r="B478" s="11" t="s">
-        <v>9</v>
-      </c>
-      <c r="C478" s="12" t="s">
+      <c r="A478" s="34" t="s">
         <v>1052</v>
+      </c>
+      <c r="B478" s="26" t="s">
+        <v>53</v>
+      </c>
+      <c r="C478" s="35" t="s">
+        <v>1053</v>
       </c>
       <c r="D478" s="4"/>
       <c r="E478" s="4"/>
@@ -13732,14 +13756,14 @@
       <c r="K478" s="9"/>
     </row>
     <row r="479" ht="15.75" customHeight="1">
-      <c r="A479" s="25" t="s">
-        <v>1053</v>
+      <c r="A479" s="15" t="s">
+        <v>1054</v>
       </c>
       <c r="B479" s="16" t="s">
         <v>9</v>
       </c>
-      <c r="C479" s="17" t="s">
-        <v>1054</v>
+      <c r="C479" s="24" t="s">
+        <v>1055</v>
       </c>
       <c r="D479" s="4"/>
       <c r="E479" s="4"/>
@@ -13752,13 +13776,13 @@
     </row>
     <row r="480" ht="15.75" customHeight="1">
       <c r="A480" s="10" t="s">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="B480" s="11" t="s">
         <v>9</v>
       </c>
       <c r="C480" s="12" t="s">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D480" s="4"/>
       <c r="E480" s="4"/>
@@ -13771,13 +13795,13 @@
     </row>
     <row r="481" ht="15.75" customHeight="1">
       <c r="A481" s="15" t="s">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="B481" s="16" t="s">
         <v>9</v>
       </c>
       <c r="C481" s="24" t="s">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="D481" s="4"/>
       <c r="E481" s="4"/>
@@ -13789,14 +13813,14 @@
       <c r="K481" s="9"/>
     </row>
     <row r="482" ht="15.75" customHeight="1">
-      <c r="A482" s="47" t="s">
-        <v>1059</v>
+      <c r="A482" s="22" t="s">
+        <v>1060</v>
       </c>
       <c r="B482" s="11" t="s">
-        <v>153</v>
-      </c>
-      <c r="C482" s="48" t="s">
-        <v>1060</v>
+        <v>9</v>
+      </c>
+      <c r="C482" s="20" t="s">
+        <v>1061</v>
       </c>
       <c r="D482" s="4"/>
       <c r="E482" s="4"/>
@@ -13809,13 +13833,13 @@
     </row>
     <row r="483" ht="15.75" customHeight="1">
       <c r="A483" s="15" t="s">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="B483" s="16" t="s">
-        <v>369</v>
+        <v>9</v>
       </c>
       <c r="C483" s="24" t="s">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D483" s="4"/>
       <c r="E483" s="4"/>
@@ -13828,13 +13852,13 @@
     </row>
     <row r="484" ht="15.75" customHeight="1">
       <c r="A484" s="10" t="s">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="B484" s="11" t="s">
-        <v>369</v>
+        <v>9</v>
       </c>
       <c r="C484" s="12" t="s">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="D484" s="4"/>
       <c r="E484" s="4"/>
@@ -13846,14 +13870,14 @@
       <c r="K484" s="9"/>
     </row>
     <row r="485" ht="15.75" customHeight="1">
-      <c r="A485" s="15" t="s">
-        <v>1065</v>
+      <c r="A485" s="53" t="s">
+        <v>1066</v>
       </c>
       <c r="B485" s="16" t="s">
-        <v>369</v>
-      </c>
-      <c r="C485" s="24" t="s">
-        <v>1066</v>
+        <v>153</v>
+      </c>
+      <c r="C485" s="46" t="s">
+        <v>1067</v>
       </c>
       <c r="D485" s="4"/>
       <c r="E485" s="4"/>
@@ -13865,14 +13889,14 @@
       <c r="K485" s="9"/>
     </row>
     <row r="486" ht="15.75" customHeight="1">
-      <c r="A486" s="53" t="s">
-        <v>1067</v>
-      </c>
-      <c r="B486" s="54" t="s">
-        <v>9</v>
-      </c>
-      <c r="C486" s="55" t="s">
+      <c r="A486" s="10" t="s">
         <v>1068</v>
+      </c>
+      <c r="B486" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="C486" s="12" t="s">
+        <v>1069</v>
       </c>
       <c r="D486" s="4"/>
       <c r="E486" s="4"/>
@@ -13883,10 +13907,67 @@
       <c r="J486" s="9"/>
       <c r="K486" s="9"/>
     </row>
+    <row r="487" ht="15.75" customHeight="1">
+      <c r="A487" s="15" t="s">
+        <v>1070</v>
+      </c>
+      <c r="B487" s="16" t="s">
+        <v>369</v>
+      </c>
+      <c r="C487" s="24" t="s">
+        <v>1071</v>
+      </c>
+      <c r="D487" s="4"/>
+      <c r="E487" s="4"/>
+      <c r="F487" s="4"/>
+      <c r="G487" s="4"/>
+      <c r="H487" s="4"/>
+      <c r="I487" s="4"/>
+      <c r="J487" s="9"/>
+      <c r="K487" s="9"/>
+    </row>
+    <row r="488" ht="15.75" customHeight="1">
+      <c r="A488" s="10" t="s">
+        <v>1072</v>
+      </c>
+      <c r="B488" s="11" t="s">
+        <v>369</v>
+      </c>
+      <c r="C488" s="12" t="s">
+        <v>1073</v>
+      </c>
+      <c r="D488" s="4"/>
+      <c r="E488" s="4"/>
+      <c r="F488" s="4"/>
+      <c r="G488" s="4"/>
+      <c r="H488" s="4"/>
+      <c r="I488" s="4"/>
+      <c r="J488" s="9"/>
+      <c r="K488" s="9"/>
+    </row>
+    <row r="489" ht="15.75" customHeight="1">
+      <c r="A489" s="54" t="s">
+        <v>1074</v>
+      </c>
+      <c r="B489" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C489" s="56" t="s">
+        <v>1075</v>
+      </c>
+      <c r="D489" s="4"/>
+      <c r="E489" s="4"/>
+      <c r="F489" s="4"/>
+      <c r="G489" s="4"/>
+      <c r="H489" s="4"/>
+      <c r="I489" s="4"/>
+      <c r="J489" s="9"/>
+      <c r="K489" s="9"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B486">
-      <formula1>"adjective,adjective-adverb,adverb,auxiliary,conjunction,interjection,noun,numeral,preposition,pronoun,verb"</formula1>
+    <dataValidation type="list" allowBlank="1" sqref="B2:B489">
+      <formula1>"adjective,adjective-adverb,adverb,auxiliary,conjunction,interjection,noun,numeral,preposition,pronoun,verb,prefix,suffix"</formula1>
     </dataValidation>
   </dataValidations>
   <printOptions/>
@@ -13910,1286 +13991,1286 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="56" t="s">
-        <v>1069</v>
-      </c>
-      <c r="D1" s="56" t="s">
-        <v>1070</v>
-      </c>
-      <c r="G1" s="57"/>
-      <c r="H1" s="57"/>
-      <c r="I1" s="57"/>
+      <c r="A1" s="57" t="s">
+        <v>1076</v>
+      </c>
+      <c r="D1" s="57" t="s">
+        <v>1077</v>
+      </c>
+      <c r="G1" s="58"/>
+      <c r="H1" s="58"/>
+      <c r="I1" s="58"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="56" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B2" s="58" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D2" s="56" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E2" s="58" t="s">
-        <v>912</v>
-      </c>
-      <c r="G2" s="57"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
+      <c r="A2" s="57" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B2" s="59" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D2" s="57" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E2" s="59" t="s">
+        <v>917</v>
+      </c>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="56" t="s">
+      <c r="A3" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="B3" s="58" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D3" s="56" t="s">
+      <c r="B3" s="59" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D3" s="57" t="s">
         <v>113</v>
       </c>
-      <c r="E3" s="58" t="s">
-        <v>1074</v>
-      </c>
-      <c r="G3" s="57"/>
-      <c r="H3" s="57"/>
-      <c r="I3" s="57"/>
+      <c r="E3" s="59" t="s">
+        <v>1081</v>
+      </c>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="59"/>
-      <c r="B4" s="60" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C4" s="60" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D4" s="59"/>
-      <c r="E4" s="60" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F4" s="60" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G4" s="57"/>
-      <c r="H4" s="57"/>
-      <c r="I4" s="57"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="61" t="s">
+        <v>1082</v>
+      </c>
+      <c r="C4" s="61" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D4" s="60"/>
+      <c r="E4" s="61" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F4" s="61" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="56" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B5" s="58" t="s">
+      <c r="A5" s="57" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C5" s="59" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D5" s="57" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>1087</v>
+      </c>
+      <c r="F5" s="59" t="s">
+        <v>1088</v>
+      </c>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="57" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B6" s="59" t="s">
+        <v>1090</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>1091</v>
+      </c>
+      <c r="D6" s="57" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>1092</v>
+      </c>
+      <c r="F6" s="59" t="s">
+        <v>1093</v>
+      </c>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="57" t="s">
+        <v>1094</v>
+      </c>
+      <c r="D7" s="57" t="s">
+        <v>1095</v>
+      </c>
+      <c r="G7" s="57" t="s">
+        <v>1096</v>
+      </c>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
+      <c r="A8" s="57" t="s">
         <v>1078</v>
       </c>
-      <c r="C5" s="58" t="s">
+      <c r="B8" s="59" t="s">
         <v>1079</v>
       </c>
-      <c r="D5" s="56" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E5" s="58" t="s">
+      <c r="D8" s="57" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>804</v>
+      </c>
+      <c r="G8" s="57" t="s">
+        <v>1078</v>
+      </c>
+      <c r="H8" s="59" t="s">
+        <v>900</v>
+      </c>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="B9" s="59" t="s">
         <v>1080</v>
       </c>
-      <c r="F5" s="58" t="s">
-        <v>1081</v>
-      </c>
-      <c r="G5" s="57"/>
-      <c r="H5" s="57"/>
-      <c r="I5" s="57"/>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="56" t="s">
+      <c r="D9" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E9" s="59" t="s">
+        <v>1097</v>
+      </c>
+      <c r="G9" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="H9" s="59" t="s">
+        <v>1098</v>
+      </c>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="60"/>
+      <c r="B10" s="61" t="s">
         <v>1082</v>
       </c>
-      <c r="B6" s="58" t="s">
+      <c r="C10" s="61" t="s">
         <v>1083</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="D10" s="60"/>
+      <c r="E10" s="61" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F10" s="61" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G10" s="60"/>
+      <c r="H10" s="61" t="s">
+        <v>1082</v>
+      </c>
+      <c r="I10" s="61" t="s">
+        <v>1083</v>
+      </c>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="57" t="s">
         <v>1084</v>
       </c>
-      <c r="D6" s="56" t="s">
+      <c r="B11" s="59" t="s">
+        <v>1085</v>
+      </c>
+      <c r="C11" s="59" t="s">
+        <v>1086</v>
+      </c>
+      <c r="D11" s="57" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E11" s="59" t="s">
+        <v>1099</v>
+      </c>
+      <c r="F11" s="59" t="s">
+        <v>1100</v>
+      </c>
+      <c r="G11" s="57" t="s">
+        <v>1084</v>
+      </c>
+      <c r="H11" s="59" t="s">
+        <v>1101</v>
+      </c>
+      <c r="I11" s="59" t="s">
+        <v>1102</v>
+      </c>
+    </row>
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="57" t="s">
+        <v>1089</v>
+      </c>
+      <c r="B12" s="59" t="s">
+        <v>1103</v>
+      </c>
+      <c r="C12" s="59" t="s">
+        <v>1104</v>
+      </c>
+      <c r="D12" s="57" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E12" s="59" t="s">
+        <v>1105</v>
+      </c>
+      <c r="F12" s="59" t="s">
+        <v>1106</v>
+      </c>
+      <c r="G12" s="57" t="s">
+        <v>1089</v>
+      </c>
+      <c r="H12" s="59" t="s">
+        <v>1107</v>
+      </c>
+      <c r="I12" s="59" t="s">
+        <v>1108</v>
+      </c>
+    </row>
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="57" t="s">
+        <v>1109</v>
+      </c>
+      <c r="D13" s="57" t="s">
+        <v>1110</v>
+      </c>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="A14" s="57" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B14" s="59" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D14" s="57" t="s">
+        <v>1078</v>
+      </c>
+      <c r="E14" s="59" t="s">
+        <v>798</v>
+      </c>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="B15" s="59" t="s">
+        <v>1080</v>
+      </c>
+      <c r="D15" s="57" t="s">
+        <v>113</v>
+      </c>
+      <c r="E15" s="59" t="s">
+        <v>1111</v>
+      </c>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+    </row>
+    <row r="16" ht="18.75" customHeight="1">
+      <c r="A16" s="60"/>
+      <c r="B16" s="61" t="s">
         <v>1082</v>
       </c>
-      <c r="E6" s="58" t="s">
+      <c r="C16" s="61" t="s">
+        <v>1083</v>
+      </c>
+      <c r="D16" s="60"/>
+      <c r="E16" s="61" t="s">
+        <v>1082</v>
+      </c>
+      <c r="F16" s="61" t="s">
+        <v>1083</v>
+      </c>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+    </row>
+    <row r="17" ht="18.75" customHeight="1">
+      <c r="A17" s="57" t="s">
+        <v>1084</v>
+      </c>
+      <c r="B17" s="59" t="s">
         <v>1085</v>
       </c>
-      <c r="F6" s="58" t="s">
+      <c r="C17" s="59" t="s">
         <v>1086</v>
       </c>
-      <c r="G6" s="57"/>
-      <c r="H6" s="57"/>
-      <c r="I6" s="57"/>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="56" t="s">
-        <v>1087</v>
-      </c>
-      <c r="D7" s="56" t="s">
-        <v>1088</v>
-      </c>
-      <c r="G7" s="56" t="s">
+      <c r="D17" s="57" t="s">
+        <v>1084</v>
+      </c>
+      <c r="E17" s="59" t="s">
+        <v>1112</v>
+      </c>
+      <c r="F17" s="59" t="s">
+        <v>1113</v>
+      </c>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+    </row>
+    <row r="18" ht="18.75" customHeight="1">
+      <c r="A18" s="57" t="s">
         <v>1089</v>
       </c>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="56" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B8" s="58" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D8" s="56" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E8" s="58" t="s">
-        <v>799</v>
-      </c>
-      <c r="G8" s="56" t="s">
-        <v>1071</v>
-      </c>
-      <c r="H8" s="58" t="s">
-        <v>895</v>
-      </c>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D9" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="E9" s="58" t="s">
-        <v>1090</v>
-      </c>
-      <c r="G9" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="H9" s="58" t="s">
-        <v>1091</v>
-      </c>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="59"/>
-      <c r="B10" s="60" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C10" s="60" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D10" s="59"/>
-      <c r="E10" s="60" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F10" s="60" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G10" s="59"/>
-      <c r="H10" s="60" t="s">
-        <v>1075</v>
-      </c>
-      <c r="I10" s="60" t="s">
-        <v>1076</v>
-      </c>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="56" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C11" s="58" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D11" s="56" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E11" s="58" t="s">
-        <v>1092</v>
-      </c>
-      <c r="F11" s="58" t="s">
-        <v>1093</v>
-      </c>
-      <c r="G11" s="56" t="s">
-        <v>1077</v>
-      </c>
-      <c r="H11" s="58" t="s">
-        <v>1094</v>
-      </c>
-      <c r="I11" s="58" t="s">
-        <v>1095</v>
-      </c>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="56" t="s">
-        <v>1082</v>
-      </c>
-      <c r="B12" s="58" t="s">
-        <v>1096</v>
-      </c>
-      <c r="C12" s="58" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D12" s="56" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E12" s="58" t="s">
-        <v>1098</v>
-      </c>
-      <c r="F12" s="58" t="s">
-        <v>1099</v>
-      </c>
-      <c r="G12" s="56" t="s">
-        <v>1082</v>
-      </c>
-      <c r="H12" s="58" t="s">
-        <v>1100</v>
-      </c>
-      <c r="I12" s="58" t="s">
-        <v>1101</v>
-      </c>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="56" t="s">
-        <v>1102</v>
-      </c>
-      <c r="D13" s="56" t="s">
-        <v>1103</v>
-      </c>
-      <c r="G13" s="57"/>
-      <c r="H13" s="57"/>
-      <c r="I13" s="57"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="56" t="s">
-        <v>1071</v>
-      </c>
-      <c r="B14" s="58" t="s">
-        <v>1072</v>
-      </c>
-      <c r="D14" s="56" t="s">
-        <v>1071</v>
-      </c>
-      <c r="E14" s="58" t="s">
-        <v>793</v>
-      </c>
-      <c r="G14" s="57"/>
-      <c r="H14" s="57"/>
-      <c r="I14" s="57"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="B15" s="58" t="s">
-        <v>1073</v>
-      </c>
-      <c r="D15" s="56" t="s">
-        <v>113</v>
-      </c>
-      <c r="E15" s="58" t="s">
+      <c r="B18" s="59" t="s">
+        <v>1114</v>
+      </c>
+      <c r="C18" s="59" t="s">
         <v>1104</v>
       </c>
-      <c r="G15" s="57"/>
-      <c r="H15" s="57"/>
-      <c r="I15" s="57"/>
-    </row>
-    <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="59"/>
-      <c r="B16" s="60" t="s">
-        <v>1075</v>
-      </c>
-      <c r="C16" s="60" t="s">
-        <v>1076</v>
-      </c>
-      <c r="D16" s="59"/>
-      <c r="E16" s="60" t="s">
-        <v>1075</v>
-      </c>
-      <c r="F16" s="60" t="s">
-        <v>1076</v>
-      </c>
-      <c r="G16" s="57"/>
-      <c r="H16" s="57"/>
-      <c r="I16" s="57"/>
-    </row>
-    <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="56" t="s">
-        <v>1077</v>
-      </c>
-      <c r="B17" s="58" t="s">
-        <v>1078</v>
-      </c>
-      <c r="C17" s="58" t="s">
-        <v>1079</v>
-      </c>
-      <c r="D17" s="56" t="s">
-        <v>1077</v>
-      </c>
-      <c r="E17" s="58" t="s">
-        <v>1105</v>
-      </c>
-      <c r="F17" s="58" t="s">
-        <v>1106</v>
-      </c>
-      <c r="G17" s="57"/>
-      <c r="H17" s="57"/>
-      <c r="I17" s="57"/>
-    </row>
-    <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="56" t="s">
-        <v>1082</v>
-      </c>
-      <c r="B18" s="58" t="s">
-        <v>1107</v>
-      </c>
-      <c r="C18" s="58" t="s">
-        <v>1097</v>
-      </c>
-      <c r="D18" s="56" t="s">
-        <v>1082</v>
-      </c>
-      <c r="E18" s="58" t="s">
-        <v>1108</v>
-      </c>
-      <c r="F18" s="58" t="s">
-        <v>1109</v>
-      </c>
-      <c r="G18" s="57"/>
-      <c r="H18" s="57"/>
-      <c r="I18" s="57"/>
+      <c r="D18" s="57" t="s">
+        <v>1089</v>
+      </c>
+      <c r="E18" s="59" t="s">
+        <v>1115</v>
+      </c>
+      <c r="F18" s="59" t="s">
+        <v>1116</v>
+      </c>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="61"/>
-      <c r="B19" s="61"/>
-      <c r="C19" s="61"/>
-      <c r="D19" s="61"/>
-      <c r="E19" s="61"/>
-      <c r="F19" s="61"/>
-      <c r="G19" s="61"/>
-      <c r="H19" s="61"/>
-      <c r="I19" s="61"/>
+      <c r="A19" s="62"/>
+      <c r="B19" s="62"/>
+      <c r="C19" s="62"/>
+      <c r="D19" s="62"/>
+      <c r="E19" s="62"/>
+      <c r="F19" s="62"/>
+      <c r="G19" s="62"/>
+      <c r="H19" s="62"/>
+      <c r="I19" s="62"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="62" t="s">
-        <v>1110</v>
-      </c>
-      <c r="B20" s="63" t="s">
-        <v>1111</v>
-      </c>
-      <c r="D20" s="63" t="s">
-        <v>1112</v>
-      </c>
-      <c r="F20" s="61"/>
-      <c r="G20" s="61"/>
-      <c r="H20" s="61"/>
-      <c r="I20" s="61"/>
+      <c r="A20" s="63" t="s">
+        <v>1117</v>
+      </c>
+      <c r="B20" s="64" t="s">
+        <v>1118</v>
+      </c>
+      <c r="D20" s="64" t="s">
+        <v>1119</v>
+      </c>
+      <c r="F20" s="62"/>
+      <c r="G20" s="62"/>
+      <c r="H20" s="62"/>
+      <c r="I20" s="62"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="B21" s="64" t="s">
-        <v>1113</v>
-      </c>
-      <c r="C21" s="64" t="s">
-        <v>1114</v>
-      </c>
-      <c r="D21" s="64" t="s">
-        <v>1113</v>
-      </c>
-      <c r="E21" s="64" t="s">
-        <v>1114</v>
-      </c>
-      <c r="F21" s="61"/>
-      <c r="G21" s="61"/>
-      <c r="H21" s="61"/>
-      <c r="I21" s="61"/>
+      <c r="B21" s="65" t="s">
+        <v>1120</v>
+      </c>
+      <c r="C21" s="65" t="s">
+        <v>1121</v>
+      </c>
+      <c r="D21" s="65" t="s">
+        <v>1120</v>
+      </c>
+      <c r="E21" s="65" t="s">
+        <v>1121</v>
+      </c>
+      <c r="F21" s="62"/>
+      <c r="G21" s="62"/>
+      <c r="H21" s="62"/>
+      <c r="I21" s="62"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="65" t="s">
-        <v>1115</v>
-      </c>
-      <c r="B22" s="58" t="s">
+      <c r="A22" s="66" t="s">
+        <v>1122</v>
+      </c>
+      <c r="B22" s="59" t="s">
         <v>26</v>
       </c>
-      <c r="C22" s="58" t="s">
-        <v>1116</v>
-      </c>
-      <c r="D22" s="58" t="s">
-        <v>1117</v>
-      </c>
-      <c r="E22" s="58" t="s">
-        <v>1118</v>
-      </c>
-      <c r="F22" s="61"/>
-      <c r="G22" s="61"/>
-      <c r="H22" s="61"/>
-      <c r="I22" s="61"/>
+      <c r="C22" s="59" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D22" s="59" t="s">
+        <v>1124</v>
+      </c>
+      <c r="E22" s="59" t="s">
+        <v>1125</v>
+      </c>
+      <c r="F22" s="62"/>
+      <c r="G22" s="62"/>
+      <c r="H22" s="62"/>
+      <c r="I22" s="62"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="63" t="s">
-        <v>1119</v>
-      </c>
-      <c r="B23" s="58" t="s">
-        <v>1120</v>
-      </c>
-      <c r="C23" s="58" t="s">
-        <v>1121</v>
-      </c>
-      <c r="D23" s="58" t="s">
-        <v>1122</v>
-      </c>
-      <c r="E23" s="58" t="s">
-        <v>1123</v>
-      </c>
-      <c r="F23" s="61"/>
-      <c r="G23" s="61"/>
-      <c r="H23" s="61"/>
-      <c r="I23" s="61"/>
+      <c r="A23" s="64" t="s">
+        <v>1126</v>
+      </c>
+      <c r="B23" s="59" t="s">
+        <v>1127</v>
+      </c>
+      <c r="C23" s="59" t="s">
+        <v>1128</v>
+      </c>
+      <c r="D23" s="59" t="s">
+        <v>1129</v>
+      </c>
+      <c r="E23" s="59" t="s">
+        <v>1130</v>
+      </c>
+      <c r="F23" s="62"/>
+      <c r="G23" s="62"/>
+      <c r="H23" s="62"/>
+      <c r="I23" s="62"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="D24" s="66"/>
-      <c r="E24" s="61"/>
-      <c r="F24" s="61"/>
-      <c r="G24" s="61"/>
-      <c r="H24" s="61"/>
-      <c r="I24" s="61"/>
+      <c r="D24" s="67"/>
+      <c r="E24" s="62"/>
+      <c r="F24" s="62"/>
+      <c r="G24" s="62"/>
+      <c r="H24" s="62"/>
+      <c r="I24" s="62"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="67"/>
-      <c r="B25" s="67"/>
-      <c r="C25" s="67"/>
-      <c r="D25" s="67"/>
-      <c r="E25" s="67"/>
-      <c r="F25" s="61"/>
-      <c r="G25" s="61"/>
-      <c r="H25" s="61"/>
-      <c r="I25" s="61"/>
+      <c r="A25" s="68"/>
+      <c r="B25" s="68"/>
+      <c r="C25" s="68"/>
+      <c r="D25" s="68"/>
+      <c r="E25" s="68"/>
+      <c r="F25" s="62"/>
+      <c r="G25" s="62"/>
+      <c r="H25" s="62"/>
+      <c r="I25" s="62"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="67"/>
-      <c r="B26" s="67"/>
-      <c r="C26" s="67"/>
-      <c r="D26" s="67"/>
-      <c r="E26" s="67"/>
-      <c r="F26" s="61"/>
-      <c r="G26" s="61"/>
-      <c r="H26" s="61"/>
-      <c r="I26" s="61"/>
+      <c r="A26" s="68"/>
+      <c r="B26" s="68"/>
+      <c r="C26" s="68"/>
+      <c r="D26" s="68"/>
+      <c r="E26" s="68"/>
+      <c r="F26" s="62"/>
+      <c r="G26" s="62"/>
+      <c r="H26" s="62"/>
+      <c r="I26" s="62"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="67"/>
-      <c r="B27" s="67"/>
-      <c r="C27" s="67"/>
-      <c r="D27" s="67"/>
-      <c r="E27" s="67"/>
-      <c r="F27" s="61"/>
-      <c r="G27" s="61"/>
-      <c r="H27" s="61"/>
-      <c r="I27" s="61"/>
+      <c r="A27" s="68"/>
+      <c r="B27" s="68"/>
+      <c r="C27" s="68"/>
+      <c r="D27" s="68"/>
+      <c r="E27" s="68"/>
+      <c r="F27" s="62"/>
+      <c r="G27" s="62"/>
+      <c r="H27" s="62"/>
+      <c r="I27" s="62"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="67"/>
-      <c r="B28" s="67"/>
-      <c r="C28" s="67"/>
-      <c r="D28" s="67"/>
-      <c r="E28" s="67"/>
-      <c r="F28" s="61"/>
-      <c r="G28" s="61"/>
-      <c r="H28" s="61"/>
-      <c r="I28" s="61"/>
+      <c r="A28" s="68"/>
+      <c r="B28" s="68"/>
+      <c r="C28" s="68"/>
+      <c r="D28" s="68"/>
+      <c r="E28" s="68"/>
+      <c r="F28" s="62"/>
+      <c r="G28" s="62"/>
+      <c r="H28" s="62"/>
+      <c r="I28" s="62"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="61"/>
-      <c r="B29" s="61"/>
-      <c r="C29" s="61"/>
-      <c r="D29" s="61"/>
-      <c r="E29" s="61"/>
-      <c r="F29" s="61"/>
-      <c r="G29" s="61"/>
-      <c r="H29" s="61"/>
-      <c r="I29" s="61"/>
+      <c r="A29" s="62"/>
+      <c r="B29" s="62"/>
+      <c r="C29" s="62"/>
+      <c r="D29" s="62"/>
+      <c r="E29" s="62"/>
+      <c r="F29" s="62"/>
+      <c r="G29" s="62"/>
+      <c r="H29" s="62"/>
+      <c r="I29" s="62"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="61"/>
-      <c r="B30" s="61"/>
-      <c r="C30" s="61"/>
-      <c r="D30" s="61"/>
-      <c r="E30" s="61"/>
-      <c r="F30" s="61"/>
-      <c r="G30" s="61"/>
-      <c r="H30" s="61"/>
-      <c r="I30" s="61"/>
+      <c r="A30" s="62"/>
+      <c r="B30" s="62"/>
+      <c r="C30" s="62"/>
+      <c r="D30" s="62"/>
+      <c r="E30" s="62"/>
+      <c r="F30" s="62"/>
+      <c r="G30" s="62"/>
+      <c r="H30" s="62"/>
+      <c r="I30" s="62"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="61"/>
-      <c r="B31" s="61"/>
-      <c r="C31" s="61"/>
-      <c r="D31" s="61"/>
-      <c r="E31" s="61"/>
-      <c r="F31" s="61"/>
-      <c r="G31" s="61"/>
-      <c r="H31" s="61"/>
-      <c r="I31" s="61"/>
+      <c r="A31" s="62"/>
+      <c r="B31" s="62"/>
+      <c r="C31" s="62"/>
+      <c r="D31" s="62"/>
+      <c r="E31" s="62"/>
+      <c r="F31" s="62"/>
+      <c r="G31" s="62"/>
+      <c r="H31" s="62"/>
+      <c r="I31" s="62"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="61"/>
-      <c r="B32" s="61"/>
-      <c r="C32" s="61"/>
-      <c r="D32" s="61"/>
-      <c r="E32" s="61"/>
-      <c r="F32" s="61"/>
-      <c r="G32" s="61"/>
-      <c r="H32" s="61"/>
-      <c r="I32" s="61"/>
+      <c r="A32" s="62"/>
+      <c r="B32" s="62"/>
+      <c r="C32" s="62"/>
+      <c r="D32" s="62"/>
+      <c r="E32" s="62"/>
+      <c r="F32" s="62"/>
+      <c r="G32" s="62"/>
+      <c r="H32" s="62"/>
+      <c r="I32" s="62"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="61"/>
-      <c r="B33" s="61"/>
-      <c r="C33" s="61"/>
-      <c r="D33" s="61"/>
-      <c r="E33" s="61"/>
-      <c r="F33" s="61"/>
-      <c r="G33" s="61"/>
-      <c r="H33" s="61"/>
-      <c r="I33" s="61"/>
+      <c r="A33" s="62"/>
+      <c r="B33" s="62"/>
+      <c r="C33" s="62"/>
+      <c r="D33" s="62"/>
+      <c r="E33" s="62"/>
+      <c r="F33" s="62"/>
+      <c r="G33" s="62"/>
+      <c r="H33" s="62"/>
+      <c r="I33" s="62"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="61"/>
-      <c r="B34" s="61"/>
-      <c r="C34" s="61"/>
-      <c r="D34" s="61"/>
-      <c r="E34" s="61"/>
-      <c r="F34" s="61"/>
-      <c r="G34" s="61"/>
-      <c r="H34" s="61"/>
-      <c r="I34" s="61"/>
+      <c r="A34" s="62"/>
+      <c r="B34" s="62"/>
+      <c r="C34" s="62"/>
+      <c r="D34" s="62"/>
+      <c r="E34" s="62"/>
+      <c r="F34" s="62"/>
+      <c r="G34" s="62"/>
+      <c r="H34" s="62"/>
+      <c r="I34" s="62"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="61"/>
-      <c r="B35" s="61"/>
-      <c r="C35" s="61"/>
-      <c r="D35" s="61"/>
-      <c r="E35" s="61"/>
-      <c r="F35" s="61"/>
-      <c r="G35" s="61"/>
-      <c r="H35" s="61"/>
-      <c r="I35" s="61"/>
+      <c r="A35" s="62"/>
+      <c r="B35" s="62"/>
+      <c r="C35" s="62"/>
+      <c r="D35" s="62"/>
+      <c r="E35" s="62"/>
+      <c r="F35" s="62"/>
+      <c r="G35" s="62"/>
+      <c r="H35" s="62"/>
+      <c r="I35" s="62"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="61"/>
-      <c r="B36" s="61"/>
-      <c r="C36" s="61"/>
-      <c r="D36" s="61"/>
-      <c r="E36" s="61"/>
-      <c r="F36" s="61"/>
-      <c r="G36" s="61"/>
-      <c r="H36" s="61"/>
-      <c r="I36" s="61"/>
+      <c r="A36" s="62"/>
+      <c r="B36" s="62"/>
+      <c r="C36" s="62"/>
+      <c r="D36" s="62"/>
+      <c r="E36" s="62"/>
+      <c r="F36" s="62"/>
+      <c r="G36" s="62"/>
+      <c r="H36" s="62"/>
+      <c r="I36" s="62"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="61"/>
-      <c r="B37" s="61"/>
-      <c r="C37" s="61"/>
-      <c r="D37" s="61"/>
-      <c r="E37" s="61"/>
-      <c r="F37" s="61"/>
-      <c r="G37" s="61"/>
-      <c r="H37" s="61"/>
-      <c r="I37" s="61"/>
+      <c r="A37" s="62"/>
+      <c r="B37" s="62"/>
+      <c r="C37" s="62"/>
+      <c r="D37" s="62"/>
+      <c r="E37" s="62"/>
+      <c r="F37" s="62"/>
+      <c r="G37" s="62"/>
+      <c r="H37" s="62"/>
+      <c r="I37" s="62"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="61"/>
-      <c r="B38" s="61"/>
-      <c r="C38" s="61"/>
-      <c r="D38" s="61"/>
-      <c r="E38" s="61"/>
-      <c r="F38" s="61"/>
-      <c r="G38" s="61"/>
-      <c r="H38" s="61"/>
-      <c r="I38" s="61"/>
+      <c r="A38" s="62"/>
+      <c r="B38" s="62"/>
+      <c r="C38" s="62"/>
+      <c r="D38" s="62"/>
+      <c r="E38" s="62"/>
+      <c r="F38" s="62"/>
+      <c r="G38" s="62"/>
+      <c r="H38" s="62"/>
+      <c r="I38" s="62"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="61"/>
-      <c r="B39" s="61"/>
-      <c r="C39" s="61"/>
-      <c r="D39" s="61"/>
-      <c r="E39" s="61"/>
-      <c r="F39" s="61"/>
-      <c r="G39" s="61"/>
-      <c r="H39" s="61"/>
-      <c r="I39" s="61"/>
+      <c r="A39" s="62"/>
+      <c r="B39" s="62"/>
+      <c r="C39" s="62"/>
+      <c r="D39" s="62"/>
+      <c r="E39" s="62"/>
+      <c r="F39" s="62"/>
+      <c r="G39" s="62"/>
+      <c r="H39" s="62"/>
+      <c r="I39" s="62"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="61"/>
-      <c r="B40" s="61"/>
-      <c r="C40" s="61"/>
-      <c r="D40" s="61"/>
-      <c r="E40" s="61"/>
-      <c r="F40" s="61"/>
-      <c r="G40" s="61"/>
-      <c r="H40" s="61"/>
-      <c r="I40" s="61"/>
+      <c r="A40" s="62"/>
+      <c r="B40" s="62"/>
+      <c r="C40" s="62"/>
+      <c r="D40" s="62"/>
+      <c r="E40" s="62"/>
+      <c r="F40" s="62"/>
+      <c r="G40" s="62"/>
+      <c r="H40" s="62"/>
+      <c r="I40" s="62"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="61"/>
-      <c r="B41" s="61"/>
-      <c r="C41" s="61"/>
-      <c r="D41" s="61"/>
-      <c r="E41" s="61"/>
-      <c r="F41" s="61"/>
-      <c r="G41" s="61"/>
-      <c r="H41" s="61"/>
-      <c r="I41" s="61"/>
+      <c r="A41" s="62"/>
+      <c r="B41" s="62"/>
+      <c r="C41" s="62"/>
+      <c r="D41" s="62"/>
+      <c r="E41" s="62"/>
+      <c r="F41" s="62"/>
+      <c r="G41" s="62"/>
+      <c r="H41" s="62"/>
+      <c r="I41" s="62"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="61"/>
-      <c r="B42" s="61"/>
-      <c r="C42" s="61"/>
-      <c r="D42" s="61"/>
-      <c r="E42" s="61"/>
-      <c r="F42" s="61"/>
-      <c r="G42" s="61"/>
-      <c r="H42" s="61"/>
-      <c r="I42" s="61"/>
+      <c r="A42" s="62"/>
+      <c r="B42" s="62"/>
+      <c r="C42" s="62"/>
+      <c r="D42" s="62"/>
+      <c r="E42" s="62"/>
+      <c r="F42" s="62"/>
+      <c r="G42" s="62"/>
+      <c r="H42" s="62"/>
+      <c r="I42" s="62"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="61"/>
-      <c r="B43" s="61"/>
-      <c r="C43" s="61"/>
-      <c r="D43" s="61"/>
-      <c r="E43" s="61"/>
-      <c r="F43" s="61"/>
-      <c r="G43" s="61"/>
-      <c r="H43" s="61"/>
-      <c r="I43" s="61"/>
+      <c r="A43" s="62"/>
+      <c r="B43" s="62"/>
+      <c r="C43" s="62"/>
+      <c r="D43" s="62"/>
+      <c r="E43" s="62"/>
+      <c r="F43" s="62"/>
+      <c r="G43" s="62"/>
+      <c r="H43" s="62"/>
+      <c r="I43" s="62"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" s="61"/>
-      <c r="B44" s="61"/>
-      <c r="C44" s="61"/>
-      <c r="D44" s="61"/>
-      <c r="E44" s="61"/>
-      <c r="F44" s="61"/>
-      <c r="G44" s="61"/>
-      <c r="H44" s="61"/>
-      <c r="I44" s="61"/>
+      <c r="A44" s="62"/>
+      <c r="B44" s="62"/>
+      <c r="C44" s="62"/>
+      <c r="D44" s="62"/>
+      <c r="E44" s="62"/>
+      <c r="F44" s="62"/>
+      <c r="G44" s="62"/>
+      <c r="H44" s="62"/>
+      <c r="I44" s="62"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" s="61"/>
-      <c r="B45" s="61"/>
-      <c r="C45" s="61"/>
-      <c r="D45" s="61"/>
-      <c r="E45" s="61"/>
-      <c r="F45" s="61"/>
-      <c r="G45" s="61"/>
-      <c r="H45" s="61"/>
-      <c r="I45" s="61"/>
+      <c r="A45" s="62"/>
+      <c r="B45" s="62"/>
+      <c r="C45" s="62"/>
+      <c r="D45" s="62"/>
+      <c r="E45" s="62"/>
+      <c r="F45" s="62"/>
+      <c r="G45" s="62"/>
+      <c r="H45" s="62"/>
+      <c r="I45" s="62"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" s="61"/>
-      <c r="B46" s="61"/>
-      <c r="C46" s="61"/>
-      <c r="D46" s="61"/>
-      <c r="E46" s="61"/>
-      <c r="F46" s="61"/>
-      <c r="G46" s="61"/>
-      <c r="H46" s="61"/>
-      <c r="I46" s="61"/>
+      <c r="A46" s="62"/>
+      <c r="B46" s="62"/>
+      <c r="C46" s="62"/>
+      <c r="D46" s="62"/>
+      <c r="E46" s="62"/>
+      <c r="F46" s="62"/>
+      <c r="G46" s="62"/>
+      <c r="H46" s="62"/>
+      <c r="I46" s="62"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
-      <c r="A47" s="61"/>
-      <c r="B47" s="61"/>
-      <c r="C47" s="61"/>
-      <c r="D47" s="61"/>
-      <c r="E47" s="61"/>
-      <c r="F47" s="61"/>
-      <c r="G47" s="61"/>
-      <c r="H47" s="61"/>
-      <c r="I47" s="61"/>
+      <c r="A47" s="62"/>
+      <c r="B47" s="62"/>
+      <c r="C47" s="62"/>
+      <c r="D47" s="62"/>
+      <c r="E47" s="62"/>
+      <c r="F47" s="62"/>
+      <c r="G47" s="62"/>
+      <c r="H47" s="62"/>
+      <c r="I47" s="62"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
-      <c r="A48" s="61"/>
-      <c r="B48" s="61"/>
-      <c r="C48" s="61"/>
-      <c r="D48" s="61"/>
-      <c r="E48" s="61"/>
-      <c r="F48" s="61"/>
-      <c r="G48" s="61"/>
-      <c r="H48" s="61"/>
-      <c r="I48" s="61"/>
+      <c r="A48" s="62"/>
+      <c r="B48" s="62"/>
+      <c r="C48" s="62"/>
+      <c r="D48" s="62"/>
+      <c r="E48" s="62"/>
+      <c r="F48" s="62"/>
+      <c r="G48" s="62"/>
+      <c r="H48" s="62"/>
+      <c r="I48" s="62"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" s="61"/>
-      <c r="B49" s="61"/>
-      <c r="C49" s="61"/>
-      <c r="D49" s="61"/>
-      <c r="E49" s="61"/>
-      <c r="F49" s="61"/>
-      <c r="G49" s="61"/>
-      <c r="H49" s="61"/>
-      <c r="I49" s="61"/>
+      <c r="A49" s="62"/>
+      <c r="B49" s="62"/>
+      <c r="C49" s="62"/>
+      <c r="D49" s="62"/>
+      <c r="E49" s="62"/>
+      <c r="F49" s="62"/>
+      <c r="G49" s="62"/>
+      <c r="H49" s="62"/>
+      <c r="I49" s="62"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="A50" s="61"/>
-      <c r="B50" s="61"/>
-      <c r="C50" s="61"/>
-      <c r="D50" s="61"/>
-      <c r="E50" s="61"/>
-      <c r="F50" s="61"/>
-      <c r="G50" s="61"/>
-      <c r="H50" s="61"/>
-      <c r="I50" s="61"/>
+      <c r="A50" s="62"/>
+      <c r="B50" s="62"/>
+      <c r="C50" s="62"/>
+      <c r="D50" s="62"/>
+      <c r="E50" s="62"/>
+      <c r="F50" s="62"/>
+      <c r="G50" s="62"/>
+      <c r="H50" s="62"/>
+      <c r="I50" s="62"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
-      <c r="A51" s="61"/>
-      <c r="B51" s="61"/>
-      <c r="C51" s="61"/>
-      <c r="D51" s="61"/>
-      <c r="E51" s="61"/>
-      <c r="F51" s="61"/>
-      <c r="G51" s="61"/>
-      <c r="H51" s="61"/>
-      <c r="I51" s="61"/>
+      <c r="A51" s="62"/>
+      <c r="B51" s="62"/>
+      <c r="C51" s="62"/>
+      <c r="D51" s="62"/>
+      <c r="E51" s="62"/>
+      <c r="F51" s="62"/>
+      <c r="G51" s="62"/>
+      <c r="H51" s="62"/>
+      <c r="I51" s="62"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
-      <c r="A52" s="61"/>
-      <c r="B52" s="61"/>
-      <c r="C52" s="61"/>
-      <c r="D52" s="61"/>
-      <c r="E52" s="61"/>
-      <c r="F52" s="61"/>
-      <c r="G52" s="61"/>
-      <c r="H52" s="61"/>
-      <c r="I52" s="61"/>
+      <c r="A52" s="62"/>
+      <c r="B52" s="62"/>
+      <c r="C52" s="62"/>
+      <c r="D52" s="62"/>
+      <c r="E52" s="62"/>
+      <c r="F52" s="62"/>
+      <c r="G52" s="62"/>
+      <c r="H52" s="62"/>
+      <c r="I52" s="62"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
-      <c r="A53" s="61"/>
-      <c r="B53" s="61"/>
-      <c r="C53" s="61"/>
-      <c r="D53" s="61"/>
-      <c r="E53" s="61"/>
-      <c r="F53" s="61"/>
-      <c r="G53" s="61"/>
-      <c r="H53" s="61"/>
-      <c r="I53" s="61"/>
+      <c r="A53" s="62"/>
+      <c r="B53" s="62"/>
+      <c r="C53" s="62"/>
+      <c r="D53" s="62"/>
+      <c r="E53" s="62"/>
+      <c r="F53" s="62"/>
+      <c r="G53" s="62"/>
+      <c r="H53" s="62"/>
+      <c r="I53" s="62"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" s="61"/>
-      <c r="B54" s="61"/>
-      <c r="C54" s="61"/>
-      <c r="D54" s="61"/>
-      <c r="E54" s="61"/>
-      <c r="F54" s="61"/>
-      <c r="G54" s="61"/>
-      <c r="H54" s="61"/>
-      <c r="I54" s="61"/>
+      <c r="A54" s="62"/>
+      <c r="B54" s="62"/>
+      <c r="C54" s="62"/>
+      <c r="D54" s="62"/>
+      <c r="E54" s="62"/>
+      <c r="F54" s="62"/>
+      <c r="G54" s="62"/>
+      <c r="H54" s="62"/>
+      <c r="I54" s="62"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
-      <c r="A55" s="61"/>
-      <c r="B55" s="61"/>
-      <c r="C55" s="61"/>
-      <c r="D55" s="61"/>
-      <c r="E55" s="61"/>
-      <c r="F55" s="61"/>
-      <c r="G55" s="61"/>
-      <c r="H55" s="61"/>
-      <c r="I55" s="61"/>
+      <c r="A55" s="62"/>
+      <c r="B55" s="62"/>
+      <c r="C55" s="62"/>
+      <c r="D55" s="62"/>
+      <c r="E55" s="62"/>
+      <c r="F55" s="62"/>
+      <c r="G55" s="62"/>
+      <c r="H55" s="62"/>
+      <c r="I55" s="62"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
-      <c r="A56" s="61"/>
-      <c r="B56" s="61"/>
-      <c r="C56" s="61"/>
-      <c r="D56" s="61"/>
-      <c r="E56" s="61"/>
-      <c r="F56" s="61"/>
-      <c r="G56" s="61"/>
-      <c r="H56" s="61"/>
-      <c r="I56" s="61"/>
+      <c r="A56" s="62"/>
+      <c r="B56" s="62"/>
+      <c r="C56" s="62"/>
+      <c r="D56" s="62"/>
+      <c r="E56" s="62"/>
+      <c r="F56" s="62"/>
+      <c r="G56" s="62"/>
+      <c r="H56" s="62"/>
+      <c r="I56" s="62"/>
     </row>
     <row r="57" ht="18.75" customHeight="1">
-      <c r="A57" s="61"/>
-      <c r="B57" s="61"/>
-      <c r="C57" s="61"/>
-      <c r="D57" s="61"/>
-      <c r="E57" s="61"/>
-      <c r="F57" s="61"/>
-      <c r="G57" s="61"/>
-      <c r="H57" s="61"/>
-      <c r="I57" s="61"/>
+      <c r="A57" s="62"/>
+      <c r="B57" s="62"/>
+      <c r="C57" s="62"/>
+      <c r="D57" s="62"/>
+      <c r="E57" s="62"/>
+      <c r="F57" s="62"/>
+      <c r="G57" s="62"/>
+      <c r="H57" s="62"/>
+      <c r="I57" s="62"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
-      <c r="A58" s="61"/>
-      <c r="B58" s="61"/>
-      <c r="C58" s="61"/>
-      <c r="D58" s="61"/>
-      <c r="E58" s="61"/>
-      <c r="F58" s="61"/>
-      <c r="G58" s="61"/>
-      <c r="H58" s="61"/>
-      <c r="I58" s="61"/>
+      <c r="A58" s="62"/>
+      <c r="B58" s="62"/>
+      <c r="C58" s="62"/>
+      <c r="D58" s="62"/>
+      <c r="E58" s="62"/>
+      <c r="F58" s="62"/>
+      <c r="G58" s="62"/>
+      <c r="H58" s="62"/>
+      <c r="I58" s="62"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
-      <c r="A59" s="61"/>
-      <c r="B59" s="61"/>
-      <c r="C59" s="61"/>
-      <c r="D59" s="61"/>
-      <c r="E59" s="61"/>
-      <c r="F59" s="61"/>
-      <c r="G59" s="61"/>
-      <c r="H59" s="61"/>
-      <c r="I59" s="61"/>
+      <c r="A59" s="62"/>
+      <c r="B59" s="62"/>
+      <c r="C59" s="62"/>
+      <c r="D59" s="62"/>
+      <c r="E59" s="62"/>
+      <c r="F59" s="62"/>
+      <c r="G59" s="62"/>
+      <c r="H59" s="62"/>
+      <c r="I59" s="62"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
-      <c r="A60" s="61"/>
-      <c r="B60" s="61"/>
-      <c r="C60" s="61"/>
-      <c r="D60" s="61"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="61"/>
+      <c r="A60" s="62"/>
+      <c r="B60" s="62"/>
+      <c r="C60" s="62"/>
+      <c r="D60" s="62"/>
+      <c r="E60" s="62"/>
+      <c r="F60" s="62"/>
+      <c r="G60" s="62"/>
+      <c r="H60" s="62"/>
+      <c r="I60" s="62"/>
     </row>
     <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" s="61"/>
-      <c r="B61" s="61"/>
-      <c r="C61" s="61"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61"/>
+      <c r="A61" s="62"/>
+      <c r="B61" s="62"/>
+      <c r="C61" s="62"/>
+      <c r="D61" s="62"/>
+      <c r="E61" s="62"/>
+      <c r="F61" s="62"/>
+      <c r="G61" s="62"/>
+      <c r="H61" s="62"/>
+      <c r="I61" s="62"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
-      <c r="A62" s="61"/>
-      <c r="B62" s="61"/>
-      <c r="C62" s="61"/>
-      <c r="D62" s="61"/>
-      <c r="E62" s="61"/>
-      <c r="F62" s="61"/>
-      <c r="G62" s="61"/>
-      <c r="H62" s="61"/>
-      <c r="I62" s="61"/>
+      <c r="A62" s="62"/>
+      <c r="B62" s="62"/>
+      <c r="C62" s="62"/>
+      <c r="D62" s="62"/>
+      <c r="E62" s="62"/>
+      <c r="F62" s="62"/>
+      <c r="G62" s="62"/>
+      <c r="H62" s="62"/>
+      <c r="I62" s="62"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
-      <c r="A63" s="61"/>
-      <c r="B63" s="61"/>
-      <c r="C63" s="61"/>
-      <c r="D63" s="61"/>
-      <c r="E63" s="61"/>
-      <c r="F63" s="61"/>
-      <c r="G63" s="61"/>
-      <c r="H63" s="61"/>
-      <c r="I63" s="61"/>
+      <c r="A63" s="62"/>
+      <c r="B63" s="62"/>
+      <c r="C63" s="62"/>
+      <c r="D63" s="62"/>
+      <c r="E63" s="62"/>
+      <c r="F63" s="62"/>
+      <c r="G63" s="62"/>
+      <c r="H63" s="62"/>
+      <c r="I63" s="62"/>
     </row>
     <row r="64" ht="18.75" customHeight="1">
-      <c r="A64" s="61"/>
-      <c r="B64" s="61"/>
-      <c r="C64" s="61"/>
-      <c r="D64" s="61"/>
-      <c r="E64" s="61"/>
-      <c r="F64" s="61"/>
-      <c r="G64" s="61"/>
-      <c r="H64" s="61"/>
-      <c r="I64" s="61"/>
+      <c r="A64" s="62"/>
+      <c r="B64" s="62"/>
+      <c r="C64" s="62"/>
+      <c r="D64" s="62"/>
+      <c r="E64" s="62"/>
+      <c r="F64" s="62"/>
+      <c r="G64" s="62"/>
+      <c r="H64" s="62"/>
+      <c r="I64" s="62"/>
     </row>
     <row r="65" ht="18.75" customHeight="1">
-      <c r="A65" s="61"/>
-      <c r="B65" s="61"/>
-      <c r="C65" s="61"/>
-      <c r="D65" s="61"/>
-      <c r="E65" s="61"/>
-      <c r="F65" s="61"/>
-      <c r="G65" s="61"/>
-      <c r="H65" s="61"/>
-      <c r="I65" s="61"/>
+      <c r="A65" s="62"/>
+      <c r="B65" s="62"/>
+      <c r="C65" s="62"/>
+      <c r="D65" s="62"/>
+      <c r="E65" s="62"/>
+      <c r="F65" s="62"/>
+      <c r="G65" s="62"/>
+      <c r="H65" s="62"/>
+      <c r="I65" s="62"/>
     </row>
     <row r="66" ht="18.75" customHeight="1">
-      <c r="A66" s="61"/>
-      <c r="B66" s="61"/>
-      <c r="C66" s="61"/>
-      <c r="D66" s="61"/>
-      <c r="E66" s="61"/>
-      <c r="F66" s="61"/>
-      <c r="G66" s="61"/>
-      <c r="H66" s="61"/>
-      <c r="I66" s="61"/>
+      <c r="A66" s="62"/>
+      <c r="B66" s="62"/>
+      <c r="C66" s="62"/>
+      <c r="D66" s="62"/>
+      <c r="E66" s="62"/>
+      <c r="F66" s="62"/>
+      <c r="G66" s="62"/>
+      <c r="H66" s="62"/>
+      <c r="I66" s="62"/>
     </row>
     <row r="67" ht="18.75" customHeight="1">
-      <c r="A67" s="61"/>
-      <c r="B67" s="61"/>
-      <c r="C67" s="61"/>
-      <c r="D67" s="61"/>
-      <c r="E67" s="61"/>
-      <c r="F67" s="61"/>
-      <c r="G67" s="61"/>
-      <c r="H67" s="61"/>
-      <c r="I67" s="61"/>
+      <c r="A67" s="62"/>
+      <c r="B67" s="62"/>
+      <c r="C67" s="62"/>
+      <c r="D67" s="62"/>
+      <c r="E67" s="62"/>
+      <c r="F67" s="62"/>
+      <c r="G67" s="62"/>
+      <c r="H67" s="62"/>
+      <c r="I67" s="62"/>
     </row>
     <row r="68" ht="18.75" customHeight="1">
-      <c r="A68" s="61"/>
-      <c r="B68" s="61"/>
-      <c r="C68" s="61"/>
-      <c r="D68" s="61"/>
-      <c r="E68" s="61"/>
-      <c r="F68" s="61"/>
-      <c r="G68" s="61"/>
-      <c r="H68" s="61"/>
-      <c r="I68" s="61"/>
+      <c r="A68" s="62"/>
+      <c r="B68" s="62"/>
+      <c r="C68" s="62"/>
+      <c r="D68" s="62"/>
+      <c r="E68" s="62"/>
+      <c r="F68" s="62"/>
+      <c r="G68" s="62"/>
+      <c r="H68" s="62"/>
+      <c r="I68" s="62"/>
     </row>
     <row r="69" ht="18.75" customHeight="1">
-      <c r="A69" s="61"/>
-      <c r="B69" s="61"/>
-      <c r="C69" s="61"/>
-      <c r="D69" s="61"/>
-      <c r="E69" s="61"/>
-      <c r="F69" s="61"/>
-      <c r="G69" s="61"/>
-      <c r="H69" s="61"/>
-      <c r="I69" s="61"/>
+      <c r="A69" s="62"/>
+      <c r="B69" s="62"/>
+      <c r="C69" s="62"/>
+      <c r="D69" s="62"/>
+      <c r="E69" s="62"/>
+      <c r="F69" s="62"/>
+      <c r="G69" s="62"/>
+      <c r="H69" s="62"/>
+      <c r="I69" s="62"/>
     </row>
     <row r="70" ht="18.75" customHeight="1">
-      <c r="A70" s="61"/>
-      <c r="B70" s="61"/>
-      <c r="C70" s="61"/>
-      <c r="D70" s="61"/>
-      <c r="E70" s="61"/>
-      <c r="F70" s="61"/>
-      <c r="G70" s="61"/>
-      <c r="H70" s="61"/>
-      <c r="I70" s="61"/>
+      <c r="A70" s="62"/>
+      <c r="B70" s="62"/>
+      <c r="C70" s="62"/>
+      <c r="D70" s="62"/>
+      <c r="E70" s="62"/>
+      <c r="F70" s="62"/>
+      <c r="G70" s="62"/>
+      <c r="H70" s="62"/>
+      <c r="I70" s="62"/>
     </row>
     <row r="71" ht="18.75" customHeight="1">
-      <c r="A71" s="61"/>
-      <c r="B71" s="61"/>
-      <c r="C71" s="61"/>
-      <c r="D71" s="61"/>
-      <c r="E71" s="61"/>
-      <c r="F71" s="61"/>
-      <c r="G71" s="61"/>
-      <c r="H71" s="61"/>
-      <c r="I71" s="61"/>
+      <c r="A71" s="62"/>
+      <c r="B71" s="62"/>
+      <c r="C71" s="62"/>
+      <c r="D71" s="62"/>
+      <c r="E71" s="62"/>
+      <c r="F71" s="62"/>
+      <c r="G71" s="62"/>
+      <c r="H71" s="62"/>
+      <c r="I71" s="62"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
-      <c r="A72" s="61"/>
-      <c r="B72" s="61"/>
-      <c r="C72" s="61"/>
-      <c r="D72" s="61"/>
-      <c r="E72" s="61"/>
-      <c r="F72" s="61"/>
-      <c r="G72" s="61"/>
-      <c r="H72" s="61"/>
-      <c r="I72" s="61"/>
+      <c r="A72" s="62"/>
+      <c r="B72" s="62"/>
+      <c r="C72" s="62"/>
+      <c r="D72" s="62"/>
+      <c r="E72" s="62"/>
+      <c r="F72" s="62"/>
+      <c r="G72" s="62"/>
+      <c r="H72" s="62"/>
+      <c r="I72" s="62"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
-      <c r="A73" s="61"/>
-      <c r="B73" s="61"/>
-      <c r="C73" s="61"/>
-      <c r="D73" s="61"/>
-      <c r="E73" s="61"/>
-      <c r="F73" s="61"/>
-      <c r="G73" s="61"/>
-      <c r="H73" s="61"/>
-      <c r="I73" s="61"/>
+      <c r="A73" s="62"/>
+      <c r="B73" s="62"/>
+      <c r="C73" s="62"/>
+      <c r="D73" s="62"/>
+      <c r="E73" s="62"/>
+      <c r="F73" s="62"/>
+      <c r="G73" s="62"/>
+      <c r="H73" s="62"/>
+      <c r="I73" s="62"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
-      <c r="A74" s="61"/>
-      <c r="B74" s="61"/>
-      <c r="C74" s="61"/>
-      <c r="D74" s="61"/>
-      <c r="E74" s="61"/>
-      <c r="F74" s="61"/>
-      <c r="G74" s="61"/>
-      <c r="H74" s="61"/>
-      <c r="I74" s="61"/>
+      <c r="A74" s="62"/>
+      <c r="B74" s="62"/>
+      <c r="C74" s="62"/>
+      <c r="D74" s="62"/>
+      <c r="E74" s="62"/>
+      <c r="F74" s="62"/>
+      <c r="G74" s="62"/>
+      <c r="H74" s="62"/>
+      <c r="I74" s="62"/>
     </row>
     <row r="75" ht="18.75" customHeight="1">
-      <c r="A75" s="61"/>
-      <c r="B75" s="61"/>
-      <c r="C75" s="61"/>
-      <c r="D75" s="61"/>
-      <c r="E75" s="61"/>
-      <c r="F75" s="61"/>
-      <c r="G75" s="61"/>
-      <c r="H75" s="61"/>
-      <c r="I75" s="61"/>
+      <c r="A75" s="62"/>
+      <c r="B75" s="62"/>
+      <c r="C75" s="62"/>
+      <c r="D75" s="62"/>
+      <c r="E75" s="62"/>
+      <c r="F75" s="62"/>
+      <c r="G75" s="62"/>
+      <c r="H75" s="62"/>
+      <c r="I75" s="62"/>
     </row>
     <row r="76" ht="18.75" customHeight="1">
-      <c r="A76" s="61"/>
-      <c r="B76" s="61"/>
-      <c r="C76" s="61"/>
-      <c r="D76" s="61"/>
-      <c r="E76" s="61"/>
-      <c r="F76" s="61"/>
-      <c r="G76" s="61"/>
-      <c r="H76" s="61"/>
-      <c r="I76" s="61"/>
+      <c r="A76" s="62"/>
+      <c r="B76" s="62"/>
+      <c r="C76" s="62"/>
+      <c r="D76" s="62"/>
+      <c r="E76" s="62"/>
+      <c r="F76" s="62"/>
+      <c r="G76" s="62"/>
+      <c r="H76" s="62"/>
+      <c r="I76" s="62"/>
     </row>
     <row r="77" ht="18.75" customHeight="1">
-      <c r="A77" s="61"/>
-      <c r="B77" s="61"/>
-      <c r="C77" s="61"/>
-      <c r="D77" s="61"/>
-      <c r="E77" s="61"/>
-      <c r="F77" s="61"/>
-      <c r="G77" s="61"/>
-      <c r="H77" s="61"/>
-      <c r="I77" s="61"/>
+      <c r="A77" s="62"/>
+      <c r="B77" s="62"/>
+      <c r="C77" s="62"/>
+      <c r="D77" s="62"/>
+      <c r="E77" s="62"/>
+      <c r="F77" s="62"/>
+      <c r="G77" s="62"/>
+      <c r="H77" s="62"/>
+      <c r="I77" s="62"/>
     </row>
     <row r="78" ht="18.75" customHeight="1">
-      <c r="A78" s="61"/>
-      <c r="B78" s="61"/>
-      <c r="C78" s="61"/>
-      <c r="D78" s="61"/>
-      <c r="E78" s="61"/>
-      <c r="F78" s="61"/>
-      <c r="G78" s="61"/>
-      <c r="H78" s="61"/>
-      <c r="I78" s="61"/>
+      <c r="A78" s="62"/>
+      <c r="B78" s="62"/>
+      <c r="C78" s="62"/>
+      <c r="D78" s="62"/>
+      <c r="E78" s="62"/>
+      <c r="F78" s="62"/>
+      <c r="G78" s="62"/>
+      <c r="H78" s="62"/>
+      <c r="I78" s="62"/>
     </row>
     <row r="79" ht="18.75" customHeight="1">
-      <c r="A79" s="61"/>
-      <c r="B79" s="61"/>
-      <c r="C79" s="61"/>
-      <c r="D79" s="61"/>
-      <c r="E79" s="61"/>
-      <c r="F79" s="61"/>
-      <c r="G79" s="61"/>
-      <c r="H79" s="61"/>
-      <c r="I79" s="61"/>
+      <c r="A79" s="62"/>
+      <c r="B79" s="62"/>
+      <c r="C79" s="62"/>
+      <c r="D79" s="62"/>
+      <c r="E79" s="62"/>
+      <c r="F79" s="62"/>
+      <c r="G79" s="62"/>
+      <c r="H79" s="62"/>
+      <c r="I79" s="62"/>
     </row>
     <row r="80" ht="18.75" customHeight="1">
-      <c r="A80" s="61"/>
-      <c r="B80" s="61"/>
-      <c r="C80" s="61"/>
-      <c r="D80" s="61"/>
-      <c r="E80" s="61"/>
-      <c r="F80" s="61"/>
-      <c r="G80" s="61"/>
-      <c r="H80" s="61"/>
-      <c r="I80" s="61"/>
+      <c r="A80" s="62"/>
+      <c r="B80" s="62"/>
+      <c r="C80" s="62"/>
+      <c r="D80" s="62"/>
+      <c r="E80" s="62"/>
+      <c r="F80" s="62"/>
+      <c r="G80" s="62"/>
+      <c r="H80" s="62"/>
+      <c r="I80" s="62"/>
     </row>
     <row r="81" ht="18.75" customHeight="1">
-      <c r="A81" s="61"/>
-      <c r="B81" s="61"/>
-      <c r="C81" s="61"/>
-      <c r="D81" s="61"/>
-      <c r="E81" s="61"/>
-      <c r="F81" s="61"/>
-      <c r="G81" s="61"/>
-      <c r="H81" s="61"/>
-      <c r="I81" s="61"/>
+      <c r="A81" s="62"/>
+      <c r="B81" s="62"/>
+      <c r="C81" s="62"/>
+      <c r="D81" s="62"/>
+      <c r="E81" s="62"/>
+      <c r="F81" s="62"/>
+      <c r="G81" s="62"/>
+      <c r="H81" s="62"/>
+      <c r="I81" s="62"/>
     </row>
     <row r="82" ht="18.75" customHeight="1">
-      <c r="A82" s="61"/>
-      <c r="B82" s="61"/>
-      <c r="C82" s="61"/>
-      <c r="D82" s="61"/>
-      <c r="E82" s="61"/>
-      <c r="F82" s="61"/>
-      <c r="G82" s="61"/>
-      <c r="H82" s="61"/>
-      <c r="I82" s="61"/>
+      <c r="A82" s="62"/>
+      <c r="B82" s="62"/>
+      <c r="C82" s="62"/>
+      <c r="D82" s="62"/>
+      <c r="E82" s="62"/>
+      <c r="F82" s="62"/>
+      <c r="G82" s="62"/>
+      <c r="H82" s="62"/>
+      <c r="I82" s="62"/>
     </row>
     <row r="83" ht="18.75" customHeight="1">
-      <c r="A83" s="61"/>
-      <c r="B83" s="61"/>
-      <c r="C83" s="61"/>
-      <c r="D83" s="61"/>
-      <c r="E83" s="61"/>
-      <c r="F83" s="61"/>
-      <c r="G83" s="61"/>
-      <c r="H83" s="61"/>
-      <c r="I83" s="61"/>
+      <c r="A83" s="62"/>
+      <c r="B83" s="62"/>
+      <c r="C83" s="62"/>
+      <c r="D83" s="62"/>
+      <c r="E83" s="62"/>
+      <c r="F83" s="62"/>
+      <c r="G83" s="62"/>
+      <c r="H83" s="62"/>
+      <c r="I83" s="62"/>
     </row>
     <row r="84" ht="18.75" customHeight="1">
-      <c r="A84" s="61"/>
-      <c r="B84" s="61"/>
-      <c r="C84" s="61"/>
-      <c r="D84" s="61"/>
-      <c r="E84" s="61"/>
-      <c r="F84" s="61"/>
-      <c r="G84" s="61"/>
-      <c r="H84" s="61"/>
-      <c r="I84" s="61"/>
+      <c r="A84" s="62"/>
+      <c r="B84" s="62"/>
+      <c r="C84" s="62"/>
+      <c r="D84" s="62"/>
+      <c r="E84" s="62"/>
+      <c r="F84" s="62"/>
+      <c r="G84" s="62"/>
+      <c r="H84" s="62"/>
+      <c r="I84" s="62"/>
     </row>
     <row r="85" ht="18.75" customHeight="1">
-      <c r="A85" s="61"/>
-      <c r="B85" s="61"/>
-      <c r="C85" s="61"/>
-      <c r="D85" s="61"/>
-      <c r="E85" s="61"/>
-      <c r="F85" s="61"/>
-      <c r="G85" s="61"/>
-      <c r="H85" s="61"/>
-      <c r="I85" s="61"/>
+      <c r="A85" s="62"/>
+      <c r="B85" s="62"/>
+      <c r="C85" s="62"/>
+      <c r="D85" s="62"/>
+      <c r="E85" s="62"/>
+      <c r="F85" s="62"/>
+      <c r="G85" s="62"/>
+      <c r="H85" s="62"/>
+      <c r="I85" s="62"/>
     </row>
     <row r="86" ht="18.75" customHeight="1">
-      <c r="A86" s="61"/>
-      <c r="B86" s="61"/>
-      <c r="C86" s="61"/>
-      <c r="D86" s="61"/>
-      <c r="E86" s="61"/>
-      <c r="F86" s="61"/>
-      <c r="G86" s="61"/>
-      <c r="H86" s="61"/>
-      <c r="I86" s="61"/>
+      <c r="A86" s="62"/>
+      <c r="B86" s="62"/>
+      <c r="C86" s="62"/>
+      <c r="D86" s="62"/>
+      <c r="E86" s="62"/>
+      <c r="F86" s="62"/>
+      <c r="G86" s="62"/>
+      <c r="H86" s="62"/>
+      <c r="I86" s="62"/>
     </row>
     <row r="87" ht="18.75" customHeight="1">
-      <c r="A87" s="61"/>
-      <c r="B87" s="61"/>
-      <c r="C87" s="61"/>
-      <c r="D87" s="61"/>
-      <c r="E87" s="61"/>
-      <c r="F87" s="61"/>
-      <c r="G87" s="61"/>
-      <c r="H87" s="61"/>
-      <c r="I87" s="61"/>
+      <c r="A87" s="62"/>
+      <c r="B87" s="62"/>
+      <c r="C87" s="62"/>
+      <c r="D87" s="62"/>
+      <c r="E87" s="62"/>
+      <c r="F87" s="62"/>
+      <c r="G87" s="62"/>
+      <c r="H87" s="62"/>
+      <c r="I87" s="62"/>
     </row>
     <row r="88" ht="18.75" customHeight="1">
-      <c r="A88" s="61"/>
-      <c r="B88" s="61"/>
-      <c r="C88" s="61"/>
-      <c r="D88" s="61"/>
-      <c r="E88" s="61"/>
-      <c r="F88" s="61"/>
-      <c r="G88" s="61"/>
-      <c r="H88" s="61"/>
-      <c r="I88" s="61"/>
+      <c r="A88" s="62"/>
+      <c r="B88" s="62"/>
+      <c r="C88" s="62"/>
+      <c r="D88" s="62"/>
+      <c r="E88" s="62"/>
+      <c r="F88" s="62"/>
+      <c r="G88" s="62"/>
+      <c r="H88" s="62"/>
+      <c r="I88" s="62"/>
     </row>
     <row r="89" ht="18.75" customHeight="1">
-      <c r="A89" s="61"/>
-      <c r="B89" s="61"/>
-      <c r="C89" s="61"/>
-      <c r="D89" s="61"/>
-      <c r="E89" s="61"/>
-      <c r="F89" s="61"/>
-      <c r="G89" s="61"/>
-      <c r="H89" s="61"/>
-      <c r="I89" s="61"/>
+      <c r="A89" s="62"/>
+      <c r="B89" s="62"/>
+      <c r="C89" s="62"/>
+      <c r="D89" s="62"/>
+      <c r="E89" s="62"/>
+      <c r="F89" s="62"/>
+      <c r="G89" s="62"/>
+      <c r="H89" s="62"/>
+      <c r="I89" s="62"/>
     </row>
     <row r="90" ht="18.75" customHeight="1">
-      <c r="A90" s="61"/>
-      <c r="B90" s="61"/>
-      <c r="C90" s="61"/>
-      <c r="D90" s="61"/>
-      <c r="E90" s="61"/>
-      <c r="F90" s="61"/>
-      <c r="G90" s="61"/>
-      <c r="H90" s="61"/>
-      <c r="I90" s="61"/>
+      <c r="A90" s="62"/>
+      <c r="B90" s="62"/>
+      <c r="C90" s="62"/>
+      <c r="D90" s="62"/>
+      <c r="E90" s="62"/>
+      <c r="F90" s="62"/>
+      <c r="G90" s="62"/>
+      <c r="H90" s="62"/>
+      <c r="I90" s="62"/>
     </row>
     <row r="91" ht="18.75" customHeight="1">
-      <c r="A91" s="61"/>
-      <c r="B91" s="61"/>
-      <c r="C91" s="61"/>
-      <c r="D91" s="61"/>
-      <c r="E91" s="61"/>
-      <c r="F91" s="61"/>
-      <c r="G91" s="61"/>
-      <c r="H91" s="61"/>
-      <c r="I91" s="61"/>
+      <c r="A91" s="62"/>
+      <c r="B91" s="62"/>
+      <c r="C91" s="62"/>
+      <c r="D91" s="62"/>
+      <c r="E91" s="62"/>
+      <c r="F91" s="62"/>
+      <c r="G91" s="62"/>
+      <c r="H91" s="62"/>
+      <c r="I91" s="62"/>
     </row>
     <row r="92" ht="18.75" customHeight="1">
-      <c r="A92" s="61"/>
-      <c r="B92" s="61"/>
-      <c r="C92" s="61"/>
-      <c r="D92" s="61"/>
-      <c r="E92" s="61"/>
-      <c r="F92" s="61"/>
-      <c r="G92" s="61"/>
-      <c r="H92" s="61"/>
-      <c r="I92" s="61"/>
+      <c r="A92" s="62"/>
+      <c r="B92" s="62"/>
+      <c r="C92" s="62"/>
+      <c r="D92" s="62"/>
+      <c r="E92" s="62"/>
+      <c r="F92" s="62"/>
+      <c r="G92" s="62"/>
+      <c r="H92" s="62"/>
+      <c r="I92" s="62"/>
     </row>
     <row r="93" ht="18.75" customHeight="1">
-      <c r="A93" s="61"/>
-      <c r="B93" s="61"/>
-      <c r="C93" s="61"/>
-      <c r="D93" s="61"/>
-      <c r="E93" s="61"/>
-      <c r="F93" s="61"/>
-      <c r="G93" s="61"/>
-      <c r="H93" s="61"/>
-      <c r="I93" s="61"/>
+      <c r="A93" s="62"/>
+      <c r="B93" s="62"/>
+      <c r="C93" s="62"/>
+      <c r="D93" s="62"/>
+      <c r="E93" s="62"/>
+      <c r="F93" s="62"/>
+      <c r="G93" s="62"/>
+      <c r="H93" s="62"/>
+      <c r="I93" s="62"/>
     </row>
     <row r="94" ht="18.75" customHeight="1">
-      <c r="A94" s="61"/>
-      <c r="B94" s="61"/>
-      <c r="C94" s="61"/>
-      <c r="D94" s="61"/>
-      <c r="E94" s="61"/>
-      <c r="F94" s="61"/>
-      <c r="G94" s="61"/>
-      <c r="H94" s="61"/>
-      <c r="I94" s="61"/>
+      <c r="A94" s="62"/>
+      <c r="B94" s="62"/>
+      <c r="C94" s="62"/>
+      <c r="D94" s="62"/>
+      <c r="E94" s="62"/>
+      <c r="F94" s="62"/>
+      <c r="G94" s="62"/>
+      <c r="H94" s="62"/>
+      <c r="I94" s="62"/>
     </row>
     <row r="95" ht="18.75" customHeight="1">
-      <c r="A95" s="61"/>
-      <c r="B95" s="61"/>
-      <c r="C95" s="61"/>
-      <c r="D95" s="61"/>
-      <c r="E95" s="61"/>
-      <c r="F95" s="61"/>
-      <c r="G95" s="61"/>
-      <c r="H95" s="61"/>
-      <c r="I95" s="61"/>
+      <c r="A95" s="62"/>
+      <c r="B95" s="62"/>
+      <c r="C95" s="62"/>
+      <c r="D95" s="62"/>
+      <c r="E95" s="62"/>
+      <c r="F95" s="62"/>
+      <c r="G95" s="62"/>
+      <c r="H95" s="62"/>
+      <c r="I95" s="62"/>
     </row>
     <row r="96" ht="18.75" customHeight="1">
-      <c r="A96" s="61"/>
-      <c r="B96" s="61"/>
-      <c r="C96" s="61"/>
-      <c r="D96" s="61"/>
-      <c r="E96" s="61"/>
-      <c r="F96" s="61"/>
-      <c r="G96" s="61"/>
-      <c r="H96" s="61"/>
-      <c r="I96" s="61"/>
+      <c r="A96" s="62"/>
+      <c r="B96" s="62"/>
+      <c r="C96" s="62"/>
+      <c r="D96" s="62"/>
+      <c r="E96" s="62"/>
+      <c r="F96" s="62"/>
+      <c r="G96" s="62"/>
+      <c r="H96" s="62"/>
+      <c r="I96" s="62"/>
     </row>
     <row r="97" ht="18.75" customHeight="1">
-      <c r="A97" s="61"/>
-      <c r="B97" s="61"/>
-      <c r="C97" s="61"/>
-      <c r="D97" s="61"/>
-      <c r="E97" s="61"/>
-      <c r="F97" s="61"/>
-      <c r="G97" s="61"/>
-      <c r="H97" s="61"/>
-      <c r="I97" s="61"/>
+      <c r="A97" s="62"/>
+      <c r="B97" s="62"/>
+      <c r="C97" s="62"/>
+      <c r="D97" s="62"/>
+      <c r="E97" s="62"/>
+      <c r="F97" s="62"/>
+      <c r="G97" s="62"/>
+      <c r="H97" s="62"/>
+      <c r="I97" s="62"/>
     </row>
     <row r="98" ht="18.75" customHeight="1">
-      <c r="A98" s="61"/>
-      <c r="B98" s="61"/>
-      <c r="C98" s="61"/>
-      <c r="D98" s="61"/>
-      <c r="E98" s="61"/>
-      <c r="F98" s="61"/>
-      <c r="G98" s="61"/>
-      <c r="H98" s="61"/>
-      <c r="I98" s="61"/>
+      <c r="A98" s="62"/>
+      <c r="B98" s="62"/>
+      <c r="C98" s="62"/>
+      <c r="D98" s="62"/>
+      <c r="E98" s="62"/>
+      <c r="F98" s="62"/>
+      <c r="G98" s="62"/>
+      <c r="H98" s="62"/>
+      <c r="I98" s="62"/>
     </row>
     <row r="99" ht="18.75" customHeight="1">
-      <c r="A99" s="61"/>
-      <c r="B99" s="61"/>
-      <c r="C99" s="61"/>
-      <c r="D99" s="61"/>
-      <c r="E99" s="61"/>
-      <c r="F99" s="61"/>
-      <c r="G99" s="61"/>
-      <c r="H99" s="61"/>
-      <c r="I99" s="61"/>
+      <c r="A99" s="62"/>
+      <c r="B99" s="62"/>
+      <c r="C99" s="62"/>
+      <c r="D99" s="62"/>
+      <c r="E99" s="62"/>
+      <c r="F99" s="62"/>
+      <c r="G99" s="62"/>
+      <c r="H99" s="62"/>
+      <c r="I99" s="62"/>
     </row>
     <row r="100" ht="18.75" customHeight="1">
-      <c r="A100" s="61"/>
-      <c r="B100" s="61"/>
-      <c r="C100" s="61"/>
-      <c r="D100" s="61"/>
-      <c r="E100" s="61"/>
-      <c r="F100" s="61"/>
-      <c r="G100" s="61"/>
-      <c r="H100" s="61"/>
-      <c r="I100" s="61"/>
+      <c r="A100" s="62"/>
+      <c r="B100" s="62"/>
+      <c r="C100" s="62"/>
+      <c r="D100" s="62"/>
+      <c r="E100" s="62"/>
+      <c r="F100" s="62"/>
+      <c r="G100" s="62"/>
+      <c r="H100" s="62"/>
+      <c r="I100" s="62"/>
     </row>
   </sheetData>
   <mergeCells count="24">
@@ -15233,1129 +15314,1129 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="56" t="s">
-        <v>1124</v>
-      </c>
-      <c r="C1" s="57"/>
-      <c r="D1" s="58"/>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="58"/>
-      <c r="H1" s="58"/>
-      <c r="I1" s="58"/>
+      <c r="A1" s="57" t="s">
+        <v>1131</v>
+      </c>
+      <c r="C1" s="58"/>
+      <c r="D1" s="59"/>
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="59"/>
+      <c r="H1" s="59"/>
+      <c r="I1" s="59"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="56" t="s">
-        <v>1125</v>
-      </c>
-      <c r="B2" s="56" t="s">
-        <v>1126</v>
-      </c>
-      <c r="C2" s="58"/>
-      <c r="D2" s="58"/>
-      <c r="E2" s="58"/>
-      <c r="F2" s="58"/>
-      <c r="G2" s="58"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
+      <c r="A2" s="57" t="s">
+        <v>1132</v>
+      </c>
+      <c r="B2" s="57" t="s">
+        <v>1133</v>
+      </c>
+      <c r="C2" s="59"/>
+      <c r="D2" s="59"/>
+      <c r="E2" s="59"/>
+      <c r="F2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="58" t="s">
-        <v>1127</v>
-      </c>
-      <c r="B3" s="58" t="s">
-        <v>1128</v>
-      </c>
-      <c r="C3" s="58"/>
-      <c r="D3" s="58"/>
-      <c r="E3" s="58"/>
-      <c r="F3" s="58"/>
-      <c r="G3" s="58"/>
-      <c r="H3" s="58"/>
-      <c r="I3" s="58"/>
+      <c r="A3" s="59" t="s">
+        <v>1134</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>1135</v>
+      </c>
+      <c r="C3" s="59"/>
+      <c r="D3" s="59"/>
+      <c r="E3" s="59"/>
+      <c r="F3" s="59"/>
+      <c r="G3" s="59"/>
+      <c r="H3" s="59"/>
+      <c r="I3" s="59"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="58" t="s">
-        <v>1128</v>
-      </c>
-      <c r="B4" s="58" t="s">
+      <c r="A4" s="59" t="s">
+        <v>1135</v>
+      </c>
+      <c r="B4" s="59" t="s">
         <v>405</v>
       </c>
-      <c r="C4" s="58"/>
-      <c r="D4" s="58"/>
-      <c r="E4" s="58"/>
-      <c r="F4" s="58"/>
-      <c r="G4" s="58"/>
-      <c r="H4" s="58"/>
-      <c r="I4" s="58"/>
+      <c r="C4" s="59"/>
+      <c r="D4" s="59"/>
+      <c r="E4" s="59"/>
+      <c r="F4" s="59"/>
+      <c r="G4" s="59"/>
+      <c r="H4" s="59"/>
+      <c r="I4" s="59"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="58" t="s">
-        <v>1129</v>
-      </c>
-      <c r="B5" s="58" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C5" s="58"/>
-      <c r="D5" s="58"/>
-      <c r="E5" s="58"/>
-      <c r="F5" s="58"/>
-      <c r="G5" s="58"/>
-      <c r="H5" s="58"/>
-      <c r="I5" s="58"/>
+      <c r="A5" s="59" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C5" s="59"/>
+      <c r="D5" s="59"/>
+      <c r="E5" s="59"/>
+      <c r="F5" s="59"/>
+      <c r="G5" s="59"/>
+      <c r="H5" s="59"/>
+      <c r="I5" s="59"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="58" t="s">
+      <c r="A6" s="59" t="s">
         <v>405</v>
       </c>
-      <c r="B6" s="58" t="s">
-        <v>1131</v>
-      </c>
-      <c r="C6" s="58"/>
-      <c r="D6" s="58"/>
-      <c r="E6" s="58"/>
-      <c r="F6" s="58"/>
-      <c r="G6" s="58"/>
-      <c r="H6" s="58"/>
-      <c r="I6" s="58"/>
+      <c r="B6" s="59" t="s">
+        <v>1138</v>
+      </c>
+      <c r="C6" s="59"/>
+      <c r="D6" s="59"/>
+      <c r="E6" s="59"/>
+      <c r="F6" s="59"/>
+      <c r="G6" s="59"/>
+      <c r="H6" s="59"/>
+      <c r="I6" s="59"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="58" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B7" s="58" t="s">
-        <v>1130</v>
-      </c>
-      <c r="C7" s="58"/>
-      <c r="D7" s="58"/>
-      <c r="E7" s="58"/>
-      <c r="F7" s="58"/>
-      <c r="G7" s="58"/>
-      <c r="H7" s="58"/>
-      <c r="I7" s="58"/>
+      <c r="A7" s="59" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B7" s="59" t="s">
+        <v>1137</v>
+      </c>
+      <c r="C7" s="59"/>
+      <c r="D7" s="59"/>
+      <c r="E7" s="59"/>
+      <c r="F7" s="59"/>
+      <c r="G7" s="59"/>
+      <c r="H7" s="59"/>
+      <c r="I7" s="59"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="C8" s="58"/>
-      <c r="D8" s="58"/>
-      <c r="E8" s="58"/>
-      <c r="F8" s="58"/>
-      <c r="G8" s="58"/>
-      <c r="H8" s="58"/>
-      <c r="I8" s="58"/>
+      <c r="C8" s="59"/>
+      <c r="D8" s="59"/>
+      <c r="E8" s="59"/>
+      <c r="F8" s="59"/>
+      <c r="G8" s="59"/>
+      <c r="H8" s="59"/>
+      <c r="I8" s="59"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="58" t="s">
-        <v>1133</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>1134</v>
-      </c>
-      <c r="C9" s="58"/>
-      <c r="D9" s="58"/>
-      <c r="E9" s="58"/>
-      <c r="F9" s="58"/>
-      <c r="G9" s="58"/>
-      <c r="H9" s="58"/>
-      <c r="I9" s="58"/>
+      <c r="A9" s="59" t="s">
+        <v>1140</v>
+      </c>
+      <c r="B9" s="59" t="s">
+        <v>1141</v>
+      </c>
+      <c r="C9" s="59"/>
+      <c r="D9" s="59"/>
+      <c r="E9" s="59"/>
+      <c r="F9" s="59"/>
+      <c r="G9" s="59"/>
+      <c r="H9" s="59"/>
+      <c r="I9" s="59"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="C10" s="58"/>
-      <c r="D10" s="58"/>
-      <c r="E10" s="58"/>
-      <c r="F10" s="58"/>
-      <c r="G10" s="58"/>
-      <c r="H10" s="58"/>
-      <c r="I10" s="58"/>
+      <c r="C10" s="59"/>
+      <c r="D10" s="59"/>
+      <c r="E10" s="59"/>
+      <c r="F10" s="59"/>
+      <c r="G10" s="59"/>
+      <c r="H10" s="59"/>
+      <c r="I10" s="59"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="58"/>
-      <c r="D11" s="58"/>
-      <c r="E11" s="58"/>
-      <c r="F11" s="58"/>
-      <c r="G11" s="58"/>
-      <c r="H11" s="58"/>
-      <c r="I11" s="58"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="59"/>
+      <c r="D11" s="59"/>
+      <c r="E11" s="59"/>
+      <c r="F11" s="59"/>
+      <c r="G11" s="59"/>
+      <c r="H11" s="59"/>
+      <c r="I11" s="59"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="58"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="58"/>
-      <c r="D12" s="58"/>
-      <c r="E12" s="58"/>
-      <c r="F12" s="58"/>
-      <c r="G12" s="58"/>
-      <c r="H12" s="58"/>
-      <c r="I12" s="58"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="59"/>
+      <c r="D12" s="59"/>
+      <c r="E12" s="59"/>
+      <c r="F12" s="59"/>
+      <c r="G12" s="59"/>
+      <c r="H12" s="59"/>
+      <c r="I12" s="59"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="58"/>
-      <c r="B13" s="58"/>
-      <c r="C13" s="58"/>
-      <c r="D13" s="58"/>
-      <c r="E13" s="58"/>
-      <c r="F13" s="58"/>
-      <c r="G13" s="58"/>
-      <c r="H13" s="58"/>
-      <c r="I13" s="58"/>
+      <c r="A13" s="59"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="59"/>
+      <c r="D13" s="59"/>
+      <c r="E13" s="59"/>
+      <c r="F13" s="59"/>
+      <c r="G13" s="59"/>
+      <c r="H13" s="59"/>
+      <c r="I13" s="59"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="58"/>
-      <c r="D14" s="58"/>
-      <c r="E14" s="58"/>
-      <c r="F14" s="58"/>
-      <c r="G14" s="58"/>
-      <c r="H14" s="58"/>
-      <c r="I14" s="58"/>
+      <c r="A14" s="59"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="59"/>
+      <c r="D14" s="59"/>
+      <c r="E14" s="59"/>
+      <c r="F14" s="59"/>
+      <c r="G14" s="59"/>
+      <c r="H14" s="59"/>
+      <c r="I14" s="59"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="58"/>
-      <c r="D15" s="58"/>
-      <c r="E15" s="58"/>
-      <c r="F15" s="58"/>
-      <c r="G15" s="58"/>
-      <c r="H15" s="58"/>
-      <c r="I15" s="58"/>
+      <c r="A15" s="59"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="59"/>
+      <c r="D15" s="59"/>
+      <c r="E15" s="59"/>
+      <c r="F15" s="59"/>
+      <c r="G15" s="59"/>
+      <c r="H15" s="59"/>
+      <c r="I15" s="59"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="58"/>
-      <c r="D16" s="58"/>
-      <c r="E16" s="58"/>
-      <c r="F16" s="58"/>
-      <c r="G16" s="58"/>
-      <c r="H16" s="58"/>
-      <c r="I16" s="58"/>
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="59"/>
+      <c r="D16" s="59"/>
+      <c r="E16" s="59"/>
+      <c r="F16" s="59"/>
+      <c r="G16" s="59"/>
+      <c r="H16" s="59"/>
+      <c r="I16" s="59"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="58"/>
-      <c r="B17" s="58"/>
-      <c r="C17" s="58"/>
-      <c r="D17" s="58"/>
-      <c r="E17" s="58"/>
-      <c r="F17" s="58"/>
-      <c r="G17" s="58"/>
-      <c r="H17" s="58"/>
-      <c r="I17" s="58"/>
+      <c r="A17" s="59"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="59"/>
+      <c r="D17" s="59"/>
+      <c r="E17" s="59"/>
+      <c r="F17" s="59"/>
+      <c r="G17" s="59"/>
+      <c r="H17" s="59"/>
+      <c r="I17" s="59"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="58"/>
-      <c r="B18" s="58"/>
-      <c r="C18" s="58"/>
-      <c r="D18" s="58"/>
-      <c r="E18" s="58"/>
-      <c r="F18" s="58"/>
-      <c r="G18" s="58"/>
-      <c r="H18" s="58"/>
-      <c r="I18" s="58"/>
+      <c r="A18" s="59"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="59"/>
+      <c r="D18" s="59"/>
+      <c r="E18" s="59"/>
+      <c r="F18" s="59"/>
+      <c r="G18" s="59"/>
+      <c r="H18" s="59"/>
+      <c r="I18" s="59"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="58"/>
-      <c r="B19" s="58"/>
-      <c r="C19" s="58"/>
-      <c r="D19" s="58"/>
-      <c r="E19" s="58"/>
-      <c r="F19" s="58"/>
-      <c r="G19" s="58"/>
-      <c r="H19" s="58"/>
-      <c r="I19" s="58"/>
+      <c r="A19" s="59"/>
+      <c r="B19" s="59"/>
+      <c r="C19" s="59"/>
+      <c r="D19" s="59"/>
+      <c r="E19" s="59"/>
+      <c r="F19" s="59"/>
+      <c r="G19" s="59"/>
+      <c r="H19" s="59"/>
+      <c r="I19" s="59"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="58"/>
-      <c r="B20" s="58"/>
-      <c r="C20" s="58"/>
-      <c r="D20" s="58"/>
-      <c r="E20" s="58"/>
-      <c r="F20" s="58"/>
-      <c r="G20" s="58"/>
-      <c r="H20" s="58"/>
-      <c r="I20" s="58"/>
+      <c r="A20" s="59"/>
+      <c r="B20" s="59"/>
+      <c r="C20" s="59"/>
+      <c r="D20" s="59"/>
+      <c r="E20" s="59"/>
+      <c r="F20" s="59"/>
+      <c r="G20" s="59"/>
+      <c r="H20" s="59"/>
+      <c r="I20" s="59"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="58"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="58"/>
-      <c r="D21" s="58"/>
-      <c r="E21" s="58"/>
-      <c r="F21" s="58"/>
-      <c r="G21" s="58"/>
-      <c r="H21" s="58"/>
-      <c r="I21" s="58"/>
+      <c r="A21" s="59"/>
+      <c r="B21" s="59"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="59"/>
+      <c r="E21" s="59"/>
+      <c r="F21" s="59"/>
+      <c r="G21" s="59"/>
+      <c r="H21" s="59"/>
+      <c r="I21" s="59"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="58"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="58"/>
-      <c r="D22" s="58"/>
-      <c r="E22" s="58"/>
-      <c r="F22" s="58"/>
-      <c r="G22" s="58"/>
-      <c r="H22" s="58"/>
-      <c r="I22" s="58"/>
+      <c r="A22" s="59"/>
+      <c r="B22" s="59"/>
+      <c r="C22" s="59"/>
+      <c r="D22" s="59"/>
+      <c r="E22" s="59"/>
+      <c r="F22" s="59"/>
+      <c r="G22" s="59"/>
+      <c r="H22" s="59"/>
+      <c r="I22" s="59"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="58"/>
-      <c r="B23" s="58"/>
-      <c r="C23" s="58"/>
-      <c r="D23" s="58"/>
-      <c r="E23" s="58"/>
-      <c r="F23" s="58"/>
-      <c r="G23" s="58"/>
-      <c r="H23" s="58"/>
-      <c r="I23" s="58"/>
+      <c r="A23" s="59"/>
+      <c r="B23" s="59"/>
+      <c r="C23" s="59"/>
+      <c r="D23" s="59"/>
+      <c r="E23" s="59"/>
+      <c r="F23" s="59"/>
+      <c r="G23" s="59"/>
+      <c r="H23" s="59"/>
+      <c r="I23" s="59"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="58"/>
-      <c r="B24" s="58"/>
-      <c r="C24" s="58"/>
-      <c r="D24" s="58"/>
-      <c r="E24" s="58"/>
-      <c r="F24" s="58"/>
-      <c r="G24" s="58"/>
-      <c r="H24" s="58"/>
-      <c r="I24" s="58"/>
+      <c r="A24" s="59"/>
+      <c r="B24" s="59"/>
+      <c r="C24" s="59"/>
+      <c r="D24" s="59"/>
+      <c r="E24" s="59"/>
+      <c r="F24" s="59"/>
+      <c r="G24" s="59"/>
+      <c r="H24" s="59"/>
+      <c r="I24" s="59"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="58"/>
-      <c r="B25" s="58"/>
-      <c r="C25" s="58"/>
-      <c r="D25" s="58"/>
-      <c r="E25" s="58"/>
-      <c r="F25" s="58"/>
-      <c r="G25" s="58"/>
-      <c r="H25" s="58"/>
-      <c r="I25" s="58"/>
+      <c r="A25" s="59"/>
+      <c r="B25" s="59"/>
+      <c r="C25" s="59"/>
+      <c r="D25" s="59"/>
+      <c r="E25" s="59"/>
+      <c r="F25" s="59"/>
+      <c r="G25" s="59"/>
+      <c r="H25" s="59"/>
+      <c r="I25" s="59"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="58"/>
-      <c r="B26" s="58"/>
-      <c r="C26" s="58"/>
-      <c r="D26" s="58"/>
-      <c r="E26" s="58"/>
-      <c r="F26" s="58"/>
-      <c r="G26" s="58"/>
-      <c r="H26" s="58"/>
-      <c r="I26" s="58"/>
+      <c r="A26" s="59"/>
+      <c r="B26" s="59"/>
+      <c r="C26" s="59"/>
+      <c r="D26" s="59"/>
+      <c r="E26" s="59"/>
+      <c r="F26" s="59"/>
+      <c r="G26" s="59"/>
+      <c r="H26" s="59"/>
+      <c r="I26" s="59"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="58"/>
-      <c r="B27" s="58"/>
-      <c r="C27" s="58"/>
-      <c r="D27" s="58"/>
-      <c r="E27" s="58"/>
-      <c r="F27" s="58"/>
-      <c r="G27" s="58"/>
-      <c r="H27" s="58"/>
-      <c r="I27" s="58"/>
+      <c r="A27" s="59"/>
+      <c r="B27" s="59"/>
+      <c r="C27" s="59"/>
+      <c r="D27" s="59"/>
+      <c r="E27" s="59"/>
+      <c r="F27" s="59"/>
+      <c r="G27" s="59"/>
+      <c r="H27" s="59"/>
+      <c r="I27" s="59"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="58"/>
-      <c r="B28" s="58"/>
-      <c r="C28" s="58"/>
-      <c r="D28" s="58"/>
-      <c r="E28" s="58"/>
-      <c r="F28" s="58"/>
-      <c r="G28" s="58"/>
-      <c r="H28" s="58"/>
-      <c r="I28" s="58"/>
+      <c r="A28" s="59"/>
+      <c r="B28" s="59"/>
+      <c r="C28" s="59"/>
+      <c r="D28" s="59"/>
+      <c r="E28" s="59"/>
+      <c r="F28" s="59"/>
+      <c r="G28" s="59"/>
+      <c r="H28" s="59"/>
+      <c r="I28" s="59"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="58"/>
-      <c r="B29" s="58"/>
-      <c r="C29" s="58"/>
-      <c r="D29" s="58"/>
-      <c r="E29" s="58"/>
-      <c r="F29" s="58"/>
-      <c r="G29" s="58"/>
-      <c r="H29" s="58"/>
-      <c r="I29" s="58"/>
+      <c r="A29" s="59"/>
+      <c r="B29" s="59"/>
+      <c r="C29" s="59"/>
+      <c r="D29" s="59"/>
+      <c r="E29" s="59"/>
+      <c r="F29" s="59"/>
+      <c r="G29" s="59"/>
+      <c r="H29" s="59"/>
+      <c r="I29" s="59"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="58"/>
-      <c r="B30" s="58"/>
-      <c r="C30" s="58"/>
-      <c r="D30" s="58"/>
-      <c r="E30" s="58"/>
-      <c r="F30" s="58"/>
-      <c r="G30" s="58"/>
-      <c r="H30" s="58"/>
-      <c r="I30" s="58"/>
+      <c r="A30" s="59"/>
+      <c r="B30" s="59"/>
+      <c r="C30" s="59"/>
+      <c r="D30" s="59"/>
+      <c r="E30" s="59"/>
+      <c r="F30" s="59"/>
+      <c r="G30" s="59"/>
+      <c r="H30" s="59"/>
+      <c r="I30" s="59"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="58"/>
-      <c r="B31" s="58"/>
-      <c r="C31" s="58"/>
-      <c r="D31" s="58"/>
-      <c r="E31" s="58"/>
-      <c r="F31" s="58"/>
-      <c r="G31" s="58"/>
-      <c r="H31" s="58"/>
-      <c r="I31" s="58"/>
+      <c r="A31" s="59"/>
+      <c r="B31" s="59"/>
+      <c r="C31" s="59"/>
+      <c r="D31" s="59"/>
+      <c r="E31" s="59"/>
+      <c r="F31" s="59"/>
+      <c r="G31" s="59"/>
+      <c r="H31" s="59"/>
+      <c r="I31" s="59"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="58"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="58"/>
-      <c r="D32" s="58"/>
-      <c r="E32" s="58"/>
-      <c r="F32" s="58"/>
-      <c r="G32" s="58"/>
-      <c r="H32" s="58"/>
-      <c r="I32" s="58"/>
+      <c r="A32" s="59"/>
+      <c r="B32" s="59"/>
+      <c r="C32" s="59"/>
+      <c r="D32" s="59"/>
+      <c r="E32" s="59"/>
+      <c r="F32" s="59"/>
+      <c r="G32" s="59"/>
+      <c r="H32" s="59"/>
+      <c r="I32" s="59"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="58"/>
-      <c r="B33" s="58"/>
-      <c r="C33" s="58"/>
-      <c r="D33" s="58"/>
-      <c r="E33" s="58"/>
-      <c r="F33" s="58"/>
-      <c r="G33" s="58"/>
-      <c r="H33" s="58"/>
-      <c r="I33" s="58"/>
+      <c r="A33" s="59"/>
+      <c r="B33" s="59"/>
+      <c r="C33" s="59"/>
+      <c r="D33" s="59"/>
+      <c r="E33" s="59"/>
+      <c r="F33" s="59"/>
+      <c r="G33" s="59"/>
+      <c r="H33" s="59"/>
+      <c r="I33" s="59"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="58"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="58"/>
-      <c r="D34" s="58"/>
-      <c r="E34" s="58"/>
-      <c r="F34" s="58"/>
-      <c r="G34" s="58"/>
-      <c r="H34" s="58"/>
-      <c r="I34" s="58"/>
+      <c r="A34" s="59"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="59"/>
+      <c r="D34" s="59"/>
+      <c r="E34" s="59"/>
+      <c r="F34" s="59"/>
+      <c r="G34" s="59"/>
+      <c r="H34" s="59"/>
+      <c r="I34" s="59"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="58"/>
-      <c r="D35" s="58"/>
-      <c r="E35" s="58"/>
-      <c r="F35" s="58"/>
-      <c r="G35" s="58"/>
-      <c r="H35" s="58"/>
-      <c r="I35" s="58"/>
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="59"/>
+      <c r="D35" s="59"/>
+      <c r="E35" s="59"/>
+      <c r="F35" s="59"/>
+      <c r="G35" s="59"/>
+      <c r="H35" s="59"/>
+      <c r="I35" s="59"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="58"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="58"/>
-      <c r="D36" s="58"/>
-      <c r="E36" s="58"/>
-      <c r="F36" s="58"/>
-      <c r="G36" s="58"/>
-      <c r="H36" s="58"/>
-      <c r="I36" s="58"/>
+      <c r="A36" s="59"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="59"/>
+      <c r="D36" s="59"/>
+      <c r="E36" s="59"/>
+      <c r="F36" s="59"/>
+      <c r="G36" s="59"/>
+      <c r="H36" s="59"/>
+      <c r="I36" s="59"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="58"/>
-      <c r="B37" s="58"/>
-      <c r="C37" s="58"/>
-      <c r="D37" s="58"/>
-      <c r="E37" s="58"/>
-      <c r="F37" s="58"/>
-      <c r="G37" s="58"/>
-      <c r="H37" s="58"/>
-      <c r="I37" s="58"/>
+      <c r="A37" s="59"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="59"/>
+      <c r="D37" s="59"/>
+      <c r="E37" s="59"/>
+      <c r="F37" s="59"/>
+      <c r="G37" s="59"/>
+      <c r="H37" s="59"/>
+      <c r="I37" s="59"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="58"/>
-      <c r="B38" s="58"/>
-      <c r="C38" s="58"/>
-      <c r="D38" s="58"/>
-      <c r="E38" s="58"/>
-      <c r="F38" s="58"/>
-      <c r="G38" s="58"/>
-      <c r="H38" s="58"/>
-      <c r="I38" s="58"/>
+      <c r="A38" s="59"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="59"/>
+      <c r="D38" s="59"/>
+      <c r="E38" s="59"/>
+      <c r="F38" s="59"/>
+      <c r="G38" s="59"/>
+      <c r="H38" s="59"/>
+      <c r="I38" s="59"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="A39" s="58"/>
-      <c r="B39" s="58"/>
-      <c r="C39" s="58"/>
-      <c r="D39" s="58"/>
-      <c r="E39" s="58"/>
-      <c r="F39" s="58"/>
-      <c r="G39" s="58"/>
-      <c r="H39" s="58"/>
-      <c r="I39" s="58"/>
+      <c r="A39" s="59"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="59"/>
+      <c r="D39" s="59"/>
+      <c r="E39" s="59"/>
+      <c r="F39" s="59"/>
+      <c r="G39" s="59"/>
+      <c r="H39" s="59"/>
+      <c r="I39" s="59"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="58"/>
-      <c r="B40" s="58"/>
-      <c r="C40" s="58"/>
-      <c r="D40" s="58"/>
-      <c r="E40" s="58"/>
-      <c r="F40" s="58"/>
-      <c r="G40" s="58"/>
-      <c r="H40" s="58"/>
-      <c r="I40" s="58"/>
+      <c r="A40" s="59"/>
+      <c r="B40" s="59"/>
+      <c r="C40" s="59"/>
+      <c r="D40" s="59"/>
+      <c r="E40" s="59"/>
+      <c r="F40" s="59"/>
+      <c r="G40" s="59"/>
+      <c r="H40" s="59"/>
+      <c r="I40" s="59"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="58"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="58"/>
-      <c r="D41" s="58"/>
-      <c r="E41" s="58"/>
-      <c r="F41" s="58"/>
-      <c r="G41" s="58"/>
-      <c r="H41" s="58"/>
-      <c r="I41" s="58"/>
+      <c r="A41" s="59"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="59"/>
+      <c r="D41" s="59"/>
+      <c r="E41" s="59"/>
+      <c r="F41" s="59"/>
+      <c r="G41" s="59"/>
+      <c r="H41" s="59"/>
+      <c r="I41" s="59"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="58"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="58"/>
-      <c r="D42" s="58"/>
-      <c r="E42" s="58"/>
-      <c r="F42" s="58"/>
-      <c r="G42" s="58"/>
-      <c r="H42" s="58"/>
-      <c r="I42" s="58"/>
+      <c r="A42" s="59"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="59"/>
+      <c r="D42" s="59"/>
+      <c r="E42" s="59"/>
+      <c r="F42" s="59"/>
+      <c r="G42" s="59"/>
+      <c r="H42" s="59"/>
+      <c r="I42" s="59"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58"/>
-      <c r="C43" s="58"/>
-      <c r="D43" s="58"/>
-      <c r="E43" s="58"/>
-      <c r="F43" s="58"/>
-      <c r="G43" s="58"/>
-      <c r="H43" s="58"/>
-      <c r="I43" s="58"/>
+      <c r="A43" s="59"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="59"/>
+      <c r="D43" s="59"/>
+      <c r="E43" s="59"/>
+      <c r="F43" s="59"/>
+      <c r="G43" s="59"/>
+      <c r="H43" s="59"/>
+      <c r="I43" s="59"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="58"/>
-      <c r="D44" s="58"/>
-      <c r="E44" s="58"/>
-      <c r="F44" s="58"/>
-      <c r="G44" s="58"/>
-      <c r="H44" s="58"/>
-      <c r="I44" s="58"/>
+      <c r="A44" s="59"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="59"/>
+      <c r="D44" s="59"/>
+      <c r="E44" s="59"/>
+      <c r="F44" s="59"/>
+      <c r="G44" s="59"/>
+      <c r="H44" s="59"/>
+      <c r="I44" s="59"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="58"/>
-      <c r="D45" s="58"/>
-      <c r="E45" s="58"/>
-      <c r="F45" s="58"/>
-      <c r="G45" s="58"/>
-      <c r="H45" s="58"/>
-      <c r="I45" s="58"/>
+      <c r="A45" s="59"/>
+      <c r="B45" s="59"/>
+      <c r="C45" s="59"/>
+      <c r="D45" s="59"/>
+      <c r="E45" s="59"/>
+      <c r="F45" s="59"/>
+      <c r="G45" s="59"/>
+      <c r="H45" s="59"/>
+      <c r="I45" s="59"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="58"/>
-      <c r="D46" s="58"/>
-      <c r="E46" s="58"/>
-      <c r="F46" s="58"/>
-      <c r="G46" s="58"/>
-      <c r="H46" s="58"/>
-      <c r="I46" s="58"/>
+      <c r="A46" s="59"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="59"/>
+      <c r="D46" s="59"/>
+      <c r="E46" s="59"/>
+      <c r="F46" s="59"/>
+      <c r="G46" s="59"/>
+      <c r="H46" s="59"/>
+      <c r="I46" s="59"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
-      <c r="A47" s="58"/>
-      <c r="B47" s="58"/>
-      <c r="C47" s="58"/>
-      <c r="D47" s="58"/>
-      <c r="E47" s="58"/>
-      <c r="F47" s="58"/>
-      <c r="G47" s="58"/>
-      <c r="H47" s="58"/>
-      <c r="I47" s="58"/>
+      <c r="A47" s="59"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="59"/>
+      <c r="D47" s="59"/>
+      <c r="E47" s="59"/>
+      <c r="F47" s="59"/>
+      <c r="G47" s="59"/>
+      <c r="H47" s="59"/>
+      <c r="I47" s="59"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
-      <c r="A48" s="58"/>
-      <c r="B48" s="58"/>
-      <c r="C48" s="58"/>
-      <c r="D48" s="58"/>
-      <c r="E48" s="58"/>
-      <c r="F48" s="58"/>
-      <c r="G48" s="58"/>
-      <c r="H48" s="58"/>
-      <c r="I48" s="58"/>
+      <c r="A48" s="59"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="59"/>
+      <c r="D48" s="59"/>
+      <c r="E48" s="59"/>
+      <c r="F48" s="59"/>
+      <c r="G48" s="59"/>
+      <c r="H48" s="59"/>
+      <c r="I48" s="59"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" s="58"/>
-      <c r="B49" s="58"/>
-      <c r="C49" s="58"/>
-      <c r="D49" s="58"/>
-      <c r="E49" s="58"/>
-      <c r="F49" s="58"/>
-      <c r="G49" s="58"/>
-      <c r="H49" s="58"/>
-      <c r="I49" s="58"/>
+      <c r="A49" s="59"/>
+      <c r="B49" s="59"/>
+      <c r="C49" s="59"/>
+      <c r="D49" s="59"/>
+      <c r="E49" s="59"/>
+      <c r="F49" s="59"/>
+      <c r="G49" s="59"/>
+      <c r="H49" s="59"/>
+      <c r="I49" s="59"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="A50" s="58"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="58"/>
-      <c r="D50" s="58"/>
-      <c r="E50" s="58"/>
-      <c r="F50" s="58"/>
-      <c r="G50" s="58"/>
-      <c r="H50" s="58"/>
-      <c r="I50" s="58"/>
+      <c r="A50" s="59"/>
+      <c r="B50" s="59"/>
+      <c r="C50" s="59"/>
+      <c r="D50" s="59"/>
+      <c r="E50" s="59"/>
+      <c r="F50" s="59"/>
+      <c r="G50" s="59"/>
+      <c r="H50" s="59"/>
+      <c r="I50" s="59"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
-      <c r="A51" s="58"/>
-      <c r="B51" s="58"/>
-      <c r="C51" s="58"/>
-      <c r="D51" s="58"/>
-      <c r="E51" s="58"/>
-      <c r="F51" s="58"/>
-      <c r="G51" s="58"/>
-      <c r="H51" s="58"/>
-      <c r="I51" s="58"/>
+      <c r="A51" s="59"/>
+      <c r="B51" s="59"/>
+      <c r="C51" s="59"/>
+      <c r="D51" s="59"/>
+      <c r="E51" s="59"/>
+      <c r="F51" s="59"/>
+      <c r="G51" s="59"/>
+      <c r="H51" s="59"/>
+      <c r="I51" s="59"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
-      <c r="A52" s="58"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="58"/>
-      <c r="D52" s="58"/>
-      <c r="E52" s="58"/>
-      <c r="F52" s="58"/>
-      <c r="G52" s="58"/>
-      <c r="H52" s="58"/>
-      <c r="I52" s="58"/>
+      <c r="A52" s="59"/>
+      <c r="B52" s="59"/>
+      <c r="C52" s="59"/>
+      <c r="D52" s="59"/>
+      <c r="E52" s="59"/>
+      <c r="F52" s="59"/>
+      <c r="G52" s="59"/>
+      <c r="H52" s="59"/>
+      <c r="I52" s="59"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
-      <c r="A53" s="58"/>
-      <c r="B53" s="58"/>
-      <c r="C53" s="58"/>
-      <c r="D53" s="58"/>
-      <c r="E53" s="58"/>
-      <c r="F53" s="58"/>
-      <c r="G53" s="58"/>
-      <c r="H53" s="58"/>
-      <c r="I53" s="58"/>
+      <c r="A53" s="59"/>
+      <c r="B53" s="59"/>
+      <c r="C53" s="59"/>
+      <c r="D53" s="59"/>
+      <c r="E53" s="59"/>
+      <c r="F53" s="59"/>
+      <c r="G53" s="59"/>
+      <c r="H53" s="59"/>
+      <c r="I53" s="59"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" s="58"/>
-      <c r="B54" s="58"/>
-      <c r="C54" s="58"/>
-      <c r="D54" s="58"/>
-      <c r="E54" s="58"/>
-      <c r="F54" s="58"/>
-      <c r="G54" s="58"/>
-      <c r="H54" s="58"/>
-      <c r="I54" s="58"/>
+      <c r="A54" s="59"/>
+      <c r="B54" s="59"/>
+      <c r="C54" s="59"/>
+      <c r="D54" s="59"/>
+      <c r="E54" s="59"/>
+      <c r="F54" s="59"/>
+      <c r="G54" s="59"/>
+      <c r="H54" s="59"/>
+      <c r="I54" s="59"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
-      <c r="A55" s="58"/>
-      <c r="B55" s="58"/>
-      <c r="C55" s="58"/>
-      <c r="D55" s="58"/>
-      <c r="E55" s="58"/>
-      <c r="F55" s="58"/>
-      <c r="G55" s="58"/>
-      <c r="H55" s="58"/>
-      <c r="I55" s="58"/>
+      <c r="A55" s="59"/>
+      <c r="B55" s="59"/>
+      <c r="C55" s="59"/>
+      <c r="D55" s="59"/>
+      <c r="E55" s="59"/>
+      <c r="F55" s="59"/>
+      <c r="G55" s="59"/>
+      <c r="H55" s="59"/>
+      <c r="I55" s="59"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
-      <c r="A56" s="58"/>
-      <c r="B56" s="58"/>
-      <c r="C56" s="58"/>
-      <c r="D56" s="58"/>
-      <c r="E56" s="58"/>
-      <c r="F56" s="58"/>
-      <c r="G56" s="58"/>
-      <c r="H56" s="58"/>
-      <c r="I56" s="58"/>
+      <c r="A56" s="59"/>
+      <c r="B56" s="59"/>
+      <c r="C56" s="59"/>
+      <c r="D56" s="59"/>
+      <c r="E56" s="59"/>
+      <c r="F56" s="59"/>
+      <c r="G56" s="59"/>
+      <c r="H56" s="59"/>
+      <c r="I56" s="59"/>
     </row>
     <row r="57" ht="18.75" customHeight="1">
-      <c r="A57" s="58"/>
-      <c r="B57" s="58"/>
-      <c r="C57" s="58"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="58"/>
-      <c r="F57" s="58"/>
-      <c r="G57" s="58"/>
-      <c r="H57" s="58"/>
-      <c r="I57" s="58"/>
+      <c r="A57" s="59"/>
+      <c r="B57" s="59"/>
+      <c r="C57" s="59"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="59"/>
+      <c r="G57" s="59"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="59"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
-      <c r="A58" s="58"/>
-      <c r="B58" s="58"/>
-      <c r="C58" s="58"/>
-      <c r="D58" s="58"/>
-      <c r="E58" s="58"/>
-      <c r="F58" s="58"/>
-      <c r="G58" s="58"/>
-      <c r="H58" s="58"/>
-      <c r="I58" s="58"/>
+      <c r="A58" s="59"/>
+      <c r="B58" s="59"/>
+      <c r="C58" s="59"/>
+      <c r="D58" s="59"/>
+      <c r="E58" s="59"/>
+      <c r="F58" s="59"/>
+      <c r="G58" s="59"/>
+      <c r="H58" s="59"/>
+      <c r="I58" s="59"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
-      <c r="A59" s="58"/>
-      <c r="B59" s="58"/>
-      <c r="C59" s="58"/>
-      <c r="D59" s="58"/>
-      <c r="E59" s="58"/>
-      <c r="F59" s="58"/>
-      <c r="G59" s="58"/>
-      <c r="H59" s="58"/>
-      <c r="I59" s="58"/>
+      <c r="A59" s="59"/>
+      <c r="B59" s="59"/>
+      <c r="C59" s="59"/>
+      <c r="D59" s="59"/>
+      <c r="E59" s="59"/>
+      <c r="F59" s="59"/>
+      <c r="G59" s="59"/>
+      <c r="H59" s="59"/>
+      <c r="I59" s="59"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
-      <c r="A60" s="58"/>
-      <c r="B60" s="58"/>
-      <c r="C60" s="58"/>
-      <c r="D60" s="58"/>
-      <c r="E60" s="58"/>
-      <c r="F60" s="58"/>
-      <c r="G60" s="58"/>
-      <c r="H60" s="58"/>
-      <c r="I60" s="58"/>
+      <c r="A60" s="59"/>
+      <c r="B60" s="59"/>
+      <c r="C60" s="59"/>
+      <c r="D60" s="59"/>
+      <c r="E60" s="59"/>
+      <c r="F60" s="59"/>
+      <c r="G60" s="59"/>
+      <c r="H60" s="59"/>
+      <c r="I60" s="59"/>
     </row>
     <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" s="58"/>
-      <c r="B61" s="58"/>
-      <c r="C61" s="58"/>
-      <c r="D61" s="58"/>
-      <c r="E61" s="58"/>
-      <c r="F61" s="58"/>
-      <c r="G61" s="58"/>
-      <c r="H61" s="58"/>
-      <c r="I61" s="58"/>
+      <c r="A61" s="59"/>
+      <c r="B61" s="59"/>
+      <c r="C61" s="59"/>
+      <c r="D61" s="59"/>
+      <c r="E61" s="59"/>
+      <c r="F61" s="59"/>
+      <c r="G61" s="59"/>
+      <c r="H61" s="59"/>
+      <c r="I61" s="59"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
-      <c r="A62" s="58"/>
-      <c r="B62" s="58"/>
-      <c r="C62" s="58"/>
-      <c r="D62" s="58"/>
-      <c r="E62" s="58"/>
-      <c r="F62" s="58"/>
-      <c r="G62" s="58"/>
-      <c r="H62" s="58"/>
-      <c r="I62" s="58"/>
+      <c r="A62" s="59"/>
+      <c r="B62" s="59"/>
+      <c r="C62" s="59"/>
+      <c r="D62" s="59"/>
+      <c r="E62" s="59"/>
+      <c r="F62" s="59"/>
+      <c r="G62" s="59"/>
+      <c r="H62" s="59"/>
+      <c r="I62" s="59"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
-      <c r="A63" s="58"/>
-      <c r="B63" s="58"/>
-      <c r="C63" s="58"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="58"/>
-      <c r="F63" s="58"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="58"/>
-      <c r="I63" s="58"/>
+      <c r="A63" s="59"/>
+      <c r="B63" s="59"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="59"/>
+      <c r="E63" s="59"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="59"/>
     </row>
     <row r="64" ht="18.75" customHeight="1">
-      <c r="A64" s="58"/>
-      <c r="B64" s="58"/>
-      <c r="C64" s="58"/>
-      <c r="D64" s="58"/>
-      <c r="E64" s="58"/>
-      <c r="F64" s="58"/>
-      <c r="G64" s="58"/>
-      <c r="H64" s="58"/>
-      <c r="I64" s="58"/>
+      <c r="A64" s="59"/>
+      <c r="B64" s="59"/>
+      <c r="C64" s="59"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
     </row>
     <row r="65" ht="18.75" customHeight="1">
-      <c r="A65" s="58"/>
-      <c r="B65" s="58"/>
-      <c r="C65" s="58"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="58"/>
-      <c r="I65" s="58"/>
+      <c r="A65" s="59"/>
+      <c r="B65" s="59"/>
+      <c r="C65" s="59"/>
+      <c r="D65" s="59"/>
+      <c r="E65" s="59"/>
+      <c r="F65" s="59"/>
+      <c r="G65" s="59"/>
+      <c r="H65" s="59"/>
+      <c r="I65" s="59"/>
     </row>
     <row r="66" ht="18.75" customHeight="1">
-      <c r="A66" s="58"/>
-      <c r="B66" s="58"/>
-      <c r="C66" s="58"/>
-      <c r="D66" s="58"/>
-      <c r="E66" s="58"/>
-      <c r="F66" s="58"/>
-      <c r="G66" s="58"/>
-      <c r="H66" s="58"/>
-      <c r="I66" s="58"/>
+      <c r="A66" s="59"/>
+      <c r="B66" s="59"/>
+      <c r="C66" s="59"/>
+      <c r="D66" s="59"/>
+      <c r="E66" s="59"/>
+      <c r="F66" s="59"/>
+      <c r="G66" s="59"/>
+      <c r="H66" s="59"/>
+      <c r="I66" s="59"/>
     </row>
     <row r="67" ht="18.75" customHeight="1">
-      <c r="A67" s="58"/>
-      <c r="B67" s="58"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="58"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58"/>
-      <c r="I67" s="58"/>
+      <c r="A67" s="59"/>
+      <c r="B67" s="59"/>
+      <c r="C67" s="59"/>
+      <c r="D67" s="59"/>
+      <c r="E67" s="59"/>
+      <c r="F67" s="59"/>
+      <c r="G67" s="59"/>
+      <c r="H67" s="59"/>
+      <c r="I67" s="59"/>
     </row>
     <row r="68" ht="18.75" customHeight="1">
-      <c r="A68" s="58"/>
-      <c r="B68" s="58"/>
-      <c r="C68" s="58"/>
-      <c r="D68" s="58"/>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58"/>
-      <c r="I68" s="58"/>
+      <c r="A68" s="59"/>
+      <c r="B68" s="59"/>
+      <c r="C68" s="59"/>
+      <c r="D68" s="59"/>
+      <c r="E68" s="59"/>
+      <c r="F68" s="59"/>
+      <c r="G68" s="59"/>
+      <c r="H68" s="59"/>
+      <c r="I68" s="59"/>
     </row>
     <row r="69" ht="18.75" customHeight="1">
-      <c r="A69" s="58"/>
-      <c r="B69" s="58"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="58"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="58"/>
-      <c r="I69" s="58"/>
+      <c r="A69" s="59"/>
+      <c r="B69" s="59"/>
+      <c r="C69" s="59"/>
+      <c r="D69" s="59"/>
+      <c r="E69" s="59"/>
+      <c r="F69" s="59"/>
+      <c r="G69" s="59"/>
+      <c r="H69" s="59"/>
+      <c r="I69" s="59"/>
     </row>
     <row r="70" ht="18.75" customHeight="1">
-      <c r="A70" s="58"/>
-      <c r="B70" s="58"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="58"/>
-      <c r="E70" s="58"/>
-      <c r="F70" s="58"/>
-      <c r="G70" s="58"/>
-      <c r="H70" s="58"/>
-      <c r="I70" s="58"/>
+      <c r="A70" s="59"/>
+      <c r="B70" s="59"/>
+      <c r="C70" s="59"/>
+      <c r="D70" s="59"/>
+      <c r="E70" s="59"/>
+      <c r="F70" s="59"/>
+      <c r="G70" s="59"/>
+      <c r="H70" s="59"/>
+      <c r="I70" s="59"/>
     </row>
     <row r="71" ht="18.75" customHeight="1">
-      <c r="A71" s="58"/>
-      <c r="B71" s="58"/>
-      <c r="C71" s="58"/>
-      <c r="D71" s="58"/>
-      <c r="E71" s="58"/>
-      <c r="F71" s="58"/>
-      <c r="G71" s="58"/>
-      <c r="H71" s="58"/>
-      <c r="I71" s="58"/>
+      <c r="A71" s="59"/>
+      <c r="B71" s="59"/>
+      <c r="C71" s="59"/>
+      <c r="D71" s="59"/>
+      <c r="E71" s="59"/>
+      <c r="F71" s="59"/>
+      <c r="G71" s="59"/>
+      <c r="H71" s="59"/>
+      <c r="I71" s="59"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
-      <c r="A72" s="58"/>
-      <c r="B72" s="58"/>
-      <c r="C72" s="58"/>
-      <c r="D72" s="58"/>
-      <c r="E72" s="58"/>
-      <c r="F72" s="58"/>
-      <c r="G72" s="58"/>
-      <c r="H72" s="58"/>
-      <c r="I72" s="58"/>
+      <c r="A72" s="59"/>
+      <c r="B72" s="59"/>
+      <c r="C72" s="59"/>
+      <c r="D72" s="59"/>
+      <c r="E72" s="59"/>
+      <c r="F72" s="59"/>
+      <c r="G72" s="59"/>
+      <c r="H72" s="59"/>
+      <c r="I72" s="59"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
-      <c r="A73" s="58"/>
-      <c r="B73" s="58"/>
-      <c r="C73" s="58"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="58"/>
-      <c r="I73" s="58"/>
+      <c r="A73" s="59"/>
+      <c r="B73" s="59"/>
+      <c r="C73" s="59"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="59"/>
+      <c r="F73" s="59"/>
+      <c r="G73" s="59"/>
+      <c r="H73" s="59"/>
+      <c r="I73" s="59"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
-      <c r="A74" s="58"/>
-      <c r="B74" s="58"/>
-      <c r="C74" s="58"/>
-      <c r="D74" s="58"/>
-      <c r="E74" s="58"/>
-      <c r="F74" s="58"/>
-      <c r="G74" s="58"/>
-      <c r="H74" s="58"/>
-      <c r="I74" s="58"/>
+      <c r="A74" s="59"/>
+      <c r="B74" s="59"/>
+      <c r="C74" s="59"/>
+      <c r="D74" s="59"/>
+      <c r="E74" s="59"/>
+      <c r="F74" s="59"/>
+      <c r="G74" s="59"/>
+      <c r="H74" s="59"/>
+      <c r="I74" s="59"/>
     </row>
     <row r="75" ht="18.75" customHeight="1">
-      <c r="A75" s="58"/>
-      <c r="B75" s="58"/>
-      <c r="C75" s="58"/>
-      <c r="D75" s="58"/>
-      <c r="E75" s="58"/>
-      <c r="F75" s="58"/>
-      <c r="G75" s="58"/>
-      <c r="H75" s="58"/>
-      <c r="I75" s="58"/>
+      <c r="A75" s="59"/>
+      <c r="B75" s="59"/>
+      <c r="C75" s="59"/>
+      <c r="D75" s="59"/>
+      <c r="E75" s="59"/>
+      <c r="F75" s="59"/>
+      <c r="G75" s="59"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="59"/>
     </row>
     <row r="76" ht="18.75" customHeight="1">
-      <c r="A76" s="58"/>
-      <c r="B76" s="58"/>
-      <c r="C76" s="58"/>
-      <c r="D76" s="58"/>
-      <c r="E76" s="58"/>
-      <c r="F76" s="58"/>
-      <c r="G76" s="58"/>
-      <c r="H76" s="58"/>
-      <c r="I76" s="58"/>
+      <c r="A76" s="59"/>
+      <c r="B76" s="59"/>
+      <c r="C76" s="59"/>
+      <c r="D76" s="59"/>
+      <c r="E76" s="59"/>
+      <c r="F76" s="59"/>
+      <c r="G76" s="59"/>
+      <c r="H76" s="59"/>
+      <c r="I76" s="59"/>
     </row>
     <row r="77" ht="18.75" customHeight="1">
-      <c r="A77" s="58"/>
-      <c r="B77" s="58"/>
-      <c r="C77" s="58"/>
-      <c r="D77" s="58"/>
-      <c r="E77" s="58"/>
-      <c r="F77" s="58"/>
-      <c r="G77" s="58"/>
-      <c r="H77" s="58"/>
-      <c r="I77" s="58"/>
+      <c r="A77" s="59"/>
+      <c r="B77" s="59"/>
+      <c r="C77" s="59"/>
+      <c r="D77" s="59"/>
+      <c r="E77" s="59"/>
+      <c r="F77" s="59"/>
+      <c r="G77" s="59"/>
+      <c r="H77" s="59"/>
+      <c r="I77" s="59"/>
     </row>
     <row r="78" ht="18.75" customHeight="1">
-      <c r="A78" s="58"/>
-      <c r="B78" s="58"/>
-      <c r="C78" s="58"/>
-      <c r="D78" s="58"/>
-      <c r="E78" s="58"/>
-      <c r="F78" s="58"/>
-      <c r="G78" s="58"/>
-      <c r="H78" s="58"/>
-      <c r="I78" s="58"/>
+      <c r="A78" s="59"/>
+      <c r="B78" s="59"/>
+      <c r="C78" s="59"/>
+      <c r="D78" s="59"/>
+      <c r="E78" s="59"/>
+      <c r="F78" s="59"/>
+      <c r="G78" s="59"/>
+      <c r="H78" s="59"/>
+      <c r="I78" s="59"/>
     </row>
     <row r="79" ht="18.75" customHeight="1">
-      <c r="A79" s="58"/>
-      <c r="B79" s="58"/>
-      <c r="C79" s="58"/>
-      <c r="D79" s="58"/>
-      <c r="E79" s="58"/>
-      <c r="F79" s="58"/>
-      <c r="G79" s="58"/>
-      <c r="H79" s="58"/>
-      <c r="I79" s="58"/>
+      <c r="A79" s="59"/>
+      <c r="B79" s="59"/>
+      <c r="C79" s="59"/>
+      <c r="D79" s="59"/>
+      <c r="E79" s="59"/>
+      <c r="F79" s="59"/>
+      <c r="G79" s="59"/>
+      <c r="H79" s="59"/>
+      <c r="I79" s="59"/>
     </row>
     <row r="80" ht="18.75" customHeight="1">
-      <c r="A80" s="58"/>
-      <c r="B80" s="58"/>
-      <c r="C80" s="58"/>
-      <c r="D80" s="58"/>
-      <c r="E80" s="58"/>
-      <c r="F80" s="58"/>
-      <c r="G80" s="58"/>
-      <c r="H80" s="58"/>
-      <c r="I80" s="58"/>
+      <c r="A80" s="59"/>
+      <c r="B80" s="59"/>
+      <c r="C80" s="59"/>
+      <c r="D80" s="59"/>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59"/>
+      <c r="G80" s="59"/>
+      <c r="H80" s="59"/>
+      <c r="I80" s="59"/>
     </row>
     <row r="81" ht="18.75" customHeight="1">
-      <c r="A81" s="58"/>
-      <c r="B81" s="58"/>
-      <c r="C81" s="58"/>
-      <c r="D81" s="58"/>
-      <c r="E81" s="58"/>
-      <c r="F81" s="58"/>
-      <c r="G81" s="58"/>
-      <c r="H81" s="58"/>
-      <c r="I81" s="58"/>
+      <c r="A81" s="59"/>
+      <c r="B81" s="59"/>
+      <c r="C81" s="59"/>
+      <c r="D81" s="59"/>
+      <c r="E81" s="59"/>
+      <c r="F81" s="59"/>
+      <c r="G81" s="59"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="59"/>
     </row>
     <row r="82" ht="18.75" customHeight="1">
-      <c r="A82" s="58"/>
-      <c r="B82" s="58"/>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58"/>
-      <c r="E82" s="58"/>
-      <c r="F82" s="58"/>
-      <c r="G82" s="58"/>
-      <c r="H82" s="58"/>
-      <c r="I82" s="58"/>
+      <c r="A82" s="59"/>
+      <c r="B82" s="59"/>
+      <c r="C82" s="59"/>
+      <c r="D82" s="59"/>
+      <c r="E82" s="59"/>
+      <c r="F82" s="59"/>
+      <c r="G82" s="59"/>
+      <c r="H82" s="59"/>
+      <c r="I82" s="59"/>
     </row>
     <row r="83" ht="18.75" customHeight="1">
-      <c r="A83" s="58"/>
-      <c r="B83" s="58"/>
-      <c r="C83" s="58"/>
-      <c r="D83" s="58"/>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58"/>
-      <c r="G83" s="58"/>
-      <c r="H83" s="58"/>
-      <c r="I83" s="58"/>
+      <c r="A83" s="59"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="59"/>
+      <c r="D83" s="59"/>
+      <c r="E83" s="59"/>
+      <c r="F83" s="59"/>
+      <c r="G83" s="59"/>
+      <c r="H83" s="59"/>
+      <c r="I83" s="59"/>
     </row>
     <row r="84" ht="18.75" customHeight="1">
-      <c r="A84" s="58"/>
-      <c r="B84" s="58"/>
-      <c r="C84" s="58"/>
-      <c r="D84" s="58"/>
-      <c r="E84" s="58"/>
-      <c r="F84" s="58"/>
-      <c r="G84" s="58"/>
-      <c r="H84" s="58"/>
-      <c r="I84" s="58"/>
+      <c r="A84" s="59"/>
+      <c r="B84" s="59"/>
+      <c r="C84" s="59"/>
+      <c r="D84" s="59"/>
+      <c r="E84" s="59"/>
+      <c r="F84" s="59"/>
+      <c r="G84" s="59"/>
+      <c r="H84" s="59"/>
+      <c r="I84" s="59"/>
     </row>
     <row r="85" ht="18.75" customHeight="1">
-      <c r="A85" s="58"/>
-      <c r="B85" s="58"/>
-      <c r="C85" s="58"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="58"/>
-      <c r="F85" s="58"/>
-      <c r="G85" s="58"/>
-      <c r="H85" s="58"/>
-      <c r="I85" s="58"/>
+      <c r="A85" s="59"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="59"/>
+      <c r="D85" s="59"/>
+      <c r="E85" s="59"/>
+      <c r="F85" s="59"/>
+      <c r="G85" s="59"/>
+      <c r="H85" s="59"/>
+      <c r="I85" s="59"/>
     </row>
     <row r="86" ht="18.75" customHeight="1">
-      <c r="A86" s="58"/>
-      <c r="B86" s="58"/>
-      <c r="C86" s="58"/>
-      <c r="D86" s="58"/>
-      <c r="E86" s="58"/>
-      <c r="F86" s="58"/>
-      <c r="G86" s="58"/>
-      <c r="H86" s="58"/>
-      <c r="I86" s="58"/>
+      <c r="A86" s="59"/>
+      <c r="B86" s="59"/>
+      <c r="C86" s="59"/>
+      <c r="D86" s="59"/>
+      <c r="E86" s="59"/>
+      <c r="F86" s="59"/>
+      <c r="G86" s="59"/>
+      <c r="H86" s="59"/>
+      <c r="I86" s="59"/>
     </row>
     <row r="87" ht="18.75" customHeight="1">
-      <c r="A87" s="58"/>
-      <c r="B87" s="58"/>
-      <c r="C87" s="58"/>
-      <c r="D87" s="58"/>
-      <c r="E87" s="58"/>
-      <c r="F87" s="58"/>
-      <c r="G87" s="58"/>
-      <c r="H87" s="58"/>
-      <c r="I87" s="58"/>
+      <c r="A87" s="59"/>
+      <c r="B87" s="59"/>
+      <c r="C87" s="59"/>
+      <c r="D87" s="59"/>
+      <c r="E87" s="59"/>
+      <c r="F87" s="59"/>
+      <c r="G87" s="59"/>
+      <c r="H87" s="59"/>
+      <c r="I87" s="59"/>
     </row>
     <row r="88" ht="18.75" customHeight="1">
-      <c r="A88" s="58"/>
-      <c r="B88" s="58"/>
-      <c r="C88" s="58"/>
-      <c r="D88" s="58"/>
-      <c r="E88" s="58"/>
-      <c r="F88" s="58"/>
-      <c r="G88" s="58"/>
-      <c r="H88" s="58"/>
-      <c r="I88" s="58"/>
+      <c r="A88" s="59"/>
+      <c r="B88" s="59"/>
+      <c r="C88" s="59"/>
+      <c r="D88" s="59"/>
+      <c r="E88" s="59"/>
+      <c r="F88" s="59"/>
+      <c r="G88" s="59"/>
+      <c r="H88" s="59"/>
+      <c r="I88" s="59"/>
     </row>
     <row r="89" ht="18.75" customHeight="1">
-      <c r="A89" s="58"/>
-      <c r="B89" s="58"/>
-      <c r="C89" s="58"/>
-      <c r="D89" s="58"/>
-      <c r="E89" s="58"/>
-      <c r="F89" s="58"/>
-      <c r="G89" s="58"/>
-      <c r="H89" s="58"/>
-      <c r="I89" s="58"/>
+      <c r="A89" s="59"/>
+      <c r="B89" s="59"/>
+      <c r="C89" s="59"/>
+      <c r="D89" s="59"/>
+      <c r="E89" s="59"/>
+      <c r="F89" s="59"/>
+      <c r="G89" s="59"/>
+      <c r="H89" s="59"/>
+      <c r="I89" s="59"/>
     </row>
     <row r="90" ht="18.75" customHeight="1">
-      <c r="A90" s="58"/>
-      <c r="B90" s="58"/>
-      <c r="C90" s="58"/>
-      <c r="D90" s="58"/>
-      <c r="E90" s="58"/>
-      <c r="F90" s="58"/>
-      <c r="G90" s="58"/>
-      <c r="H90" s="58"/>
-      <c r="I90" s="58"/>
+      <c r="A90" s="59"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="59"/>
+      <c r="D90" s="59"/>
+      <c r="E90" s="59"/>
+      <c r="F90" s="59"/>
+      <c r="G90" s="59"/>
+      <c r="H90" s="59"/>
+      <c r="I90" s="59"/>
     </row>
     <row r="91" ht="18.75" customHeight="1">
-      <c r="A91" s="58"/>
-      <c r="B91" s="58"/>
-      <c r="C91" s="58"/>
-      <c r="D91" s="58"/>
-      <c r="E91" s="58"/>
-      <c r="F91" s="58"/>
-      <c r="G91" s="58"/>
-      <c r="H91" s="58"/>
-      <c r="I91" s="58"/>
+      <c r="A91" s="59"/>
+      <c r="B91" s="59"/>
+      <c r="C91" s="59"/>
+      <c r="D91" s="59"/>
+      <c r="E91" s="59"/>
+      <c r="F91" s="59"/>
+      <c r="G91" s="59"/>
+      <c r="H91" s="59"/>
+      <c r="I91" s="59"/>
     </row>
     <row r="92" ht="18.75" customHeight="1">
-      <c r="A92" s="58"/>
-      <c r="B92" s="58"/>
-      <c r="C92" s="58"/>
-      <c r="D92" s="58"/>
-      <c r="E92" s="58"/>
-      <c r="F92" s="58"/>
-      <c r="G92" s="58"/>
-      <c r="H92" s="58"/>
-      <c r="I92" s="58"/>
+      <c r="A92" s="59"/>
+      <c r="B92" s="59"/>
+      <c r="C92" s="59"/>
+      <c r="D92" s="59"/>
+      <c r="E92" s="59"/>
+      <c r="F92" s="59"/>
+      <c r="G92" s="59"/>
+      <c r="H92" s="59"/>
+      <c r="I92" s="59"/>
     </row>
     <row r="93" ht="18.75" customHeight="1">
-      <c r="A93" s="58"/>
-      <c r="B93" s="58"/>
-      <c r="C93" s="58"/>
-      <c r="D93" s="58"/>
-      <c r="E93" s="58"/>
-      <c r="F93" s="58"/>
-      <c r="G93" s="58"/>
-      <c r="H93" s="58"/>
-      <c r="I93" s="58"/>
+      <c r="A93" s="59"/>
+      <c r="B93" s="59"/>
+      <c r="C93" s="59"/>
+      <c r="D93" s="59"/>
+      <c r="E93" s="59"/>
+      <c r="F93" s="59"/>
+      <c r="G93" s="59"/>
+      <c r="H93" s="59"/>
+      <c r="I93" s="59"/>
     </row>
     <row r="94" ht="18.75" customHeight="1">
-      <c r="A94" s="58"/>
-      <c r="B94" s="58"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="58"/>
-      <c r="E94" s="58"/>
-      <c r="F94" s="58"/>
-      <c r="G94" s="58"/>
-      <c r="H94" s="58"/>
-      <c r="I94" s="58"/>
+      <c r="A94" s="59"/>
+      <c r="B94" s="59"/>
+      <c r="C94" s="59"/>
+      <c r="D94" s="59"/>
+      <c r="E94" s="59"/>
+      <c r="F94" s="59"/>
+      <c r="G94" s="59"/>
+      <c r="H94" s="59"/>
+      <c r="I94" s="59"/>
     </row>
     <row r="95" ht="18.75" customHeight="1">
-      <c r="A95" s="58"/>
-      <c r="B95" s="58"/>
-      <c r="C95" s="58"/>
-      <c r="D95" s="58"/>
-      <c r="E95" s="58"/>
-      <c r="F95" s="58"/>
-      <c r="G95" s="58"/>
-      <c r="H95" s="58"/>
-      <c r="I95" s="58"/>
+      <c r="A95" s="59"/>
+      <c r="B95" s="59"/>
+      <c r="C95" s="59"/>
+      <c r="D95" s="59"/>
+      <c r="E95" s="59"/>
+      <c r="F95" s="59"/>
+      <c r="G95" s="59"/>
+      <c r="H95" s="59"/>
+      <c r="I95" s="59"/>
     </row>
     <row r="96" ht="18.75" customHeight="1">
-      <c r="A96" s="58"/>
-      <c r="B96" s="58"/>
-      <c r="C96" s="58"/>
-      <c r="D96" s="58"/>
-      <c r="E96" s="58"/>
-      <c r="F96" s="58"/>
-      <c r="G96" s="58"/>
-      <c r="H96" s="58"/>
-      <c r="I96" s="58"/>
+      <c r="A96" s="59"/>
+      <c r="B96" s="59"/>
+      <c r="C96" s="59"/>
+      <c r="D96" s="59"/>
+      <c r="E96" s="59"/>
+      <c r="F96" s="59"/>
+      <c r="G96" s="59"/>
+      <c r="H96" s="59"/>
+      <c r="I96" s="59"/>
     </row>
     <row r="97" ht="18.75" customHeight="1">
-      <c r="A97" s="58"/>
-      <c r="B97" s="58"/>
-      <c r="C97" s="58"/>
-      <c r="D97" s="58"/>
-      <c r="E97" s="58"/>
-      <c r="F97" s="58"/>
-      <c r="G97" s="58"/>
-      <c r="H97" s="58"/>
-      <c r="I97" s="58"/>
+      <c r="A97" s="59"/>
+      <c r="B97" s="59"/>
+      <c r="C97" s="59"/>
+      <c r="D97" s="59"/>
+      <c r="E97" s="59"/>
+      <c r="F97" s="59"/>
+      <c r="G97" s="59"/>
+      <c r="H97" s="59"/>
+      <c r="I97" s="59"/>
     </row>
     <row r="98" ht="18.75" customHeight="1">
-      <c r="A98" s="58"/>
-      <c r="B98" s="58"/>
-      <c r="C98" s="58"/>
-      <c r="D98" s="58"/>
-      <c r="E98" s="58"/>
-      <c r="F98" s="58"/>
-      <c r="G98" s="58"/>
-      <c r="H98" s="58"/>
-      <c r="I98" s="58"/>
+      <c r="A98" s="59"/>
+      <c r="B98" s="59"/>
+      <c r="C98" s="59"/>
+      <c r="D98" s="59"/>
+      <c r="E98" s="59"/>
+      <c r="F98" s="59"/>
+      <c r="G98" s="59"/>
+      <c r="H98" s="59"/>
+      <c r="I98" s="59"/>
     </row>
     <row r="99" ht="18.75" customHeight="1">
-      <c r="A99" s="58"/>
-      <c r="B99" s="58"/>
-      <c r="C99" s="58"/>
-      <c r="D99" s="58"/>
-      <c r="E99" s="58"/>
-      <c r="F99" s="58"/>
-      <c r="G99" s="58"/>
-      <c r="H99" s="58"/>
-      <c r="I99" s="58"/>
+      <c r="A99" s="59"/>
+      <c r="B99" s="59"/>
+      <c r="C99" s="59"/>
+      <c r="D99" s="59"/>
+      <c r="E99" s="59"/>
+      <c r="F99" s="59"/>
+      <c r="G99" s="59"/>
+      <c r="H99" s="59"/>
+      <c r="I99" s="59"/>
     </row>
     <row r="100" ht="18.75" customHeight="1">
-      <c r="A100" s="58"/>
-      <c r="B100" s="58"/>
-      <c r="C100" s="58"/>
-      <c r="D100" s="58"/>
-      <c r="E100" s="58"/>
-      <c r="F100" s="58"/>
-      <c r="G100" s="58"/>
-      <c r="H100" s="58"/>
-      <c r="I100" s="58"/>
+      <c r="A100" s="59"/>
+      <c r="B100" s="59"/>
+      <c r="C100" s="59"/>
+      <c r="D100" s="59"/>
+      <c r="E100" s="59"/>
+      <c r="F100" s="59"/>
+      <c r="G100" s="59"/>
+      <c r="H100" s="59"/>
+      <c r="I100" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="1">
@@ -16376,1248 +16457,1248 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="68" t="s">
+      <c r="A1" s="69" t="s">
+        <v>1142</v>
+      </c>
+      <c r="C1" s="70"/>
+      <c r="D1" s="71" t="s">
+        <v>1143</v>
+      </c>
+      <c r="H1" s="72"/>
+      <c r="I1" s="72"/>
+    </row>
+    <row r="2" ht="18.75" customHeight="1">
+      <c r="A2" s="71" t="s">
+        <v>1144</v>
+      </c>
+      <c r="B2" s="71" t="s">
+        <v>1145</v>
+      </c>
+      <c r="C2" s="72"/>
+      <c r="D2" s="71" t="s">
+        <v>1144</v>
+      </c>
+      <c r="E2" s="71" t="s">
+        <v>1145</v>
+      </c>
+      <c r="H2" s="72"/>
+      <c r="I2" s="72"/>
+    </row>
+    <row r="3" ht="18.75" customHeight="1">
+      <c r="A3" s="73" t="s">
+        <v>1146</v>
+      </c>
+      <c r="B3" s="59" t="s">
+        <v>131</v>
+      </c>
+      <c r="C3" s="73"/>
+      <c r="D3" s="59" t="s">
+        <v>1147</v>
+      </c>
+      <c r="E3" s="59" t="s">
+        <v>1148</v>
+      </c>
+      <c r="H3" s="72"/>
+      <c r="I3" s="72"/>
+    </row>
+    <row r="4" ht="18.75" customHeight="1">
+      <c r="A4" s="59" t="s">
+        <v>1149</v>
+      </c>
+      <c r="B4" s="59" t="s">
+        <v>1150</v>
+      </c>
+      <c r="C4" s="73"/>
+      <c r="D4" s="73" t="s">
+        <v>1151</v>
+      </c>
+      <c r="E4" s="73" t="s">
+        <v>1152</v>
+      </c>
+      <c r="F4" s="73"/>
+      <c r="G4" s="73"/>
+      <c r="H4" s="73"/>
+      <c r="I4" s="73"/>
+    </row>
+    <row r="5" ht="18.75" customHeight="1">
+      <c r="A5" s="59" t="s">
+        <v>128</v>
+      </c>
+      <c r="B5" s="59" t="s">
+        <v>135</v>
+      </c>
+      <c r="C5" s="73"/>
+      <c r="D5" s="59" t="s">
+        <v>1153</v>
+      </c>
+      <c r="E5" s="59" t="s">
+        <v>1154</v>
+      </c>
+      <c r="F5" s="73"/>
+      <c r="G5" s="73"/>
+      <c r="H5" s="73"/>
+      <c r="I5" s="73"/>
+    </row>
+    <row r="6" ht="18.75" customHeight="1">
+      <c r="A6" s="73" t="s">
         <v>1135</v>
       </c>
-      <c r="C1" s="69"/>
-      <c r="D1" s="70" t="s">
-        <v>1136</v>
-      </c>
-      <c r="H1" s="71"/>
-      <c r="I1" s="71"/>
-    </row>
-    <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="70" t="s">
+      <c r="B6" s="73" t="s">
+        <v>143</v>
+      </c>
+      <c r="C6" s="73"/>
+      <c r="D6" s="59" t="s">
+        <v>1155</v>
+      </c>
+      <c r="E6" s="59" t="s">
+        <v>1156</v>
+      </c>
+      <c r="F6" s="73"/>
+      <c r="G6" s="73"/>
+      <c r="H6" s="73"/>
+      <c r="I6" s="73"/>
+    </row>
+    <row r="7" ht="18.75" customHeight="1">
+      <c r="A7" s="73" t="s">
+        <v>405</v>
+      </c>
+      <c r="B7" s="73" t="s">
+        <v>147</v>
+      </c>
+      <c r="C7" s="73"/>
+      <c r="D7" s="59" t="s">
+        <v>1157</v>
+      </c>
+      <c r="E7" s="59" t="s">
+        <v>1158</v>
+      </c>
+      <c r="F7" s="73"/>
+      <c r="G7" s="73"/>
+      <c r="H7" s="73"/>
+      <c r="I7" s="73"/>
+    </row>
+    <row r="8" ht="18.75" customHeight="1">
+      <c r="A8" s="73" t="s">
+        <v>1159</v>
+      </c>
+      <c r="B8" s="59" t="s">
+        <v>151</v>
+      </c>
+      <c r="C8" s="73"/>
+      <c r="D8" s="59" t="s">
+        <v>1160</v>
+      </c>
+      <c r="E8" s="59" t="s">
+        <v>1161</v>
+      </c>
+      <c r="F8" s="73"/>
+      <c r="G8" s="73"/>
+      <c r="H8" s="73"/>
+      <c r="I8" s="73"/>
+    </row>
+    <row r="9" ht="18.75" customHeight="1">
+      <c r="A9" s="59" t="s">
         <v>1137</v>
       </c>
-      <c r="B2" s="70" t="s">
+      <c r="B9" s="59" t="s">
+        <v>1162</v>
+      </c>
+      <c r="C9" s="73"/>
+      <c r="D9" s="73"/>
+      <c r="E9" s="74"/>
+      <c r="F9" s="74"/>
+      <c r="G9" s="74"/>
+      <c r="H9" s="74"/>
+      <c r="I9" s="74"/>
+    </row>
+    <row r="10" ht="18.75" customHeight="1">
+      <c r="A10" s="73" t="s">
+        <v>1139</v>
+      </c>
+      <c r="B10" s="59" t="s">
+        <v>156</v>
+      </c>
+      <c r="C10" s="73"/>
+      <c r="D10" s="73"/>
+      <c r="E10" s="74"/>
+      <c r="F10" s="73"/>
+      <c r="G10" s="73"/>
+      <c r="H10" s="73"/>
+      <c r="I10" s="73"/>
+    </row>
+    <row r="11" ht="18.75" customHeight="1">
+      <c r="A11" s="73" t="s">
         <v>1138</v>
       </c>
-      <c r="C2" s="71"/>
-      <c r="D2" s="70" t="s">
-        <v>1137</v>
-      </c>
-      <c r="E2" s="70" t="s">
-        <v>1138</v>
-      </c>
-      <c r="H2" s="71"/>
-      <c r="I2" s="71"/>
-    </row>
-    <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="72" t="s">
-        <v>1139</v>
-      </c>
-      <c r="B3" s="58" t="s">
-        <v>131</v>
-      </c>
-      <c r="C3" s="72"/>
-      <c r="D3" s="58" t="s">
-        <v>1140</v>
-      </c>
-      <c r="E3" s="58" t="s">
-        <v>1141</v>
-      </c>
-      <c r="H3" s="71"/>
-      <c r="I3" s="71"/>
-    </row>
-    <row r="4" ht="18.75" customHeight="1">
-      <c r="A4" s="58" t="s">
-        <v>1142</v>
-      </c>
-      <c r="B4" s="58" t="s">
-        <v>1143</v>
-      </c>
-      <c r="C4" s="72"/>
-      <c r="D4" s="72" t="s">
+      <c r="B11" s="59" t="s">
+        <v>162</v>
+      </c>
+      <c r="C11" s="73"/>
+      <c r="D11" s="73"/>
+      <c r="E11" s="74"/>
+      <c r="F11" s="74"/>
+      <c r="G11" s="74"/>
+      <c r="H11" s="74"/>
+      <c r="I11" s="74"/>
+    </row>
+    <row r="12" ht="18.75" customHeight="1">
+      <c r="A12" s="73"/>
+      <c r="B12" s="73"/>
+      <c r="C12" s="73"/>
+      <c r="D12" s="73"/>
+      <c r="E12" s="74"/>
+      <c r="F12" s="74"/>
+      <c r="G12" s="74"/>
+      <c r="H12" s="74"/>
+      <c r="I12" s="74"/>
+    </row>
+    <row r="13" ht="18.75" customHeight="1">
+      <c r="A13" s="74"/>
+      <c r="B13" s="74"/>
+      <c r="C13" s="74"/>
+      <c r="D13" s="74"/>
+      <c r="E13" s="74"/>
+      <c r="F13" s="74"/>
+      <c r="G13" s="74"/>
+      <c r="H13" s="74"/>
+      <c r="I13" s="74"/>
+    </row>
+    <row r="14" ht="18.75" customHeight="1">
+      <c r="A14" s="71" t="s">
+        <v>1163</v>
+      </c>
+      <c r="C14" s="72"/>
+      <c r="D14" s="72"/>
+      <c r="E14" s="74"/>
+      <c r="F14" s="74"/>
+      <c r="G14" s="74"/>
+      <c r="H14" s="74"/>
+      <c r="I14" s="74"/>
+    </row>
+    <row r="15" ht="18.75" customHeight="1">
+      <c r="A15" s="71" t="s">
         <v>1144</v>
       </c>
-      <c r="E4" s="72" t="s">
+      <c r="B15" s="71" t="s">
         <v>1145</v>
       </c>
-      <c r="F4" s="72"/>
-      <c r="G4" s="72"/>
-      <c r="H4" s="72"/>
-      <c r="I4" s="72"/>
-    </row>
-    <row r="5" ht="18.75" customHeight="1">
-      <c r="A5" s="58" t="s">
-        <v>128</v>
-      </c>
-      <c r="B5" s="58" t="s">
-        <v>135</v>
-      </c>
-      <c r="C5" s="72"/>
-      <c r="D5" s="58" t="s">
-        <v>1146</v>
-      </c>
-      <c r="E5" s="58" t="s">
-        <v>1147</v>
-      </c>
-      <c r="F5" s="72"/>
-      <c r="G5" s="72"/>
-      <c r="H5" s="72"/>
-      <c r="I5" s="72"/>
-    </row>
-    <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="72" t="s">
-        <v>1128</v>
-      </c>
-      <c r="B6" s="72" t="s">
-        <v>143</v>
-      </c>
-      <c r="C6" s="72"/>
-      <c r="D6" s="58" t="s">
-        <v>1148</v>
-      </c>
-      <c r="E6" s="58" t="s">
-        <v>1149</v>
-      </c>
-      <c r="F6" s="72"/>
-      <c r="G6" s="72"/>
-      <c r="H6" s="72"/>
-      <c r="I6" s="72"/>
-    </row>
-    <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="72" t="s">
-        <v>405</v>
-      </c>
-      <c r="B7" s="72" t="s">
-        <v>147</v>
-      </c>
-      <c r="C7" s="72"/>
-      <c r="D7" s="58" t="s">
-        <v>1150</v>
-      </c>
-      <c r="E7" s="58" t="s">
-        <v>1151</v>
-      </c>
-      <c r="F7" s="72"/>
-      <c r="G7" s="72"/>
-      <c r="H7" s="72"/>
-      <c r="I7" s="72"/>
-    </row>
-    <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="72" t="s">
-        <v>1152</v>
-      </c>
-      <c r="B8" s="58" t="s">
-        <v>151</v>
-      </c>
-      <c r="C8" s="72"/>
-      <c r="D8" s="58" t="s">
-        <v>1153</v>
-      </c>
-      <c r="E8" s="58" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F8" s="72"/>
-      <c r="G8" s="72"/>
-      <c r="H8" s="72"/>
-      <c r="I8" s="72"/>
-    </row>
-    <row r="9" ht="18.75" customHeight="1">
-      <c r="A9" s="58" t="s">
-        <v>1130</v>
-      </c>
-      <c r="B9" s="58" t="s">
-        <v>1155</v>
-      </c>
-      <c r="C9" s="72"/>
-      <c r="D9" s="72"/>
-      <c r="E9" s="73"/>
-      <c r="F9" s="73"/>
-      <c r="G9" s="73"/>
-      <c r="H9" s="73"/>
-      <c r="I9" s="73"/>
-    </row>
-    <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="72" t="s">
-        <v>1132</v>
-      </c>
-      <c r="B10" s="58" t="s">
-        <v>156</v>
-      </c>
-      <c r="C10" s="72"/>
-      <c r="D10" s="72"/>
-      <c r="E10" s="73"/>
-      <c r="F10" s="72"/>
-      <c r="G10" s="72"/>
-      <c r="H10" s="72"/>
-      <c r="I10" s="72"/>
-    </row>
-    <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="72" t="s">
-        <v>1131</v>
-      </c>
-      <c r="B11" s="58" t="s">
-        <v>162</v>
-      </c>
-      <c r="C11" s="72"/>
-      <c r="D11" s="72"/>
-      <c r="E11" s="73"/>
-      <c r="F11" s="73"/>
-      <c r="G11" s="73"/>
-      <c r="H11" s="73"/>
-      <c r="I11" s="73"/>
-    </row>
-    <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="72"/>
-      <c r="B12" s="72"/>
-      <c r="C12" s="72"/>
-      <c r="D12" s="72"/>
-      <c r="E12" s="73"/>
-      <c r="F12" s="73"/>
-      <c r="G12" s="73"/>
-      <c r="H12" s="73"/>
-      <c r="I12" s="73"/>
-    </row>
-    <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="73"/>
-      <c r="B13" s="73"/>
-      <c r="C13" s="73"/>
-      <c r="D13" s="73"/>
-      <c r="E13" s="73"/>
-      <c r="F13" s="73"/>
-      <c r="G13" s="73"/>
-      <c r="H13" s="73"/>
-      <c r="I13" s="73"/>
-    </row>
-    <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="70" t="s">
-        <v>1156</v>
-      </c>
-      <c r="C14" s="71"/>
-      <c r="D14" s="71"/>
-      <c r="E14" s="73"/>
-      <c r="F14" s="73"/>
-      <c r="G14" s="73"/>
-      <c r="H14" s="73"/>
-      <c r="I14" s="73"/>
-    </row>
-    <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="70" t="s">
-        <v>1137</v>
-      </c>
-      <c r="B15" s="70" t="s">
-        <v>1138</v>
-      </c>
-      <c r="C15" s="71"/>
-      <c r="D15" s="71"/>
-      <c r="E15" s="73"/>
-      <c r="F15" s="73"/>
-      <c r="G15" s="73"/>
-      <c r="H15" s="73"/>
-      <c r="I15" s="73"/>
+      <c r="C15" s="72"/>
+      <c r="D15" s="72"/>
+      <c r="E15" s="74"/>
+      <c r="F15" s="74"/>
+      <c r="G15" s="74"/>
+      <c r="H15" s="74"/>
+      <c r="I15" s="74"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="72" t="s">
-        <v>1157</v>
-      </c>
-      <c r="B16" s="72" t="s">
-        <v>1158</v>
-      </c>
-      <c r="C16" s="71"/>
-      <c r="D16" s="71"/>
-      <c r="E16" s="73"/>
-      <c r="F16" s="73"/>
-      <c r="G16" s="73"/>
-      <c r="H16" s="73"/>
-      <c r="I16" s="73"/>
+      <c r="A16" s="73" t="s">
+        <v>1164</v>
+      </c>
+      <c r="B16" s="73" t="s">
+        <v>1165</v>
+      </c>
+      <c r="C16" s="72"/>
+      <c r="D16" s="72"/>
+      <c r="E16" s="74"/>
+      <c r="F16" s="74"/>
+      <c r="G16" s="74"/>
+      <c r="H16" s="74"/>
+      <c r="I16" s="74"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="72" t="s">
-        <v>1159</v>
-      </c>
-      <c r="B17" s="72" t="s">
-        <v>1160</v>
-      </c>
-      <c r="C17" s="71"/>
-      <c r="D17" s="71"/>
-      <c r="E17" s="73"/>
-      <c r="F17" s="73"/>
-      <c r="G17" s="73"/>
-      <c r="H17" s="73"/>
-      <c r="I17" s="73"/>
+      <c r="A17" s="73" t="s">
+        <v>1166</v>
+      </c>
+      <c r="B17" s="73" t="s">
+        <v>1167</v>
+      </c>
+      <c r="C17" s="72"/>
+      <c r="D17" s="72"/>
+      <c r="E17" s="74"/>
+      <c r="F17" s="74"/>
+      <c r="G17" s="74"/>
+      <c r="H17" s="74"/>
+      <c r="I17" s="74"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="72" t="s">
-        <v>1161</v>
-      </c>
-      <c r="B18" s="72" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C18" s="71"/>
-      <c r="D18" s="71"/>
-      <c r="E18" s="73"/>
-      <c r="F18" s="73"/>
-      <c r="G18" s="73"/>
-      <c r="H18" s="73"/>
-      <c r="I18" s="73"/>
+      <c r="A18" s="73" t="s">
+        <v>1168</v>
+      </c>
+      <c r="B18" s="73" t="s">
+        <v>1169</v>
+      </c>
+      <c r="C18" s="72"/>
+      <c r="D18" s="72"/>
+      <c r="E18" s="74"/>
+      <c r="F18" s="74"/>
+      <c r="G18" s="74"/>
+      <c r="H18" s="74"/>
+      <c r="I18" s="74"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="72" t="s">
-        <v>1163</v>
-      </c>
-      <c r="B19" s="72" t="s">
-        <v>1164</v>
-      </c>
-      <c r="C19" s="71"/>
-      <c r="D19" s="71"/>
-      <c r="E19" s="73"/>
-      <c r="F19" s="73"/>
-      <c r="G19" s="73"/>
-      <c r="H19" s="73"/>
-      <c r="I19" s="73"/>
+      <c r="A19" s="73" t="s">
+        <v>1170</v>
+      </c>
+      <c r="B19" s="73" t="s">
+        <v>1171</v>
+      </c>
+      <c r="C19" s="72"/>
+      <c r="D19" s="72"/>
+      <c r="E19" s="74"/>
+      <c r="F19" s="74"/>
+      <c r="G19" s="74"/>
+      <c r="H19" s="74"/>
+      <c r="I19" s="74"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
-      <c r="A20" s="58" t="s">
-        <v>1165</v>
-      </c>
-      <c r="B20" s="72" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C20" s="71"/>
-      <c r="D20" s="71"/>
-      <c r="E20" s="73"/>
-      <c r="F20" s="73"/>
-      <c r="G20" s="73"/>
-      <c r="H20" s="73"/>
-      <c r="I20" s="73"/>
+      <c r="A20" s="59" t="s">
+        <v>1172</v>
+      </c>
+      <c r="B20" s="73" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C20" s="72"/>
+      <c r="D20" s="72"/>
+      <c r="E20" s="74"/>
+      <c r="F20" s="74"/>
+      <c r="G20" s="74"/>
+      <c r="H20" s="74"/>
+      <c r="I20" s="74"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
-      <c r="A21" s="58" t="s">
-        <v>1167</v>
-      </c>
-      <c r="B21" s="72" t="s">
-        <v>1166</v>
-      </c>
-      <c r="C21" s="71"/>
-      <c r="D21" s="71"/>
-      <c r="E21" s="73"/>
-      <c r="F21" s="73"/>
-      <c r="G21" s="73"/>
-      <c r="H21" s="73"/>
-      <c r="I21" s="73"/>
+      <c r="A21" s="59" t="s">
+        <v>1174</v>
+      </c>
+      <c r="B21" s="73" t="s">
+        <v>1173</v>
+      </c>
+      <c r="C21" s="72"/>
+      <c r="D21" s="72"/>
+      <c r="E21" s="74"/>
+      <c r="F21" s="74"/>
+      <c r="G21" s="74"/>
+      <c r="H21" s="74"/>
+      <c r="I21" s="74"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
-      <c r="A22" s="58" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B22" s="58" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C22" s="71"/>
-      <c r="D22" s="71"/>
-      <c r="E22" s="73"/>
-      <c r="F22" s="73"/>
-      <c r="G22" s="73"/>
-      <c r="H22" s="73"/>
-      <c r="I22" s="73"/>
+      <c r="A22" s="59" t="s">
+        <v>1175</v>
+      </c>
+      <c r="B22" s="59" t="s">
+        <v>1176</v>
+      </c>
+      <c r="C22" s="72"/>
+      <c r="D22" s="72"/>
+      <c r="E22" s="74"/>
+      <c r="F22" s="74"/>
+      <c r="G22" s="74"/>
+      <c r="H22" s="74"/>
+      <c r="I22" s="74"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
-      <c r="A23" s="58" t="s">
-        <v>1170</v>
-      </c>
-      <c r="B23" s="72" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C23" s="71"/>
-      <c r="D23" s="71"/>
-      <c r="E23" s="73"/>
-      <c r="F23" s="73"/>
-      <c r="G23" s="73"/>
-      <c r="H23" s="73"/>
-      <c r="I23" s="73"/>
+      <c r="A23" s="59" t="s">
+        <v>1177</v>
+      </c>
+      <c r="B23" s="73" t="s">
+        <v>1178</v>
+      </c>
+      <c r="C23" s="72"/>
+      <c r="D23" s="72"/>
+      <c r="E23" s="74"/>
+      <c r="F23" s="74"/>
+      <c r="G23" s="74"/>
+      <c r="H23" s="74"/>
+      <c r="I23" s="74"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
-      <c r="A24" s="58" t="s">
-        <v>1172</v>
-      </c>
-      <c r="C24" s="71"/>
-      <c r="D24" s="71"/>
-      <c r="E24" s="73"/>
-      <c r="F24" s="73"/>
-      <c r="G24" s="73"/>
-      <c r="H24" s="73"/>
-      <c r="I24" s="73"/>
+      <c r="A24" s="59" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C24" s="72"/>
+      <c r="D24" s="72"/>
+      <c r="E24" s="74"/>
+      <c r="F24" s="74"/>
+      <c r="G24" s="74"/>
+      <c r="H24" s="74"/>
+      <c r="I24" s="74"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="72" t="s">
-        <v>1173</v>
-      </c>
-      <c r="B25" s="72" t="s">
-        <v>1174</v>
-      </c>
-      <c r="C25" s="71"/>
-      <c r="D25" s="71"/>
-      <c r="E25" s="73"/>
-      <c r="F25" s="73"/>
-      <c r="G25" s="73"/>
-      <c r="H25" s="73"/>
-      <c r="I25" s="73"/>
+      <c r="A25" s="73" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B25" s="73" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C25" s="72"/>
+      <c r="D25" s="72"/>
+      <c r="E25" s="74"/>
+      <c r="F25" s="74"/>
+      <c r="G25" s="74"/>
+      <c r="H25" s="74"/>
+      <c r="I25" s="74"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="72" t="s">
-        <v>1175</v>
-      </c>
-      <c r="B26" s="72" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C26" s="71"/>
-      <c r="D26" s="71"/>
-      <c r="E26" s="73"/>
-      <c r="F26" s="73"/>
-      <c r="G26" s="73"/>
-      <c r="H26" s="73"/>
-      <c r="I26" s="73"/>
+      <c r="A26" s="73" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B26" s="73" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C26" s="72"/>
+      <c r="D26" s="72"/>
+      <c r="E26" s="74"/>
+      <c r="F26" s="74"/>
+      <c r="G26" s="74"/>
+      <c r="H26" s="74"/>
+      <c r="I26" s="74"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="72" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B27" s="72" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C27" s="71"/>
-      <c r="D27" s="71"/>
-      <c r="E27" s="73"/>
-      <c r="F27" s="73"/>
-      <c r="G27" s="73"/>
-      <c r="H27" s="73"/>
-      <c r="I27" s="73"/>
+      <c r="A27" s="73" t="s">
+        <v>1184</v>
+      </c>
+      <c r="B27" s="73" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C27" s="72"/>
+      <c r="D27" s="72"/>
+      <c r="E27" s="74"/>
+      <c r="F27" s="74"/>
+      <c r="G27" s="74"/>
+      <c r="H27" s="74"/>
+      <c r="I27" s="74"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="72" t="s">
-        <v>1179</v>
-      </c>
-      <c r="B28" s="72" t="s">
-        <v>1180</v>
-      </c>
-      <c r="C28" s="71"/>
-      <c r="D28" s="71"/>
-      <c r="E28" s="73"/>
-      <c r="F28" s="73"/>
-      <c r="G28" s="73"/>
-      <c r="H28" s="73"/>
-      <c r="I28" s="73"/>
+      <c r="A28" s="73" t="s">
+        <v>1186</v>
+      </c>
+      <c r="B28" s="73" t="s">
+        <v>1187</v>
+      </c>
+      <c r="C28" s="72"/>
+      <c r="D28" s="72"/>
+      <c r="E28" s="74"/>
+      <c r="F28" s="74"/>
+      <c r="G28" s="74"/>
+      <c r="H28" s="74"/>
+      <c r="I28" s="74"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="72" t="s">
-        <v>1181</v>
-      </c>
-      <c r="B29" s="72" t="s">
-        <v>1182</v>
-      </c>
-      <c r="C29" s="71"/>
-      <c r="D29" s="71"/>
-      <c r="E29" s="73"/>
-      <c r="F29" s="73"/>
-      <c r="G29" s="73"/>
-      <c r="H29" s="73"/>
-      <c r="I29" s="73"/>
+      <c r="A29" s="73" t="s">
+        <v>1188</v>
+      </c>
+      <c r="B29" s="73" t="s">
+        <v>1189</v>
+      </c>
+      <c r="C29" s="72"/>
+      <c r="D29" s="72"/>
+      <c r="E29" s="74"/>
+      <c r="F29" s="74"/>
+      <c r="G29" s="74"/>
+      <c r="H29" s="74"/>
+      <c r="I29" s="74"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="72" t="s">
-        <v>1183</v>
-      </c>
-      <c r="B30" s="72" t="s">
-        <v>1184</v>
-      </c>
-      <c r="C30" s="71"/>
-      <c r="D30" s="71"/>
-      <c r="E30" s="73"/>
-      <c r="F30" s="73"/>
-      <c r="G30" s="73"/>
-      <c r="H30" s="73"/>
-      <c r="I30" s="73"/>
+      <c r="A30" s="73" t="s">
+        <v>1190</v>
+      </c>
+      <c r="B30" s="73" t="s">
+        <v>1191</v>
+      </c>
+      <c r="C30" s="72"/>
+      <c r="D30" s="72"/>
+      <c r="E30" s="74"/>
+      <c r="F30" s="74"/>
+      <c r="G30" s="74"/>
+      <c r="H30" s="74"/>
+      <c r="I30" s="74"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="72" t="s">
-        <v>1185</v>
-      </c>
-      <c r="B31" s="72" t="s">
-        <v>1186</v>
-      </c>
-      <c r="C31" s="71"/>
-      <c r="D31" s="71"/>
-      <c r="E31" s="73"/>
-      <c r="F31" s="73"/>
-      <c r="G31" s="73"/>
-      <c r="H31" s="73"/>
-      <c r="I31" s="73"/>
+      <c r="A31" s="73" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B31" s="73" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C31" s="72"/>
+      <c r="D31" s="72"/>
+      <c r="E31" s="74"/>
+      <c r="F31" s="74"/>
+      <c r="G31" s="74"/>
+      <c r="H31" s="74"/>
+      <c r="I31" s="74"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="72" t="s">
-        <v>1187</v>
-      </c>
-      <c r="B32" s="72" t="s">
+      <c r="A32" s="73" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B32" s="73" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="71"/>
-      <c r="D32" s="71"/>
-      <c r="E32" s="73"/>
-      <c r="F32" s="73"/>
-      <c r="G32" s="73"/>
-      <c r="H32" s="73"/>
-      <c r="I32" s="73"/>
+      <c r="C32" s="72"/>
+      <c r="D32" s="72"/>
+      <c r="E32" s="74"/>
+      <c r="F32" s="74"/>
+      <c r="G32" s="74"/>
+      <c r="H32" s="74"/>
+      <c r="I32" s="74"/>
     </row>
     <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="72" t="s">
-        <v>1188</v>
-      </c>
-      <c r="B33" s="72" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C33" s="71"/>
-      <c r="D33" s="71"/>
-      <c r="E33" s="73"/>
-      <c r="F33" s="73"/>
-      <c r="G33" s="73"/>
-      <c r="H33" s="73"/>
-      <c r="I33" s="73"/>
+      <c r="A33" s="73" t="s">
+        <v>1195</v>
+      </c>
+      <c r="B33" s="73" t="s">
+        <v>1196</v>
+      </c>
+      <c r="C33" s="72"/>
+      <c r="D33" s="72"/>
+      <c r="E33" s="74"/>
+      <c r="F33" s="74"/>
+      <c r="G33" s="74"/>
+      <c r="H33" s="74"/>
+      <c r="I33" s="74"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="72" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B34" s="72" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C34" s="71"/>
-      <c r="D34" s="71"/>
-      <c r="E34" s="73"/>
-      <c r="F34" s="73"/>
-      <c r="G34" s="73"/>
-      <c r="H34" s="73"/>
-      <c r="I34" s="73"/>
+      <c r="A34" s="73" t="s">
+        <v>1197</v>
+      </c>
+      <c r="B34" s="73" t="s">
+        <v>1198</v>
+      </c>
+      <c r="C34" s="72"/>
+      <c r="D34" s="72"/>
+      <c r="E34" s="74"/>
+      <c r="F34" s="74"/>
+      <c r="G34" s="74"/>
+      <c r="H34" s="74"/>
+      <c r="I34" s="74"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="72" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B35" s="58" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C35" s="71"/>
-      <c r="D35" s="71"/>
-      <c r="E35" s="73"/>
-      <c r="F35" s="73"/>
-      <c r="G35" s="73"/>
-      <c r="H35" s="73"/>
-      <c r="I35" s="73"/>
+      <c r="A35" s="73" t="s">
+        <v>1199</v>
+      </c>
+      <c r="B35" s="59" t="s">
+        <v>1200</v>
+      </c>
+      <c r="C35" s="72"/>
+      <c r="D35" s="72"/>
+      <c r="E35" s="74"/>
+      <c r="F35" s="74"/>
+      <c r="G35" s="74"/>
+      <c r="H35" s="74"/>
+      <c r="I35" s="74"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="72" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B36" s="58" t="s">
-        <v>1195</v>
-      </c>
-      <c r="C36" s="71"/>
-      <c r="D36" s="71"/>
-      <c r="E36" s="73"/>
-      <c r="F36" s="73"/>
-      <c r="G36" s="73"/>
-      <c r="H36" s="73"/>
-      <c r="I36" s="73"/>
+      <c r="A36" s="73" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B36" s="59" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C36" s="72"/>
+      <c r="D36" s="72"/>
+      <c r="E36" s="74"/>
+      <c r="F36" s="74"/>
+      <c r="G36" s="74"/>
+      <c r="H36" s="74"/>
+      <c r="I36" s="74"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="72" t="s">
-        <v>1196</v>
-      </c>
-      <c r="B37" s="72" t="s">
-        <v>1197</v>
-      </c>
-      <c r="C37" s="71"/>
-      <c r="D37" s="71"/>
-      <c r="E37" s="73"/>
-      <c r="F37" s="73"/>
-      <c r="G37" s="73"/>
-      <c r="H37" s="73"/>
-      <c r="I37" s="73"/>
+      <c r="A37" s="73" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B37" s="73" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C37" s="72"/>
+      <c r="D37" s="72"/>
+      <c r="E37" s="74"/>
+      <c r="F37" s="74"/>
+      <c r="G37" s="74"/>
+      <c r="H37" s="74"/>
+      <c r="I37" s="74"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="72" t="s">
-        <v>1198</v>
-      </c>
-      <c r="B38" s="72" t="s">
-        <v>1199</v>
-      </c>
-      <c r="C38" s="71"/>
-      <c r="D38" s="71"/>
-      <c r="E38" s="73"/>
-      <c r="F38" s="73"/>
-      <c r="G38" s="73"/>
-      <c r="H38" s="73"/>
-      <c r="I38" s="73"/>
+      <c r="A38" s="73" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B38" s="73" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C38" s="72"/>
+      <c r="D38" s="72"/>
+      <c r="E38" s="74"/>
+      <c r="F38" s="74"/>
+      <c r="G38" s="74"/>
+      <c r="H38" s="74"/>
+      <c r="I38" s="74"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="C39" s="71"/>
-      <c r="D39" s="71"/>
-      <c r="E39" s="73"/>
-      <c r="F39" s="73"/>
-      <c r="G39" s="73"/>
-      <c r="H39" s="73"/>
-      <c r="I39" s="73"/>
+      <c r="C39" s="72"/>
+      <c r="D39" s="72"/>
+      <c r="E39" s="74"/>
+      <c r="F39" s="74"/>
+      <c r="G39" s="74"/>
+      <c r="H39" s="74"/>
+      <c r="I39" s="74"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="72"/>
-      <c r="B40" s="72"/>
-      <c r="C40" s="71"/>
-      <c r="D40" s="71"/>
-      <c r="E40" s="73"/>
-      <c r="F40" s="73"/>
-      <c r="G40" s="73"/>
-      <c r="H40" s="73"/>
-      <c r="I40" s="73"/>
+      <c r="A40" s="73"/>
+      <c r="B40" s="73"/>
+      <c r="C40" s="72"/>
+      <c r="D40" s="72"/>
+      <c r="E40" s="74"/>
+      <c r="F40" s="74"/>
+      <c r="G40" s="74"/>
+      <c r="H40" s="74"/>
+      <c r="I40" s="74"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="72"/>
-      <c r="B41" s="72"/>
-      <c r="C41" s="71"/>
-      <c r="D41" s="71"/>
-      <c r="E41" s="73"/>
-      <c r="F41" s="73"/>
-      <c r="G41" s="73"/>
-      <c r="H41" s="73"/>
-      <c r="I41" s="73"/>
+      <c r="A41" s="73"/>
+      <c r="B41" s="73"/>
+      <c r="C41" s="72"/>
+      <c r="D41" s="72"/>
+      <c r="E41" s="74"/>
+      <c r="F41" s="74"/>
+      <c r="G41" s="74"/>
+      <c r="H41" s="74"/>
+      <c r="I41" s="74"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="72"/>
-      <c r="B42" s="72"/>
-      <c r="C42" s="71"/>
-      <c r="D42" s="71"/>
-      <c r="E42" s="73"/>
-      <c r="F42" s="73"/>
-      <c r="G42" s="73"/>
-      <c r="H42" s="73"/>
-      <c r="I42" s="73"/>
+      <c r="A42" s="73"/>
+      <c r="B42" s="73"/>
+      <c r="C42" s="72"/>
+      <c r="D42" s="72"/>
+      <c r="E42" s="74"/>
+      <c r="F42" s="74"/>
+      <c r="G42" s="74"/>
+      <c r="H42" s="74"/>
+      <c r="I42" s="74"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="72"/>
-      <c r="B43" s="72"/>
-      <c r="C43" s="71"/>
-      <c r="D43" s="71"/>
-      <c r="E43" s="73"/>
-      <c r="F43" s="73"/>
-      <c r="G43" s="73"/>
-      <c r="H43" s="73"/>
-      <c r="I43" s="73"/>
+      <c r="A43" s="73"/>
+      <c r="B43" s="73"/>
+      <c r="C43" s="72"/>
+      <c r="D43" s="72"/>
+      <c r="E43" s="74"/>
+      <c r="F43" s="74"/>
+      <c r="G43" s="74"/>
+      <c r="H43" s="74"/>
+      <c r="I43" s="74"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="C44" s="71"/>
-      <c r="D44" s="71"/>
-      <c r="E44" s="73"/>
-      <c r="F44" s="73"/>
-      <c r="G44" s="73"/>
-      <c r="H44" s="73"/>
-      <c r="I44" s="73"/>
+      <c r="C44" s="72"/>
+      <c r="D44" s="72"/>
+      <c r="E44" s="74"/>
+      <c r="F44" s="74"/>
+      <c r="G44" s="74"/>
+      <c r="H44" s="74"/>
+      <c r="I44" s="74"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="C45" s="71"/>
-      <c r="D45" s="71"/>
-      <c r="E45" s="73"/>
-      <c r="F45" s="73"/>
-      <c r="G45" s="73"/>
-      <c r="H45" s="73"/>
-      <c r="I45" s="73"/>
+      <c r="C45" s="72"/>
+      <c r="D45" s="72"/>
+      <c r="E45" s="74"/>
+      <c r="F45" s="74"/>
+      <c r="G45" s="74"/>
+      <c r="H45" s="74"/>
+      <c r="I45" s="74"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" s="72"/>
-      <c r="B46" s="72"/>
-      <c r="C46" s="71"/>
-      <c r="D46" s="71"/>
-      <c r="E46" s="73"/>
-      <c r="F46" s="73"/>
-      <c r="G46" s="73"/>
-      <c r="H46" s="73"/>
-      <c r="I46" s="73"/>
+      <c r="A46" s="73"/>
+      <c r="B46" s="73"/>
+      <c r="C46" s="72"/>
+      <c r="D46" s="72"/>
+      <c r="E46" s="74"/>
+      <c r="F46" s="74"/>
+      <c r="G46" s="74"/>
+      <c r="H46" s="74"/>
+      <c r="I46" s="74"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
-      <c r="C47" s="71"/>
-      <c r="D47" s="71"/>
-      <c r="E47" s="73"/>
-      <c r="F47" s="73"/>
-      <c r="G47" s="73"/>
-      <c r="H47" s="73"/>
-      <c r="I47" s="73"/>
+      <c r="C47" s="72"/>
+      <c r="D47" s="72"/>
+      <c r="E47" s="74"/>
+      <c r="F47" s="74"/>
+      <c r="G47" s="74"/>
+      <c r="H47" s="74"/>
+      <c r="I47" s="74"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
-      <c r="C48" s="71"/>
-      <c r="D48" s="71"/>
-      <c r="E48" s="73"/>
-      <c r="F48" s="73"/>
-      <c r="G48" s="73"/>
-      <c r="H48" s="73"/>
-      <c r="I48" s="73"/>
+      <c r="C48" s="72"/>
+      <c r="D48" s="72"/>
+      <c r="E48" s="74"/>
+      <c r="F48" s="74"/>
+      <c r="G48" s="74"/>
+      <c r="H48" s="74"/>
+      <c r="I48" s="74"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" s="72"/>
-      <c r="B49" s="72"/>
-      <c r="C49" s="71"/>
-      <c r="D49" s="71"/>
-      <c r="E49" s="73"/>
-      <c r="F49" s="73"/>
-      <c r="G49" s="73"/>
-      <c r="H49" s="73"/>
-      <c r="I49" s="73"/>
+      <c r="A49" s="73"/>
+      <c r="B49" s="73"/>
+      <c r="C49" s="72"/>
+      <c r="D49" s="72"/>
+      <c r="E49" s="74"/>
+      <c r="F49" s="74"/>
+      <c r="G49" s="74"/>
+      <c r="H49" s="74"/>
+      <c r="I49" s="74"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="C50" s="71"/>
-      <c r="D50" s="71"/>
-      <c r="E50" s="73"/>
-      <c r="F50" s="73"/>
-      <c r="G50" s="73"/>
-      <c r="H50" s="73"/>
-      <c r="I50" s="73"/>
+      <c r="C50" s="72"/>
+      <c r="D50" s="72"/>
+      <c r="E50" s="74"/>
+      <c r="F50" s="74"/>
+      <c r="G50" s="74"/>
+      <c r="H50" s="74"/>
+      <c r="I50" s="74"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
-      <c r="C51" s="71"/>
-      <c r="D51" s="71"/>
-      <c r="E51" s="73"/>
-      <c r="F51" s="73"/>
-      <c r="G51" s="73"/>
-      <c r="H51" s="73"/>
-      <c r="I51" s="73"/>
+      <c r="C51" s="72"/>
+      <c r="D51" s="72"/>
+      <c r="E51" s="74"/>
+      <c r="F51" s="74"/>
+      <c r="G51" s="74"/>
+      <c r="H51" s="74"/>
+      <c r="I51" s="74"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
-      <c r="A52" s="72"/>
-      <c r="B52" s="72"/>
-      <c r="C52" s="71"/>
-      <c r="D52" s="71"/>
-      <c r="E52" s="73"/>
-      <c r="F52" s="73"/>
-      <c r="G52" s="73"/>
-      <c r="H52" s="73"/>
-      <c r="I52" s="73"/>
+      <c r="A52" s="73"/>
+      <c r="B52" s="73"/>
+      <c r="C52" s="72"/>
+      <c r="D52" s="72"/>
+      <c r="E52" s="74"/>
+      <c r="F52" s="74"/>
+      <c r="G52" s="74"/>
+      <c r="H52" s="74"/>
+      <c r="I52" s="74"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
-      <c r="A53" s="72"/>
-      <c r="B53" s="72"/>
-      <c r="C53" s="71"/>
-      <c r="D53" s="71"/>
-      <c r="E53" s="73"/>
-      <c r="F53" s="73"/>
-      <c r="G53" s="73"/>
-      <c r="H53" s="73"/>
-      <c r="I53" s="73"/>
+      <c r="A53" s="73"/>
+      <c r="B53" s="73"/>
+      <c r="C53" s="72"/>
+      <c r="D53" s="72"/>
+      <c r="E53" s="74"/>
+      <c r="F53" s="74"/>
+      <c r="G53" s="74"/>
+      <c r="H53" s="74"/>
+      <c r="I53" s="74"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" s="72"/>
-      <c r="B54" s="72"/>
-      <c r="C54" s="71"/>
-      <c r="D54" s="71"/>
-      <c r="E54" s="73"/>
-      <c r="F54" s="73"/>
-      <c r="G54" s="73"/>
-      <c r="H54" s="73"/>
-      <c r="I54" s="73"/>
+      <c r="A54" s="73"/>
+      <c r="B54" s="73"/>
+      <c r="C54" s="72"/>
+      <c r="D54" s="72"/>
+      <c r="E54" s="74"/>
+      <c r="F54" s="74"/>
+      <c r="G54" s="74"/>
+      <c r="H54" s="74"/>
+      <c r="I54" s="74"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
-      <c r="A55" s="72"/>
-      <c r="B55" s="72"/>
-      <c r="C55" s="71"/>
-      <c r="D55" s="71"/>
-      <c r="E55" s="73"/>
-      <c r="F55" s="73"/>
-      <c r="G55" s="73"/>
-      <c r="H55" s="73"/>
-      <c r="I55" s="73"/>
+      <c r="A55" s="73"/>
+      <c r="B55" s="73"/>
+      <c r="C55" s="72"/>
+      <c r="D55" s="72"/>
+      <c r="E55" s="74"/>
+      <c r="F55" s="74"/>
+      <c r="G55" s="74"/>
+      <c r="H55" s="74"/>
+      <c r="I55" s="74"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
-      <c r="A56" s="72"/>
-      <c r="B56" s="72"/>
-      <c r="C56" s="71"/>
-      <c r="D56" s="71"/>
-      <c r="E56" s="73"/>
-      <c r="F56" s="73"/>
-      <c r="G56" s="73"/>
-      <c r="H56" s="73"/>
-      <c r="I56" s="73"/>
+      <c r="A56" s="73"/>
+      <c r="B56" s="73"/>
+      <c r="C56" s="72"/>
+      <c r="D56" s="72"/>
+      <c r="E56" s="74"/>
+      <c r="F56" s="74"/>
+      <c r="G56" s="74"/>
+      <c r="H56" s="74"/>
+      <c r="I56" s="74"/>
     </row>
     <row r="57" ht="18.75" customHeight="1">
-      <c r="A57" s="72"/>
-      <c r="B57" s="72"/>
-      <c r="C57" s="71"/>
-      <c r="D57" s="71"/>
-      <c r="E57" s="73"/>
-      <c r="F57" s="73"/>
-      <c r="G57" s="73"/>
-      <c r="H57" s="73"/>
-      <c r="I57" s="73"/>
+      <c r="A57" s="73"/>
+      <c r="B57" s="73"/>
+      <c r="C57" s="72"/>
+      <c r="D57" s="72"/>
+      <c r="E57" s="74"/>
+      <c r="F57" s="74"/>
+      <c r="G57" s="74"/>
+      <c r="H57" s="74"/>
+      <c r="I57" s="74"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
-      <c r="A58" s="72"/>
-      <c r="B58" s="72"/>
-      <c r="C58" s="71"/>
-      <c r="D58" s="71"/>
-      <c r="E58" s="73"/>
-      <c r="F58" s="73"/>
-      <c r="G58" s="73"/>
-      <c r="H58" s="73"/>
-      <c r="I58" s="73"/>
+      <c r="A58" s="73"/>
+      <c r="B58" s="73"/>
+      <c r="C58" s="72"/>
+      <c r="D58" s="72"/>
+      <c r="E58" s="74"/>
+      <c r="F58" s="74"/>
+      <c r="G58" s="74"/>
+      <c r="H58" s="74"/>
+      <c r="I58" s="74"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
-      <c r="A59" s="72"/>
-      <c r="B59" s="72"/>
-      <c r="C59" s="71"/>
-      <c r="D59" s="71"/>
-      <c r="E59" s="73"/>
-      <c r="F59" s="73"/>
-      <c r="G59" s="73"/>
-      <c r="H59" s="73"/>
-      <c r="I59" s="73"/>
+      <c r="A59" s="73"/>
+      <c r="B59" s="73"/>
+      <c r="C59" s="72"/>
+      <c r="D59" s="72"/>
+      <c r="E59" s="74"/>
+      <c r="F59" s="74"/>
+      <c r="G59" s="74"/>
+      <c r="H59" s="74"/>
+      <c r="I59" s="74"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
-      <c r="A60" s="72"/>
-      <c r="B60" s="72"/>
-      <c r="C60" s="71"/>
-      <c r="D60" s="71"/>
-      <c r="E60" s="73"/>
-      <c r="F60" s="73"/>
-      <c r="G60" s="73"/>
-      <c r="H60" s="73"/>
-      <c r="I60" s="73"/>
+      <c r="A60" s="73"/>
+      <c r="B60" s="73"/>
+      <c r="C60" s="72"/>
+      <c r="D60" s="72"/>
+      <c r="E60" s="74"/>
+      <c r="F60" s="74"/>
+      <c r="G60" s="74"/>
+      <c r="H60" s="74"/>
+      <c r="I60" s="74"/>
     </row>
     <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" s="72"/>
-      <c r="B61" s="72"/>
-      <c r="C61" s="71"/>
-      <c r="D61" s="71"/>
-      <c r="E61" s="73"/>
-      <c r="F61" s="73"/>
-      <c r="G61" s="73"/>
-      <c r="H61" s="73"/>
-      <c r="I61" s="73"/>
+      <c r="A61" s="73"/>
+      <c r="B61" s="73"/>
+      <c r="C61" s="72"/>
+      <c r="D61" s="72"/>
+      <c r="E61" s="74"/>
+      <c r="F61" s="74"/>
+      <c r="G61" s="74"/>
+      <c r="H61" s="74"/>
+      <c r="I61" s="74"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
-      <c r="A62" s="72"/>
-      <c r="B62" s="72"/>
-      <c r="C62" s="71"/>
-      <c r="D62" s="71"/>
-      <c r="E62" s="73"/>
-      <c r="F62" s="73"/>
-      <c r="G62" s="73"/>
-      <c r="H62" s="73"/>
-      <c r="I62" s="73"/>
+      <c r="A62" s="73"/>
+      <c r="B62" s="73"/>
+      <c r="C62" s="72"/>
+      <c r="D62" s="72"/>
+      <c r="E62" s="74"/>
+      <c r="F62" s="74"/>
+      <c r="G62" s="74"/>
+      <c r="H62" s="74"/>
+      <c r="I62" s="74"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
-      <c r="A63" s="58"/>
-      <c r="B63" s="58"/>
-      <c r="C63" s="58"/>
-      <c r="D63" s="58"/>
-      <c r="E63" s="58"/>
-      <c r="F63" s="58"/>
-      <c r="G63" s="58"/>
-      <c r="H63" s="58"/>
-      <c r="I63" s="58"/>
+      <c r="A63" s="59"/>
+      <c r="B63" s="59"/>
+      <c r="C63" s="59"/>
+      <c r="D63" s="59"/>
+      <c r="E63" s="59"/>
+      <c r="F63" s="59"/>
+      <c r="G63" s="59"/>
+      <c r="H63" s="59"/>
+      <c r="I63" s="59"/>
     </row>
     <row r="64" ht="18.75" customHeight="1">
-      <c r="A64" s="58"/>
-      <c r="B64" s="58"/>
-      <c r="C64" s="58"/>
-      <c r="D64" s="58"/>
-      <c r="E64" s="58"/>
-      <c r="F64" s="58"/>
-      <c r="G64" s="58"/>
-      <c r="H64" s="58"/>
-      <c r="I64" s="58"/>
+      <c r="A64" s="59"/>
+      <c r="B64" s="59"/>
+      <c r="C64" s="59"/>
+      <c r="D64" s="59"/>
+      <c r="E64" s="59"/>
+      <c r="F64" s="59"/>
+      <c r="G64" s="59"/>
+      <c r="H64" s="59"/>
+      <c r="I64" s="59"/>
     </row>
     <row r="65" ht="18.75" customHeight="1">
-      <c r="A65" s="58"/>
-      <c r="B65" s="58"/>
-      <c r="C65" s="58"/>
-      <c r="D65" s="58"/>
-      <c r="E65" s="58"/>
-      <c r="F65" s="58"/>
-      <c r="G65" s="58"/>
-      <c r="H65" s="58"/>
-      <c r="I65" s="58"/>
+      <c r="A65" s="59"/>
+      <c r="B65" s="59"/>
+      <c r="C65" s="59"/>
+      <c r="D65" s="59"/>
+      <c r="E65" s="59"/>
+      <c r="F65" s="59"/>
+      <c r="G65" s="59"/>
+      <c r="H65" s="59"/>
+      <c r="I65" s="59"/>
     </row>
     <row r="66" ht="18.75" customHeight="1">
-      <c r="A66" s="58"/>
-      <c r="B66" s="58"/>
-      <c r="C66" s="58"/>
-      <c r="D66" s="58"/>
-      <c r="E66" s="58"/>
-      <c r="F66" s="58"/>
-      <c r="G66" s="58"/>
-      <c r="H66" s="58"/>
-      <c r="I66" s="58"/>
+      <c r="A66" s="59"/>
+      <c r="B66" s="59"/>
+      <c r="C66" s="59"/>
+      <c r="D66" s="59"/>
+      <c r="E66" s="59"/>
+      <c r="F66" s="59"/>
+      <c r="G66" s="59"/>
+      <c r="H66" s="59"/>
+      <c r="I66" s="59"/>
     </row>
     <row r="67" ht="18.75" customHeight="1">
-      <c r="A67" s="58"/>
-      <c r="B67" s="58"/>
-      <c r="C67" s="58"/>
-      <c r="D67" s="58"/>
-      <c r="E67" s="58"/>
-      <c r="F67" s="58"/>
-      <c r="G67" s="58"/>
-      <c r="H67" s="58"/>
-      <c r="I67" s="58"/>
+      <c r="A67" s="59"/>
+      <c r="B67" s="59"/>
+      <c r="C67" s="59"/>
+      <c r="D67" s="59"/>
+      <c r="E67" s="59"/>
+      <c r="F67" s="59"/>
+      <c r="G67" s="59"/>
+      <c r="H67" s="59"/>
+      <c r="I67" s="59"/>
     </row>
     <row r="68" ht="18.75" customHeight="1">
-      <c r="A68" s="58"/>
-      <c r="B68" s="58"/>
-      <c r="C68" s="58"/>
-      <c r="D68" s="58"/>
-      <c r="E68" s="58"/>
-      <c r="F68" s="58"/>
-      <c r="G68" s="58"/>
-      <c r="H68" s="58"/>
-      <c r="I68" s="58"/>
+      <c r="A68" s="59"/>
+      <c r="B68" s="59"/>
+      <c r="C68" s="59"/>
+      <c r="D68" s="59"/>
+      <c r="E68" s="59"/>
+      <c r="F68" s="59"/>
+      <c r="G68" s="59"/>
+      <c r="H68" s="59"/>
+      <c r="I68" s="59"/>
     </row>
     <row r="69" ht="18.75" customHeight="1">
-      <c r="A69" s="58"/>
-      <c r="B69" s="58"/>
-      <c r="C69" s="58"/>
-      <c r="D69" s="58"/>
-      <c r="E69" s="58"/>
-      <c r="F69" s="58"/>
-      <c r="G69" s="58"/>
-      <c r="H69" s="58"/>
-      <c r="I69" s="58"/>
+      <c r="A69" s="59"/>
+      <c r="B69" s="59"/>
+      <c r="C69" s="59"/>
+      <c r="D69" s="59"/>
+      <c r="E69" s="59"/>
+      <c r="F69" s="59"/>
+      <c r="G69" s="59"/>
+      <c r="H69" s="59"/>
+      <c r="I69" s="59"/>
     </row>
     <row r="70" ht="18.75" customHeight="1">
-      <c r="A70" s="58"/>
-      <c r="B70" s="58"/>
-      <c r="C70" s="58"/>
-      <c r="D70" s="58"/>
-      <c r="E70" s="58"/>
-      <c r="F70" s="58"/>
-      <c r="G70" s="58"/>
-      <c r="H70" s="58"/>
-      <c r="I70" s="58"/>
+      <c r="A70" s="59"/>
+      <c r="B70" s="59"/>
+      <c r="C70" s="59"/>
+      <c r="D70" s="59"/>
+      <c r="E70" s="59"/>
+      <c r="F70" s="59"/>
+      <c r="G70" s="59"/>
+      <c r="H70" s="59"/>
+      <c r="I70" s="59"/>
     </row>
     <row r="71" ht="18.75" customHeight="1">
-      <c r="A71" s="58"/>
-      <c r="B71" s="58"/>
-      <c r="C71" s="58"/>
-      <c r="D71" s="58"/>
-      <c r="E71" s="58"/>
-      <c r="F71" s="58"/>
-      <c r="G71" s="58"/>
-      <c r="H71" s="58"/>
-      <c r="I71" s="58"/>
+      <c r="A71" s="59"/>
+      <c r="B71" s="59"/>
+      <c r="C71" s="59"/>
+      <c r="D71" s="59"/>
+      <c r="E71" s="59"/>
+      <c r="F71" s="59"/>
+      <c r="G71" s="59"/>
+      <c r="H71" s="59"/>
+      <c r="I71" s="59"/>
     </row>
     <row r="72" ht="18.75" customHeight="1">
-      <c r="A72" s="58"/>
-      <c r="B72" s="58"/>
-      <c r="C72" s="58"/>
-      <c r="D72" s="58"/>
-      <c r="E72" s="58"/>
-      <c r="F72" s="58"/>
-      <c r="G72" s="58"/>
-      <c r="H72" s="58"/>
-      <c r="I72" s="58"/>
+      <c r="A72" s="59"/>
+      <c r="B72" s="59"/>
+      <c r="C72" s="59"/>
+      <c r="D72" s="59"/>
+      <c r="E72" s="59"/>
+      <c r="F72" s="59"/>
+      <c r="G72" s="59"/>
+      <c r="H72" s="59"/>
+      <c r="I72" s="59"/>
     </row>
     <row r="73" ht="18.75" customHeight="1">
-      <c r="A73" s="58"/>
-      <c r="B73" s="58"/>
-      <c r="C73" s="58"/>
-      <c r="D73" s="58"/>
-      <c r="E73" s="58"/>
-      <c r="F73" s="58"/>
-      <c r="G73" s="58"/>
-      <c r="H73" s="58"/>
-      <c r="I73" s="58"/>
+      <c r="A73" s="59"/>
+      <c r="B73" s="59"/>
+      <c r="C73" s="59"/>
+      <c r="D73" s="59"/>
+      <c r="E73" s="59"/>
+      <c r="F73" s="59"/>
+      <c r="G73" s="59"/>
+      <c r="H73" s="59"/>
+      <c r="I73" s="59"/>
     </row>
     <row r="74" ht="18.75" customHeight="1">
-      <c r="A74" s="58"/>
-      <c r="B74" s="58"/>
-      <c r="C74" s="58"/>
-      <c r="D74" s="58"/>
-      <c r="E74" s="58"/>
-      <c r="F74" s="58"/>
-      <c r="G74" s="58"/>
-      <c r="H74" s="58"/>
-      <c r="I74" s="58"/>
+      <c r="A74" s="59"/>
+      <c r="B74" s="59"/>
+      <c r="C74" s="59"/>
+      <c r="D74" s="59"/>
+      <c r="E74" s="59"/>
+      <c r="F74" s="59"/>
+      <c r="G74" s="59"/>
+      <c r="H74" s="59"/>
+      <c r="I74" s="59"/>
     </row>
     <row r="75" ht="18.75" customHeight="1">
-      <c r="A75" s="58"/>
-      <c r="B75" s="58"/>
-      <c r="C75" s="58"/>
-      <c r="D75" s="58"/>
-      <c r="E75" s="58"/>
-      <c r="F75" s="58"/>
-      <c r="G75" s="58"/>
-      <c r="H75" s="58"/>
-      <c r="I75" s="58"/>
+      <c r="A75" s="59"/>
+      <c r="B75" s="59"/>
+      <c r="C75" s="59"/>
+      <c r="D75" s="59"/>
+      <c r="E75" s="59"/>
+      <c r="F75" s="59"/>
+      <c r="G75" s="59"/>
+      <c r="H75" s="59"/>
+      <c r="I75" s="59"/>
     </row>
     <row r="76" ht="18.75" customHeight="1">
-      <c r="A76" s="58"/>
-      <c r="B76" s="58"/>
-      <c r="C76" s="58"/>
-      <c r="D76" s="58"/>
-      <c r="E76" s="58"/>
-      <c r="F76" s="58"/>
-      <c r="G76" s="58"/>
-      <c r="H76" s="58"/>
-      <c r="I76" s="58"/>
+      <c r="A76" s="59"/>
+      <c r="B76" s="59"/>
+      <c r="C76" s="59"/>
+      <c r="D76" s="59"/>
+      <c r="E76" s="59"/>
+      <c r="F76" s="59"/>
+      <c r="G76" s="59"/>
+      <c r="H76" s="59"/>
+      <c r="I76" s="59"/>
     </row>
     <row r="77" ht="18.75" customHeight="1">
-      <c r="A77" s="58"/>
-      <c r="B77" s="58"/>
-      <c r="C77" s="58"/>
-      <c r="D77" s="58"/>
-      <c r="E77" s="58"/>
-      <c r="F77" s="58"/>
-      <c r="G77" s="58"/>
-      <c r="H77" s="58"/>
-      <c r="I77" s="58"/>
+      <c r="A77" s="59"/>
+      <c r="B77" s="59"/>
+      <c r="C77" s="59"/>
+      <c r="D77" s="59"/>
+      <c r="E77" s="59"/>
+      <c r="F77" s="59"/>
+      <c r="G77" s="59"/>
+      <c r="H77" s="59"/>
+      <c r="I77" s="59"/>
     </row>
     <row r="78" ht="18.75" customHeight="1">
-      <c r="A78" s="58"/>
-      <c r="B78" s="58"/>
-      <c r="C78" s="58"/>
-      <c r="D78" s="58"/>
-      <c r="E78" s="58"/>
-      <c r="F78" s="58"/>
-      <c r="G78" s="58"/>
-      <c r="H78" s="58"/>
-      <c r="I78" s="58"/>
+      <c r="A78" s="59"/>
+      <c r="B78" s="59"/>
+      <c r="C78" s="59"/>
+      <c r="D78" s="59"/>
+      <c r="E78" s="59"/>
+      <c r="F78" s="59"/>
+      <c r="G78" s="59"/>
+      <c r="H78" s="59"/>
+      <c r="I78" s="59"/>
     </row>
     <row r="79" ht="18.75" customHeight="1">
-      <c r="A79" s="58"/>
-      <c r="B79" s="58"/>
-      <c r="C79" s="58"/>
-      <c r="D79" s="58"/>
-      <c r="E79" s="58"/>
-      <c r="F79" s="58"/>
-      <c r="G79" s="58"/>
-      <c r="H79" s="58"/>
-      <c r="I79" s="58"/>
+      <c r="A79" s="59"/>
+      <c r="B79" s="59"/>
+      <c r="C79" s="59"/>
+      <c r="D79" s="59"/>
+      <c r="E79" s="59"/>
+      <c r="F79" s="59"/>
+      <c r="G79" s="59"/>
+      <c r="H79" s="59"/>
+      <c r="I79" s="59"/>
     </row>
     <row r="80" ht="18.75" customHeight="1">
-      <c r="A80" s="58"/>
-      <c r="B80" s="58"/>
-      <c r="C80" s="58"/>
-      <c r="D80" s="58"/>
-      <c r="E80" s="58"/>
-      <c r="F80" s="58"/>
-      <c r="G80" s="58"/>
-      <c r="H80" s="58"/>
-      <c r="I80" s="58"/>
+      <c r="A80" s="59"/>
+      <c r="B80" s="59"/>
+      <c r="C80" s="59"/>
+      <c r="D80" s="59"/>
+      <c r="E80" s="59"/>
+      <c r="F80" s="59"/>
+      <c r="G80" s="59"/>
+      <c r="H80" s="59"/>
+      <c r="I80" s="59"/>
     </row>
     <row r="81" ht="18.75" customHeight="1">
-      <c r="A81" s="58"/>
-      <c r="B81" s="58"/>
-      <c r="C81" s="58"/>
-      <c r="D81" s="58"/>
-      <c r="E81" s="58"/>
-      <c r="F81" s="58"/>
-      <c r="G81" s="58"/>
-      <c r="H81" s="58"/>
-      <c r="I81" s="58"/>
+      <c r="A81" s="59"/>
+      <c r="B81" s="59"/>
+      <c r="C81" s="59"/>
+      <c r="D81" s="59"/>
+      <c r="E81" s="59"/>
+      <c r="F81" s="59"/>
+      <c r="G81" s="59"/>
+      <c r="H81" s="59"/>
+      <c r="I81" s="59"/>
     </row>
     <row r="82" ht="18.75" customHeight="1">
-      <c r="A82" s="58"/>
-      <c r="B82" s="58"/>
-      <c r="C82" s="58"/>
-      <c r="D82" s="58"/>
-      <c r="E82" s="58"/>
-      <c r="F82" s="58"/>
-      <c r="G82" s="58"/>
-      <c r="H82" s="58"/>
-      <c r="I82" s="58"/>
+      <c r="A82" s="59"/>
+      <c r="B82" s="59"/>
+      <c r="C82" s="59"/>
+      <c r="D82" s="59"/>
+      <c r="E82" s="59"/>
+      <c r="F82" s="59"/>
+      <c r="G82" s="59"/>
+      <c r="H82" s="59"/>
+      <c r="I82" s="59"/>
     </row>
     <row r="83" ht="18.75" customHeight="1">
-      <c r="A83" s="58"/>
-      <c r="B83" s="58"/>
-      <c r="C83" s="58"/>
-      <c r="D83" s="58"/>
-      <c r="E83" s="58"/>
-      <c r="F83" s="58"/>
-      <c r="G83" s="58"/>
-      <c r="H83" s="58"/>
-      <c r="I83" s="58"/>
+      <c r="A83" s="59"/>
+      <c r="B83" s="59"/>
+      <c r="C83" s="59"/>
+      <c r="D83" s="59"/>
+      <c r="E83" s="59"/>
+      <c r="F83" s="59"/>
+      <c r="G83" s="59"/>
+      <c r="H83" s="59"/>
+      <c r="I83" s="59"/>
     </row>
     <row r="84" ht="18.75" customHeight="1">
-      <c r="A84" s="58"/>
-      <c r="B84" s="58"/>
-      <c r="C84" s="58"/>
-      <c r="D84" s="58"/>
-      <c r="E84" s="58"/>
-      <c r="F84" s="58"/>
-      <c r="G84" s="58"/>
-      <c r="H84" s="58"/>
-      <c r="I84" s="58"/>
+      <c r="A84" s="59"/>
+      <c r="B84" s="59"/>
+      <c r="C84" s="59"/>
+      <c r="D84" s="59"/>
+      <c r="E84" s="59"/>
+      <c r="F84" s="59"/>
+      <c r="G84" s="59"/>
+      <c r="H84" s="59"/>
+      <c r="I84" s="59"/>
     </row>
     <row r="85" ht="18.75" customHeight="1">
-      <c r="A85" s="58"/>
-      <c r="B85" s="58"/>
-      <c r="C85" s="58"/>
-      <c r="D85" s="58"/>
-      <c r="E85" s="58"/>
-      <c r="F85" s="58"/>
-      <c r="G85" s="58"/>
-      <c r="H85" s="58"/>
-      <c r="I85" s="58"/>
+      <c r="A85" s="59"/>
+      <c r="B85" s="59"/>
+      <c r="C85" s="59"/>
+      <c r="D85" s="59"/>
+      <c r="E85" s="59"/>
+      <c r="F85" s="59"/>
+      <c r="G85" s="59"/>
+      <c r="H85" s="59"/>
+      <c r="I85" s="59"/>
     </row>
     <row r="86" ht="18.75" customHeight="1">
-      <c r="A86" s="58"/>
-      <c r="B86" s="58"/>
-      <c r="C86" s="58"/>
-      <c r="D86" s="58"/>
-      <c r="E86" s="58"/>
-      <c r="F86" s="58"/>
-      <c r="G86" s="58"/>
-      <c r="H86" s="58"/>
-      <c r="I86" s="58"/>
+      <c r="A86" s="59"/>
+      <c r="B86" s="59"/>
+      <c r="C86" s="59"/>
+      <c r="D86" s="59"/>
+      <c r="E86" s="59"/>
+      <c r="F86" s="59"/>
+      <c r="G86" s="59"/>
+      <c r="H86" s="59"/>
+      <c r="I86" s="59"/>
     </row>
     <row r="87" ht="18.75" customHeight="1">
-      <c r="A87" s="58"/>
-      <c r="B87" s="58"/>
-      <c r="C87" s="58"/>
-      <c r="D87" s="58"/>
-      <c r="E87" s="58"/>
-      <c r="F87" s="58"/>
-      <c r="G87" s="58"/>
-      <c r="H87" s="58"/>
-      <c r="I87" s="58"/>
+      <c r="A87" s="59"/>
+      <c r="B87" s="59"/>
+      <c r="C87" s="59"/>
+      <c r="D87" s="59"/>
+      <c r="E87" s="59"/>
+      <c r="F87" s="59"/>
+      <c r="G87" s="59"/>
+      <c r="H87" s="59"/>
+      <c r="I87" s="59"/>
     </row>
     <row r="88" ht="18.75" customHeight="1">
-      <c r="A88" s="58"/>
-      <c r="B88" s="58"/>
-      <c r="C88" s="58"/>
-      <c r="D88" s="58"/>
-      <c r="E88" s="58"/>
-      <c r="F88" s="58"/>
-      <c r="G88" s="58"/>
-      <c r="H88" s="58"/>
-      <c r="I88" s="58"/>
+      <c r="A88" s="59"/>
+      <c r="B88" s="59"/>
+      <c r="C88" s="59"/>
+      <c r="D88" s="59"/>
+      <c r="E88" s="59"/>
+      <c r="F88" s="59"/>
+      <c r="G88" s="59"/>
+      <c r="H88" s="59"/>
+      <c r="I88" s="59"/>
     </row>
     <row r="89" ht="18.75" customHeight="1">
-      <c r="A89" s="58"/>
-      <c r="B89" s="58"/>
-      <c r="C89" s="58"/>
-      <c r="D89" s="58"/>
-      <c r="E89" s="58"/>
-      <c r="F89" s="58"/>
-      <c r="G89" s="58"/>
-      <c r="H89" s="58"/>
-      <c r="I89" s="58"/>
+      <c r="A89" s="59"/>
+      <c r="B89" s="59"/>
+      <c r="C89" s="59"/>
+      <c r="D89" s="59"/>
+      <c r="E89" s="59"/>
+      <c r="F89" s="59"/>
+      <c r="G89" s="59"/>
+      <c r="H89" s="59"/>
+      <c r="I89" s="59"/>
     </row>
     <row r="90" ht="18.75" customHeight="1">
-      <c r="A90" s="58"/>
-      <c r="B90" s="58"/>
-      <c r="C90" s="58"/>
-      <c r="D90" s="58"/>
-      <c r="E90" s="58"/>
-      <c r="F90" s="58"/>
-      <c r="G90" s="58"/>
-      <c r="H90" s="58"/>
-      <c r="I90" s="58"/>
+      <c r="A90" s="59"/>
+      <c r="B90" s="59"/>
+      <c r="C90" s="59"/>
+      <c r="D90" s="59"/>
+      <c r="E90" s="59"/>
+      <c r="F90" s="59"/>
+      <c r="G90" s="59"/>
+      <c r="H90" s="59"/>
+      <c r="I90" s="59"/>
     </row>
     <row r="91" ht="18.75" customHeight="1">
-      <c r="A91" s="58"/>
-      <c r="B91" s="58"/>
-      <c r="C91" s="58"/>
-      <c r="D91" s="58"/>
-      <c r="E91" s="58"/>
-      <c r="F91" s="58"/>
-      <c r="G91" s="58"/>
-      <c r="H91" s="58"/>
-      <c r="I91" s="58"/>
+      <c r="A91" s="59"/>
+      <c r="B91" s="59"/>
+      <c r="C91" s="59"/>
+      <c r="D91" s="59"/>
+      <c r="E91" s="59"/>
+      <c r="F91" s="59"/>
+      <c r="G91" s="59"/>
+      <c r="H91" s="59"/>
+      <c r="I91" s="59"/>
     </row>
     <row r="92" ht="18.75" customHeight="1">
-      <c r="A92" s="58"/>
-      <c r="B92" s="58"/>
-      <c r="C92" s="58"/>
-      <c r="D92" s="58"/>
-      <c r="E92" s="58"/>
-      <c r="F92" s="58"/>
-      <c r="G92" s="58"/>
-      <c r="H92" s="58"/>
-      <c r="I92" s="58"/>
+      <c r="A92" s="59"/>
+      <c r="B92" s="59"/>
+      <c r="C92" s="59"/>
+      <c r="D92" s="59"/>
+      <c r="E92" s="59"/>
+      <c r="F92" s="59"/>
+      <c r="G92" s="59"/>
+      <c r="H92" s="59"/>
+      <c r="I92" s="59"/>
     </row>
     <row r="93" ht="18.75" customHeight="1">
-      <c r="A93" s="58"/>
-      <c r="B93" s="58"/>
-      <c r="C93" s="58"/>
-      <c r="D93" s="58"/>
-      <c r="E93" s="58"/>
-      <c r="F93" s="58"/>
-      <c r="G93" s="58"/>
-      <c r="H93" s="58"/>
-      <c r="I93" s="58"/>
+      <c r="A93" s="59"/>
+      <c r="B93" s="59"/>
+      <c r="C93" s="59"/>
+      <c r="D93" s="59"/>
+      <c r="E93" s="59"/>
+      <c r="F93" s="59"/>
+      <c r="G93" s="59"/>
+      <c r="H93" s="59"/>
+      <c r="I93" s="59"/>
     </row>
     <row r="94" ht="18.75" customHeight="1">
-      <c r="A94" s="58"/>
-      <c r="B94" s="58"/>
-      <c r="C94" s="58"/>
-      <c r="D94" s="58"/>
-      <c r="E94" s="58"/>
-      <c r="F94" s="58"/>
-      <c r="G94" s="58"/>
-      <c r="H94" s="58"/>
-      <c r="I94" s="58"/>
+      <c r="A94" s="59"/>
+      <c r="B94" s="59"/>
+      <c r="C94" s="59"/>
+      <c r="D94" s="59"/>
+      <c r="E94" s="59"/>
+      <c r="F94" s="59"/>
+      <c r="G94" s="59"/>
+      <c r="H94" s="59"/>
+      <c r="I94" s="59"/>
     </row>
     <row r="95" ht="18.75" customHeight="1">
-      <c r="A95" s="58"/>
-      <c r="B95" s="58"/>
-      <c r="C95" s="58"/>
-      <c r="D95" s="58"/>
-      <c r="E95" s="58"/>
-      <c r="F95" s="58"/>
-      <c r="G95" s="58"/>
-      <c r="H95" s="58"/>
-      <c r="I95" s="58"/>
+      <c r="A95" s="59"/>
+      <c r="B95" s="59"/>
+      <c r="C95" s="59"/>
+      <c r="D95" s="59"/>
+      <c r="E95" s="59"/>
+      <c r="F95" s="59"/>
+      <c r="G95" s="59"/>
+      <c r="H95" s="59"/>
+      <c r="I95" s="59"/>
     </row>
     <row r="96" ht="18.75" customHeight="1">
-      <c r="A96" s="58"/>
-      <c r="B96" s="58"/>
-      <c r="C96" s="58"/>
-      <c r="D96" s="58"/>
-      <c r="E96" s="58"/>
-      <c r="F96" s="58"/>
-      <c r="G96" s="58"/>
-      <c r="H96" s="58"/>
-      <c r="I96" s="58"/>
+      <c r="A96" s="59"/>
+      <c r="B96" s="59"/>
+      <c r="C96" s="59"/>
+      <c r="D96" s="59"/>
+      <c r="E96" s="59"/>
+      <c r="F96" s="59"/>
+      <c r="G96" s="59"/>
+      <c r="H96" s="59"/>
+      <c r="I96" s="59"/>
     </row>
     <row r="97" ht="18.75" customHeight="1">
-      <c r="A97" s="58"/>
-      <c r="B97" s="58"/>
-      <c r="C97" s="58"/>
-      <c r="D97" s="58"/>
-      <c r="E97" s="58"/>
-      <c r="F97" s="58"/>
-      <c r="G97" s="58"/>
-      <c r="H97" s="58"/>
-      <c r="I97" s="58"/>
+      <c r="A97" s="59"/>
+      <c r="B97" s="59"/>
+      <c r="C97" s="59"/>
+      <c r="D97" s="59"/>
+      <c r="E97" s="59"/>
+      <c r="F97" s="59"/>
+      <c r="G97" s="59"/>
+      <c r="H97" s="59"/>
+      <c r="I97" s="59"/>
     </row>
     <row r="98" ht="18.75" customHeight="1">
-      <c r="A98" s="58"/>
-      <c r="B98" s="58"/>
-      <c r="C98" s="58"/>
-      <c r="D98" s="58"/>
-      <c r="E98" s="58"/>
-      <c r="F98" s="58"/>
-      <c r="G98" s="58"/>
-      <c r="H98" s="58"/>
-      <c r="I98" s="58"/>
+      <c r="A98" s="59"/>
+      <c r="B98" s="59"/>
+      <c r="C98" s="59"/>
+      <c r="D98" s="59"/>
+      <c r="E98" s="59"/>
+      <c r="F98" s="59"/>
+      <c r="G98" s="59"/>
+      <c r="H98" s="59"/>
+      <c r="I98" s="59"/>
     </row>
     <row r="99" ht="18.75" customHeight="1">
-      <c r="A99" s="58"/>
-      <c r="B99" s="58"/>
-      <c r="C99" s="58"/>
-      <c r="D99" s="58"/>
-      <c r="E99" s="58"/>
-      <c r="F99" s="58"/>
-      <c r="G99" s="58"/>
-      <c r="H99" s="58"/>
-      <c r="I99" s="58"/>
+      <c r="A99" s="59"/>
+      <c r="B99" s="59"/>
+      <c r="C99" s="59"/>
+      <c r="D99" s="59"/>
+      <c r="E99" s="59"/>
+      <c r="F99" s="59"/>
+      <c r="G99" s="59"/>
+      <c r="H99" s="59"/>
+      <c r="I99" s="59"/>
     </row>
     <row r="100" ht="18.75" customHeight="1">
-      <c r="A100" s="58"/>
-      <c r="B100" s="58"/>
-      <c r="C100" s="58"/>
-      <c r="D100" s="58"/>
-      <c r="E100" s="58"/>
-      <c r="F100" s="58"/>
-      <c r="G100" s="58"/>
-      <c r="H100" s="58"/>
-      <c r="I100" s="58"/>
+      <c r="A100" s="59"/>
+      <c r="B100" s="59"/>
+      <c r="C100" s="59"/>
+      <c r="D100" s="59"/>
+      <c r="E100" s="59"/>
+      <c r="F100" s="59"/>
+      <c r="G100" s="59"/>
+      <c r="H100" s="59"/>
+      <c r="I100" s="59"/>
     </row>
   </sheetData>
   <mergeCells count="4">

--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -3273,13 +3273,13 @@
     <t>present</t>
   </si>
   <si>
-    <t>-ø</t>
+    <t>-er</t>
   </si>
   <si>
     <t>-inde</t>
   </si>
   <si>
-    <t>solg</t>
+    <t>solger</t>
   </si>
   <si>
     <t>solginde</t>
@@ -3315,7 +3315,7 @@
     <t>råde</t>
   </si>
   <si>
-    <t>hæst</t>
+    <t>hæster</t>
   </si>
   <si>
     <t>hæstinde</t>
@@ -3336,7 +3336,7 @@
     <t>hesdde</t>
   </si>
   <si>
-    <t>hestent</t>
+    <t>hestend</t>
   </si>
   <si>
     <t>rødde</t>
@@ -3354,7 +3354,7 @@
     <t>dute</t>
   </si>
   <si>
-    <t>dut</t>
+    <t>duter</t>
   </si>
   <si>
     <t>dutinde</t>
@@ -3363,10 +3363,10 @@
     <t>-ede</t>
   </si>
   <si>
-    <t>dutede</t>
-  </si>
-  <si>
-    <t>dutend</t>
+    <t>døtede</t>
+  </si>
+  <si>
+    <t>døtend</t>
   </si>
   <si>
     <t>plåk (no ending)</t>

--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -405,7 +405,7 @@
     <t>å</t>
   </si>
   <si>
-    <t>at</t>
+    <t>at; infinitive marker (don't use in the first verb of imperative sentences or questions)</t>
   </si>
   <si>
     <t>A</t>

--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -9,14 +9,14 @@
     <sheet state="visible" name="Pronunciation" sheetId="4" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$489</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">Lexicon!$A$1:$C$492</definedName>
   </definedNames>
   <calcPr/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1776" uniqueCount="1207">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1804" uniqueCount="1220">
   <si>
     <t>Word</t>
   </si>
@@ -3015,7 +3015,7 @@
     <t>verb negator prefix</t>
   </si>
   <si>
-    <t>æg</t>
+    <t>veldig</t>
   </si>
   <si>
     <t>very, or really</t>
@@ -3246,6 +3246,24 @@
     <t>zombie</t>
   </si>
   <si>
+    <t>juren</t>
+  </si>
+  <si>
+    <t>to rain</t>
+  </si>
+  <si>
+    <t>hagl</t>
+  </si>
+  <si>
+    <t>hail</t>
+  </si>
+  <si>
+    <t>hagl-sterm</t>
+  </si>
+  <si>
+    <t>hailstorm</t>
+  </si>
+  <si>
     <t>normal verbs</t>
   </si>
   <si>
@@ -3369,9 +3387,6 @@
     <t>døtend</t>
   </si>
   <si>
-    <t>plåk (no ending)</t>
-  </si>
-  <si>
     <t>singular</t>
   </si>
   <si>
@@ -3387,28 +3402,49 @@
     <t>non-genitive</t>
   </si>
   <si>
-    <t>plåk-en</t>
-  </si>
-  <si>
-    <t>plåk-er</t>
-  </si>
-  <si>
-    <t>plåk-ene</t>
+    <t>toll-en</t>
+  </si>
+  <si>
+    <t>toll-er</t>
+  </si>
+  <si>
+    <t>toll-ene</t>
   </si>
   <si>
     <t>genitive</t>
   </si>
   <si>
-    <t>plåk-s</t>
-  </si>
-  <si>
-    <t>plåk-ens</t>
-  </si>
-  <si>
-    <t>plåk-ers</t>
-  </si>
-  <si>
-    <t>plåk-enes</t>
+    <t>tolle-s</t>
+  </si>
+  <si>
+    <t>toll-ens</t>
+  </si>
+  <si>
+    <t>toll-ers</t>
+  </si>
+  <si>
+    <t>toll-enes</t>
+  </si>
+  <si>
+    <t>hagl (-gl, -rd, -ll, -sk endings)</t>
+  </si>
+  <si>
+    <t>hagl-et</t>
+  </si>
+  <si>
+    <t>hagl-er</t>
+  </si>
+  <si>
+    <t>hagl-ene</t>
+  </si>
+  <si>
+    <t>hagl-ets</t>
+  </si>
+  <si>
+    <t>hagl-ers</t>
+  </si>
+  <si>
+    <t>hagl-enes</t>
   </si>
   <si>
     <t>I-shift chart</t>
@@ -3580,6 +3616,9 @@
   </si>
   <si>
     <t>/l/</t>
+  </si>
+  <si>
+    <t>-l</t>
   </si>
   <si>
     <t>m</t>
@@ -3902,10 +3941,10 @@
         <color rgb="FF284E3F"/>
       </left>
       <right style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3913,13 +3952,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </right>
       <top style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3927,13 +3966,13 @@
     </border>
     <border>
       <left style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </left>
       <right style="thin">
         <color rgb="FF284E3F"/>
       </right>
       <top style="thin">
-        <color rgb="FFF6F8F9"/>
+        <color rgb="FFFFFFFF"/>
       </top>
       <bottom style="thin">
         <color rgb="FF284E3F"/>
@@ -3943,7 +3982,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="75">
+  <cellXfs count="74">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -4144,9 +4183,6 @@
     <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
-    </xf>
     <xf borderId="0" fillId="6" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -4235,8 +4271,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C489" displayName="Table1" name="Table1" id="1">
-  <autoFilter ref="$A$1:$C$489"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" ref="A1:C492" displayName="Table1" name="Table1" id="1">
+  <autoFilter ref="$A$1:$C$492"/>
   <tableColumns count="3">
     <tableColumn name="Word" id="1"/>
     <tableColumn name="Type" id="2"/>
@@ -4566,7 +4602,7 @@
         <v>25</v>
       </c>
       <c r="H4" s="21" t="str">
-        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C489, REGEXMATCH(C2:C489, I3)), 2, TRUE)"),"ibyrten")</f>
+        <f>IFERROR(__xludf.DUMMYFUNCTION("SORT(FILTER(A2:C492, REGEXMATCH(C2:C492, I3)), 2, TRUE)"),"ibyrten")</f>
         <v>ibyrten</v>
       </c>
       <c r="I4" s="4" t="str">
@@ -13946,13 +13982,13 @@
       <c r="K488" s="9"/>
     </row>
     <row r="489" ht="15.75" customHeight="1">
-      <c r="A489" s="54" t="s">
+      <c r="A489" s="15" t="s">
         <v>1074</v>
       </c>
-      <c r="B489" s="55" t="s">
-        <v>9</v>
-      </c>
-      <c r="C489" s="56" t="s">
+      <c r="B489" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C489" s="24" t="s">
         <v>1075</v>
       </c>
       <c r="D489" s="4"/>
@@ -13964,9 +14000,66 @@
       <c r="J489" s="9"/>
       <c r="K489" s="9"/>
     </row>
+    <row r="490" ht="15.75" customHeight="1">
+      <c r="A490" s="10" t="s">
+        <v>1076</v>
+      </c>
+      <c r="B490" s="11" t="s">
+        <v>48</v>
+      </c>
+      <c r="C490" s="12" t="s">
+        <v>1077</v>
+      </c>
+      <c r="D490" s="4"/>
+      <c r="E490" s="4"/>
+      <c r="F490" s="4"/>
+      <c r="G490" s="4"/>
+      <c r="H490" s="4"/>
+      <c r="I490" s="4"/>
+      <c r="J490" s="9"/>
+      <c r="K490" s="9"/>
+    </row>
+    <row r="491" ht="15.75" customHeight="1">
+      <c r="A491" s="15" t="s">
+        <v>1078</v>
+      </c>
+      <c r="B491" s="16" t="s">
+        <v>9</v>
+      </c>
+      <c r="C491" s="24" t="s">
+        <v>1079</v>
+      </c>
+      <c r="D491" s="4"/>
+      <c r="E491" s="4"/>
+      <c r="F491" s="4"/>
+      <c r="G491" s="4"/>
+      <c r="H491" s="4"/>
+      <c r="I491" s="4"/>
+      <c r="J491" s="9"/>
+      <c r="K491" s="9"/>
+    </row>
+    <row r="492" ht="15.75" customHeight="1">
+      <c r="A492" s="54" t="s">
+        <v>1080</v>
+      </c>
+      <c r="B492" s="55" t="s">
+        <v>9</v>
+      </c>
+      <c r="C492" s="56" t="s">
+        <v>1081</v>
+      </c>
+      <c r="D492" s="4"/>
+      <c r="E492" s="4"/>
+      <c r="F492" s="4"/>
+      <c r="G492" s="4"/>
+      <c r="H492" s="4"/>
+      <c r="I492" s="4"/>
+      <c r="J492" s="9"/>
+      <c r="K492" s="9"/>
+    </row>
   </sheetData>
   <dataValidations>
-    <dataValidation type="list" allowBlank="1" sqref="B2:B489">
+    <dataValidation type="list" allowBlank="1" sqref="B2:B492">
       <formula1>"adjective,adjective-adverb,adverb,auxiliary,conjunction,interjection,noun,numeral,preposition,pronoun,verb,prefix,suffix"</formula1>
     </dataValidation>
   </dataValidations>
@@ -13992,10 +14085,10 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>1076</v>
+        <v>1082</v>
       </c>
       <c r="D1" s="57" t="s">
-        <v>1077</v>
+        <v>1083</v>
       </c>
       <c r="G1" s="58"/>
       <c r="H1" s="58"/>
@@ -14003,13 +14096,13 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="B2" s="59" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="D2" s="57" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="E2" s="59" t="s">
         <v>917</v>
@@ -14023,13 +14116,13 @@
         <v>113</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="D3" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>1081</v>
+        <v>1087</v>
       </c>
       <c r="G3" s="58"/>
       <c r="H3" s="58"/>
@@ -14038,17 +14131,17 @@
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="60"/>
       <c r="B4" s="61" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="C4" s="61" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="D4" s="60"/>
       <c r="E4" s="61" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="F4" s="61" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="G4" s="58"/>
       <c r="H4" s="58"/>
@@ -14056,22 +14149,22 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="57" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C5" s="59" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="D5" s="57" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>1087</v>
+        <v>1093</v>
       </c>
       <c r="F5" s="59" t="s">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="G5" s="58"/>
       <c r="H5" s="58"/>
@@ -14079,22 +14172,22 @@
     </row>
     <row r="6" ht="18.75" customHeight="1">
       <c r="A6" s="57" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1090</v>
+        <v>1096</v>
       </c>
       <c r="C6" s="59" t="s">
-        <v>1091</v>
+        <v>1097</v>
       </c>
       <c r="D6" s="57" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1092</v>
+        <v>1098</v>
       </c>
       <c r="F6" s="59" t="s">
-        <v>1093</v>
+        <v>1099</v>
       </c>
       <c r="G6" s="58"/>
       <c r="H6" s="58"/>
@@ -14102,30 +14195,30 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="57" t="s">
-        <v>1094</v>
+        <v>1100</v>
       </c>
       <c r="D7" s="57" t="s">
-        <v>1095</v>
+        <v>1101</v>
       </c>
       <c r="G7" s="57" t="s">
-        <v>1096</v>
+        <v>1102</v>
       </c>
     </row>
     <row r="8" ht="18.75" customHeight="1">
       <c r="A8" s="57" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="B8" s="59" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="D8" s="57" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="E8" s="59" t="s">
         <v>804</v>
       </c>
       <c r="G8" s="57" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="H8" s="59" t="s">
         <v>900</v>
@@ -14136,108 +14229,108 @@
         <v>113</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="D9" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E9" s="59" t="s">
-        <v>1097</v>
+        <v>1103</v>
       </c>
       <c r="G9" s="57" t="s">
         <v>113</v>
       </c>
       <c r="H9" s="59" t="s">
-        <v>1098</v>
+        <v>1104</v>
       </c>
     </row>
     <row r="10" ht="18.75" customHeight="1">
       <c r="A10" s="60"/>
       <c r="B10" s="61" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="C10" s="61" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="D10" s="60"/>
       <c r="E10" s="61" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="F10" s="61" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="G10" s="60"/>
       <c r="H10" s="61" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="I10" s="61" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
     </row>
     <row r="11" ht="18.75" customHeight="1">
       <c r="A11" s="57" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="B11" s="59" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C11" s="59" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="D11" s="57" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="E11" s="59" t="s">
-        <v>1099</v>
+        <v>1105</v>
       </c>
       <c r="F11" s="59" t="s">
-        <v>1100</v>
+        <v>1106</v>
       </c>
       <c r="G11" s="57" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="H11" s="59" t="s">
-        <v>1101</v>
+        <v>1107</v>
       </c>
       <c r="I11" s="59" t="s">
-        <v>1102</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="12" ht="18.75" customHeight="1">
       <c r="A12" s="57" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="B12" s="59" t="s">
-        <v>1103</v>
+        <v>1109</v>
       </c>
       <c r="C12" s="59" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="D12" s="57" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="E12" s="59" t="s">
-        <v>1105</v>
+        <v>1111</v>
       </c>
       <c r="F12" s="59" t="s">
-        <v>1106</v>
+        <v>1112</v>
       </c>
       <c r="G12" s="57" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="H12" s="59" t="s">
-        <v>1107</v>
+        <v>1113</v>
       </c>
       <c r="I12" s="59" t="s">
-        <v>1108</v>
+        <v>1114</v>
       </c>
     </row>
     <row r="13" ht="18.75" customHeight="1">
       <c r="A13" s="57" t="s">
-        <v>1109</v>
+        <v>1115</v>
       </c>
       <c r="D13" s="57" t="s">
-        <v>1110</v>
+        <v>1116</v>
       </c>
       <c r="G13" s="58"/>
       <c r="H13" s="58"/>
@@ -14245,13 +14338,13 @@
     </row>
     <row r="14" ht="18.75" customHeight="1">
       <c r="A14" s="57" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="B14" s="59" t="s">
-        <v>1079</v>
+        <v>1085</v>
       </c>
       <c r="D14" s="57" t="s">
-        <v>1078</v>
+        <v>1084</v>
       </c>
       <c r="E14" s="59" t="s">
         <v>798</v>
@@ -14265,13 +14358,13 @@
         <v>113</v>
       </c>
       <c r="B15" s="59" t="s">
-        <v>1080</v>
+        <v>1086</v>
       </c>
       <c r="D15" s="57" t="s">
         <v>113</v>
       </c>
       <c r="E15" s="59" t="s">
-        <v>1111</v>
+        <v>1117</v>
       </c>
       <c r="G15" s="58"/>
       <c r="H15" s="58"/>
@@ -14280,17 +14373,17 @@
     <row r="16" ht="18.75" customHeight="1">
       <c r="A16" s="60"/>
       <c r="B16" s="61" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="C16" s="61" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="D16" s="60"/>
       <c r="E16" s="61" t="s">
-        <v>1082</v>
+        <v>1088</v>
       </c>
       <c r="F16" s="61" t="s">
-        <v>1083</v>
+        <v>1089</v>
       </c>
       <c r="G16" s="58"/>
       <c r="H16" s="58"/>
@@ -14298,22 +14391,22 @@
     </row>
     <row r="17" ht="18.75" customHeight="1">
       <c r="A17" s="57" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="B17" s="59" t="s">
-        <v>1085</v>
+        <v>1091</v>
       </c>
       <c r="C17" s="59" t="s">
-        <v>1086</v>
+        <v>1092</v>
       </c>
       <c r="D17" s="57" t="s">
-        <v>1084</v>
+        <v>1090</v>
       </c>
       <c r="E17" s="59" t="s">
-        <v>1112</v>
+        <v>1118</v>
       </c>
       <c r="F17" s="59" t="s">
-        <v>1113</v>
+        <v>1119</v>
       </c>
       <c r="G17" s="58"/>
       <c r="H17" s="58"/>
@@ -14321,22 +14414,22 @@
     </row>
     <row r="18" ht="18.75" customHeight="1">
       <c r="A18" s="57" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="B18" s="59" t="s">
-        <v>1114</v>
+        <v>1120</v>
       </c>
       <c r="C18" s="59" t="s">
-        <v>1104</v>
+        <v>1110</v>
       </c>
       <c r="D18" s="57" t="s">
-        <v>1089</v>
+        <v>1095</v>
       </c>
       <c r="E18" s="59" t="s">
-        <v>1115</v>
+        <v>1121</v>
       </c>
       <c r="F18" s="59" t="s">
-        <v>1116</v>
+        <v>1122</v>
       </c>
       <c r="G18" s="58"/>
       <c r="H18" s="58"/>
@@ -14355,13 +14448,13 @@
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="63" t="s">
-        <v>1117</v>
+        <v>720</v>
       </c>
       <c r="B20" s="64" t="s">
-        <v>1118</v>
+        <v>1123</v>
       </c>
       <c r="D20" s="64" t="s">
-        <v>1119</v>
+        <v>1124</v>
       </c>
       <c r="F20" s="62"/>
       <c r="G20" s="62"/>
@@ -14370,16 +14463,16 @@
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="B21" s="65" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="C21" s="65" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="D21" s="65" t="s">
-        <v>1120</v>
+        <v>1125</v>
       </c>
       <c r="E21" s="65" t="s">
-        <v>1121</v>
+        <v>1126</v>
       </c>
       <c r="F21" s="62"/>
       <c r="G21" s="62"/>
@@ -14388,19 +14481,19 @@
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="66" t="s">
-        <v>1122</v>
+        <v>1127</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>26</v>
+        <v>720</v>
       </c>
       <c r="C22" s="59" t="s">
-        <v>1123</v>
+        <v>1128</v>
       </c>
       <c r="D22" s="59" t="s">
-        <v>1124</v>
+        <v>1129</v>
       </c>
       <c r="E22" s="59" t="s">
-        <v>1125</v>
+        <v>1130</v>
       </c>
       <c r="F22" s="62"/>
       <c r="G22" s="62"/>
@@ -14409,19 +14502,19 @@
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="64" t="s">
-        <v>1126</v>
+        <v>1131</v>
       </c>
       <c r="B23" s="59" t="s">
-        <v>1127</v>
+        <v>1132</v>
       </c>
       <c r="C23" s="59" t="s">
-        <v>1128</v>
+        <v>1133</v>
       </c>
       <c r="D23" s="59" t="s">
-        <v>1129</v>
+        <v>1134</v>
       </c>
       <c r="E23" s="59" t="s">
-        <v>1130</v>
+        <v>1135</v>
       </c>
       <c r="F23" s="62"/>
       <c r="G23" s="62"/>
@@ -14437,44 +14530,75 @@
       <c r="I24" s="62"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="68"/>
-      <c r="B25" s="68"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
+      <c r="A25" s="63" t="s">
+        <v>1136</v>
+      </c>
+      <c r="B25" s="64" t="s">
+        <v>1123</v>
+      </c>
+      <c r="D25" s="64" t="s">
+        <v>1124</v>
+      </c>
       <c r="F25" s="62"/>
       <c r="G25" s="62"/>
       <c r="H25" s="62"/>
       <c r="I25" s="62"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="68"/>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
+      <c r="B26" s="65" t="s">
+        <v>1125</v>
+      </c>
+      <c r="C26" s="65" t="s">
+        <v>1126</v>
+      </c>
+      <c r="D26" s="65" t="s">
+        <v>1125</v>
+      </c>
+      <c r="E26" s="65" t="s">
+        <v>1126</v>
+      </c>
       <c r="F26" s="62"/>
       <c r="G26" s="62"/>
       <c r="H26" s="62"/>
       <c r="I26" s="62"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="68"/>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
+      <c r="A27" s="66" t="s">
+        <v>1127</v>
+      </c>
+      <c r="B27" s="59" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C27" s="59" t="s">
+        <v>1137</v>
+      </c>
+      <c r="D27" s="59" t="s">
+        <v>1138</v>
+      </c>
+      <c r="E27" s="59" t="s">
+        <v>1139</v>
+      </c>
       <c r="F27" s="62"/>
       <c r="G27" s="62"/>
       <c r="H27" s="62"/>
       <c r="I27" s="62"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="68"/>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
+      <c r="A28" s="64" t="s">
+        <v>1131</v>
+      </c>
+      <c r="B28" s="59" t="s">
+        <v>1078</v>
+      </c>
+      <c r="C28" s="59" t="s">
+        <v>1140</v>
+      </c>
+      <c r="D28" s="59" t="s">
+        <v>1141</v>
+      </c>
+      <c r="E28" s="59" t="s">
+        <v>1142</v>
+      </c>
       <c r="F28" s="62"/>
       <c r="G28" s="62"/>
       <c r="H28" s="62"/>
@@ -15273,7 +15397,7 @@
       <c r="I100" s="62"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="27">
     <mergeCell ref="D7:F7"/>
     <mergeCell ref="G7:I7"/>
     <mergeCell ref="B8:C8"/>
@@ -15291,6 +15415,9 @@
     <mergeCell ref="A7:C7"/>
     <mergeCell ref="B20:C20"/>
     <mergeCell ref="D20:E20"/>
+    <mergeCell ref="B25:C25"/>
+    <mergeCell ref="D25:E25"/>
+    <mergeCell ref="A25:A26"/>
     <mergeCell ref="A13:C13"/>
     <mergeCell ref="D13:F13"/>
     <mergeCell ref="B14:C14"/>
@@ -15315,7 +15442,7 @@
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
       <c r="A1" s="57" t="s">
-        <v>1131</v>
+        <v>1143</v>
       </c>
       <c r="C1" s="58"/>
       <c r="D1" s="59"/>
@@ -15327,10 +15454,10 @@
     </row>
     <row r="2" ht="18.75" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>1132</v>
+        <v>1144</v>
       </c>
       <c r="B2" s="57" t="s">
-        <v>1133</v>
+        <v>1145</v>
       </c>
       <c r="C2" s="59"/>
       <c r="D2" s="59"/>
@@ -15342,10 +15469,10 @@
     </row>
     <row r="3" ht="18.75" customHeight="1">
       <c r="A3" s="59" t="s">
-        <v>1134</v>
+        <v>1146</v>
       </c>
       <c r="B3" s="59" t="s">
-        <v>1135</v>
+        <v>1147</v>
       </c>
       <c r="C3" s="59"/>
       <c r="D3" s="59"/>
@@ -15357,7 +15484,7 @@
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="59" t="s">
-        <v>1135</v>
+        <v>1147</v>
       </c>
       <c r="B4" s="59" t="s">
         <v>405</v>
@@ -15372,10 +15499,10 @@
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="59" t="s">
-        <v>1136</v>
+        <v>1148</v>
       </c>
       <c r="B5" s="59" t="s">
-        <v>1137</v>
+        <v>1149</v>
       </c>
       <c r="C5" s="59"/>
       <c r="D5" s="59"/>
@@ -15390,7 +15517,7 @@
         <v>405</v>
       </c>
       <c r="B6" s="59" t="s">
-        <v>1138</v>
+        <v>1150</v>
       </c>
       <c r="C6" s="59"/>
       <c r="D6" s="59"/>
@@ -15402,10 +15529,10 @@
     </row>
     <row r="7" ht="18.75" customHeight="1">
       <c r="A7" s="59" t="s">
-        <v>1139</v>
+        <v>1151</v>
       </c>
       <c r="B7" s="59" t="s">
-        <v>1137</v>
+        <v>1149</v>
       </c>
       <c r="C7" s="59"/>
       <c r="D7" s="59"/>
@@ -15426,10 +15553,10 @@
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="59" t="s">
-        <v>1140</v>
+        <v>1152</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1141</v>
+        <v>1153</v>
       </c>
       <c r="C9" s="59"/>
       <c r="D9" s="59"/>
@@ -16457,68 +16584,68 @@
   </cols>
   <sheetData>
     <row r="1" ht="18.75" customHeight="1">
-      <c r="A1" s="69" t="s">
-        <v>1142</v>
-      </c>
-      <c r="C1" s="70"/>
-      <c r="D1" s="71" t="s">
-        <v>1143</v>
-      </c>
-      <c r="H1" s="72"/>
-      <c r="I1" s="72"/>
+      <c r="A1" s="68" t="s">
+        <v>1154</v>
+      </c>
+      <c r="C1" s="69"/>
+      <c r="D1" s="70" t="s">
+        <v>1155</v>
+      </c>
+      <c r="H1" s="71"/>
+      <c r="I1" s="71"/>
     </row>
     <row r="2" ht="18.75" customHeight="1">
-      <c r="A2" s="71" t="s">
-        <v>1144</v>
-      </c>
-      <c r="B2" s="71" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C2" s="72"/>
-      <c r="D2" s="71" t="s">
-        <v>1144</v>
-      </c>
-      <c r="E2" s="71" t="s">
-        <v>1145</v>
-      </c>
-      <c r="H2" s="72"/>
-      <c r="I2" s="72"/>
+      <c r="A2" s="70" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B2" s="70" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C2" s="71"/>
+      <c r="D2" s="70" t="s">
+        <v>1156</v>
+      </c>
+      <c r="E2" s="70" t="s">
+        <v>1157</v>
+      </c>
+      <c r="H2" s="71"/>
+      <c r="I2" s="71"/>
     </row>
     <row r="3" ht="18.75" customHeight="1">
-      <c r="A3" s="73" t="s">
-        <v>1146</v>
+      <c r="A3" s="72" t="s">
+        <v>1158</v>
       </c>
       <c r="B3" s="59" t="s">
         <v>131</v>
       </c>
-      <c r="C3" s="73"/>
+      <c r="C3" s="72"/>
       <c r="D3" s="59" t="s">
-        <v>1147</v>
+        <v>1159</v>
       </c>
       <c r="E3" s="59" t="s">
-        <v>1148</v>
-      </c>
-      <c r="H3" s="72"/>
-      <c r="I3" s="72"/>
+        <v>1160</v>
+      </c>
+      <c r="H3" s="71"/>
+      <c r="I3" s="71"/>
     </row>
     <row r="4" ht="18.75" customHeight="1">
       <c r="A4" s="59" t="s">
-        <v>1149</v>
+        <v>1161</v>
       </c>
       <c r="B4" s="59" t="s">
-        <v>1150</v>
-      </c>
-      <c r="C4" s="73"/>
-      <c r="D4" s="73" t="s">
-        <v>1151</v>
-      </c>
-      <c r="E4" s="73" t="s">
-        <v>1152</v>
-      </c>
-      <c r="F4" s="73"/>
-      <c r="G4" s="73"/>
-      <c r="H4" s="73"/>
-      <c r="I4" s="73"/>
+        <v>1162</v>
+      </c>
+      <c r="C4" s="72"/>
+      <c r="D4" s="72" t="s">
+        <v>1163</v>
+      </c>
+      <c r="E4" s="72" t="s">
+        <v>1164</v>
+      </c>
+      <c r="F4" s="72"/>
+      <c r="G4" s="72"/>
+      <c r="H4" s="72"/>
+      <c r="I4" s="72"/>
     </row>
     <row r="5" ht="18.75" customHeight="1">
       <c r="A5" s="59" t="s">
@@ -16527,760 +16654,766 @@
       <c r="B5" s="59" t="s">
         <v>135</v>
       </c>
-      <c r="C5" s="73"/>
+      <c r="C5" s="72"/>
       <c r="D5" s="59" t="s">
-        <v>1153</v>
+        <v>1165</v>
       </c>
       <c r="E5" s="59" t="s">
-        <v>1154</v>
-      </c>
-      <c r="F5" s="73"/>
-      <c r="G5" s="73"/>
-      <c r="H5" s="73"/>
-      <c r="I5" s="73"/>
+        <v>1166</v>
+      </c>
+      <c r="F5" s="72"/>
+      <c r="G5" s="72"/>
+      <c r="H5" s="72"/>
+      <c r="I5" s="72"/>
     </row>
     <row r="6" ht="18.75" customHeight="1">
-      <c r="A6" s="73" t="s">
-        <v>1135</v>
-      </c>
-      <c r="B6" s="73" t="s">
+      <c r="A6" s="72" t="s">
+        <v>1147</v>
+      </c>
+      <c r="B6" s="72" t="s">
         <v>143</v>
       </c>
-      <c r="C6" s="73"/>
+      <c r="C6" s="72"/>
       <c r="D6" s="59" t="s">
-        <v>1155</v>
+        <v>1167</v>
       </c>
       <c r="E6" s="59" t="s">
-        <v>1156</v>
-      </c>
-      <c r="F6" s="73"/>
-      <c r="G6" s="73"/>
-      <c r="H6" s="73"/>
-      <c r="I6" s="73"/>
+        <v>1168</v>
+      </c>
+      <c r="F6" s="72"/>
+      <c r="G6" s="72"/>
+      <c r="H6" s="72"/>
+      <c r="I6" s="72"/>
     </row>
     <row r="7" ht="18.75" customHeight="1">
-      <c r="A7" s="73" t="s">
+      <c r="A7" s="72" t="s">
         <v>405</v>
       </c>
-      <c r="B7" s="73" t="s">
+      <c r="B7" s="72" t="s">
         <v>147</v>
       </c>
-      <c r="C7" s="73"/>
+      <c r="C7" s="72"/>
       <c r="D7" s="59" t="s">
-        <v>1157</v>
+        <v>1169</v>
       </c>
       <c r="E7" s="59" t="s">
-        <v>1158</v>
-      </c>
-      <c r="F7" s="73"/>
-      <c r="G7" s="73"/>
-      <c r="H7" s="73"/>
-      <c r="I7" s="73"/>
+        <v>1170</v>
+      </c>
+      <c r="F7" s="72"/>
+      <c r="G7" s="72"/>
+      <c r="H7" s="72"/>
+      <c r="I7" s="72"/>
     </row>
     <row r="8" ht="18.75" customHeight="1">
-      <c r="A8" s="73" t="s">
-        <v>1159</v>
+      <c r="A8" s="72" t="s">
+        <v>1171</v>
       </c>
       <c r="B8" s="59" t="s">
         <v>151</v>
       </c>
-      <c r="C8" s="73"/>
+      <c r="C8" s="72"/>
       <c r="D8" s="59" t="s">
-        <v>1160</v>
+        <v>1172</v>
       </c>
       <c r="E8" s="59" t="s">
-        <v>1161</v>
-      </c>
-      <c r="F8" s="73"/>
-      <c r="G8" s="73"/>
-      <c r="H8" s="73"/>
-      <c r="I8" s="73"/>
+        <v>1173</v>
+      </c>
+      <c r="F8" s="72"/>
+      <c r="G8" s="72"/>
+      <c r="H8" s="72"/>
+      <c r="I8" s="72"/>
     </row>
     <row r="9" ht="18.75" customHeight="1">
       <c r="A9" s="59" t="s">
-        <v>1137</v>
+        <v>1149</v>
       </c>
       <c r="B9" s="59" t="s">
-        <v>1162</v>
-      </c>
-      <c r="C9" s="73"/>
-      <c r="D9" s="73"/>
-      <c r="E9" s="74"/>
-      <c r="F9" s="74"/>
-      <c r="G9" s="74"/>
-      <c r="H9" s="74"/>
-      <c r="I9" s="74"/>
+        <v>1174</v>
+      </c>
+      <c r="C9" s="72"/>
+      <c r="D9" s="72"/>
+      <c r="E9" s="73"/>
+      <c r="F9" s="73"/>
+      <c r="G9" s="73"/>
+      <c r="H9" s="73"/>
+      <c r="I9" s="73"/>
     </row>
     <row r="10" ht="18.75" customHeight="1">
-      <c r="A10" s="73" t="s">
-        <v>1139</v>
+      <c r="A10" s="72" t="s">
+        <v>1151</v>
       </c>
       <c r="B10" s="59" t="s">
         <v>156</v>
       </c>
-      <c r="C10" s="73"/>
-      <c r="D10" s="73"/>
-      <c r="E10" s="74"/>
-      <c r="F10" s="73"/>
-      <c r="G10" s="73"/>
-      <c r="H10" s="73"/>
-      <c r="I10" s="73"/>
+      <c r="C10" s="72"/>
+      <c r="D10" s="72"/>
+      <c r="E10" s="73"/>
+      <c r="F10" s="72"/>
+      <c r="G10" s="72"/>
+      <c r="H10" s="72"/>
+      <c r="I10" s="72"/>
     </row>
     <row r="11" ht="18.75" customHeight="1">
-      <c r="A11" s="73" t="s">
-        <v>1138</v>
+      <c r="A11" s="72" t="s">
+        <v>1150</v>
       </c>
       <c r="B11" s="59" t="s">
         <v>162</v>
       </c>
-      <c r="C11" s="73"/>
-      <c r="D11" s="73"/>
-      <c r="E11" s="74"/>
-      <c r="F11" s="74"/>
-      <c r="G11" s="74"/>
-      <c r="H11" s="74"/>
-      <c r="I11" s="74"/>
+      <c r="C11" s="72"/>
+      <c r="D11" s="72"/>
+      <c r="E11" s="73"/>
+      <c r="F11" s="73"/>
+      <c r="G11" s="73"/>
+      <c r="H11" s="73"/>
+      <c r="I11" s="73"/>
     </row>
     <row r="12" ht="18.75" customHeight="1">
-      <c r="A12" s="73"/>
-      <c r="B12" s="73"/>
-      <c r="C12" s="73"/>
-      <c r="D12" s="73"/>
-      <c r="E12" s="74"/>
-      <c r="F12" s="74"/>
-      <c r="G12" s="74"/>
-      <c r="H12" s="74"/>
-      <c r="I12" s="74"/>
+      <c r="A12" s="72"/>
+      <c r="B12" s="72"/>
+      <c r="C12" s="72"/>
+      <c r="D12" s="72"/>
+      <c r="E12" s="73"/>
+      <c r="F12" s="73"/>
+      <c r="G12" s="73"/>
+      <c r="H12" s="73"/>
+      <c r="I12" s="73"/>
     </row>
     <row r="13" ht="18.75" customHeight="1">
-      <c r="A13" s="74"/>
-      <c r="B13" s="74"/>
-      <c r="C13" s="74"/>
-      <c r="D13" s="74"/>
-      <c r="E13" s="74"/>
-      <c r="F13" s="74"/>
-      <c r="G13" s="74"/>
-      <c r="H13" s="74"/>
-      <c r="I13" s="74"/>
+      <c r="A13" s="73"/>
+      <c r="B13" s="73"/>
+      <c r="C13" s="73"/>
+      <c r="D13" s="73"/>
+      <c r="E13" s="73"/>
+      <c r="F13" s="73"/>
+      <c r="G13" s="73"/>
+      <c r="H13" s="73"/>
+      <c r="I13" s="73"/>
     </row>
     <row r="14" ht="18.75" customHeight="1">
-      <c r="A14" s="71" t="s">
-        <v>1163</v>
-      </c>
-      <c r="C14" s="72"/>
-      <c r="D14" s="72"/>
-      <c r="E14" s="74"/>
-      <c r="F14" s="74"/>
-      <c r="G14" s="74"/>
-      <c r="H14" s="74"/>
-      <c r="I14" s="74"/>
+      <c r="A14" s="70" t="s">
+        <v>1175</v>
+      </c>
+      <c r="C14" s="71"/>
+      <c r="D14" s="71"/>
+      <c r="E14" s="73"/>
+      <c r="F14" s="73"/>
+      <c r="G14" s="73"/>
+      <c r="H14" s="73"/>
+      <c r="I14" s="73"/>
     </row>
     <row r="15" ht="18.75" customHeight="1">
-      <c r="A15" s="71" t="s">
-        <v>1144</v>
-      </c>
-      <c r="B15" s="71" t="s">
-        <v>1145</v>
-      </c>
-      <c r="C15" s="72"/>
-      <c r="D15" s="72"/>
-      <c r="E15" s="74"/>
-      <c r="F15" s="74"/>
-      <c r="G15" s="74"/>
-      <c r="H15" s="74"/>
-      <c r="I15" s="74"/>
+      <c r="A15" s="70" t="s">
+        <v>1156</v>
+      </c>
+      <c r="B15" s="70" t="s">
+        <v>1157</v>
+      </c>
+      <c r="C15" s="71"/>
+      <c r="D15" s="71"/>
+      <c r="E15" s="73"/>
+      <c r="F15" s="73"/>
+      <c r="G15" s="73"/>
+      <c r="H15" s="73"/>
+      <c r="I15" s="73"/>
     </row>
     <row r="16" ht="18.75" customHeight="1">
-      <c r="A16" s="73" t="s">
-        <v>1164</v>
-      </c>
-      <c r="B16" s="73" t="s">
-        <v>1165</v>
-      </c>
-      <c r="C16" s="72"/>
-      <c r="D16" s="72"/>
-      <c r="E16" s="74"/>
-      <c r="F16" s="74"/>
-      <c r="G16" s="74"/>
-      <c r="H16" s="74"/>
-      <c r="I16" s="74"/>
+      <c r="A16" s="72" t="s">
+        <v>1176</v>
+      </c>
+      <c r="B16" s="72" t="s">
+        <v>1177</v>
+      </c>
+      <c r="C16" s="71"/>
+      <c r="D16" s="71"/>
+      <c r="E16" s="73"/>
+      <c r="F16" s="73"/>
+      <c r="G16" s="73"/>
+      <c r="H16" s="73"/>
+      <c r="I16" s="73"/>
     </row>
     <row r="17" ht="18.75" customHeight="1">
-      <c r="A17" s="73" t="s">
-        <v>1166</v>
-      </c>
-      <c r="B17" s="73" t="s">
-        <v>1167</v>
-      </c>
-      <c r="C17" s="72"/>
-      <c r="D17" s="72"/>
-      <c r="E17" s="74"/>
-      <c r="F17" s="74"/>
-      <c r="G17" s="74"/>
-      <c r="H17" s="74"/>
-      <c r="I17" s="74"/>
+      <c r="A17" s="72" t="s">
+        <v>1178</v>
+      </c>
+      <c r="B17" s="72" t="s">
+        <v>1179</v>
+      </c>
+      <c r="C17" s="71"/>
+      <c r="D17" s="71"/>
+      <c r="E17" s="73"/>
+      <c r="F17" s="73"/>
+      <c r="G17" s="73"/>
+      <c r="H17" s="73"/>
+      <c r="I17" s="73"/>
     </row>
     <row r="18" ht="18.75" customHeight="1">
-      <c r="A18" s="73" t="s">
-        <v>1168</v>
-      </c>
-      <c r="B18" s="73" t="s">
-        <v>1169</v>
-      </c>
-      <c r="C18" s="72"/>
-      <c r="D18" s="72"/>
-      <c r="E18" s="74"/>
-      <c r="F18" s="74"/>
-      <c r="G18" s="74"/>
-      <c r="H18" s="74"/>
-      <c r="I18" s="74"/>
+      <c r="A18" s="72" t="s">
+        <v>1180</v>
+      </c>
+      <c r="B18" s="72" t="s">
+        <v>1181</v>
+      </c>
+      <c r="C18" s="71"/>
+      <c r="D18" s="71"/>
+      <c r="E18" s="73"/>
+      <c r="F18" s="73"/>
+      <c r="G18" s="73"/>
+      <c r="H18" s="73"/>
+      <c r="I18" s="73"/>
     </row>
     <row r="19" ht="18.75" customHeight="1">
-      <c r="A19" s="73" t="s">
-        <v>1170</v>
-      </c>
-      <c r="B19" s="73" t="s">
-        <v>1171</v>
-      </c>
-      <c r="C19" s="72"/>
-      <c r="D19" s="72"/>
-      <c r="E19" s="74"/>
-      <c r="F19" s="74"/>
-      <c r="G19" s="74"/>
-      <c r="H19" s="74"/>
-      <c r="I19" s="74"/>
+      <c r="A19" s="72" t="s">
+        <v>1182</v>
+      </c>
+      <c r="B19" s="72" t="s">
+        <v>1183</v>
+      </c>
+      <c r="C19" s="71"/>
+      <c r="D19" s="71"/>
+      <c r="E19" s="73"/>
+      <c r="F19" s="73"/>
+      <c r="G19" s="73"/>
+      <c r="H19" s="73"/>
+      <c r="I19" s="73"/>
     </row>
     <row r="20" ht="18.75" customHeight="1">
       <c r="A20" s="59" t="s">
-        <v>1172</v>
-      </c>
-      <c r="B20" s="73" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C20" s="72"/>
-      <c r="D20" s="72"/>
-      <c r="E20" s="74"/>
-      <c r="F20" s="74"/>
-      <c r="G20" s="74"/>
-      <c r="H20" s="74"/>
-      <c r="I20" s="74"/>
+        <v>1184</v>
+      </c>
+      <c r="B20" s="72" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C20" s="71"/>
+      <c r="D20" s="71"/>
+      <c r="E20" s="73"/>
+      <c r="F20" s="73"/>
+      <c r="G20" s="73"/>
+      <c r="H20" s="73"/>
+      <c r="I20" s="73"/>
     </row>
     <row r="21" ht="18.75" customHeight="1">
       <c r="A21" s="59" t="s">
-        <v>1174</v>
-      </c>
-      <c r="B21" s="73" t="s">
-        <v>1173</v>
-      </c>
-      <c r="C21" s="72"/>
-      <c r="D21" s="72"/>
-      <c r="E21" s="74"/>
-      <c r="F21" s="74"/>
-      <c r="G21" s="74"/>
-      <c r="H21" s="74"/>
-      <c r="I21" s="74"/>
+        <v>1186</v>
+      </c>
+      <c r="B21" s="72" t="s">
+        <v>1185</v>
+      </c>
+      <c r="C21" s="71"/>
+      <c r="D21" s="71"/>
+      <c r="E21" s="73"/>
+      <c r="F21" s="73"/>
+      <c r="G21" s="73"/>
+      <c r="H21" s="73"/>
+      <c r="I21" s="73"/>
     </row>
     <row r="22" ht="18.75" customHeight="1">
       <c r="A22" s="59" t="s">
-        <v>1175</v>
+        <v>1187</v>
       </c>
       <c r="B22" s="59" t="s">
-        <v>1176</v>
-      </c>
-      <c r="C22" s="72"/>
-      <c r="D22" s="72"/>
-      <c r="E22" s="74"/>
-      <c r="F22" s="74"/>
-      <c r="G22" s="74"/>
-      <c r="H22" s="74"/>
-      <c r="I22" s="74"/>
+        <v>1188</v>
+      </c>
+      <c r="C22" s="71"/>
+      <c r="D22" s="71"/>
+      <c r="E22" s="73"/>
+      <c r="F22" s="73"/>
+      <c r="G22" s="73"/>
+      <c r="H22" s="73"/>
+      <c r="I22" s="73"/>
     </row>
     <row r="23" ht="18.75" customHeight="1">
       <c r="A23" s="59" t="s">
-        <v>1177</v>
-      </c>
-      <c r="B23" s="73" t="s">
-        <v>1178</v>
-      </c>
-      <c r="C23" s="72"/>
-      <c r="D23" s="72"/>
-      <c r="E23" s="74"/>
-      <c r="F23" s="74"/>
-      <c r="G23" s="74"/>
-      <c r="H23" s="74"/>
-      <c r="I23" s="74"/>
+        <v>1189</v>
+      </c>
+      <c r="B23" s="72" t="s">
+        <v>1190</v>
+      </c>
+      <c r="C23" s="71"/>
+      <c r="D23" s="71"/>
+      <c r="E23" s="73"/>
+      <c r="F23" s="73"/>
+      <c r="G23" s="73"/>
+      <c r="H23" s="73"/>
+      <c r="I23" s="73"/>
     </row>
     <row r="24" ht="18.75" customHeight="1">
       <c r="A24" s="59" t="s">
-        <v>1179</v>
-      </c>
-      <c r="C24" s="72"/>
-      <c r="D24" s="72"/>
-      <c r="E24" s="74"/>
-      <c r="F24" s="74"/>
-      <c r="G24" s="74"/>
-      <c r="H24" s="74"/>
-      <c r="I24" s="74"/>
+        <v>1191</v>
+      </c>
+      <c r="C24" s="71"/>
+      <c r="D24" s="71"/>
+      <c r="E24" s="73"/>
+      <c r="F24" s="73"/>
+      <c r="G24" s="73"/>
+      <c r="H24" s="73"/>
+      <c r="I24" s="73"/>
     </row>
     <row r="25" ht="18.75" customHeight="1">
-      <c r="A25" s="73" t="s">
-        <v>1180</v>
-      </c>
-      <c r="B25" s="73" t="s">
-        <v>1181</v>
-      </c>
-      <c r="C25" s="72"/>
-      <c r="D25" s="72"/>
-      <c r="E25" s="74"/>
-      <c r="F25" s="74"/>
-      <c r="G25" s="74"/>
-      <c r="H25" s="74"/>
-      <c r="I25" s="74"/>
+      <c r="A25" s="72" t="s">
+        <v>1192</v>
+      </c>
+      <c r="B25" s="72" t="s">
+        <v>1193</v>
+      </c>
+      <c r="C25" s="71"/>
+      <c r="D25" s="71"/>
+      <c r="E25" s="73"/>
+      <c r="F25" s="73"/>
+      <c r="G25" s="73"/>
+      <c r="H25" s="73"/>
+      <c r="I25" s="73"/>
     </row>
     <row r="26" ht="18.75" customHeight="1">
-      <c r="A26" s="73" t="s">
-        <v>1182</v>
-      </c>
-      <c r="B26" s="73" t="s">
-        <v>1183</v>
-      </c>
-      <c r="C26" s="72"/>
-      <c r="D26" s="72"/>
-      <c r="E26" s="74"/>
-      <c r="F26" s="74"/>
-      <c r="G26" s="74"/>
-      <c r="H26" s="74"/>
-      <c r="I26" s="74"/>
+      <c r="A26" s="72" t="s">
+        <v>1194</v>
+      </c>
+      <c r="B26" s="72" t="s">
+        <v>1195</v>
+      </c>
+      <c r="C26" s="71"/>
+      <c r="D26" s="71"/>
+      <c r="E26" s="73"/>
+      <c r="F26" s="73"/>
+      <c r="G26" s="73"/>
+      <c r="H26" s="73"/>
+      <c r="I26" s="73"/>
     </row>
     <row r="27" ht="18.75" customHeight="1">
-      <c r="A27" s="73" t="s">
-        <v>1184</v>
-      </c>
-      <c r="B27" s="73" t="s">
-        <v>1185</v>
-      </c>
-      <c r="C27" s="72"/>
-      <c r="D27" s="72"/>
-      <c r="E27" s="74"/>
-      <c r="F27" s="74"/>
-      <c r="G27" s="74"/>
-      <c r="H27" s="74"/>
-      <c r="I27" s="74"/>
+      <c r="A27" s="72" t="s">
+        <v>1196</v>
+      </c>
+      <c r="B27" s="72" t="s">
+        <v>1197</v>
+      </c>
+      <c r="C27" s="71"/>
+      <c r="D27" s="71"/>
+      <c r="E27" s="73"/>
+      <c r="F27" s="73"/>
+      <c r="G27" s="73"/>
+      <c r="H27" s="73"/>
+      <c r="I27" s="73"/>
     </row>
     <row r="28" ht="18.75" customHeight="1">
-      <c r="A28" s="73" t="s">
-        <v>1186</v>
-      </c>
-      <c r="B28" s="73" t="s">
-        <v>1187</v>
-      </c>
-      <c r="C28" s="72"/>
-      <c r="D28" s="72"/>
-      <c r="E28" s="74"/>
-      <c r="F28" s="74"/>
-      <c r="G28" s="74"/>
-      <c r="H28" s="74"/>
-      <c r="I28" s="74"/>
+      <c r="A28" s="72" t="s">
+        <v>1198</v>
+      </c>
+      <c r="B28" s="72" t="s">
+        <v>1199</v>
+      </c>
+      <c r="C28" s="71"/>
+      <c r="D28" s="71"/>
+      <c r="E28" s="73"/>
+      <c r="F28" s="73"/>
+      <c r="G28" s="73"/>
+      <c r="H28" s="73"/>
+      <c r="I28" s="73"/>
     </row>
     <row r="29" ht="18.75" customHeight="1">
-      <c r="A29" s="73" t="s">
-        <v>1188</v>
-      </c>
-      <c r="B29" s="73" t="s">
-        <v>1189</v>
-      </c>
-      <c r="C29" s="72"/>
-      <c r="D29" s="72"/>
-      <c r="E29" s="74"/>
-      <c r="F29" s="74"/>
-      <c r="G29" s="74"/>
-      <c r="H29" s="74"/>
-      <c r="I29" s="74"/>
+      <c r="A29" s="59" t="s">
+        <v>1200</v>
+      </c>
+      <c r="B29" s="59" t="s">
+        <v>178</v>
+      </c>
+      <c r="C29" s="71"/>
+      <c r="D29" s="71"/>
+      <c r="E29" s="73"/>
+      <c r="F29" s="73"/>
+      <c r="G29" s="73"/>
+      <c r="H29" s="73"/>
+      <c r="I29" s="73"/>
     </row>
     <row r="30" ht="18.75" customHeight="1">
-      <c r="A30" s="73" t="s">
-        <v>1190</v>
-      </c>
-      <c r="B30" s="73" t="s">
-        <v>1191</v>
-      </c>
-      <c r="C30" s="72"/>
-      <c r="D30" s="72"/>
-      <c r="E30" s="74"/>
-      <c r="F30" s="74"/>
-      <c r="G30" s="74"/>
-      <c r="H30" s="74"/>
-      <c r="I30" s="74"/>
+      <c r="A30" s="72" t="s">
+        <v>1201</v>
+      </c>
+      <c r="B30" s="72" t="s">
+        <v>1202</v>
+      </c>
+      <c r="C30" s="71"/>
+      <c r="D30" s="71"/>
+      <c r="E30" s="73"/>
+      <c r="F30" s="73"/>
+      <c r="G30" s="73"/>
+      <c r="H30" s="73"/>
+      <c r="I30" s="73"/>
     </row>
     <row r="31" ht="18.75" customHeight="1">
-      <c r="A31" s="73" t="s">
-        <v>1192</v>
-      </c>
-      <c r="B31" s="73" t="s">
-        <v>1193</v>
-      </c>
-      <c r="C31" s="72"/>
-      <c r="D31" s="72"/>
-      <c r="E31" s="74"/>
-      <c r="F31" s="74"/>
-      <c r="G31" s="74"/>
-      <c r="H31" s="74"/>
-      <c r="I31" s="74"/>
+      <c r="A31" s="72" t="s">
+        <v>1203</v>
+      </c>
+      <c r="B31" s="72" t="s">
+        <v>1204</v>
+      </c>
+      <c r="C31" s="71"/>
+      <c r="D31" s="71"/>
+      <c r="E31" s="73"/>
+      <c r="F31" s="73"/>
+      <c r="G31" s="73"/>
+      <c r="H31" s="73"/>
+      <c r="I31" s="73"/>
     </row>
     <row r="32" ht="18.75" customHeight="1">
-      <c r="A32" s="73" t="s">
-        <v>1194</v>
-      </c>
-      <c r="B32" s="73" t="s">
+      <c r="A32" s="72" t="s">
+        <v>1205</v>
+      </c>
+      <c r="B32" s="72" t="s">
+        <v>1206</v>
+      </c>
+      <c r="C32" s="71"/>
+      <c r="D32" s="71"/>
+      <c r="E32" s="73"/>
+      <c r="F32" s="73"/>
+      <c r="G32" s="73"/>
+      <c r="H32" s="73"/>
+      <c r="I32" s="73"/>
+    </row>
+    <row r="33" ht="18.75" customHeight="1">
+      <c r="A33" s="72" t="s">
+        <v>1207</v>
+      </c>
+      <c r="B33" s="72" t="s">
         <v>174</v>
       </c>
-      <c r="C32" s="72"/>
-      <c r="D32" s="72"/>
-      <c r="E32" s="74"/>
-      <c r="F32" s="74"/>
-      <c r="G32" s="74"/>
-      <c r="H32" s="74"/>
-      <c r="I32" s="74"/>
-    </row>
-    <row r="33" ht="18.75" customHeight="1">
-      <c r="A33" s="73" t="s">
-        <v>1195</v>
-      </c>
-      <c r="B33" s="73" t="s">
-        <v>1196</v>
-      </c>
-      <c r="C33" s="72"/>
-      <c r="D33" s="72"/>
-      <c r="E33" s="74"/>
-      <c r="F33" s="74"/>
-      <c r="G33" s="74"/>
-      <c r="H33" s="74"/>
-      <c r="I33" s="74"/>
+      <c r="C33" s="71"/>
+      <c r="D33" s="71"/>
+      <c r="E33" s="73"/>
+      <c r="F33" s="73"/>
+      <c r="G33" s="73"/>
+      <c r="H33" s="73"/>
+      <c r="I33" s="73"/>
     </row>
     <row r="34" ht="18.75" customHeight="1">
-      <c r="A34" s="73" t="s">
-        <v>1197</v>
-      </c>
-      <c r="B34" s="73" t="s">
-        <v>1198</v>
-      </c>
-      <c r="C34" s="72"/>
-      <c r="D34" s="72"/>
-      <c r="E34" s="74"/>
-      <c r="F34" s="74"/>
-      <c r="G34" s="74"/>
-      <c r="H34" s="74"/>
-      <c r="I34" s="74"/>
+      <c r="A34" s="72" t="s">
+        <v>1208</v>
+      </c>
+      <c r="B34" s="72" t="s">
+        <v>1209</v>
+      </c>
+      <c r="C34" s="71"/>
+      <c r="D34" s="71"/>
+      <c r="E34" s="73"/>
+      <c r="F34" s="73"/>
+      <c r="G34" s="73"/>
+      <c r="H34" s="73"/>
+      <c r="I34" s="73"/>
     </row>
     <row r="35" ht="18.75" customHeight="1">
-      <c r="A35" s="73" t="s">
-        <v>1199</v>
-      </c>
-      <c r="B35" s="59" t="s">
-        <v>1200</v>
-      </c>
-      <c r="C35" s="72"/>
-      <c r="D35" s="72"/>
-      <c r="E35" s="74"/>
-      <c r="F35" s="74"/>
-      <c r="G35" s="74"/>
-      <c r="H35" s="74"/>
-      <c r="I35" s="74"/>
+      <c r="A35" s="72" t="s">
+        <v>1210</v>
+      </c>
+      <c r="B35" s="72" t="s">
+        <v>1211</v>
+      </c>
+      <c r="C35" s="71"/>
+      <c r="D35" s="71"/>
+      <c r="E35" s="73"/>
+      <c r="F35" s="73"/>
+      <c r="G35" s="73"/>
+      <c r="H35" s="73"/>
+      <c r="I35" s="73"/>
     </row>
     <row r="36" ht="18.75" customHeight="1">
-      <c r="A36" s="73" t="s">
-        <v>1201</v>
+      <c r="A36" s="72" t="s">
+        <v>1212</v>
       </c>
       <c r="B36" s="59" t="s">
-        <v>1202</v>
-      </c>
-      <c r="C36" s="72"/>
-      <c r="D36" s="72"/>
-      <c r="E36" s="74"/>
-      <c r="F36" s="74"/>
-      <c r="G36" s="74"/>
-      <c r="H36" s="74"/>
-      <c r="I36" s="74"/>
+        <v>1213</v>
+      </c>
+      <c r="C36" s="71"/>
+      <c r="D36" s="71"/>
+      <c r="E36" s="73"/>
+      <c r="F36" s="73"/>
+      <c r="G36" s="73"/>
+      <c r="H36" s="73"/>
+      <c r="I36" s="73"/>
     </row>
     <row r="37" ht="18.75" customHeight="1">
-      <c r="A37" s="73" t="s">
-        <v>1203</v>
-      </c>
-      <c r="B37" s="73" t="s">
-        <v>1204</v>
-      </c>
-      <c r="C37" s="72"/>
-      <c r="D37" s="72"/>
-      <c r="E37" s="74"/>
-      <c r="F37" s="74"/>
-      <c r="G37" s="74"/>
-      <c r="H37" s="74"/>
-      <c r="I37" s="74"/>
+      <c r="A37" s="72" t="s">
+        <v>1214</v>
+      </c>
+      <c r="B37" s="59" t="s">
+        <v>1215</v>
+      </c>
+      <c r="C37" s="71"/>
+      <c r="D37" s="71"/>
+      <c r="E37" s="73"/>
+      <c r="F37" s="73"/>
+      <c r="G37" s="73"/>
+      <c r="H37" s="73"/>
+      <c r="I37" s="73"/>
     </row>
     <row r="38" ht="18.75" customHeight="1">
-      <c r="A38" s="73" t="s">
-        <v>1205</v>
-      </c>
-      <c r="B38" s="73" t="s">
-        <v>1206</v>
-      </c>
-      <c r="C38" s="72"/>
-      <c r="D38" s="72"/>
-      <c r="E38" s="74"/>
-      <c r="F38" s="74"/>
-      <c r="G38" s="74"/>
-      <c r="H38" s="74"/>
-      <c r="I38" s="74"/>
+      <c r="A38" s="72" t="s">
+        <v>1216</v>
+      </c>
+      <c r="B38" s="72" t="s">
+        <v>1217</v>
+      </c>
+      <c r="C38" s="71"/>
+      <c r="D38" s="71"/>
+      <c r="E38" s="73"/>
+      <c r="F38" s="73"/>
+      <c r="G38" s="73"/>
+      <c r="H38" s="73"/>
+      <c r="I38" s="73"/>
     </row>
     <row r="39" ht="18.75" customHeight="1">
-      <c r="C39" s="72"/>
-      <c r="D39" s="72"/>
-      <c r="E39" s="74"/>
-      <c r="F39" s="74"/>
-      <c r="G39" s="74"/>
-      <c r="H39" s="74"/>
-      <c r="I39" s="74"/>
+      <c r="A39" s="72" t="s">
+        <v>1218</v>
+      </c>
+      <c r="B39" s="72" t="s">
+        <v>1219</v>
+      </c>
+      <c r="C39" s="71"/>
+      <c r="D39" s="71"/>
+      <c r="E39" s="73"/>
+      <c r="F39" s="73"/>
+      <c r="G39" s="73"/>
+      <c r="H39" s="73"/>
+      <c r="I39" s="73"/>
     </row>
     <row r="40" ht="18.75" customHeight="1">
-      <c r="A40" s="73"/>
-      <c r="B40" s="73"/>
-      <c r="C40" s="72"/>
-      <c r="D40" s="72"/>
-      <c r="E40" s="74"/>
-      <c r="F40" s="74"/>
-      <c r="G40" s="74"/>
-      <c r="H40" s="74"/>
-      <c r="I40" s="74"/>
+      <c r="A40" s="72"/>
+      <c r="B40" s="72"/>
+      <c r="C40" s="71"/>
+      <c r="D40" s="71"/>
+      <c r="E40" s="73"/>
+      <c r="F40" s="73"/>
+      <c r="G40" s="73"/>
+      <c r="H40" s="73"/>
+      <c r="I40" s="73"/>
     </row>
     <row r="41" ht="18.75" customHeight="1">
-      <c r="A41" s="73"/>
-      <c r="B41" s="73"/>
-      <c r="C41" s="72"/>
-      <c r="D41" s="72"/>
-      <c r="E41" s="74"/>
-      <c r="F41" s="74"/>
-      <c r="G41" s="74"/>
-      <c r="H41" s="74"/>
-      <c r="I41" s="74"/>
+      <c r="A41" s="72"/>
+      <c r="B41" s="72"/>
+      <c r="C41" s="71"/>
+      <c r="D41" s="71"/>
+      <c r="E41" s="73"/>
+      <c r="F41" s="73"/>
+      <c r="G41" s="73"/>
+      <c r="H41" s="73"/>
+      <c r="I41" s="73"/>
     </row>
     <row r="42" ht="18.75" customHeight="1">
-      <c r="A42" s="73"/>
-      <c r="B42" s="73"/>
-      <c r="C42" s="72"/>
-      <c r="D42" s="72"/>
-      <c r="E42" s="74"/>
-      <c r="F42" s="74"/>
-      <c r="G42" s="74"/>
-      <c r="H42" s="74"/>
-      <c r="I42" s="74"/>
+      <c r="A42" s="72"/>
+      <c r="B42" s="72"/>
+      <c r="C42" s="71"/>
+      <c r="D42" s="71"/>
+      <c r="E42" s="73"/>
+      <c r="F42" s="73"/>
+      <c r="G42" s="73"/>
+      <c r="H42" s="73"/>
+      <c r="I42" s="73"/>
     </row>
     <row r="43" ht="18.75" customHeight="1">
-      <c r="A43" s="73"/>
-      <c r="B43" s="73"/>
-      <c r="C43" s="72"/>
-      <c r="D43" s="72"/>
-      <c r="E43" s="74"/>
-      <c r="F43" s="74"/>
-      <c r="G43" s="74"/>
-      <c r="H43" s="74"/>
-      <c r="I43" s="74"/>
+      <c r="A43" s="72"/>
+      <c r="B43" s="72"/>
+      <c r="C43" s="71"/>
+      <c r="D43" s="71"/>
+      <c r="E43" s="73"/>
+      <c r="F43" s="73"/>
+      <c r="G43" s="73"/>
+      <c r="H43" s="73"/>
+      <c r="I43" s="73"/>
     </row>
     <row r="44" ht="18.75" customHeight="1">
-      <c r="C44" s="72"/>
-      <c r="D44" s="72"/>
-      <c r="E44" s="74"/>
-      <c r="F44" s="74"/>
-      <c r="G44" s="74"/>
-      <c r="H44" s="74"/>
-      <c r="I44" s="74"/>
+      <c r="C44" s="71"/>
+      <c r="D44" s="71"/>
+      <c r="E44" s="73"/>
+      <c r="F44" s="73"/>
+      <c r="G44" s="73"/>
+      <c r="H44" s="73"/>
+      <c r="I44" s="73"/>
     </row>
     <row r="45" ht="18.75" customHeight="1">
-      <c r="C45" s="72"/>
-      <c r="D45" s="72"/>
-      <c r="E45" s="74"/>
-      <c r="F45" s="74"/>
-      <c r="G45" s="74"/>
-      <c r="H45" s="74"/>
-      <c r="I45" s="74"/>
+      <c r="C45" s="71"/>
+      <c r="D45" s="71"/>
+      <c r="E45" s="73"/>
+      <c r="F45" s="73"/>
+      <c r="G45" s="73"/>
+      <c r="H45" s="73"/>
+      <c r="I45" s="73"/>
     </row>
     <row r="46" ht="18.75" customHeight="1">
-      <c r="A46" s="73"/>
-      <c r="B46" s="73"/>
-      <c r="C46" s="72"/>
-      <c r="D46" s="72"/>
-      <c r="E46" s="74"/>
-      <c r="F46" s="74"/>
-      <c r="G46" s="74"/>
-      <c r="H46" s="74"/>
-      <c r="I46" s="74"/>
+      <c r="A46" s="72"/>
+      <c r="B46" s="72"/>
+      <c r="C46" s="71"/>
+      <c r="D46" s="71"/>
+      <c r="E46" s="73"/>
+      <c r="F46" s="73"/>
+      <c r="G46" s="73"/>
+      <c r="H46" s="73"/>
+      <c r="I46" s="73"/>
     </row>
     <row r="47" ht="18.75" customHeight="1">
-      <c r="C47" s="72"/>
-      <c r="D47" s="72"/>
-      <c r="E47" s="74"/>
-      <c r="F47" s="74"/>
-      <c r="G47" s="74"/>
-      <c r="H47" s="74"/>
-      <c r="I47" s="74"/>
+      <c r="C47" s="71"/>
+      <c r="D47" s="71"/>
+      <c r="E47" s="73"/>
+      <c r="F47" s="73"/>
+      <c r="G47" s="73"/>
+      <c r="H47" s="73"/>
+      <c r="I47" s="73"/>
     </row>
     <row r="48" ht="18.75" customHeight="1">
-      <c r="C48" s="72"/>
-      <c r="D48" s="72"/>
-      <c r="E48" s="74"/>
-      <c r="F48" s="74"/>
-      <c r="G48" s="74"/>
-      <c r="H48" s="74"/>
-      <c r="I48" s="74"/>
+      <c r="C48" s="71"/>
+      <c r="D48" s="71"/>
+      <c r="E48" s="73"/>
+      <c r="F48" s="73"/>
+      <c r="G48" s="73"/>
+      <c r="H48" s="73"/>
+      <c r="I48" s="73"/>
     </row>
     <row r="49" ht="18.75" customHeight="1">
-      <c r="A49" s="73"/>
-      <c r="B49" s="73"/>
-      <c r="C49" s="72"/>
-      <c r="D49" s="72"/>
-      <c r="E49" s="74"/>
-      <c r="F49" s="74"/>
-      <c r="G49" s="74"/>
-      <c r="H49" s="74"/>
-      <c r="I49" s="74"/>
+      <c r="A49" s="72"/>
+      <c r="B49" s="72"/>
+      <c r="C49" s="71"/>
+      <c r="D49" s="71"/>
+      <c r="E49" s="73"/>
+      <c r="F49" s="73"/>
+      <c r="G49" s="73"/>
+      <c r="H49" s="73"/>
+      <c r="I49" s="73"/>
     </row>
     <row r="50" ht="18.75" customHeight="1">
-      <c r="C50" s="72"/>
-      <c r="D50" s="72"/>
-      <c r="E50" s="74"/>
-      <c r="F50" s="74"/>
-      <c r="G50" s="74"/>
-      <c r="H50" s="74"/>
-      <c r="I50" s="74"/>
+      <c r="C50" s="71"/>
+      <c r="D50" s="71"/>
+      <c r="E50" s="73"/>
+      <c r="F50" s="73"/>
+      <c r="G50" s="73"/>
+      <c r="H50" s="73"/>
+      <c r="I50" s="73"/>
     </row>
     <row r="51" ht="18.75" customHeight="1">
-      <c r="C51" s="72"/>
-      <c r="D51" s="72"/>
-      <c r="E51" s="74"/>
-      <c r="F51" s="74"/>
-      <c r="G51" s="74"/>
-      <c r="H51" s="74"/>
-      <c r="I51" s="74"/>
+      <c r="C51" s="71"/>
+      <c r="D51" s="71"/>
+      <c r="E51" s="73"/>
+      <c r="F51" s="73"/>
+      <c r="G51" s="73"/>
+      <c r="H51" s="73"/>
+      <c r="I51" s="73"/>
     </row>
     <row r="52" ht="18.75" customHeight="1">
-      <c r="A52" s="73"/>
-      <c r="B52" s="73"/>
-      <c r="C52" s="72"/>
-      <c r="D52" s="72"/>
-      <c r="E52" s="74"/>
-      <c r="F52" s="74"/>
-      <c r="G52" s="74"/>
-      <c r="H52" s="74"/>
-      <c r="I52" s="74"/>
+      <c r="A52" s="72"/>
+      <c r="B52" s="72"/>
+      <c r="C52" s="71"/>
+      <c r="D52" s="71"/>
+      <c r="E52" s="73"/>
+      <c r="F52" s="73"/>
+      <c r="G52" s="73"/>
+      <c r="H52" s="73"/>
+      <c r="I52" s="73"/>
     </row>
     <row r="53" ht="18.75" customHeight="1">
-      <c r="A53" s="73"/>
-      <c r="B53" s="73"/>
-      <c r="C53" s="72"/>
-      <c r="D53" s="72"/>
-      <c r="E53" s="74"/>
-      <c r="F53" s="74"/>
-      <c r="G53" s="74"/>
-      <c r="H53" s="74"/>
-      <c r="I53" s="74"/>
+      <c r="A53" s="72"/>
+      <c r="B53" s="72"/>
+      <c r="C53" s="71"/>
+      <c r="D53" s="71"/>
+      <c r="E53" s="73"/>
+      <c r="F53" s="73"/>
+      <c r="G53" s="73"/>
+      <c r="H53" s="73"/>
+      <c r="I53" s="73"/>
     </row>
     <row r="54" ht="18.75" customHeight="1">
-      <c r="A54" s="73"/>
-      <c r="B54" s="73"/>
-      <c r="C54" s="72"/>
-      <c r="D54" s="72"/>
-      <c r="E54" s="74"/>
-      <c r="F54" s="74"/>
-      <c r="G54" s="74"/>
-      <c r="H54" s="74"/>
-      <c r="I54" s="74"/>
+      <c r="A54" s="72"/>
+      <c r="B54" s="72"/>
+      <c r="C54" s="71"/>
+      <c r="D54" s="71"/>
+      <c r="E54" s="73"/>
+      <c r="F54" s="73"/>
+      <c r="G54" s="73"/>
+      <c r="H54" s="73"/>
+      <c r="I54" s="73"/>
     </row>
     <row r="55" ht="18.75" customHeight="1">
-      <c r="A55" s="73"/>
-      <c r="B55" s="73"/>
-      <c r="C55" s="72"/>
-      <c r="D55" s="72"/>
-      <c r="E55" s="74"/>
-      <c r="F55" s="74"/>
-      <c r="G55" s="74"/>
-      <c r="H55" s="74"/>
-      <c r="I55" s="74"/>
+      <c r="A55" s="72"/>
+      <c r="B55" s="72"/>
+      <c r="C55" s="71"/>
+      <c r="D55" s="71"/>
+      <c r="E55" s="73"/>
+      <c r="F55" s="73"/>
+      <c r="G55" s="73"/>
+      <c r="H55" s="73"/>
+      <c r="I55" s="73"/>
     </row>
     <row r="56" ht="18.75" customHeight="1">
-      <c r="A56" s="73"/>
-      <c r="B56" s="73"/>
-      <c r="C56" s="72"/>
-      <c r="D56" s="72"/>
-      <c r="E56" s="74"/>
-      <c r="F56" s="74"/>
-      <c r="G56" s="74"/>
-      <c r="H56" s="74"/>
-      <c r="I56" s="74"/>
+      <c r="A56" s="72"/>
+      <c r="B56" s="72"/>
+      <c r="C56" s="71"/>
+      <c r="D56" s="71"/>
+      <c r="E56" s="73"/>
+      <c r="F56" s="73"/>
+      <c r="G56" s="73"/>
+      <c r="H56" s="73"/>
+      <c r="I56" s="73"/>
     </row>
     <row r="57" ht="18.75" customHeight="1">
-      <c r="A57" s="73"/>
-      <c r="B57" s="73"/>
-      <c r="C57" s="72"/>
-      <c r="D57" s="72"/>
-      <c r="E57" s="74"/>
-      <c r="F57" s="74"/>
-      <c r="G57" s="74"/>
-      <c r="H57" s="74"/>
-      <c r="I57" s="74"/>
+      <c r="A57" s="72"/>
+      <c r="B57" s="72"/>
+      <c r="C57" s="71"/>
+      <c r="D57" s="71"/>
+      <c r="E57" s="73"/>
+      <c r="F57" s="73"/>
+      <c r="G57" s="73"/>
+      <c r="H57" s="73"/>
+      <c r="I57" s="73"/>
     </row>
     <row r="58" ht="18.75" customHeight="1">
-      <c r="A58" s="73"/>
-      <c r="B58" s="73"/>
-      <c r="C58" s="72"/>
-      <c r="D58" s="72"/>
-      <c r="E58" s="74"/>
-      <c r="F58" s="74"/>
-      <c r="G58" s="74"/>
-      <c r="H58" s="74"/>
-      <c r="I58" s="74"/>
+      <c r="A58" s="72"/>
+      <c r="B58" s="72"/>
+      <c r="C58" s="71"/>
+      <c r="D58" s="71"/>
+      <c r="E58" s="73"/>
+      <c r="F58" s="73"/>
+      <c r="G58" s="73"/>
+      <c r="H58" s="73"/>
+      <c r="I58" s="73"/>
     </row>
     <row r="59" ht="18.75" customHeight="1">
-      <c r="A59" s="73"/>
-      <c r="B59" s="73"/>
-      <c r="C59" s="72"/>
-      <c r="D59" s="72"/>
-      <c r="E59" s="74"/>
-      <c r="F59" s="74"/>
-      <c r="G59" s="74"/>
-      <c r="H59" s="74"/>
-      <c r="I59" s="74"/>
+      <c r="A59" s="72"/>
+      <c r="B59" s="72"/>
+      <c r="C59" s="71"/>
+      <c r="D59" s="71"/>
+      <c r="E59" s="73"/>
+      <c r="F59" s="73"/>
+      <c r="G59" s="73"/>
+      <c r="H59" s="73"/>
+      <c r="I59" s="73"/>
     </row>
     <row r="60" ht="18.75" customHeight="1">
-      <c r="A60" s="73"/>
-      <c r="B60" s="73"/>
-      <c r="C60" s="72"/>
-      <c r="D60" s="72"/>
-      <c r="E60" s="74"/>
-      <c r="F60" s="74"/>
-      <c r="G60" s="74"/>
-      <c r="H60" s="74"/>
-      <c r="I60" s="74"/>
+      <c r="A60" s="72"/>
+      <c r="B60" s="72"/>
+      <c r="C60" s="71"/>
+      <c r="D60" s="71"/>
+      <c r="E60" s="73"/>
+      <c r="F60" s="73"/>
+      <c r="G60" s="73"/>
+      <c r="H60" s="73"/>
+      <c r="I60" s="73"/>
     </row>
     <row r="61" ht="18.75" customHeight="1">
-      <c r="A61" s="73"/>
-      <c r="B61" s="73"/>
-      <c r="C61" s="72"/>
-      <c r="D61" s="72"/>
-      <c r="E61" s="74"/>
-      <c r="F61" s="74"/>
-      <c r="G61" s="74"/>
-      <c r="H61" s="74"/>
-      <c r="I61" s="74"/>
+      <c r="A61" s="72"/>
+      <c r="B61" s="72"/>
+      <c r="C61" s="71"/>
+      <c r="D61" s="71"/>
+      <c r="E61" s="73"/>
+      <c r="F61" s="73"/>
+      <c r="G61" s="73"/>
+      <c r="H61" s="73"/>
+      <c r="I61" s="73"/>
     </row>
     <row r="62" ht="18.75" customHeight="1">
-      <c r="A62" s="73"/>
-      <c r="B62" s="73"/>
-      <c r="C62" s="72"/>
-      <c r="D62" s="72"/>
-      <c r="E62" s="74"/>
-      <c r="F62" s="74"/>
-      <c r="G62" s="74"/>
-      <c r="H62" s="74"/>
-      <c r="I62" s="74"/>
+      <c r="A62" s="72"/>
+      <c r="B62" s="72"/>
+      <c r="C62" s="71"/>
+      <c r="D62" s="71"/>
+      <c r="E62" s="73"/>
+      <c r="F62" s="73"/>
+      <c r="G62" s="73"/>
+      <c r="H62" s="73"/>
+      <c r="I62" s="73"/>
     </row>
     <row r="63" ht="18.75" customHeight="1">
       <c r="A63" s="59"/>

--- a/Literature/Languages/Norvunic_Norgorvallian.xlsx
+++ b/Literature/Languages/Norvunic_Norgorvallian.xlsx
@@ -3426,7 +3426,7 @@
     <t>toll-enes</t>
   </si>
   <si>
-    <t>hagl (-gl, -rd, -ll, -sk endings)</t>
+    <t>hagl (-gl, -rd, -ll, endings)</t>
   </si>
   <si>
     <t>hagl-et</t>
